--- a/display/EcoGainsSim_HC_v4.xlsx
+++ b/display/EcoGainsSim_HC_v4.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:Y188"/>
+  <dimension ref="B2:Y190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.75" customWidth="1" min="1" max="1"/>
@@ -5768,7 +5768,7 @@
     <row r="183">
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Night Sky: SIMULATED column = bottom-up FULL-ROLLOUT value (ladder x daily-max-streak survival x active days). CURRENT is A/B-diluted, so the diff mixes rollout effect with dilution.</t>
+          <t>Night Sky: CARRIED by default (NS_SIMULATE = false in EcoGainsSim_v4.gs - the bottom-up model overestimates actual NS gains; open question). Flag true -&gt; full-rollout sim (segment ladder x survival over data_streaks max-streak p25-p90 x 1.25 effective-streak factor x active days); CURRENT is A/B-diluted, so DIFF would read as ROLLOUT EFFECT.</t>
         </is>
       </c>
     </row>
@@ -5803,7 +5803,21 @@
     <row r="188">
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>After editing a calendar: menu EcoGainsSim ▸ Precompute calendars (writes hidden cal_parsed; engine prefers it). Sanity canary: the Kite Festival row must SHRINK vs measured (D≈0.34 @0-9). If every event row equals measured, the calendar read failed.</t>
+          <t>Reward-config edits FLOW (since 2026-07-06): editing rewards or requirements on any _v2 sheet reprices its row (R = v2/base ladder at the measured rank / progress distribution). Base sheets = the measured world; leave them untouched. TaD milestone rewards are the exception (base pays 0 -&gt; no anchor -&gt; carried).</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" s="4" t="inlineStr">
+        <is>
+          <t>Kite Festival is priced as a LEADERBOARD (since 2026-07-06): payouts are zero-sum per league of 60, so duration does not move them; D=1 and the row GROWS ~x1.3 via cadence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" s="4" t="inlineStr">
+        <is>
+          <t>After editing a calendar: menu EcoGainsSim ▸ Precompute calendars (writes hidden cal_parsed; engine prefers it). Sanity canary: the Kite Festival row must GROW ~x1.3 vs measured. If every event row equals measured, the calendar read failed.</t>
         </is>
       </c>
     </row>

--- a/display/EcoGainsSim_HC_v4.xlsx
+++ b/display/EcoGainsSim_HC_v4.xlsx
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="C8" s="10">
-        <f>LET(payer, $C$3, segment, $B$6, ECOGAINS_SIM(payer, segment))</f>
+        <f>LET(payer, $C$3, segment, $B$6, ECOGAINS_SIM(payer, segment, sim_refresh!$A$1))</f>
         <v/>
       </c>
       <c r="D8" s="10" t="n"/>
@@ -716,7 +716,7 @@
       <c r="L8" s="10" t="n"/>
       <c r="M8" s="10" t="n"/>
       <c r="O8" s="11">
-        <f>LET(payer, $C$3, segment, $B$6, ECOGAINS_DIFF(payer, segment))</f>
+        <f>LET(payer, $C$3, segment, $B$6, ECOGAINS_DIFF(payer, segment, sim_refresh!$A$1))</f>
         <v/>
       </c>
       <c r="P8" s="11" t="n"/>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="C37" s="10">
-        <f>LET(payer, $C$3, segment, $B$35, ECOGAINS_SIM(payer, segment))</f>
+        <f>LET(payer, $C$3, segment, $B$35, ECOGAINS_SIM(payer, segment, sim_refresh!$A$1))</f>
         <v/>
       </c>
       <c r="D37" s="10" t="n"/>
@@ -1581,7 +1581,7 @@
       <c r="L37" s="10" t="n"/>
       <c r="M37" s="10" t="n"/>
       <c r="O37" s="11">
-        <f>LET(payer, $C$3, segment, $B$35, ECOGAINS_DIFF(payer, segment))</f>
+        <f>LET(payer, $C$3, segment, $B$35, ECOGAINS_DIFF(payer, segment, sim_refresh!$A$1))</f>
         <v/>
       </c>
       <c r="P37" s="11" t="n"/>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="C66" s="10">
-        <f>LET(payer, $C$3, segment, $B$64, ECOGAINS_SIM(payer, segment))</f>
+        <f>LET(payer, $C$3, segment, $B$64, ECOGAINS_SIM(payer, segment, sim_refresh!$A$1))</f>
         <v/>
       </c>
       <c r="D66" s="10" t="n"/>
@@ -2446,7 +2446,7 @@
       <c r="L66" s="10" t="n"/>
       <c r="M66" s="10" t="n"/>
       <c r="O66" s="11">
-        <f>LET(payer, $C$3, segment, $B$64, ECOGAINS_DIFF(payer, segment))</f>
+        <f>LET(payer, $C$3, segment, $B$64, ECOGAINS_DIFF(payer, segment, sim_refresh!$A$1))</f>
         <v/>
       </c>
       <c r="P66" s="11" t="n"/>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="C95" s="10">
-        <f>LET(payer, $C$3, segment, $B$93, ECOGAINS_SIM(payer, segment))</f>
+        <f>LET(payer, $C$3, segment, $B$93, ECOGAINS_SIM(payer, segment, sim_refresh!$A$1))</f>
         <v/>
       </c>
       <c r="D95" s="10" t="n"/>
@@ -3311,7 +3311,7 @@
       <c r="L95" s="10" t="n"/>
       <c r="M95" s="10" t="n"/>
       <c r="O95" s="11">
-        <f>LET(payer, $C$3, segment, $B$93, ECOGAINS_DIFF(payer, segment))</f>
+        <f>LET(payer, $C$3, segment, $B$93, ECOGAINS_DIFF(payer, segment, sim_refresh!$A$1))</f>
         <v/>
       </c>
       <c r="P95" s="11" t="n"/>
@@ -4162,7 +4162,7 @@
         </is>
       </c>
       <c r="C124" s="10">
-        <f>LET(payer, $C$3, segment, $B$122, ECOGAINS_SIM(payer, segment))</f>
+        <f>LET(payer, $C$3, segment, $B$122, ECOGAINS_SIM(payer, segment, sim_refresh!$A$1))</f>
         <v/>
       </c>
       <c r="D124" s="10" t="n"/>
@@ -4176,7 +4176,7 @@
       <c r="L124" s="10" t="n"/>
       <c r="M124" s="10" t="n"/>
       <c r="O124" s="11">
-        <f>LET(payer, $C$3, segment, $B$122, ECOGAINS_DIFF(payer, segment))</f>
+        <f>LET(payer, $C$3, segment, $B$122, ECOGAINS_DIFF(payer, segment, sim_refresh!$A$1))</f>
         <v/>
       </c>
       <c r="P124" s="11" t="n"/>
@@ -5027,7 +5027,7 @@
         </is>
       </c>
       <c r="C153" s="10">
-        <f>LET(payer, $C$3, segment, $B$151, ECOGAINS_SIM(payer, segment))</f>
+        <f>LET(payer, $C$3, segment, $B$151, ECOGAINS_SIM(payer, segment, sim_refresh!$A$1))</f>
         <v/>
       </c>
       <c r="D153" s="10" t="n"/>
@@ -5041,7 +5041,7 @@
       <c r="L153" s="10" t="n"/>
       <c r="M153" s="10" t="n"/>
       <c r="O153" s="11">
-        <f>LET(payer, $C$3, segment, $B$151, ECOGAINS_DIFF(payer, segment))</f>
+        <f>LET(payer, $C$3, segment, $B$151, ECOGAINS_DIFF(payer, segment, sim_refresh!$A$1))</f>
         <v/>
       </c>
       <c r="P153" s="11" t="n"/>

--- a/display/EcoGainsSim_HC_v4.xlsx
+++ b/display/EcoGainsSim_HC_v4.xlsx
@@ -524,13 +524,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:Y190"/>
+  <dimension ref="B2:AC192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.75" customWidth="1" min="1" max="1"/>
     <col width="19.25" customWidth="1" min="2" max="2"/>
     <col width="8.25" customWidth="1" min="3" max="3"/>
-    <col width="7.63" customWidth="1" min="26" max="26"/>
+    <col width="7.63" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="J3">
-        <f>JOIN(",", {B9,B10,B11,B13,B14,B16,B17,B18,B19,B21,B22,B23,B24,B26,B29,B31})</f>
+        <f>JOIN(",", {B9,B10,B11,B13,B14,B16,B17,B18,B19,B21,B22,B23,B24,B25,B26,B29,B31})</f>
         <v/>
       </c>
     </row>
@@ -572,7 +572,7 @@
           <t>0-9 Segment - Over Time Period  (uses 1-9 gains data)</t>
         </is>
       </c>
-      <c r="O6" s="6" t="inlineStr">
+      <c r="Q6" s="6" t="inlineStr">
         <is>
           <t>0-9 Segment - Over Time Period - Difference</t>
         </is>
@@ -639,59 +639,79 @@
           <t>Unlimited Lives</t>
         </is>
       </c>
+      <c r="N7" s="8" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
       <c r="O7" s="8" t="inlineStr">
         <is>
+          <t>SPTx2</t>
+        </is>
+      </c>
+      <c r="Q7" s="8" t="inlineStr">
+        <is>
           <t>HC</t>
         </is>
       </c>
-      <c r="P7" s="8" t="inlineStr">
+      <c r="R7" s="8" t="inlineStr">
         <is>
           <t>Slingshot</t>
         </is>
       </c>
-      <c r="Q7" s="8" t="inlineStr">
+      <c r="S7" s="8" t="inlineStr">
         <is>
           <t>Shuffle</t>
         </is>
       </c>
-      <c r="R7" s="8" t="inlineStr">
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>Comet</t>
         </is>
       </c>
-      <c r="S7" s="8" t="inlineStr">
+      <c r="U7" s="8" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="T7" s="8" t="inlineStr">
+      <c r="V7" s="8" t="inlineStr">
         <is>
           <t>Chuck</t>
         </is>
       </c>
-      <c r="U7" s="8" t="inlineStr">
+      <c r="W7" s="8" t="inlineStr">
         <is>
           <t>Bomb</t>
         </is>
       </c>
-      <c r="V7" s="8" t="inlineStr">
+      <c r="X7" s="8" t="inlineStr">
         <is>
           <t>UL Bomb</t>
         </is>
       </c>
-      <c r="W7" s="8" t="inlineStr">
+      <c r="Y7" s="8" t="inlineStr">
         <is>
           <t>UL Chuck</t>
         </is>
       </c>
-      <c r="X7" s="8" t="inlineStr">
+      <c r="Z7" s="8" t="inlineStr">
         <is>
           <t>UL Red</t>
         </is>
       </c>
-      <c r="Y7" s="8" t="inlineStr">
+      <c r="AA7" s="8" t="inlineStr">
         <is>
           <t>Unlimited Lives</t>
+        </is>
+      </c>
+      <c r="AB7" s="8" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
+      <c r="AC7" s="8" t="inlineStr">
+        <is>
+          <t>SPTx2</t>
         </is>
       </c>
     </row>
@@ -715,12 +735,12 @@
       <c r="K8" s="10" t="n"/>
       <c r="L8" s="10" t="n"/>
       <c r="M8" s="10" t="n"/>
-      <c r="O8" s="11">
+      <c r="N8" s="10" t="n"/>
+      <c r="O8" s="10" t="n"/>
+      <c r="Q8" s="11">
         <f>LET(payer, $C$3, segment, $B$6, ECOGAINS_DIFF(payer, segment, sim_refresh!$A$1))</f>
         <v/>
       </c>
-      <c r="P8" s="11" t="n"/>
-      <c r="Q8" s="11" t="n"/>
       <c r="R8" s="11" t="n"/>
       <c r="S8" s="11" t="n"/>
       <c r="T8" s="11" t="n"/>
@@ -729,6 +749,10 @@
       <c r="W8" s="11" t="n"/>
       <c r="X8" s="11" t="n"/>
       <c r="Y8" s="11" t="n"/>
+      <c r="Z8" s="11" t="n"/>
+      <c r="AA8" s="11" t="n"/>
+      <c r="AB8" s="11" t="n"/>
+      <c r="AC8" s="11" t="n"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="B9" s="12" t="inlineStr">
@@ -747,8 +771,8 @@
       <c r="K9" s="13" t="n"/>
       <c r="L9" s="13" t="n"/>
       <c r="M9" s="13" t="n"/>
-      <c r="O9" s="11" t="n"/>
-      <c r="P9" s="11" t="n"/>
+      <c r="N9" s="13" t="n"/>
+      <c r="O9" s="13" t="n"/>
       <c r="Q9" s="11" t="n"/>
       <c r="R9" s="11" t="n"/>
       <c r="S9" s="11" t="n"/>
@@ -758,6 +782,10 @@
       <c r="W9" s="11" t="n"/>
       <c r="X9" s="11" t="n"/>
       <c r="Y9" s="11" t="n"/>
+      <c r="Z9" s="11" t="n"/>
+      <c r="AA9" s="11" t="n"/>
+      <c r="AB9" s="11" t="n"/>
+      <c r="AC9" s="11" t="n"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="B10" s="12" t="inlineStr">
@@ -776,8 +804,8 @@
       <c r="K10" s="13" t="n"/>
       <c r="L10" s="13" t="n"/>
       <c r="M10" s="13" t="n"/>
-      <c r="O10" s="11" t="n"/>
-      <c r="P10" s="11" t="n"/>
+      <c r="N10" s="13" t="n"/>
+      <c r="O10" s="13" t="n"/>
       <c r="Q10" s="11" t="n"/>
       <c r="R10" s="11" t="n"/>
       <c r="S10" s="11" t="n"/>
@@ -787,6 +815,10 @@
       <c r="W10" s="11" t="n"/>
       <c r="X10" s="11" t="n"/>
       <c r="Y10" s="11" t="n"/>
+      <c r="Z10" s="11" t="n"/>
+      <c r="AA10" s="11" t="n"/>
+      <c r="AB10" s="11" t="n"/>
+      <c r="AC10" s="11" t="n"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="B11" s="12" t="inlineStr">
@@ -805,8 +837,8 @@
       <c r="K11" s="13" t="n"/>
       <c r="L11" s="13" t="n"/>
       <c r="M11" s="13" t="n"/>
-      <c r="O11" s="11" t="n"/>
-      <c r="P11" s="11" t="n"/>
+      <c r="N11" s="13" t="n"/>
+      <c r="O11" s="13" t="n"/>
       <c r="Q11" s="11" t="n"/>
       <c r="R11" s="11" t="n"/>
       <c r="S11" s="11" t="n"/>
@@ -816,6 +848,10 @@
       <c r="W11" s="11" t="n"/>
       <c r="X11" s="11" t="n"/>
       <c r="Y11" s="11" t="n"/>
+      <c r="Z11" s="11" t="n"/>
+      <c r="AA11" s="11" t="n"/>
+      <c r="AB11" s="11" t="n"/>
+      <c r="AC11" s="11" t="n"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="B12" s="9" t="inlineStr">
@@ -834,8 +870,8 @@
       <c r="K12" s="10" t="n"/>
       <c r="L12" s="10" t="n"/>
       <c r="M12" s="10" t="n"/>
-      <c r="O12" s="11" t="n"/>
-      <c r="P12" s="11" t="n"/>
+      <c r="N12" s="10" t="n"/>
+      <c r="O12" s="10" t="n"/>
       <c r="Q12" s="11" t="n"/>
       <c r="R12" s="11" t="n"/>
       <c r="S12" s="11" t="n"/>
@@ -845,6 +881,10 @@
       <c r="W12" s="11" t="n"/>
       <c r="X12" s="11" t="n"/>
       <c r="Y12" s="11" t="n"/>
+      <c r="Z12" s="11" t="n"/>
+      <c r="AA12" s="11" t="n"/>
+      <c r="AB12" s="11" t="n"/>
+      <c r="AC12" s="11" t="n"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="B13" s="14" t="inlineStr">
@@ -863,8 +903,8 @@
       <c r="K13" s="13" t="n"/>
       <c r="L13" s="13" t="n"/>
       <c r="M13" s="13" t="n"/>
-      <c r="O13" s="11" t="n"/>
-      <c r="P13" s="11" t="n"/>
+      <c r="N13" s="13" t="n"/>
+      <c r="O13" s="13" t="n"/>
       <c r="Q13" s="11" t="n"/>
       <c r="R13" s="11" t="n"/>
       <c r="S13" s="11" t="n"/>
@@ -874,6 +914,10 @@
       <c r="W13" s="11" t="n"/>
       <c r="X13" s="11" t="n"/>
       <c r="Y13" s="11" t="n"/>
+      <c r="Z13" s="11" t="n"/>
+      <c r="AA13" s="11" t="n"/>
+      <c r="AB13" s="11" t="n"/>
+      <c r="AC13" s="11" t="n"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="B14" s="14" t="inlineStr">
@@ -892,8 +936,8 @@
       <c r="K14" s="13" t="n"/>
       <c r="L14" s="13" t="n"/>
       <c r="M14" s="13" t="n"/>
-      <c r="O14" s="11" t="n"/>
-      <c r="P14" s="11" t="n"/>
+      <c r="N14" s="13" t="n"/>
+      <c r="O14" s="13" t="n"/>
       <c r="Q14" s="11" t="n"/>
       <c r="R14" s="11" t="n"/>
       <c r="S14" s="11" t="n"/>
@@ -903,6 +947,10 @@
       <c r="W14" s="11" t="n"/>
       <c r="X14" s="11" t="n"/>
       <c r="Y14" s="11" t="n"/>
+      <c r="Z14" s="11" t="n"/>
+      <c r="AA14" s="11" t="n"/>
+      <c r="AB14" s="11" t="n"/>
+      <c r="AC14" s="11" t="n"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="B15" s="9" t="inlineStr">
@@ -921,8 +969,8 @@
       <c r="K15" s="10" t="n"/>
       <c r="L15" s="10" t="n"/>
       <c r="M15" s="10" t="n"/>
-      <c r="O15" s="11" t="n"/>
-      <c r="P15" s="11" t="n"/>
+      <c r="N15" s="10" t="n"/>
+      <c r="O15" s="10" t="n"/>
       <c r="Q15" s="11" t="n"/>
       <c r="R15" s="11" t="n"/>
       <c r="S15" s="11" t="n"/>
@@ -932,6 +980,10 @@
       <c r="W15" s="11" t="n"/>
       <c r="X15" s="11" t="n"/>
       <c r="Y15" s="11" t="n"/>
+      <c r="Z15" s="11" t="n"/>
+      <c r="AA15" s="11" t="n"/>
+      <c r="AB15" s="11" t="n"/>
+      <c r="AC15" s="11" t="n"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="B16" s="12" t="inlineStr">
@@ -950,8 +1002,8 @@
       <c r="K16" s="13" t="n"/>
       <c r="L16" s="13" t="n"/>
       <c r="M16" s="13" t="n"/>
-      <c r="O16" s="11" t="n"/>
-      <c r="P16" s="11" t="n"/>
+      <c r="N16" s="13" t="n"/>
+      <c r="O16" s="13" t="n"/>
       <c r="Q16" s="11" t="n"/>
       <c r="R16" s="11" t="n"/>
       <c r="S16" s="11" t="n"/>
@@ -961,6 +1013,10 @@
       <c r="W16" s="11" t="n"/>
       <c r="X16" s="11" t="n"/>
       <c r="Y16" s="11" t="n"/>
+      <c r="Z16" s="11" t="n"/>
+      <c r="AA16" s="11" t="n"/>
+      <c r="AB16" s="11" t="n"/>
+      <c r="AC16" s="11" t="n"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="B17" s="12" t="inlineStr">
@@ -979,8 +1035,8 @@
       <c r="K17" s="13" t="n"/>
       <c r="L17" s="13" t="n"/>
       <c r="M17" s="13" t="n"/>
-      <c r="O17" s="11" t="n"/>
-      <c r="P17" s="11" t="n"/>
+      <c r="N17" s="13" t="n"/>
+      <c r="O17" s="13" t="n"/>
       <c r="Q17" s="11" t="n"/>
       <c r="R17" s="11" t="n"/>
       <c r="S17" s="11" t="n"/>
@@ -990,6 +1046,10 @@
       <c r="W17" s="11" t="n"/>
       <c r="X17" s="11" t="n"/>
       <c r="Y17" s="11" t="n"/>
+      <c r="Z17" s="11" t="n"/>
+      <c r="AA17" s="11" t="n"/>
+      <c r="AB17" s="11" t="n"/>
+      <c r="AC17" s="11" t="n"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="B18" s="12" t="inlineStr">
@@ -1008,8 +1068,8 @@
       <c r="K18" s="13" t="n"/>
       <c r="L18" s="13" t="n"/>
       <c r="M18" s="13" t="n"/>
-      <c r="O18" s="11" t="n"/>
-      <c r="P18" s="11" t="n"/>
+      <c r="N18" s="13" t="n"/>
+      <c r="O18" s="13" t="n"/>
       <c r="Q18" s="11" t="n"/>
       <c r="R18" s="11" t="n"/>
       <c r="S18" s="11" t="n"/>
@@ -1019,6 +1079,10 @@
       <c r="W18" s="11" t="n"/>
       <c r="X18" s="11" t="n"/>
       <c r="Y18" s="11" t="n"/>
+      <c r="Z18" s="11" t="n"/>
+      <c r="AA18" s="11" t="n"/>
+      <c r="AB18" s="11" t="n"/>
+      <c r="AC18" s="11" t="n"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="B19" s="12" t="inlineStr">
@@ -1037,8 +1101,8 @@
       <c r="K19" s="13" t="n"/>
       <c r="L19" s="13" t="n"/>
       <c r="M19" s="13" t="n"/>
-      <c r="O19" s="11" t="n"/>
-      <c r="P19" s="11" t="n"/>
+      <c r="N19" s="13" t="n"/>
+      <c r="O19" s="13" t="n"/>
       <c r="Q19" s="11" t="n"/>
       <c r="R19" s="11" t="n"/>
       <c r="S19" s="11" t="n"/>
@@ -1048,6 +1112,10 @@
       <c r="W19" s="11" t="n"/>
       <c r="X19" s="11" t="n"/>
       <c r="Y19" s="11" t="n"/>
+      <c r="Z19" s="11" t="n"/>
+      <c r="AA19" s="11" t="n"/>
+      <c r="AB19" s="11" t="n"/>
+      <c r="AC19" s="11" t="n"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="B20" s="9" t="inlineStr">
@@ -1066,8 +1134,8 @@
       <c r="K20" s="10" t="n"/>
       <c r="L20" s="10" t="n"/>
       <c r="M20" s="10" t="n"/>
-      <c r="O20" s="11" t="n"/>
-      <c r="P20" s="11" t="n"/>
+      <c r="N20" s="10" t="n"/>
+      <c r="O20" s="10" t="n"/>
       <c r="Q20" s="11" t="n"/>
       <c r="R20" s="11" t="n"/>
       <c r="S20" s="11" t="n"/>
@@ -1077,6 +1145,10 @@
       <c r="W20" s="11" t="n"/>
       <c r="X20" s="11" t="n"/>
       <c r="Y20" s="11" t="n"/>
+      <c r="Z20" s="11" t="n"/>
+      <c r="AA20" s="11" t="n"/>
+      <c r="AB20" s="11" t="n"/>
+      <c r="AC20" s="11" t="n"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="B21" s="12" t="inlineStr">
@@ -1095,8 +1167,8 @@
       <c r="K21" s="13" t="n"/>
       <c r="L21" s="13" t="n"/>
       <c r="M21" s="13" t="n"/>
-      <c r="O21" s="11" t="n"/>
-      <c r="P21" s="11" t="n"/>
+      <c r="N21" s="13" t="n"/>
+      <c r="O21" s="13" t="n"/>
       <c r="Q21" s="11" t="n"/>
       <c r="R21" s="11" t="n"/>
       <c r="S21" s="11" t="n"/>
@@ -1106,6 +1178,10 @@
       <c r="W21" s="11" t="n"/>
       <c r="X21" s="11" t="n"/>
       <c r="Y21" s="11" t="n"/>
+      <c r="Z21" s="11" t="n"/>
+      <c r="AA21" s="11" t="n"/>
+      <c r="AB21" s="11" t="n"/>
+      <c r="AC21" s="11" t="n"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="B22" s="12" t="inlineStr">
@@ -1124,8 +1200,8 @@
       <c r="K22" s="13" t="n"/>
       <c r="L22" s="13" t="n"/>
       <c r="M22" s="13" t="n"/>
-      <c r="O22" s="11" t="n"/>
-      <c r="P22" s="11" t="n"/>
+      <c r="N22" s="13" t="n"/>
+      <c r="O22" s="13" t="n"/>
       <c r="Q22" s="11" t="n"/>
       <c r="R22" s="11" t="n"/>
       <c r="S22" s="11" t="n"/>
@@ -1135,6 +1211,10 @@
       <c r="W22" s="11" t="n"/>
       <c r="X22" s="11" t="n"/>
       <c r="Y22" s="11" t="n"/>
+      <c r="Z22" s="11" t="n"/>
+      <c r="AA22" s="11" t="n"/>
+      <c r="AB22" s="11" t="n"/>
+      <c r="AC22" s="11" t="n"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="B23" s="12" t="inlineStr">
@@ -1153,8 +1233,8 @@
       <c r="K23" s="13" t="n"/>
       <c r="L23" s="13" t="n"/>
       <c r="M23" s="13" t="n"/>
-      <c r="O23" s="11" t="n"/>
-      <c r="P23" s="11" t="n"/>
+      <c r="N23" s="13" t="n"/>
+      <c r="O23" s="13" t="n"/>
       <c r="Q23" s="11" t="n"/>
       <c r="R23" s="11" t="n"/>
       <c r="S23" s="11" t="n"/>
@@ -1164,6 +1244,10 @@
       <c r="W23" s="11" t="n"/>
       <c r="X23" s="11" t="n"/>
       <c r="Y23" s="11" t="n"/>
+      <c r="Z23" s="11" t="n"/>
+      <c r="AA23" s="11" t="n"/>
+      <c r="AB23" s="11" t="n"/>
+      <c r="AC23" s="11" t="n"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="B24" s="14" t="inlineStr">
@@ -1182,8 +1266,8 @@
       <c r="K24" s="13" t="n"/>
       <c r="L24" s="13" t="n"/>
       <c r="M24" s="13" t="n"/>
-      <c r="O24" s="11" t="n"/>
-      <c r="P24" s="11" t="n"/>
+      <c r="N24" s="13" t="n"/>
+      <c r="O24" s="13" t="n"/>
       <c r="Q24" s="11" t="n"/>
       <c r="R24" s="11" t="n"/>
       <c r="S24" s="11" t="n"/>
@@ -1193,26 +1277,30 @@
       <c r="W24" s="11" t="n"/>
       <c r="X24" s="11" t="n"/>
       <c r="Y24" s="11" t="n"/>
+      <c r="Z24" s="11" t="n"/>
+      <c r="AA24" s="11" t="n"/>
+      <c r="AB24" s="11" t="n"/>
+      <c r="AC24" s="11" t="n"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>Season Pass (Free)</t>
         </is>
       </c>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="10" t="n"/>
-      <c r="E25" s="10" t="n"/>
-      <c r="F25" s="10" t="n"/>
-      <c r="G25" s="10" t="n"/>
-      <c r="H25" s="10" t="n"/>
-      <c r="I25" s="10" t="n"/>
-      <c r="J25" s="10" t="n"/>
-      <c r="K25" s="10" t="n"/>
-      <c r="L25" s="10" t="n"/>
-      <c r="M25" s="10" t="n"/>
-      <c r="O25" s="11" t="n"/>
-      <c r="P25" s="11" t="n"/>
+      <c r="C25" s="13" t="n"/>
+      <c r="D25" s="13" t="n"/>
+      <c r="E25" s="13" t="n"/>
+      <c r="F25" s="13" t="n"/>
+      <c r="G25" s="13" t="n"/>
+      <c r="H25" s="13" t="n"/>
+      <c r="I25" s="13" t="n"/>
+      <c r="J25" s="13" t="n"/>
+      <c r="K25" s="13" t="n"/>
+      <c r="L25" s="13" t="n"/>
+      <c r="M25" s="13" t="n"/>
+      <c r="N25" s="13" t="n"/>
+      <c r="O25" s="13" t="n"/>
       <c r="Q25" s="11" t="n"/>
       <c r="R25" s="11" t="n"/>
       <c r="S25" s="11" t="n"/>
@@ -1222,6 +1310,10 @@
       <c r="W25" s="11" t="n"/>
       <c r="X25" s="11" t="n"/>
       <c r="Y25" s="11" t="n"/>
+      <c r="Z25" s="11" t="n"/>
+      <c r="AA25" s="11" t="n"/>
+      <c r="AB25" s="11" t="n"/>
+      <c r="AC25" s="11" t="n"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="B26" s="12" t="inlineStr">
@@ -1240,8 +1332,8 @@
       <c r="K26" s="13" t="n"/>
       <c r="L26" s="13" t="n"/>
       <c r="M26" s="13" t="n"/>
-      <c r="O26" s="11" t="n"/>
-      <c r="P26" s="11" t="n"/>
+      <c r="N26" s="13" t="n"/>
+      <c r="O26" s="13" t="n"/>
       <c r="Q26" s="11" t="n"/>
       <c r="R26" s="11" t="n"/>
       <c r="S26" s="11" t="n"/>
@@ -1251,6 +1343,10 @@
       <c r="W26" s="11" t="n"/>
       <c r="X26" s="11" t="n"/>
       <c r="Y26" s="11" t="n"/>
+      <c r="Z26" s="11" t="n"/>
+      <c r="AA26" s="11" t="n"/>
+      <c r="AB26" s="11" t="n"/>
+      <c r="AC26" s="11" t="n"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="B27" s="9" t="inlineStr">
@@ -1269,8 +1365,8 @@
       <c r="K27" s="10" t="n"/>
       <c r="L27" s="10" t="n"/>
       <c r="M27" s="10" t="n"/>
-      <c r="O27" s="11" t="n"/>
-      <c r="P27" s="11" t="n"/>
+      <c r="N27" s="10" t="n"/>
+      <c r="O27" s="10" t="n"/>
       <c r="Q27" s="11" t="n"/>
       <c r="R27" s="11" t="n"/>
       <c r="S27" s="11" t="n"/>
@@ -1280,6 +1376,10 @@
       <c r="W27" s="11" t="n"/>
       <c r="X27" s="11" t="n"/>
       <c r="Y27" s="11" t="n"/>
+      <c r="Z27" s="11" t="n"/>
+      <c r="AA27" s="11" t="n"/>
+      <c r="AB27" s="11" t="n"/>
+      <c r="AC27" s="11" t="n"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="B28" s="9" t="inlineStr">
@@ -1298,8 +1398,8 @@
       <c r="K28" s="10" t="n"/>
       <c r="L28" s="10" t="n"/>
       <c r="M28" s="10" t="n"/>
-      <c r="O28" s="11" t="n"/>
-      <c r="P28" s="11" t="n"/>
+      <c r="N28" s="10" t="n"/>
+      <c r="O28" s="10" t="n"/>
       <c r="Q28" s="11" t="n"/>
       <c r="R28" s="11" t="n"/>
       <c r="S28" s="11" t="n"/>
@@ -1309,6 +1409,10 @@
       <c r="W28" s="11" t="n"/>
       <c r="X28" s="11" t="n"/>
       <c r="Y28" s="11" t="n"/>
+      <c r="Z28" s="11" t="n"/>
+      <c r="AA28" s="11" t="n"/>
+      <c r="AB28" s="11" t="n"/>
+      <c r="AC28" s="11" t="n"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="B29" s="12" t="inlineStr">
@@ -1327,8 +1431,8 @@
       <c r="K29" s="13" t="n"/>
       <c r="L29" s="13" t="n"/>
       <c r="M29" s="13" t="n"/>
-      <c r="O29" s="11" t="n"/>
-      <c r="P29" s="11" t="n"/>
+      <c r="N29" s="13" t="n"/>
+      <c r="O29" s="13" t="n"/>
       <c r="Q29" s="11" t="n"/>
       <c r="R29" s="11" t="n"/>
       <c r="S29" s="11" t="n"/>
@@ -1338,6 +1442,10 @@
       <c r="W29" s="11" t="n"/>
       <c r="X29" s="11" t="n"/>
       <c r="Y29" s="11" t="n"/>
+      <c r="Z29" s="11" t="n"/>
+      <c r="AA29" s="11" t="n"/>
+      <c r="AB29" s="11" t="n"/>
+      <c r="AC29" s="11" t="n"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="B30" s="9" t="inlineStr">
@@ -1356,8 +1464,8 @@
       <c r="K30" s="10" t="n"/>
       <c r="L30" s="10" t="n"/>
       <c r="M30" s="10" t="n"/>
-      <c r="O30" s="11" t="n"/>
-      <c r="P30" s="11" t="n"/>
+      <c r="N30" s="10" t="n"/>
+      <c r="O30" s="10" t="n"/>
       <c r="Q30" s="11" t="n"/>
       <c r="R30" s="11" t="n"/>
       <c r="S30" s="11" t="n"/>
@@ -1367,6 +1475,10 @@
       <c r="W30" s="11" t="n"/>
       <c r="X30" s="11" t="n"/>
       <c r="Y30" s="11" t="n"/>
+      <c r="Z30" s="11" t="n"/>
+      <c r="AA30" s="11" t="n"/>
+      <c r="AB30" s="11" t="n"/>
+      <c r="AC30" s="11" t="n"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="B31" s="12" t="inlineStr">
@@ -1385,8 +1497,8 @@
       <c r="K31" s="13" t="n"/>
       <c r="L31" s="13" t="n"/>
       <c r="M31" s="13" t="n"/>
-      <c r="O31" s="11" t="n"/>
-      <c r="P31" s="11" t="n"/>
+      <c r="N31" s="13" t="n"/>
+      <c r="O31" s="13" t="n"/>
       <c r="Q31" s="11" t="n"/>
       <c r="R31" s="11" t="n"/>
       <c r="S31" s="11" t="n"/>
@@ -1396,6 +1508,10 @@
       <c r="W31" s="11" t="n"/>
       <c r="X31" s="11" t="n"/>
       <c r="Y31" s="11" t="n"/>
+      <c r="Z31" s="11" t="n"/>
+      <c r="AA31" s="11" t="n"/>
+      <c r="AB31" s="11" t="n"/>
+      <c r="AC31" s="11" t="n"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="B32" s="9" t="inlineStr">
@@ -1414,8 +1530,8 @@
       <c r="K32" s="10" t="n"/>
       <c r="L32" s="10" t="n"/>
       <c r="M32" s="10" t="n"/>
-      <c r="O32" s="11" t="n"/>
-      <c r="P32" s="11" t="n"/>
+      <c r="N32" s="10" t="n"/>
+      <c r="O32" s="10" t="n"/>
       <c r="Q32" s="11" t="n"/>
       <c r="R32" s="11" t="n"/>
       <c r="S32" s="11" t="n"/>
@@ -1425,6 +1541,10 @@
       <c r="W32" s="11" t="n"/>
       <c r="X32" s="11" t="n"/>
       <c r="Y32" s="11" t="n"/>
+      <c r="Z32" s="11" t="n"/>
+      <c r="AA32" s="11" t="n"/>
+      <c r="AB32" s="11" t="n"/>
+      <c r="AC32" s="11" t="n"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="B35" s="5" t="inlineStr">
@@ -1437,7 +1557,7 @@
           <t>10-19 Segment - Over Time Period</t>
         </is>
       </c>
-      <c r="O35" s="6" t="inlineStr">
+      <c r="Q35" s="6" t="inlineStr">
         <is>
           <t>10-19 Segment - Over Time Period - Difference</t>
         </is>
@@ -1504,59 +1624,79 @@
           <t>Unlimited Lives</t>
         </is>
       </c>
+      <c r="N36" s="8" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
       <c r="O36" s="8" t="inlineStr">
         <is>
+          <t>SPTx2</t>
+        </is>
+      </c>
+      <c r="Q36" s="8" t="inlineStr">
+        <is>
           <t>HC</t>
         </is>
       </c>
-      <c r="P36" s="8" t="inlineStr">
+      <c r="R36" s="8" t="inlineStr">
         <is>
           <t>Slingshot</t>
         </is>
       </c>
-      <c r="Q36" s="8" t="inlineStr">
+      <c r="S36" s="8" t="inlineStr">
         <is>
           <t>Shuffle</t>
         </is>
       </c>
-      <c r="R36" s="8" t="inlineStr">
+      <c r="T36" s="8" t="inlineStr">
         <is>
           <t>Comet</t>
         </is>
       </c>
-      <c r="S36" s="8" t="inlineStr">
+      <c r="U36" s="8" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="T36" s="8" t="inlineStr">
+      <c r="V36" s="8" t="inlineStr">
         <is>
           <t>Chuck</t>
         </is>
       </c>
-      <c r="U36" s="8" t="inlineStr">
+      <c r="W36" s="8" t="inlineStr">
         <is>
           <t>Bomb</t>
         </is>
       </c>
-      <c r="V36" s="8" t="inlineStr">
+      <c r="X36" s="8" t="inlineStr">
         <is>
           <t>UL Bomb</t>
         </is>
       </c>
-      <c r="W36" s="8" t="inlineStr">
+      <c r="Y36" s="8" t="inlineStr">
         <is>
           <t>UL Chuck</t>
         </is>
       </c>
-      <c r="X36" s="8" t="inlineStr">
+      <c r="Z36" s="8" t="inlineStr">
         <is>
           <t>UL Red</t>
         </is>
       </c>
-      <c r="Y36" s="8" t="inlineStr">
+      <c r="AA36" s="8" t="inlineStr">
         <is>
           <t>Unlimited Lives</t>
+        </is>
+      </c>
+      <c r="AB36" s="8" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
+      <c r="AC36" s="8" t="inlineStr">
+        <is>
+          <t>SPTx2</t>
         </is>
       </c>
     </row>
@@ -1580,12 +1720,12 @@
       <c r="K37" s="10" t="n"/>
       <c r="L37" s="10" t="n"/>
       <c r="M37" s="10" t="n"/>
-      <c r="O37" s="11">
+      <c r="N37" s="10" t="n"/>
+      <c r="O37" s="10" t="n"/>
+      <c r="Q37" s="11">
         <f>LET(payer, $C$3, segment, $B$35, ECOGAINS_DIFF(payer, segment, sim_refresh!$A$1))</f>
         <v/>
       </c>
-      <c r="P37" s="11" t="n"/>
-      <c r="Q37" s="11" t="n"/>
       <c r="R37" s="11" t="n"/>
       <c r="S37" s="11" t="n"/>
       <c r="T37" s="11" t="n"/>
@@ -1594,6 +1734,10 @@
       <c r="W37" s="11" t="n"/>
       <c r="X37" s="11" t="n"/>
       <c r="Y37" s="11" t="n"/>
+      <c r="Z37" s="11" t="n"/>
+      <c r="AA37" s="11" t="n"/>
+      <c r="AB37" s="11" t="n"/>
+      <c r="AC37" s="11" t="n"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="B38" s="12" t="inlineStr">
@@ -1612,8 +1756,8 @@
       <c r="K38" s="13" t="n"/>
       <c r="L38" s="13" t="n"/>
       <c r="M38" s="13" t="n"/>
-      <c r="O38" s="11" t="n"/>
-      <c r="P38" s="11" t="n"/>
+      <c r="N38" s="13" t="n"/>
+      <c r="O38" s="13" t="n"/>
       <c r="Q38" s="11" t="n"/>
       <c r="R38" s="11" t="n"/>
       <c r="S38" s="11" t="n"/>
@@ -1623,6 +1767,10 @@
       <c r="W38" s="11" t="n"/>
       <c r="X38" s="11" t="n"/>
       <c r="Y38" s="11" t="n"/>
+      <c r="Z38" s="11" t="n"/>
+      <c r="AA38" s="11" t="n"/>
+      <c r="AB38" s="11" t="n"/>
+      <c r="AC38" s="11" t="n"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="B39" s="12" t="inlineStr">
@@ -1641,8 +1789,8 @@
       <c r="K39" s="13" t="n"/>
       <c r="L39" s="13" t="n"/>
       <c r="M39" s="13" t="n"/>
-      <c r="O39" s="11" t="n"/>
-      <c r="P39" s="11" t="n"/>
+      <c r="N39" s="13" t="n"/>
+      <c r="O39" s="13" t="n"/>
       <c r="Q39" s="11" t="n"/>
       <c r="R39" s="11" t="n"/>
       <c r="S39" s="11" t="n"/>
@@ -1652,6 +1800,10 @@
       <c r="W39" s="11" t="n"/>
       <c r="X39" s="11" t="n"/>
       <c r="Y39" s="11" t="n"/>
+      <c r="Z39" s="11" t="n"/>
+      <c r="AA39" s="11" t="n"/>
+      <c r="AB39" s="11" t="n"/>
+      <c r="AC39" s="11" t="n"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="B40" s="12" t="inlineStr">
@@ -1670,8 +1822,8 @@
       <c r="K40" s="13" t="n"/>
       <c r="L40" s="13" t="n"/>
       <c r="M40" s="13" t="n"/>
-      <c r="O40" s="11" t="n"/>
-      <c r="P40" s="11" t="n"/>
+      <c r="N40" s="13" t="n"/>
+      <c r="O40" s="13" t="n"/>
       <c r="Q40" s="11" t="n"/>
       <c r="R40" s="11" t="n"/>
       <c r="S40" s="11" t="n"/>
@@ -1681,6 +1833,10 @@
       <c r="W40" s="11" t="n"/>
       <c r="X40" s="11" t="n"/>
       <c r="Y40" s="11" t="n"/>
+      <c r="Z40" s="11" t="n"/>
+      <c r="AA40" s="11" t="n"/>
+      <c r="AB40" s="11" t="n"/>
+      <c r="AC40" s="11" t="n"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="B41" s="9" t="inlineStr">
@@ -1699,8 +1855,8 @@
       <c r="K41" s="10" t="n"/>
       <c r="L41" s="10" t="n"/>
       <c r="M41" s="10" t="n"/>
-      <c r="O41" s="11" t="n"/>
-      <c r="P41" s="11" t="n"/>
+      <c r="N41" s="10" t="n"/>
+      <c r="O41" s="10" t="n"/>
       <c r="Q41" s="11" t="n"/>
       <c r="R41" s="11" t="n"/>
       <c r="S41" s="11" t="n"/>
@@ -1710,6 +1866,10 @@
       <c r="W41" s="11" t="n"/>
       <c r="X41" s="11" t="n"/>
       <c r="Y41" s="11" t="n"/>
+      <c r="Z41" s="11" t="n"/>
+      <c r="AA41" s="11" t="n"/>
+      <c r="AB41" s="11" t="n"/>
+      <c r="AC41" s="11" t="n"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="B42" s="14" t="inlineStr">
@@ -1728,8 +1888,8 @@
       <c r="K42" s="13" t="n"/>
       <c r="L42" s="13" t="n"/>
       <c r="M42" s="13" t="n"/>
-      <c r="O42" s="11" t="n"/>
-      <c r="P42" s="11" t="n"/>
+      <c r="N42" s="13" t="n"/>
+      <c r="O42" s="13" t="n"/>
       <c r="Q42" s="11" t="n"/>
       <c r="R42" s="11" t="n"/>
       <c r="S42" s="11" t="n"/>
@@ -1739,6 +1899,10 @@
       <c r="W42" s="11" t="n"/>
       <c r="X42" s="11" t="n"/>
       <c r="Y42" s="11" t="n"/>
+      <c r="Z42" s="11" t="n"/>
+      <c r="AA42" s="11" t="n"/>
+      <c r="AB42" s="11" t="n"/>
+      <c r="AC42" s="11" t="n"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="B43" s="14" t="inlineStr">
@@ -1757,8 +1921,8 @@
       <c r="K43" s="13" t="n"/>
       <c r="L43" s="13" t="n"/>
       <c r="M43" s="13" t="n"/>
-      <c r="O43" s="11" t="n"/>
-      <c r="P43" s="11" t="n"/>
+      <c r="N43" s="13" t="n"/>
+      <c r="O43" s="13" t="n"/>
       <c r="Q43" s="11" t="n"/>
       <c r="R43" s="11" t="n"/>
       <c r="S43" s="11" t="n"/>
@@ -1768,6 +1932,10 @@
       <c r="W43" s="11" t="n"/>
       <c r="X43" s="11" t="n"/>
       <c r="Y43" s="11" t="n"/>
+      <c r="Z43" s="11" t="n"/>
+      <c r="AA43" s="11" t="n"/>
+      <c r="AB43" s="11" t="n"/>
+      <c r="AC43" s="11" t="n"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="B44" s="9" t="inlineStr">
@@ -1786,8 +1954,8 @@
       <c r="K44" s="10" t="n"/>
       <c r="L44" s="10" t="n"/>
       <c r="M44" s="10" t="n"/>
-      <c r="O44" s="11" t="n"/>
-      <c r="P44" s="11" t="n"/>
+      <c r="N44" s="10" t="n"/>
+      <c r="O44" s="10" t="n"/>
       <c r="Q44" s="11" t="n"/>
       <c r="R44" s="11" t="n"/>
       <c r="S44" s="11" t="n"/>
@@ -1797,6 +1965,10 @@
       <c r="W44" s="11" t="n"/>
       <c r="X44" s="11" t="n"/>
       <c r="Y44" s="11" t="n"/>
+      <c r="Z44" s="11" t="n"/>
+      <c r="AA44" s="11" t="n"/>
+      <c r="AB44" s="11" t="n"/>
+      <c r="AC44" s="11" t="n"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="B45" s="12" t="inlineStr">
@@ -1815,8 +1987,8 @@
       <c r="K45" s="13" t="n"/>
       <c r="L45" s="13" t="n"/>
       <c r="M45" s="13" t="n"/>
-      <c r="O45" s="11" t="n"/>
-      <c r="P45" s="11" t="n"/>
+      <c r="N45" s="13" t="n"/>
+      <c r="O45" s="13" t="n"/>
       <c r="Q45" s="11" t="n"/>
       <c r="R45" s="11" t="n"/>
       <c r="S45" s="11" t="n"/>
@@ -1826,6 +1998,10 @@
       <c r="W45" s="11" t="n"/>
       <c r="X45" s="11" t="n"/>
       <c r="Y45" s="11" t="n"/>
+      <c r="Z45" s="11" t="n"/>
+      <c r="AA45" s="11" t="n"/>
+      <c r="AB45" s="11" t="n"/>
+      <c r="AC45" s="11" t="n"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="B46" s="12" t="inlineStr">
@@ -1844,8 +2020,8 @@
       <c r="K46" s="13" t="n"/>
       <c r="L46" s="13" t="n"/>
       <c r="M46" s="13" t="n"/>
-      <c r="O46" s="11" t="n"/>
-      <c r="P46" s="11" t="n"/>
+      <c r="N46" s="13" t="n"/>
+      <c r="O46" s="13" t="n"/>
       <c r="Q46" s="11" t="n"/>
       <c r="R46" s="11" t="n"/>
       <c r="S46" s="11" t="n"/>
@@ -1855,6 +2031,10 @@
       <c r="W46" s="11" t="n"/>
       <c r="X46" s="11" t="n"/>
       <c r="Y46" s="11" t="n"/>
+      <c r="Z46" s="11" t="n"/>
+      <c r="AA46" s="11" t="n"/>
+      <c r="AB46" s="11" t="n"/>
+      <c r="AC46" s="11" t="n"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="B47" s="12" t="inlineStr">
@@ -1873,8 +2053,8 @@
       <c r="K47" s="13" t="n"/>
       <c r="L47" s="13" t="n"/>
       <c r="M47" s="13" t="n"/>
-      <c r="O47" s="11" t="n"/>
-      <c r="P47" s="11" t="n"/>
+      <c r="N47" s="13" t="n"/>
+      <c r="O47" s="13" t="n"/>
       <c r="Q47" s="11" t="n"/>
       <c r="R47" s="11" t="n"/>
       <c r="S47" s="11" t="n"/>
@@ -1884,6 +2064,10 @@
       <c r="W47" s="11" t="n"/>
       <c r="X47" s="11" t="n"/>
       <c r="Y47" s="11" t="n"/>
+      <c r="Z47" s="11" t="n"/>
+      <c r="AA47" s="11" t="n"/>
+      <c r="AB47" s="11" t="n"/>
+      <c r="AC47" s="11" t="n"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="B48" s="12" t="inlineStr">
@@ -1902,8 +2086,8 @@
       <c r="K48" s="13" t="n"/>
       <c r="L48" s="13" t="n"/>
       <c r="M48" s="13" t="n"/>
-      <c r="O48" s="11" t="n"/>
-      <c r="P48" s="11" t="n"/>
+      <c r="N48" s="13" t="n"/>
+      <c r="O48" s="13" t="n"/>
       <c r="Q48" s="11" t="n"/>
       <c r="R48" s="11" t="n"/>
       <c r="S48" s="11" t="n"/>
@@ -1913,6 +2097,10 @@
       <c r="W48" s="11" t="n"/>
       <c r="X48" s="11" t="n"/>
       <c r="Y48" s="11" t="n"/>
+      <c r="Z48" s="11" t="n"/>
+      <c r="AA48" s="11" t="n"/>
+      <c r="AB48" s="11" t="n"/>
+      <c r="AC48" s="11" t="n"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="B49" s="9" t="inlineStr">
@@ -1931,8 +2119,8 @@
       <c r="K49" s="10" t="n"/>
       <c r="L49" s="10" t="n"/>
       <c r="M49" s="10" t="n"/>
-      <c r="O49" s="11" t="n"/>
-      <c r="P49" s="11" t="n"/>
+      <c r="N49" s="10" t="n"/>
+      <c r="O49" s="10" t="n"/>
       <c r="Q49" s="11" t="n"/>
       <c r="R49" s="11" t="n"/>
       <c r="S49" s="11" t="n"/>
@@ -1942,6 +2130,10 @@
       <c r="W49" s="11" t="n"/>
       <c r="X49" s="11" t="n"/>
       <c r="Y49" s="11" t="n"/>
+      <c r="Z49" s="11" t="n"/>
+      <c r="AA49" s="11" t="n"/>
+      <c r="AB49" s="11" t="n"/>
+      <c r="AC49" s="11" t="n"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="B50" s="12" t="inlineStr">
@@ -1960,8 +2152,8 @@
       <c r="K50" s="13" t="n"/>
       <c r="L50" s="13" t="n"/>
       <c r="M50" s="13" t="n"/>
-      <c r="O50" s="11" t="n"/>
-      <c r="P50" s="11" t="n"/>
+      <c r="N50" s="13" t="n"/>
+      <c r="O50" s="13" t="n"/>
       <c r="Q50" s="11" t="n"/>
       <c r="R50" s="11" t="n"/>
       <c r="S50" s="11" t="n"/>
@@ -1971,6 +2163,10 @@
       <c r="W50" s="11" t="n"/>
       <c r="X50" s="11" t="n"/>
       <c r="Y50" s="11" t="n"/>
+      <c r="Z50" s="11" t="n"/>
+      <c r="AA50" s="11" t="n"/>
+      <c r="AB50" s="11" t="n"/>
+      <c r="AC50" s="11" t="n"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="B51" s="12" t="inlineStr">
@@ -1989,8 +2185,8 @@
       <c r="K51" s="13" t="n"/>
       <c r="L51" s="13" t="n"/>
       <c r="M51" s="13" t="n"/>
-      <c r="O51" s="11" t="n"/>
-      <c r="P51" s="11" t="n"/>
+      <c r="N51" s="13" t="n"/>
+      <c r="O51" s="13" t="n"/>
       <c r="Q51" s="11" t="n"/>
       <c r="R51" s="11" t="n"/>
       <c r="S51" s="11" t="n"/>
@@ -2000,6 +2196,10 @@
       <c r="W51" s="11" t="n"/>
       <c r="X51" s="11" t="n"/>
       <c r="Y51" s="11" t="n"/>
+      <c r="Z51" s="11" t="n"/>
+      <c r="AA51" s="11" t="n"/>
+      <c r="AB51" s="11" t="n"/>
+      <c r="AC51" s="11" t="n"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="B52" s="12" t="inlineStr">
@@ -2018,8 +2218,8 @@
       <c r="K52" s="13" t="n"/>
       <c r="L52" s="13" t="n"/>
       <c r="M52" s="13" t="n"/>
-      <c r="O52" s="11" t="n"/>
-      <c r="P52" s="11" t="n"/>
+      <c r="N52" s="13" t="n"/>
+      <c r="O52" s="13" t="n"/>
       <c r="Q52" s="11" t="n"/>
       <c r="R52" s="11" t="n"/>
       <c r="S52" s="11" t="n"/>
@@ -2029,6 +2229,10 @@
       <c r="W52" s="11" t="n"/>
       <c r="X52" s="11" t="n"/>
       <c r="Y52" s="11" t="n"/>
+      <c r="Z52" s="11" t="n"/>
+      <c r="AA52" s="11" t="n"/>
+      <c r="AB52" s="11" t="n"/>
+      <c r="AC52" s="11" t="n"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="B53" s="14" t="inlineStr">
@@ -2047,8 +2251,8 @@
       <c r="K53" s="13" t="n"/>
       <c r="L53" s="13" t="n"/>
       <c r="M53" s="13" t="n"/>
-      <c r="O53" s="11" t="n"/>
-      <c r="P53" s="11" t="n"/>
+      <c r="N53" s="13" t="n"/>
+      <c r="O53" s="13" t="n"/>
       <c r="Q53" s="11" t="n"/>
       <c r="R53" s="11" t="n"/>
       <c r="S53" s="11" t="n"/>
@@ -2058,26 +2262,30 @@
       <c r="W53" s="11" t="n"/>
       <c r="X53" s="11" t="n"/>
       <c r="Y53" s="11" t="n"/>
+      <c r="Z53" s="11" t="n"/>
+      <c r="AA53" s="11" t="n"/>
+      <c r="AB53" s="11" t="n"/>
+      <c r="AC53" s="11" t="n"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="B54" s="9" t="inlineStr">
+      <c r="B54" s="12" t="inlineStr">
         <is>
           <t>Season Pass (Free)</t>
         </is>
       </c>
-      <c r="C54" s="10" t="n"/>
-      <c r="D54" s="10" t="n"/>
-      <c r="E54" s="10" t="n"/>
-      <c r="F54" s="10" t="n"/>
-      <c r="G54" s="10" t="n"/>
-      <c r="H54" s="10" t="n"/>
-      <c r="I54" s="10" t="n"/>
-      <c r="J54" s="10" t="n"/>
-      <c r="K54" s="10" t="n"/>
-      <c r="L54" s="10" t="n"/>
-      <c r="M54" s="10" t="n"/>
-      <c r="O54" s="11" t="n"/>
-      <c r="P54" s="11" t="n"/>
+      <c r="C54" s="13" t="n"/>
+      <c r="D54" s="13" t="n"/>
+      <c r="E54" s="13" t="n"/>
+      <c r="F54" s="13" t="n"/>
+      <c r="G54" s="13" t="n"/>
+      <c r="H54" s="13" t="n"/>
+      <c r="I54" s="13" t="n"/>
+      <c r="J54" s="13" t="n"/>
+      <c r="K54" s="13" t="n"/>
+      <c r="L54" s="13" t="n"/>
+      <c r="M54" s="13" t="n"/>
+      <c r="N54" s="13" t="n"/>
+      <c r="O54" s="13" t="n"/>
       <c r="Q54" s="11" t="n"/>
       <c r="R54" s="11" t="n"/>
       <c r="S54" s="11" t="n"/>
@@ -2087,6 +2295,10 @@
       <c r="W54" s="11" t="n"/>
       <c r="X54" s="11" t="n"/>
       <c r="Y54" s="11" t="n"/>
+      <c r="Z54" s="11" t="n"/>
+      <c r="AA54" s="11" t="n"/>
+      <c r="AB54" s="11" t="n"/>
+      <c r="AC54" s="11" t="n"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="B55" s="12" t="inlineStr">
@@ -2105,8 +2317,8 @@
       <c r="K55" s="13" t="n"/>
       <c r="L55" s="13" t="n"/>
       <c r="M55" s="13" t="n"/>
-      <c r="O55" s="11" t="n"/>
-      <c r="P55" s="11" t="n"/>
+      <c r="N55" s="13" t="n"/>
+      <c r="O55" s="13" t="n"/>
       <c r="Q55" s="11" t="n"/>
       <c r="R55" s="11" t="n"/>
       <c r="S55" s="11" t="n"/>
@@ -2116,6 +2328,10 @@
       <c r="W55" s="11" t="n"/>
       <c r="X55" s="11" t="n"/>
       <c r="Y55" s="11" t="n"/>
+      <c r="Z55" s="11" t="n"/>
+      <c r="AA55" s="11" t="n"/>
+      <c r="AB55" s="11" t="n"/>
+      <c r="AC55" s="11" t="n"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="B56" s="9" t="inlineStr">
@@ -2134,8 +2350,8 @@
       <c r="K56" s="10" t="n"/>
       <c r="L56" s="10" t="n"/>
       <c r="M56" s="10" t="n"/>
-      <c r="O56" s="11" t="n"/>
-      <c r="P56" s="11" t="n"/>
+      <c r="N56" s="10" t="n"/>
+      <c r="O56" s="10" t="n"/>
       <c r="Q56" s="11" t="n"/>
       <c r="R56" s="11" t="n"/>
       <c r="S56" s="11" t="n"/>
@@ -2145,6 +2361,10 @@
       <c r="W56" s="11" t="n"/>
       <c r="X56" s="11" t="n"/>
       <c r="Y56" s="11" t="n"/>
+      <c r="Z56" s="11" t="n"/>
+      <c r="AA56" s="11" t="n"/>
+      <c r="AB56" s="11" t="n"/>
+      <c r="AC56" s="11" t="n"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="B57" s="9" t="inlineStr">
@@ -2163,8 +2383,8 @@
       <c r="K57" s="10" t="n"/>
       <c r="L57" s="10" t="n"/>
       <c r="M57" s="10" t="n"/>
-      <c r="O57" s="11" t="n"/>
-      <c r="P57" s="11" t="n"/>
+      <c r="N57" s="10" t="n"/>
+      <c r="O57" s="10" t="n"/>
       <c r="Q57" s="11" t="n"/>
       <c r="R57" s="11" t="n"/>
       <c r="S57" s="11" t="n"/>
@@ -2174,6 +2394,10 @@
       <c r="W57" s="11" t="n"/>
       <c r="X57" s="11" t="n"/>
       <c r="Y57" s="11" t="n"/>
+      <c r="Z57" s="11" t="n"/>
+      <c r="AA57" s="11" t="n"/>
+      <c r="AB57" s="11" t="n"/>
+      <c r="AC57" s="11" t="n"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="B58" s="12" t="inlineStr">
@@ -2192,8 +2416,8 @@
       <c r="K58" s="13" t="n"/>
       <c r="L58" s="13" t="n"/>
       <c r="M58" s="13" t="n"/>
-      <c r="O58" s="11" t="n"/>
-      <c r="P58" s="11" t="n"/>
+      <c r="N58" s="13" t="n"/>
+      <c r="O58" s="13" t="n"/>
       <c r="Q58" s="11" t="n"/>
       <c r="R58" s="11" t="n"/>
       <c r="S58" s="11" t="n"/>
@@ -2203,6 +2427,10 @@
       <c r="W58" s="11" t="n"/>
       <c r="X58" s="11" t="n"/>
       <c r="Y58" s="11" t="n"/>
+      <c r="Z58" s="11" t="n"/>
+      <c r="AA58" s="11" t="n"/>
+      <c r="AB58" s="11" t="n"/>
+      <c r="AC58" s="11" t="n"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="B59" s="9" t="inlineStr">
@@ -2221,8 +2449,8 @@
       <c r="K59" s="10" t="n"/>
       <c r="L59" s="10" t="n"/>
       <c r="M59" s="10" t="n"/>
-      <c r="O59" s="11" t="n"/>
-      <c r="P59" s="11" t="n"/>
+      <c r="N59" s="10" t="n"/>
+      <c r="O59" s="10" t="n"/>
       <c r="Q59" s="11" t="n"/>
       <c r="R59" s="11" t="n"/>
       <c r="S59" s="11" t="n"/>
@@ -2232,6 +2460,10 @@
       <c r="W59" s="11" t="n"/>
       <c r="X59" s="11" t="n"/>
       <c r="Y59" s="11" t="n"/>
+      <c r="Z59" s="11" t="n"/>
+      <c r="AA59" s="11" t="n"/>
+      <c r="AB59" s="11" t="n"/>
+      <c r="AC59" s="11" t="n"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="B60" s="12" t="inlineStr">
@@ -2250,8 +2482,8 @@
       <c r="K60" s="13" t="n"/>
       <c r="L60" s="13" t="n"/>
       <c r="M60" s="13" t="n"/>
-      <c r="O60" s="11" t="n"/>
-      <c r="P60" s="11" t="n"/>
+      <c r="N60" s="13" t="n"/>
+      <c r="O60" s="13" t="n"/>
       <c r="Q60" s="11" t="n"/>
       <c r="R60" s="11" t="n"/>
       <c r="S60" s="11" t="n"/>
@@ -2261,6 +2493,10 @@
       <c r="W60" s="11" t="n"/>
       <c r="X60" s="11" t="n"/>
       <c r="Y60" s="11" t="n"/>
+      <c r="Z60" s="11" t="n"/>
+      <c r="AA60" s="11" t="n"/>
+      <c r="AB60" s="11" t="n"/>
+      <c r="AC60" s="11" t="n"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="B61" s="9" t="inlineStr">
@@ -2279,8 +2515,8 @@
       <c r="K61" s="10" t="n"/>
       <c r="L61" s="10" t="n"/>
       <c r="M61" s="10" t="n"/>
-      <c r="O61" s="11" t="n"/>
-      <c r="P61" s="11" t="n"/>
+      <c r="N61" s="10" t="n"/>
+      <c r="O61" s="10" t="n"/>
       <c r="Q61" s="11" t="n"/>
       <c r="R61" s="11" t="n"/>
       <c r="S61" s="11" t="n"/>
@@ -2290,6 +2526,10 @@
       <c r="W61" s="11" t="n"/>
       <c r="X61" s="11" t="n"/>
       <c r="Y61" s="11" t="n"/>
+      <c r="Z61" s="11" t="n"/>
+      <c r="AA61" s="11" t="n"/>
+      <c r="AB61" s="11" t="n"/>
+      <c r="AC61" s="11" t="n"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="B64" s="5" t="inlineStr">
@@ -2302,7 +2542,7 @@
           <t>20-39 Segment - Over Time Period</t>
         </is>
       </c>
-      <c r="O64" s="6" t="inlineStr">
+      <c r="Q64" s="6" t="inlineStr">
         <is>
           <t>20-39 Segment - Over Time Period - Difference</t>
         </is>
@@ -2369,59 +2609,79 @@
           <t>Unlimited Lives</t>
         </is>
       </c>
+      <c r="N65" s="8" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
       <c r="O65" s="8" t="inlineStr">
         <is>
+          <t>SPTx2</t>
+        </is>
+      </c>
+      <c r="Q65" s="8" t="inlineStr">
+        <is>
           <t>HC</t>
         </is>
       </c>
-      <c r="P65" s="8" t="inlineStr">
+      <c r="R65" s="8" t="inlineStr">
         <is>
           <t>Slingshot</t>
         </is>
       </c>
-      <c r="Q65" s="8" t="inlineStr">
+      <c r="S65" s="8" t="inlineStr">
         <is>
           <t>Shuffle</t>
         </is>
       </c>
-      <c r="R65" s="8" t="inlineStr">
+      <c r="T65" s="8" t="inlineStr">
         <is>
           <t>Comet</t>
         </is>
       </c>
-      <c r="S65" s="8" t="inlineStr">
+      <c r="U65" s="8" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="T65" s="8" t="inlineStr">
+      <c r="V65" s="8" t="inlineStr">
         <is>
           <t>Chuck</t>
         </is>
       </c>
-      <c r="U65" s="8" t="inlineStr">
+      <c r="W65" s="8" t="inlineStr">
         <is>
           <t>Bomb</t>
         </is>
       </c>
-      <c r="V65" s="8" t="inlineStr">
+      <c r="X65" s="8" t="inlineStr">
         <is>
           <t>UL Bomb</t>
         </is>
       </c>
-      <c r="W65" s="8" t="inlineStr">
+      <c r="Y65" s="8" t="inlineStr">
         <is>
           <t>UL Chuck</t>
         </is>
       </c>
-      <c r="X65" s="8" t="inlineStr">
+      <c r="Z65" s="8" t="inlineStr">
         <is>
           <t>UL Red</t>
         </is>
       </c>
-      <c r="Y65" s="8" t="inlineStr">
+      <c r="AA65" s="8" t="inlineStr">
         <is>
           <t>Unlimited Lives</t>
+        </is>
+      </c>
+      <c r="AB65" s="8" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
+      <c r="AC65" s="8" t="inlineStr">
+        <is>
+          <t>SPTx2</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2705,12 @@
       <c r="K66" s="10" t="n"/>
       <c r="L66" s="10" t="n"/>
       <c r="M66" s="10" t="n"/>
-      <c r="O66" s="11">
+      <c r="N66" s="10" t="n"/>
+      <c r="O66" s="10" t="n"/>
+      <c r="Q66" s="11">
         <f>LET(payer, $C$3, segment, $B$64, ECOGAINS_DIFF(payer, segment, sim_refresh!$A$1))</f>
         <v/>
       </c>
-      <c r="P66" s="11" t="n"/>
-      <c r="Q66" s="11" t="n"/>
       <c r="R66" s="11" t="n"/>
       <c r="S66" s="11" t="n"/>
       <c r="T66" s="11" t="n"/>
@@ -2459,6 +2719,10 @@
       <c r="W66" s="11" t="n"/>
       <c r="X66" s="11" t="n"/>
       <c r="Y66" s="11" t="n"/>
+      <c r="Z66" s="11" t="n"/>
+      <c r="AA66" s="11" t="n"/>
+      <c r="AB66" s="11" t="n"/>
+      <c r="AC66" s="11" t="n"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="B67" s="12" t="inlineStr">
@@ -2477,8 +2741,8 @@
       <c r="K67" s="13" t="n"/>
       <c r="L67" s="13" t="n"/>
       <c r="M67" s="13" t="n"/>
-      <c r="O67" s="11" t="n"/>
-      <c r="P67" s="11" t="n"/>
+      <c r="N67" s="13" t="n"/>
+      <c r="O67" s="13" t="n"/>
       <c r="Q67" s="11" t="n"/>
       <c r="R67" s="11" t="n"/>
       <c r="S67" s="11" t="n"/>
@@ -2488,6 +2752,10 @@
       <c r="W67" s="11" t="n"/>
       <c r="X67" s="11" t="n"/>
       <c r="Y67" s="11" t="n"/>
+      <c r="Z67" s="11" t="n"/>
+      <c r="AA67" s="11" t="n"/>
+      <c r="AB67" s="11" t="n"/>
+      <c r="AC67" s="11" t="n"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="B68" s="12" t="inlineStr">
@@ -2506,8 +2774,8 @@
       <c r="K68" s="13" t="n"/>
       <c r="L68" s="13" t="n"/>
       <c r="M68" s="13" t="n"/>
-      <c r="O68" s="11" t="n"/>
-      <c r="P68" s="11" t="n"/>
+      <c r="N68" s="13" t="n"/>
+      <c r="O68" s="13" t="n"/>
       <c r="Q68" s="11" t="n"/>
       <c r="R68" s="11" t="n"/>
       <c r="S68" s="11" t="n"/>
@@ -2517,6 +2785,10 @@
       <c r="W68" s="11" t="n"/>
       <c r="X68" s="11" t="n"/>
       <c r="Y68" s="11" t="n"/>
+      <c r="Z68" s="11" t="n"/>
+      <c r="AA68" s="11" t="n"/>
+      <c r="AB68" s="11" t="n"/>
+      <c r="AC68" s="11" t="n"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="B69" s="12" t="inlineStr">
@@ -2535,8 +2807,8 @@
       <c r="K69" s="13" t="n"/>
       <c r="L69" s="13" t="n"/>
       <c r="M69" s="13" t="n"/>
-      <c r="O69" s="11" t="n"/>
-      <c r="P69" s="11" t="n"/>
+      <c r="N69" s="13" t="n"/>
+      <c r="O69" s="13" t="n"/>
       <c r="Q69" s="11" t="n"/>
       <c r="R69" s="11" t="n"/>
       <c r="S69" s="11" t="n"/>
@@ -2546,6 +2818,10 @@
       <c r="W69" s="11" t="n"/>
       <c r="X69" s="11" t="n"/>
       <c r="Y69" s="11" t="n"/>
+      <c r="Z69" s="11" t="n"/>
+      <c r="AA69" s="11" t="n"/>
+      <c r="AB69" s="11" t="n"/>
+      <c r="AC69" s="11" t="n"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="B70" s="9" t="inlineStr">
@@ -2564,8 +2840,8 @@
       <c r="K70" s="10" t="n"/>
       <c r="L70" s="10" t="n"/>
       <c r="M70" s="10" t="n"/>
-      <c r="O70" s="11" t="n"/>
-      <c r="P70" s="11" t="n"/>
+      <c r="N70" s="10" t="n"/>
+      <c r="O70" s="10" t="n"/>
       <c r="Q70" s="11" t="n"/>
       <c r="R70" s="11" t="n"/>
       <c r="S70" s="11" t="n"/>
@@ -2575,6 +2851,10 @@
       <c r="W70" s="11" t="n"/>
       <c r="X70" s="11" t="n"/>
       <c r="Y70" s="11" t="n"/>
+      <c r="Z70" s="11" t="n"/>
+      <c r="AA70" s="11" t="n"/>
+      <c r="AB70" s="11" t="n"/>
+      <c r="AC70" s="11" t="n"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="B71" s="14" t="inlineStr">
@@ -2593,8 +2873,8 @@
       <c r="K71" s="13" t="n"/>
       <c r="L71" s="13" t="n"/>
       <c r="M71" s="13" t="n"/>
-      <c r="O71" s="11" t="n"/>
-      <c r="P71" s="11" t="n"/>
+      <c r="N71" s="13" t="n"/>
+      <c r="O71" s="13" t="n"/>
       <c r="Q71" s="11" t="n"/>
       <c r="R71" s="11" t="n"/>
       <c r="S71" s="11" t="n"/>
@@ -2604,6 +2884,10 @@
       <c r="W71" s="11" t="n"/>
       <c r="X71" s="11" t="n"/>
       <c r="Y71" s="11" t="n"/>
+      <c r="Z71" s="11" t="n"/>
+      <c r="AA71" s="11" t="n"/>
+      <c r="AB71" s="11" t="n"/>
+      <c r="AC71" s="11" t="n"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="B72" s="14" t="inlineStr">
@@ -2622,8 +2906,8 @@
       <c r="K72" s="13" t="n"/>
       <c r="L72" s="13" t="n"/>
       <c r="M72" s="13" t="n"/>
-      <c r="O72" s="11" t="n"/>
-      <c r="P72" s="11" t="n"/>
+      <c r="N72" s="13" t="n"/>
+      <c r="O72" s="13" t="n"/>
       <c r="Q72" s="11" t="n"/>
       <c r="R72" s="11" t="n"/>
       <c r="S72" s="11" t="n"/>
@@ -2633,6 +2917,10 @@
       <c r="W72" s="11" t="n"/>
       <c r="X72" s="11" t="n"/>
       <c r="Y72" s="11" t="n"/>
+      <c r="Z72" s="11" t="n"/>
+      <c r="AA72" s="11" t="n"/>
+      <c r="AB72" s="11" t="n"/>
+      <c r="AC72" s="11" t="n"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="B73" s="9" t="inlineStr">
@@ -2651,8 +2939,8 @@
       <c r="K73" s="10" t="n"/>
       <c r="L73" s="10" t="n"/>
       <c r="M73" s="10" t="n"/>
-      <c r="O73" s="11" t="n"/>
-      <c r="P73" s="11" t="n"/>
+      <c r="N73" s="10" t="n"/>
+      <c r="O73" s="10" t="n"/>
       <c r="Q73" s="11" t="n"/>
       <c r="R73" s="11" t="n"/>
       <c r="S73" s="11" t="n"/>
@@ -2662,6 +2950,10 @@
       <c r="W73" s="11" t="n"/>
       <c r="X73" s="11" t="n"/>
       <c r="Y73" s="11" t="n"/>
+      <c r="Z73" s="11" t="n"/>
+      <c r="AA73" s="11" t="n"/>
+      <c r="AB73" s="11" t="n"/>
+      <c r="AC73" s="11" t="n"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="B74" s="12" t="inlineStr">
@@ -2680,8 +2972,8 @@
       <c r="K74" s="13" t="n"/>
       <c r="L74" s="13" t="n"/>
       <c r="M74" s="13" t="n"/>
-      <c r="O74" s="11" t="n"/>
-      <c r="P74" s="11" t="n"/>
+      <c r="N74" s="13" t="n"/>
+      <c r="O74" s="13" t="n"/>
       <c r="Q74" s="11" t="n"/>
       <c r="R74" s="11" t="n"/>
       <c r="S74" s="11" t="n"/>
@@ -2691,6 +2983,10 @@
       <c r="W74" s="11" t="n"/>
       <c r="X74" s="11" t="n"/>
       <c r="Y74" s="11" t="n"/>
+      <c r="Z74" s="11" t="n"/>
+      <c r="AA74" s="11" t="n"/>
+      <c r="AB74" s="11" t="n"/>
+      <c r="AC74" s="11" t="n"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="B75" s="12" t="inlineStr">
@@ -2709,8 +3005,8 @@
       <c r="K75" s="13" t="n"/>
       <c r="L75" s="13" t="n"/>
       <c r="M75" s="13" t="n"/>
-      <c r="O75" s="11" t="n"/>
-      <c r="P75" s="11" t="n"/>
+      <c r="N75" s="13" t="n"/>
+      <c r="O75" s="13" t="n"/>
       <c r="Q75" s="11" t="n"/>
       <c r="R75" s="11" t="n"/>
       <c r="S75" s="11" t="n"/>
@@ -2720,6 +3016,10 @@
       <c r="W75" s="11" t="n"/>
       <c r="X75" s="11" t="n"/>
       <c r="Y75" s="11" t="n"/>
+      <c r="Z75" s="11" t="n"/>
+      <c r="AA75" s="11" t="n"/>
+      <c r="AB75" s="11" t="n"/>
+      <c r="AC75" s="11" t="n"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="B76" s="12" t="inlineStr">
@@ -2738,8 +3038,8 @@
       <c r="K76" s="13" t="n"/>
       <c r="L76" s="13" t="n"/>
       <c r="M76" s="13" t="n"/>
-      <c r="O76" s="11" t="n"/>
-      <c r="P76" s="11" t="n"/>
+      <c r="N76" s="13" t="n"/>
+      <c r="O76" s="13" t="n"/>
       <c r="Q76" s="11" t="n"/>
       <c r="R76" s="11" t="n"/>
       <c r="S76" s="11" t="n"/>
@@ -2749,6 +3049,10 @@
       <c r="W76" s="11" t="n"/>
       <c r="X76" s="11" t="n"/>
       <c r="Y76" s="11" t="n"/>
+      <c r="Z76" s="11" t="n"/>
+      <c r="AA76" s="11" t="n"/>
+      <c r="AB76" s="11" t="n"/>
+      <c r="AC76" s="11" t="n"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="B77" s="12" t="inlineStr">
@@ -2767,8 +3071,8 @@
       <c r="K77" s="13" t="n"/>
       <c r="L77" s="13" t="n"/>
       <c r="M77" s="13" t="n"/>
-      <c r="O77" s="11" t="n"/>
-      <c r="P77" s="11" t="n"/>
+      <c r="N77" s="13" t="n"/>
+      <c r="O77" s="13" t="n"/>
       <c r="Q77" s="11" t="n"/>
       <c r="R77" s="11" t="n"/>
       <c r="S77" s="11" t="n"/>
@@ -2778,6 +3082,10 @@
       <c r="W77" s="11" t="n"/>
       <c r="X77" s="11" t="n"/>
       <c r="Y77" s="11" t="n"/>
+      <c r="Z77" s="11" t="n"/>
+      <c r="AA77" s="11" t="n"/>
+      <c r="AB77" s="11" t="n"/>
+      <c r="AC77" s="11" t="n"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="B78" s="9" t="inlineStr">
@@ -2796,8 +3104,8 @@
       <c r="K78" s="10" t="n"/>
       <c r="L78" s="10" t="n"/>
       <c r="M78" s="10" t="n"/>
-      <c r="O78" s="11" t="n"/>
-      <c r="P78" s="11" t="n"/>
+      <c r="N78" s="10" t="n"/>
+      <c r="O78" s="10" t="n"/>
       <c r="Q78" s="11" t="n"/>
       <c r="R78" s="11" t="n"/>
       <c r="S78" s="11" t="n"/>
@@ -2807,6 +3115,10 @@
       <c r="W78" s="11" t="n"/>
       <c r="X78" s="11" t="n"/>
       <c r="Y78" s="11" t="n"/>
+      <c r="Z78" s="11" t="n"/>
+      <c r="AA78" s="11" t="n"/>
+      <c r="AB78" s="11" t="n"/>
+      <c r="AC78" s="11" t="n"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="B79" s="12" t="inlineStr">
@@ -2825,8 +3137,8 @@
       <c r="K79" s="13" t="n"/>
       <c r="L79" s="13" t="n"/>
       <c r="M79" s="13" t="n"/>
-      <c r="O79" s="11" t="n"/>
-      <c r="P79" s="11" t="n"/>
+      <c r="N79" s="13" t="n"/>
+      <c r="O79" s="13" t="n"/>
       <c r="Q79" s="11" t="n"/>
       <c r="R79" s="11" t="n"/>
       <c r="S79" s="11" t="n"/>
@@ -2836,6 +3148,10 @@
       <c r="W79" s="11" t="n"/>
       <c r="X79" s="11" t="n"/>
       <c r="Y79" s="11" t="n"/>
+      <c r="Z79" s="11" t="n"/>
+      <c r="AA79" s="11" t="n"/>
+      <c r="AB79" s="11" t="n"/>
+      <c r="AC79" s="11" t="n"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="B80" s="12" t="inlineStr">
@@ -2854,8 +3170,8 @@
       <c r="K80" s="13" t="n"/>
       <c r="L80" s="13" t="n"/>
       <c r="M80" s="13" t="n"/>
-      <c r="O80" s="11" t="n"/>
-      <c r="P80" s="11" t="n"/>
+      <c r="N80" s="13" t="n"/>
+      <c r="O80" s="13" t="n"/>
       <c r="Q80" s="11" t="n"/>
       <c r="R80" s="11" t="n"/>
       <c r="S80" s="11" t="n"/>
@@ -2865,6 +3181,10 @@
       <c r="W80" s="11" t="n"/>
       <c r="X80" s="11" t="n"/>
       <c r="Y80" s="11" t="n"/>
+      <c r="Z80" s="11" t="n"/>
+      <c r="AA80" s="11" t="n"/>
+      <c r="AB80" s="11" t="n"/>
+      <c r="AC80" s="11" t="n"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="B81" s="12" t="inlineStr">
@@ -2883,8 +3203,8 @@
       <c r="K81" s="13" t="n"/>
       <c r="L81" s="13" t="n"/>
       <c r="M81" s="13" t="n"/>
-      <c r="O81" s="11" t="n"/>
-      <c r="P81" s="11" t="n"/>
+      <c r="N81" s="13" t="n"/>
+      <c r="O81" s="13" t="n"/>
       <c r="Q81" s="11" t="n"/>
       <c r="R81" s="11" t="n"/>
       <c r="S81" s="11" t="n"/>
@@ -2894,6 +3214,10 @@
       <c r="W81" s="11" t="n"/>
       <c r="X81" s="11" t="n"/>
       <c r="Y81" s="11" t="n"/>
+      <c r="Z81" s="11" t="n"/>
+      <c r="AA81" s="11" t="n"/>
+      <c r="AB81" s="11" t="n"/>
+      <c r="AC81" s="11" t="n"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="B82" s="14" t="inlineStr">
@@ -2912,8 +3236,8 @@
       <c r="K82" s="13" t="n"/>
       <c r="L82" s="13" t="n"/>
       <c r="M82" s="13" t="n"/>
-      <c r="O82" s="11" t="n"/>
-      <c r="P82" s="11" t="n"/>
+      <c r="N82" s="13" t="n"/>
+      <c r="O82" s="13" t="n"/>
       <c r="Q82" s="11" t="n"/>
       <c r="R82" s="11" t="n"/>
       <c r="S82" s="11" t="n"/>
@@ -2923,26 +3247,30 @@
       <c r="W82" s="11" t="n"/>
       <c r="X82" s="11" t="n"/>
       <c r="Y82" s="11" t="n"/>
+      <c r="Z82" s="11" t="n"/>
+      <c r="AA82" s="11" t="n"/>
+      <c r="AB82" s="11" t="n"/>
+      <c r="AC82" s="11" t="n"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="B83" s="9" t="inlineStr">
+      <c r="B83" s="12" t="inlineStr">
         <is>
           <t>Season Pass (Free)</t>
         </is>
       </c>
-      <c r="C83" s="10" t="n"/>
-      <c r="D83" s="10" t="n"/>
-      <c r="E83" s="10" t="n"/>
-      <c r="F83" s="10" t="n"/>
-      <c r="G83" s="10" t="n"/>
-      <c r="H83" s="10" t="n"/>
-      <c r="I83" s="10" t="n"/>
-      <c r="J83" s="10" t="n"/>
-      <c r="K83" s="10" t="n"/>
-      <c r="L83" s="10" t="n"/>
-      <c r="M83" s="10" t="n"/>
-      <c r="O83" s="11" t="n"/>
-      <c r="P83" s="11" t="n"/>
+      <c r="C83" s="13" t="n"/>
+      <c r="D83" s="13" t="n"/>
+      <c r="E83" s="13" t="n"/>
+      <c r="F83" s="13" t="n"/>
+      <c r="G83" s="13" t="n"/>
+      <c r="H83" s="13" t="n"/>
+      <c r="I83" s="13" t="n"/>
+      <c r="J83" s="13" t="n"/>
+      <c r="K83" s="13" t="n"/>
+      <c r="L83" s="13" t="n"/>
+      <c r="M83" s="13" t="n"/>
+      <c r="N83" s="13" t="n"/>
+      <c r="O83" s="13" t="n"/>
       <c r="Q83" s="11" t="n"/>
       <c r="R83" s="11" t="n"/>
       <c r="S83" s="11" t="n"/>
@@ -2952,6 +3280,10 @@
       <c r="W83" s="11" t="n"/>
       <c r="X83" s="11" t="n"/>
       <c r="Y83" s="11" t="n"/>
+      <c r="Z83" s="11" t="n"/>
+      <c r="AA83" s="11" t="n"/>
+      <c r="AB83" s="11" t="n"/>
+      <c r="AC83" s="11" t="n"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="B84" s="12" t="inlineStr">
@@ -2970,8 +3302,8 @@
       <c r="K84" s="13" t="n"/>
       <c r="L84" s="13" t="n"/>
       <c r="M84" s="13" t="n"/>
-      <c r="O84" s="11" t="n"/>
-      <c r="P84" s="11" t="n"/>
+      <c r="N84" s="13" t="n"/>
+      <c r="O84" s="13" t="n"/>
       <c r="Q84" s="11" t="n"/>
       <c r="R84" s="11" t="n"/>
       <c r="S84" s="11" t="n"/>
@@ -2981,6 +3313,10 @@
       <c r="W84" s="11" t="n"/>
       <c r="X84" s="11" t="n"/>
       <c r="Y84" s="11" t="n"/>
+      <c r="Z84" s="11" t="n"/>
+      <c r="AA84" s="11" t="n"/>
+      <c r="AB84" s="11" t="n"/>
+      <c r="AC84" s="11" t="n"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="B85" s="9" t="inlineStr">
@@ -2999,8 +3335,8 @@
       <c r="K85" s="10" t="n"/>
       <c r="L85" s="10" t="n"/>
       <c r="M85" s="10" t="n"/>
-      <c r="O85" s="11" t="n"/>
-      <c r="P85" s="11" t="n"/>
+      <c r="N85" s="10" t="n"/>
+      <c r="O85" s="10" t="n"/>
       <c r="Q85" s="11" t="n"/>
       <c r="R85" s="11" t="n"/>
       <c r="S85" s="11" t="n"/>
@@ -3010,6 +3346,10 @@
       <c r="W85" s="11" t="n"/>
       <c r="X85" s="11" t="n"/>
       <c r="Y85" s="11" t="n"/>
+      <c r="Z85" s="11" t="n"/>
+      <c r="AA85" s="11" t="n"/>
+      <c r="AB85" s="11" t="n"/>
+      <c r="AC85" s="11" t="n"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="B86" s="9" t="inlineStr">
@@ -3028,8 +3368,8 @@
       <c r="K86" s="10" t="n"/>
       <c r="L86" s="10" t="n"/>
       <c r="M86" s="10" t="n"/>
-      <c r="O86" s="11" t="n"/>
-      <c r="P86" s="11" t="n"/>
+      <c r="N86" s="10" t="n"/>
+      <c r="O86" s="10" t="n"/>
       <c r="Q86" s="11" t="n"/>
       <c r="R86" s="11" t="n"/>
       <c r="S86" s="11" t="n"/>
@@ -3039,6 +3379,10 @@
       <c r="W86" s="11" t="n"/>
       <c r="X86" s="11" t="n"/>
       <c r="Y86" s="11" t="n"/>
+      <c r="Z86" s="11" t="n"/>
+      <c r="AA86" s="11" t="n"/>
+      <c r="AB86" s="11" t="n"/>
+      <c r="AC86" s="11" t="n"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="B87" s="12" t="inlineStr">
@@ -3057,8 +3401,8 @@
       <c r="K87" s="13" t="n"/>
       <c r="L87" s="13" t="n"/>
       <c r="M87" s="13" t="n"/>
-      <c r="O87" s="11" t="n"/>
-      <c r="P87" s="11" t="n"/>
+      <c r="N87" s="13" t="n"/>
+      <c r="O87" s="13" t="n"/>
       <c r="Q87" s="11" t="n"/>
       <c r="R87" s="11" t="n"/>
       <c r="S87" s="11" t="n"/>
@@ -3068,6 +3412,10 @@
       <c r="W87" s="11" t="n"/>
       <c r="X87" s="11" t="n"/>
       <c r="Y87" s="11" t="n"/>
+      <c r="Z87" s="11" t="n"/>
+      <c r="AA87" s="11" t="n"/>
+      <c r="AB87" s="11" t="n"/>
+      <c r="AC87" s="11" t="n"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="B88" s="9" t="inlineStr">
@@ -3086,8 +3434,8 @@
       <c r="K88" s="10" t="n"/>
       <c r="L88" s="10" t="n"/>
       <c r="M88" s="10" t="n"/>
-      <c r="O88" s="11" t="n"/>
-      <c r="P88" s="11" t="n"/>
+      <c r="N88" s="10" t="n"/>
+      <c r="O88" s="10" t="n"/>
       <c r="Q88" s="11" t="n"/>
       <c r="R88" s="11" t="n"/>
       <c r="S88" s="11" t="n"/>
@@ -3097,6 +3445,10 @@
       <c r="W88" s="11" t="n"/>
       <c r="X88" s="11" t="n"/>
       <c r="Y88" s="11" t="n"/>
+      <c r="Z88" s="11" t="n"/>
+      <c r="AA88" s="11" t="n"/>
+      <c r="AB88" s="11" t="n"/>
+      <c r="AC88" s="11" t="n"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="B89" s="12" t="inlineStr">
@@ -3115,8 +3467,8 @@
       <c r="K89" s="13" t="n"/>
       <c r="L89" s="13" t="n"/>
       <c r="M89" s="13" t="n"/>
-      <c r="O89" s="11" t="n"/>
-      <c r="P89" s="11" t="n"/>
+      <c r="N89" s="13" t="n"/>
+      <c r="O89" s="13" t="n"/>
       <c r="Q89" s="11" t="n"/>
       <c r="R89" s="11" t="n"/>
       <c r="S89" s="11" t="n"/>
@@ -3126,6 +3478,10 @@
       <c r="W89" s="11" t="n"/>
       <c r="X89" s="11" t="n"/>
       <c r="Y89" s="11" t="n"/>
+      <c r="Z89" s="11" t="n"/>
+      <c r="AA89" s="11" t="n"/>
+      <c r="AB89" s="11" t="n"/>
+      <c r="AC89" s="11" t="n"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="B90" s="9" t="inlineStr">
@@ -3144,8 +3500,8 @@
       <c r="K90" s="10" t="n"/>
       <c r="L90" s="10" t="n"/>
       <c r="M90" s="10" t="n"/>
-      <c r="O90" s="11" t="n"/>
-      <c r="P90" s="11" t="n"/>
+      <c r="N90" s="10" t="n"/>
+      <c r="O90" s="10" t="n"/>
       <c r="Q90" s="11" t="n"/>
       <c r="R90" s="11" t="n"/>
       <c r="S90" s="11" t="n"/>
@@ -3155,6 +3511,10 @@
       <c r="W90" s="11" t="n"/>
       <c r="X90" s="11" t="n"/>
       <c r="Y90" s="11" t="n"/>
+      <c r="Z90" s="11" t="n"/>
+      <c r="AA90" s="11" t="n"/>
+      <c r="AB90" s="11" t="n"/>
+      <c r="AC90" s="11" t="n"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="B93" s="5" t="inlineStr">
@@ -3167,7 +3527,7 @@
           <t>40-99 Segment - Over Time Period</t>
         </is>
       </c>
-      <c r="O93" s="6" t="inlineStr">
+      <c r="Q93" s="6" t="inlineStr">
         <is>
           <t>40-99 Segment - Over Time Period - Difference</t>
         </is>
@@ -3234,59 +3594,79 @@
           <t>Unlimited Lives</t>
         </is>
       </c>
+      <c r="N94" s="8" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
       <c r="O94" s="8" t="inlineStr">
         <is>
+          <t>SPTx2</t>
+        </is>
+      </c>
+      <c r="Q94" s="8" t="inlineStr">
+        <is>
           <t>HC</t>
         </is>
       </c>
-      <c r="P94" s="8" t="inlineStr">
+      <c r="R94" s="8" t="inlineStr">
         <is>
           <t>Slingshot</t>
         </is>
       </c>
-      <c r="Q94" s="8" t="inlineStr">
+      <c r="S94" s="8" t="inlineStr">
         <is>
           <t>Shuffle</t>
         </is>
       </c>
-      <c r="R94" s="8" t="inlineStr">
+      <c r="T94" s="8" t="inlineStr">
         <is>
           <t>Comet</t>
         </is>
       </c>
-      <c r="S94" s="8" t="inlineStr">
+      <c r="U94" s="8" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="T94" s="8" t="inlineStr">
+      <c r="V94" s="8" t="inlineStr">
         <is>
           <t>Chuck</t>
         </is>
       </c>
-      <c r="U94" s="8" t="inlineStr">
+      <c r="W94" s="8" t="inlineStr">
         <is>
           <t>Bomb</t>
         </is>
       </c>
-      <c r="V94" s="8" t="inlineStr">
+      <c r="X94" s="8" t="inlineStr">
         <is>
           <t>UL Bomb</t>
         </is>
       </c>
-      <c r="W94" s="8" t="inlineStr">
+      <c r="Y94" s="8" t="inlineStr">
         <is>
           <t>UL Chuck</t>
         </is>
       </c>
-      <c r="X94" s="8" t="inlineStr">
+      <c r="Z94" s="8" t="inlineStr">
         <is>
           <t>UL Red</t>
         </is>
       </c>
-      <c r="Y94" s="8" t="inlineStr">
+      <c r="AA94" s="8" t="inlineStr">
         <is>
           <t>Unlimited Lives</t>
+        </is>
+      </c>
+      <c r="AB94" s="8" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
+      <c r="AC94" s="8" t="inlineStr">
+        <is>
+          <t>SPTx2</t>
         </is>
       </c>
     </row>
@@ -3310,12 +3690,12 @@
       <c r="K95" s="10" t="n"/>
       <c r="L95" s="10" t="n"/>
       <c r="M95" s="10" t="n"/>
-      <c r="O95" s="11">
+      <c r="N95" s="10" t="n"/>
+      <c r="O95" s="10" t="n"/>
+      <c r="Q95" s="11">
         <f>LET(payer, $C$3, segment, $B$93, ECOGAINS_DIFF(payer, segment, sim_refresh!$A$1))</f>
         <v/>
       </c>
-      <c r="P95" s="11" t="n"/>
-      <c r="Q95" s="11" t="n"/>
       <c r="R95" s="11" t="n"/>
       <c r="S95" s="11" t="n"/>
       <c r="T95" s="11" t="n"/>
@@ -3324,6 +3704,10 @@
       <c r="W95" s="11" t="n"/>
       <c r="X95" s="11" t="n"/>
       <c r="Y95" s="11" t="n"/>
+      <c r="Z95" s="11" t="n"/>
+      <c r="AA95" s="11" t="n"/>
+      <c r="AB95" s="11" t="n"/>
+      <c r="AC95" s="11" t="n"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="B96" s="12" t="inlineStr">
@@ -3342,8 +3726,8 @@
       <c r="K96" s="13" t="n"/>
       <c r="L96" s="13" t="n"/>
       <c r="M96" s="13" t="n"/>
-      <c r="O96" s="11" t="n"/>
-      <c r="P96" s="11" t="n"/>
+      <c r="N96" s="13" t="n"/>
+      <c r="O96" s="13" t="n"/>
       <c r="Q96" s="11" t="n"/>
       <c r="R96" s="11" t="n"/>
       <c r="S96" s="11" t="n"/>
@@ -3353,6 +3737,10 @@
       <c r="W96" s="11" t="n"/>
       <c r="X96" s="11" t="n"/>
       <c r="Y96" s="11" t="n"/>
+      <c r="Z96" s="11" t="n"/>
+      <c r="AA96" s="11" t="n"/>
+      <c r="AB96" s="11" t="n"/>
+      <c r="AC96" s="11" t="n"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="B97" s="12" t="inlineStr">
@@ -3371,8 +3759,8 @@
       <c r="K97" s="13" t="n"/>
       <c r="L97" s="13" t="n"/>
       <c r="M97" s="13" t="n"/>
-      <c r="O97" s="11" t="n"/>
-      <c r="P97" s="11" t="n"/>
+      <c r="N97" s="13" t="n"/>
+      <c r="O97" s="13" t="n"/>
       <c r="Q97" s="11" t="n"/>
       <c r="R97" s="11" t="n"/>
       <c r="S97" s="11" t="n"/>
@@ -3382,6 +3770,10 @@
       <c r="W97" s="11" t="n"/>
       <c r="X97" s="11" t="n"/>
       <c r="Y97" s="11" t="n"/>
+      <c r="Z97" s="11" t="n"/>
+      <c r="AA97" s="11" t="n"/>
+      <c r="AB97" s="11" t="n"/>
+      <c r="AC97" s="11" t="n"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="B98" s="12" t="inlineStr">
@@ -3400,8 +3792,8 @@
       <c r="K98" s="13" t="n"/>
       <c r="L98" s="13" t="n"/>
       <c r="M98" s="13" t="n"/>
-      <c r="O98" s="11" t="n"/>
-      <c r="P98" s="11" t="n"/>
+      <c r="N98" s="13" t="n"/>
+      <c r="O98" s="13" t="n"/>
       <c r="Q98" s="11" t="n"/>
       <c r="R98" s="11" t="n"/>
       <c r="S98" s="11" t="n"/>
@@ -3411,6 +3803,10 @@
       <c r="W98" s="11" t="n"/>
       <c r="X98" s="11" t="n"/>
       <c r="Y98" s="11" t="n"/>
+      <c r="Z98" s="11" t="n"/>
+      <c r="AA98" s="11" t="n"/>
+      <c r="AB98" s="11" t="n"/>
+      <c r="AC98" s="11" t="n"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="B99" s="9" t="inlineStr">
@@ -3429,8 +3825,8 @@
       <c r="K99" s="10" t="n"/>
       <c r="L99" s="10" t="n"/>
       <c r="M99" s="10" t="n"/>
-      <c r="O99" s="11" t="n"/>
-      <c r="P99" s="11" t="n"/>
+      <c r="N99" s="10" t="n"/>
+      <c r="O99" s="10" t="n"/>
       <c r="Q99" s="11" t="n"/>
       <c r="R99" s="11" t="n"/>
       <c r="S99" s="11" t="n"/>
@@ -3440,6 +3836,10 @@
       <c r="W99" s="11" t="n"/>
       <c r="X99" s="11" t="n"/>
       <c r="Y99" s="11" t="n"/>
+      <c r="Z99" s="11" t="n"/>
+      <c r="AA99" s="11" t="n"/>
+      <c r="AB99" s="11" t="n"/>
+      <c r="AC99" s="11" t="n"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="B100" s="14" t="inlineStr">
@@ -3458,8 +3858,8 @@
       <c r="K100" s="13" t="n"/>
       <c r="L100" s="13" t="n"/>
       <c r="M100" s="13" t="n"/>
-      <c r="O100" s="11" t="n"/>
-      <c r="P100" s="11" t="n"/>
+      <c r="N100" s="13" t="n"/>
+      <c r="O100" s="13" t="n"/>
       <c r="Q100" s="11" t="n"/>
       <c r="R100" s="11" t="n"/>
       <c r="S100" s="11" t="n"/>
@@ -3469,6 +3869,10 @@
       <c r="W100" s="11" t="n"/>
       <c r="X100" s="11" t="n"/>
       <c r="Y100" s="11" t="n"/>
+      <c r="Z100" s="11" t="n"/>
+      <c r="AA100" s="11" t="n"/>
+      <c r="AB100" s="11" t="n"/>
+      <c r="AC100" s="11" t="n"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="B101" s="14" t="inlineStr">
@@ -3487,8 +3891,8 @@
       <c r="K101" s="13" t="n"/>
       <c r="L101" s="13" t="n"/>
       <c r="M101" s="13" t="n"/>
-      <c r="O101" s="11" t="n"/>
-      <c r="P101" s="11" t="n"/>
+      <c r="N101" s="13" t="n"/>
+      <c r="O101" s="13" t="n"/>
       <c r="Q101" s="11" t="n"/>
       <c r="R101" s="11" t="n"/>
       <c r="S101" s="11" t="n"/>
@@ -3498,6 +3902,10 @@
       <c r="W101" s="11" t="n"/>
       <c r="X101" s="11" t="n"/>
       <c r="Y101" s="11" t="n"/>
+      <c r="Z101" s="11" t="n"/>
+      <c r="AA101" s="11" t="n"/>
+      <c r="AB101" s="11" t="n"/>
+      <c r="AC101" s="11" t="n"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="B102" s="9" t="inlineStr">
@@ -3516,8 +3924,8 @@
       <c r="K102" s="10" t="n"/>
       <c r="L102" s="10" t="n"/>
       <c r="M102" s="10" t="n"/>
-      <c r="O102" s="11" t="n"/>
-      <c r="P102" s="11" t="n"/>
+      <c r="N102" s="10" t="n"/>
+      <c r="O102" s="10" t="n"/>
       <c r="Q102" s="11" t="n"/>
       <c r="R102" s="11" t="n"/>
       <c r="S102" s="11" t="n"/>
@@ -3527,6 +3935,10 @@
       <c r="W102" s="11" t="n"/>
       <c r="X102" s="11" t="n"/>
       <c r="Y102" s="11" t="n"/>
+      <c r="Z102" s="11" t="n"/>
+      <c r="AA102" s="11" t="n"/>
+      <c r="AB102" s="11" t="n"/>
+      <c r="AC102" s="11" t="n"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="B103" s="12" t="inlineStr">
@@ -3545,8 +3957,8 @@
       <c r="K103" s="13" t="n"/>
       <c r="L103" s="13" t="n"/>
       <c r="M103" s="13" t="n"/>
-      <c r="O103" s="11" t="n"/>
-      <c r="P103" s="11" t="n"/>
+      <c r="N103" s="13" t="n"/>
+      <c r="O103" s="13" t="n"/>
       <c r="Q103" s="11" t="n"/>
       <c r="R103" s="11" t="n"/>
       <c r="S103" s="11" t="n"/>
@@ -3556,6 +3968,10 @@
       <c r="W103" s="11" t="n"/>
       <c r="X103" s="11" t="n"/>
       <c r="Y103" s="11" t="n"/>
+      <c r="Z103" s="11" t="n"/>
+      <c r="AA103" s="11" t="n"/>
+      <c r="AB103" s="11" t="n"/>
+      <c r="AC103" s="11" t="n"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="B104" s="12" t="inlineStr">
@@ -3574,8 +3990,8 @@
       <c r="K104" s="13" t="n"/>
       <c r="L104" s="13" t="n"/>
       <c r="M104" s="13" t="n"/>
-      <c r="O104" s="11" t="n"/>
-      <c r="P104" s="11" t="n"/>
+      <c r="N104" s="13" t="n"/>
+      <c r="O104" s="13" t="n"/>
       <c r="Q104" s="11" t="n"/>
       <c r="R104" s="11" t="n"/>
       <c r="S104" s="11" t="n"/>
@@ -3585,6 +4001,10 @@
       <c r="W104" s="11" t="n"/>
       <c r="X104" s="11" t="n"/>
       <c r="Y104" s="11" t="n"/>
+      <c r="Z104" s="11" t="n"/>
+      <c r="AA104" s="11" t="n"/>
+      <c r="AB104" s="11" t="n"/>
+      <c r="AC104" s="11" t="n"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="B105" s="12" t="inlineStr">
@@ -3603,8 +4023,8 @@
       <c r="K105" s="13" t="n"/>
       <c r="L105" s="13" t="n"/>
       <c r="M105" s="13" t="n"/>
-      <c r="O105" s="11" t="n"/>
-      <c r="P105" s="11" t="n"/>
+      <c r="N105" s="13" t="n"/>
+      <c r="O105" s="13" t="n"/>
       <c r="Q105" s="11" t="n"/>
       <c r="R105" s="11" t="n"/>
       <c r="S105" s="11" t="n"/>
@@ -3614,6 +4034,10 @@
       <c r="W105" s="11" t="n"/>
       <c r="X105" s="11" t="n"/>
       <c r="Y105" s="11" t="n"/>
+      <c r="Z105" s="11" t="n"/>
+      <c r="AA105" s="11" t="n"/>
+      <c r="AB105" s="11" t="n"/>
+      <c r="AC105" s="11" t="n"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="B106" s="12" t="inlineStr">
@@ -3632,8 +4056,8 @@
       <c r="K106" s="13" t="n"/>
       <c r="L106" s="13" t="n"/>
       <c r="M106" s="13" t="n"/>
-      <c r="O106" s="11" t="n"/>
-      <c r="P106" s="11" t="n"/>
+      <c r="N106" s="13" t="n"/>
+      <c r="O106" s="13" t="n"/>
       <c r="Q106" s="11" t="n"/>
       <c r="R106" s="11" t="n"/>
       <c r="S106" s="11" t="n"/>
@@ -3643,6 +4067,10 @@
       <c r="W106" s="11" t="n"/>
       <c r="X106" s="11" t="n"/>
       <c r="Y106" s="11" t="n"/>
+      <c r="Z106" s="11" t="n"/>
+      <c r="AA106" s="11" t="n"/>
+      <c r="AB106" s="11" t="n"/>
+      <c r="AC106" s="11" t="n"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="B107" s="9" t="inlineStr">
@@ -3661,8 +4089,8 @@
       <c r="K107" s="10" t="n"/>
       <c r="L107" s="10" t="n"/>
       <c r="M107" s="10" t="n"/>
-      <c r="O107" s="11" t="n"/>
-      <c r="P107" s="11" t="n"/>
+      <c r="N107" s="10" t="n"/>
+      <c r="O107" s="10" t="n"/>
       <c r="Q107" s="11" t="n"/>
       <c r="R107" s="11" t="n"/>
       <c r="S107" s="11" t="n"/>
@@ -3672,6 +4100,10 @@
       <c r="W107" s="11" t="n"/>
       <c r="X107" s="11" t="n"/>
       <c r="Y107" s="11" t="n"/>
+      <c r="Z107" s="11" t="n"/>
+      <c r="AA107" s="11" t="n"/>
+      <c r="AB107" s="11" t="n"/>
+      <c r="AC107" s="11" t="n"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="B108" s="12" t="inlineStr">
@@ -3690,8 +4122,8 @@
       <c r="K108" s="13" t="n"/>
       <c r="L108" s="13" t="n"/>
       <c r="M108" s="13" t="n"/>
-      <c r="O108" s="11" t="n"/>
-      <c r="P108" s="11" t="n"/>
+      <c r="N108" s="13" t="n"/>
+      <c r="O108" s="13" t="n"/>
       <c r="Q108" s="11" t="n"/>
       <c r="R108" s="11" t="n"/>
       <c r="S108" s="11" t="n"/>
@@ -3701,6 +4133,10 @@
       <c r="W108" s="11" t="n"/>
       <c r="X108" s="11" t="n"/>
       <c r="Y108" s="11" t="n"/>
+      <c r="Z108" s="11" t="n"/>
+      <c r="AA108" s="11" t="n"/>
+      <c r="AB108" s="11" t="n"/>
+      <c r="AC108" s="11" t="n"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="B109" s="12" t="inlineStr">
@@ -3719,8 +4155,8 @@
       <c r="K109" s="13" t="n"/>
       <c r="L109" s="13" t="n"/>
       <c r="M109" s="13" t="n"/>
-      <c r="O109" s="11" t="n"/>
-      <c r="P109" s="11" t="n"/>
+      <c r="N109" s="13" t="n"/>
+      <c r="O109" s="13" t="n"/>
       <c r="Q109" s="11" t="n"/>
       <c r="R109" s="11" t="n"/>
       <c r="S109" s="11" t="n"/>
@@ -3730,6 +4166,10 @@
       <c r="W109" s="11" t="n"/>
       <c r="X109" s="11" t="n"/>
       <c r="Y109" s="11" t="n"/>
+      <c r="Z109" s="11" t="n"/>
+      <c r="AA109" s="11" t="n"/>
+      <c r="AB109" s="11" t="n"/>
+      <c r="AC109" s="11" t="n"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="B110" s="12" t="inlineStr">
@@ -3748,8 +4188,8 @@
       <c r="K110" s="13" t="n"/>
       <c r="L110" s="13" t="n"/>
       <c r="M110" s="13" t="n"/>
-      <c r="O110" s="11" t="n"/>
-      <c r="P110" s="11" t="n"/>
+      <c r="N110" s="13" t="n"/>
+      <c r="O110" s="13" t="n"/>
       <c r="Q110" s="11" t="n"/>
       <c r="R110" s="11" t="n"/>
       <c r="S110" s="11" t="n"/>
@@ -3759,6 +4199,10 @@
       <c r="W110" s="11" t="n"/>
       <c r="X110" s="11" t="n"/>
       <c r="Y110" s="11" t="n"/>
+      <c r="Z110" s="11" t="n"/>
+      <c r="AA110" s="11" t="n"/>
+      <c r="AB110" s="11" t="n"/>
+      <c r="AC110" s="11" t="n"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="B111" s="14" t="inlineStr">
@@ -3777,8 +4221,8 @@
       <c r="K111" s="13" t="n"/>
       <c r="L111" s="13" t="n"/>
       <c r="M111" s="13" t="n"/>
-      <c r="O111" s="11" t="n"/>
-      <c r="P111" s="11" t="n"/>
+      <c r="N111" s="13" t="n"/>
+      <c r="O111" s="13" t="n"/>
       <c r="Q111" s="11" t="n"/>
       <c r="R111" s="11" t="n"/>
       <c r="S111" s="11" t="n"/>
@@ -3788,26 +4232,30 @@
       <c r="W111" s="11" t="n"/>
       <c r="X111" s="11" t="n"/>
       <c r="Y111" s="11" t="n"/>
+      <c r="Z111" s="11" t="n"/>
+      <c r="AA111" s="11" t="n"/>
+      <c r="AB111" s="11" t="n"/>
+      <c r="AC111" s="11" t="n"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="B112" s="9" t="inlineStr">
+      <c r="B112" s="12" t="inlineStr">
         <is>
           <t>Season Pass (Free)</t>
         </is>
       </c>
-      <c r="C112" s="10" t="n"/>
-      <c r="D112" s="10" t="n"/>
-      <c r="E112" s="10" t="n"/>
-      <c r="F112" s="10" t="n"/>
-      <c r="G112" s="10" t="n"/>
-      <c r="H112" s="10" t="n"/>
-      <c r="I112" s="10" t="n"/>
-      <c r="J112" s="10" t="n"/>
-      <c r="K112" s="10" t="n"/>
-      <c r="L112" s="10" t="n"/>
-      <c r="M112" s="10" t="n"/>
-      <c r="O112" s="11" t="n"/>
-      <c r="P112" s="11" t="n"/>
+      <c r="C112" s="13" t="n"/>
+      <c r="D112" s="13" t="n"/>
+      <c r="E112" s="13" t="n"/>
+      <c r="F112" s="13" t="n"/>
+      <c r="G112" s="13" t="n"/>
+      <c r="H112" s="13" t="n"/>
+      <c r="I112" s="13" t="n"/>
+      <c r="J112" s="13" t="n"/>
+      <c r="K112" s="13" t="n"/>
+      <c r="L112" s="13" t="n"/>
+      <c r="M112" s="13" t="n"/>
+      <c r="N112" s="13" t="n"/>
+      <c r="O112" s="13" t="n"/>
       <c r="Q112" s="11" t="n"/>
       <c r="R112" s="11" t="n"/>
       <c r="S112" s="11" t="n"/>
@@ -3817,6 +4265,10 @@
       <c r="W112" s="11" t="n"/>
       <c r="X112" s="11" t="n"/>
       <c r="Y112" s="11" t="n"/>
+      <c r="Z112" s="11" t="n"/>
+      <c r="AA112" s="11" t="n"/>
+      <c r="AB112" s="11" t="n"/>
+      <c r="AC112" s="11" t="n"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="B113" s="12" t="inlineStr">
@@ -3835,8 +4287,8 @@
       <c r="K113" s="13" t="n"/>
       <c r="L113" s="13" t="n"/>
       <c r="M113" s="13" t="n"/>
-      <c r="O113" s="11" t="n"/>
-      <c r="P113" s="11" t="n"/>
+      <c r="N113" s="13" t="n"/>
+      <c r="O113" s="13" t="n"/>
       <c r="Q113" s="11" t="n"/>
       <c r="R113" s="11" t="n"/>
       <c r="S113" s="11" t="n"/>
@@ -3846,6 +4298,10 @@
       <c r="W113" s="11" t="n"/>
       <c r="X113" s="11" t="n"/>
       <c r="Y113" s="11" t="n"/>
+      <c r="Z113" s="11" t="n"/>
+      <c r="AA113" s="11" t="n"/>
+      <c r="AB113" s="11" t="n"/>
+      <c r="AC113" s="11" t="n"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="B114" s="9" t="inlineStr">
@@ -3864,8 +4320,8 @@
       <c r="K114" s="10" t="n"/>
       <c r="L114" s="10" t="n"/>
       <c r="M114" s="10" t="n"/>
-      <c r="O114" s="11" t="n"/>
-      <c r="P114" s="11" t="n"/>
+      <c r="N114" s="10" t="n"/>
+      <c r="O114" s="10" t="n"/>
       <c r="Q114" s="11" t="n"/>
       <c r="R114" s="11" t="n"/>
       <c r="S114" s="11" t="n"/>
@@ -3875,6 +4331,10 @@
       <c r="W114" s="11" t="n"/>
       <c r="X114" s="11" t="n"/>
       <c r="Y114" s="11" t="n"/>
+      <c r="Z114" s="11" t="n"/>
+      <c r="AA114" s="11" t="n"/>
+      <c r="AB114" s="11" t="n"/>
+      <c r="AC114" s="11" t="n"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="B115" s="9" t="inlineStr">
@@ -3893,8 +4353,8 @@
       <c r="K115" s="10" t="n"/>
       <c r="L115" s="10" t="n"/>
       <c r="M115" s="10" t="n"/>
-      <c r="O115" s="11" t="n"/>
-      <c r="P115" s="11" t="n"/>
+      <c r="N115" s="10" t="n"/>
+      <c r="O115" s="10" t="n"/>
       <c r="Q115" s="11" t="n"/>
       <c r="R115" s="11" t="n"/>
       <c r="S115" s="11" t="n"/>
@@ -3904,6 +4364,10 @@
       <c r="W115" s="11" t="n"/>
       <c r="X115" s="11" t="n"/>
       <c r="Y115" s="11" t="n"/>
+      <c r="Z115" s="11" t="n"/>
+      <c r="AA115" s="11" t="n"/>
+      <c r="AB115" s="11" t="n"/>
+      <c r="AC115" s="11" t="n"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="B116" s="12" t="inlineStr">
@@ -3922,8 +4386,8 @@
       <c r="K116" s="13" t="n"/>
       <c r="L116" s="13" t="n"/>
       <c r="M116" s="13" t="n"/>
-      <c r="O116" s="11" t="n"/>
-      <c r="P116" s="11" t="n"/>
+      <c r="N116" s="13" t="n"/>
+      <c r="O116" s="13" t="n"/>
       <c r="Q116" s="11" t="n"/>
       <c r="R116" s="11" t="n"/>
       <c r="S116" s="11" t="n"/>
@@ -3933,6 +4397,10 @@
       <c r="W116" s="11" t="n"/>
       <c r="X116" s="11" t="n"/>
       <c r="Y116" s="11" t="n"/>
+      <c r="Z116" s="11" t="n"/>
+      <c r="AA116" s="11" t="n"/>
+      <c r="AB116" s="11" t="n"/>
+      <c r="AC116" s="11" t="n"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="B117" s="9" t="inlineStr">
@@ -3951,8 +4419,8 @@
       <c r="K117" s="10" t="n"/>
       <c r="L117" s="10" t="n"/>
       <c r="M117" s="10" t="n"/>
-      <c r="O117" s="11" t="n"/>
-      <c r="P117" s="11" t="n"/>
+      <c r="N117" s="10" t="n"/>
+      <c r="O117" s="10" t="n"/>
       <c r="Q117" s="11" t="n"/>
       <c r="R117" s="11" t="n"/>
       <c r="S117" s="11" t="n"/>
@@ -3962,6 +4430,10 @@
       <c r="W117" s="11" t="n"/>
       <c r="X117" s="11" t="n"/>
       <c r="Y117" s="11" t="n"/>
+      <c r="Z117" s="11" t="n"/>
+      <c r="AA117" s="11" t="n"/>
+      <c r="AB117" s="11" t="n"/>
+      <c r="AC117" s="11" t="n"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="B118" s="12" t="inlineStr">
@@ -3980,8 +4452,8 @@
       <c r="K118" s="13" t="n"/>
       <c r="L118" s="13" t="n"/>
       <c r="M118" s="13" t="n"/>
-      <c r="O118" s="11" t="n"/>
-      <c r="P118" s="11" t="n"/>
+      <c r="N118" s="13" t="n"/>
+      <c r="O118" s="13" t="n"/>
       <c r="Q118" s="11" t="n"/>
       <c r="R118" s="11" t="n"/>
       <c r="S118" s="11" t="n"/>
@@ -3991,6 +4463,10 @@
       <c r="W118" s="11" t="n"/>
       <c r="X118" s="11" t="n"/>
       <c r="Y118" s="11" t="n"/>
+      <c r="Z118" s="11" t="n"/>
+      <c r="AA118" s="11" t="n"/>
+      <c r="AB118" s="11" t="n"/>
+      <c r="AC118" s="11" t="n"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
       <c r="B119" s="9" t="inlineStr">
@@ -4009,8 +4485,8 @@
       <c r="K119" s="10" t="n"/>
       <c r="L119" s="10" t="n"/>
       <c r="M119" s="10" t="n"/>
-      <c r="O119" s="11" t="n"/>
-      <c r="P119" s="11" t="n"/>
+      <c r="N119" s="10" t="n"/>
+      <c r="O119" s="10" t="n"/>
       <c r="Q119" s="11" t="n"/>
       <c r="R119" s="11" t="n"/>
       <c r="S119" s="11" t="n"/>
@@ -4020,6 +4496,10 @@
       <c r="W119" s="11" t="n"/>
       <c r="X119" s="11" t="n"/>
       <c r="Y119" s="11" t="n"/>
+      <c r="Z119" s="11" t="n"/>
+      <c r="AA119" s="11" t="n"/>
+      <c r="AB119" s="11" t="n"/>
+      <c r="AC119" s="11" t="n"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="B122" s="5" t="inlineStr">
@@ -4032,7 +4512,7 @@
           <t>100+ Segment - Over Time Period</t>
         </is>
       </c>
-      <c r="O122" s="6" t="inlineStr">
+      <c r="Q122" s="6" t="inlineStr">
         <is>
           <t>100+ Segment - Over Time Period - Difference</t>
         </is>
@@ -4099,59 +4579,79 @@
           <t>Unlimited Lives</t>
         </is>
       </c>
+      <c r="N123" s="8" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
       <c r="O123" s="8" t="inlineStr">
         <is>
+          <t>SPTx2</t>
+        </is>
+      </c>
+      <c r="Q123" s="8" t="inlineStr">
+        <is>
           <t>HC</t>
         </is>
       </c>
-      <c r="P123" s="8" t="inlineStr">
+      <c r="R123" s="8" t="inlineStr">
         <is>
           <t>Slingshot</t>
         </is>
       </c>
-      <c r="Q123" s="8" t="inlineStr">
+      <c r="S123" s="8" t="inlineStr">
         <is>
           <t>Shuffle</t>
         </is>
       </c>
-      <c r="R123" s="8" t="inlineStr">
+      <c r="T123" s="8" t="inlineStr">
         <is>
           <t>Comet</t>
         </is>
       </c>
-      <c r="S123" s="8" t="inlineStr">
+      <c r="U123" s="8" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="T123" s="8" t="inlineStr">
+      <c r="V123" s="8" t="inlineStr">
         <is>
           <t>Chuck</t>
         </is>
       </c>
-      <c r="U123" s="8" t="inlineStr">
+      <c r="W123" s="8" t="inlineStr">
         <is>
           <t>Bomb</t>
         </is>
       </c>
-      <c r="V123" s="8" t="inlineStr">
+      <c r="X123" s="8" t="inlineStr">
         <is>
           <t>UL Bomb</t>
         </is>
       </c>
-      <c r="W123" s="8" t="inlineStr">
+      <c r="Y123" s="8" t="inlineStr">
         <is>
           <t>UL Chuck</t>
         </is>
       </c>
-      <c r="X123" s="8" t="inlineStr">
+      <c r="Z123" s="8" t="inlineStr">
         <is>
           <t>UL Red</t>
         </is>
       </c>
-      <c r="Y123" s="8" t="inlineStr">
+      <c r="AA123" s="8" t="inlineStr">
         <is>
           <t>Unlimited Lives</t>
+        </is>
+      </c>
+      <c r="AB123" s="8" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
+      <c r="AC123" s="8" t="inlineStr">
+        <is>
+          <t>SPTx2</t>
         </is>
       </c>
     </row>
@@ -4175,12 +4675,12 @@
       <c r="K124" s="10" t="n"/>
       <c r="L124" s="10" t="n"/>
       <c r="M124" s="10" t="n"/>
-      <c r="O124" s="11">
+      <c r="N124" s="10" t="n"/>
+      <c r="O124" s="10" t="n"/>
+      <c r="Q124" s="11">
         <f>LET(payer, $C$3, segment, $B$122, ECOGAINS_DIFF(payer, segment, sim_refresh!$A$1))</f>
         <v/>
       </c>
-      <c r="P124" s="11" t="n"/>
-      <c r="Q124" s="11" t="n"/>
       <c r="R124" s="11" t="n"/>
       <c r="S124" s="11" t="n"/>
       <c r="T124" s="11" t="n"/>
@@ -4189,6 +4689,10 @@
       <c r="W124" s="11" t="n"/>
       <c r="X124" s="11" t="n"/>
       <c r="Y124" s="11" t="n"/>
+      <c r="Z124" s="11" t="n"/>
+      <c r="AA124" s="11" t="n"/>
+      <c r="AB124" s="11" t="n"/>
+      <c r="AC124" s="11" t="n"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
       <c r="B125" s="12" t="inlineStr">
@@ -4207,8 +4711,8 @@
       <c r="K125" s="13" t="n"/>
       <c r="L125" s="13" t="n"/>
       <c r="M125" s="13" t="n"/>
-      <c r="O125" s="11" t="n"/>
-      <c r="P125" s="11" t="n"/>
+      <c r="N125" s="13" t="n"/>
+      <c r="O125" s="13" t="n"/>
       <c r="Q125" s="11" t="n"/>
       <c r="R125" s="11" t="n"/>
       <c r="S125" s="11" t="n"/>
@@ -4218,6 +4722,10 @@
       <c r="W125" s="11" t="n"/>
       <c r="X125" s="11" t="n"/>
       <c r="Y125" s="11" t="n"/>
+      <c r="Z125" s="11" t="n"/>
+      <c r="AA125" s="11" t="n"/>
+      <c r="AB125" s="11" t="n"/>
+      <c r="AC125" s="11" t="n"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
       <c r="B126" s="12" t="inlineStr">
@@ -4236,8 +4744,8 @@
       <c r="K126" s="13" t="n"/>
       <c r="L126" s="13" t="n"/>
       <c r="M126" s="13" t="n"/>
-      <c r="O126" s="11" t="n"/>
-      <c r="P126" s="11" t="n"/>
+      <c r="N126" s="13" t="n"/>
+      <c r="O126" s="13" t="n"/>
       <c r="Q126" s="11" t="n"/>
       <c r="R126" s="11" t="n"/>
       <c r="S126" s="11" t="n"/>
@@ -4247,6 +4755,10 @@
       <c r="W126" s="11" t="n"/>
       <c r="X126" s="11" t="n"/>
       <c r="Y126" s="11" t="n"/>
+      <c r="Z126" s="11" t="n"/>
+      <c r="AA126" s="11" t="n"/>
+      <c r="AB126" s="11" t="n"/>
+      <c r="AC126" s="11" t="n"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
       <c r="B127" s="12" t="inlineStr">
@@ -4265,8 +4777,8 @@
       <c r="K127" s="13" t="n"/>
       <c r="L127" s="13" t="n"/>
       <c r="M127" s="13" t="n"/>
-      <c r="O127" s="11" t="n"/>
-      <c r="P127" s="11" t="n"/>
+      <c r="N127" s="13" t="n"/>
+      <c r="O127" s="13" t="n"/>
       <c r="Q127" s="11" t="n"/>
       <c r="R127" s="11" t="n"/>
       <c r="S127" s="11" t="n"/>
@@ -4276,6 +4788,10 @@
       <c r="W127" s="11" t="n"/>
       <c r="X127" s="11" t="n"/>
       <c r="Y127" s="11" t="n"/>
+      <c r="Z127" s="11" t="n"/>
+      <c r="AA127" s="11" t="n"/>
+      <c r="AB127" s="11" t="n"/>
+      <c r="AC127" s="11" t="n"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
       <c r="B128" s="9" t="inlineStr">
@@ -4294,8 +4810,8 @@
       <c r="K128" s="10" t="n"/>
       <c r="L128" s="10" t="n"/>
       <c r="M128" s="10" t="n"/>
-      <c r="O128" s="11" t="n"/>
-      <c r="P128" s="11" t="n"/>
+      <c r="N128" s="10" t="n"/>
+      <c r="O128" s="10" t="n"/>
       <c r="Q128" s="11" t="n"/>
       <c r="R128" s="11" t="n"/>
       <c r="S128" s="11" t="n"/>
@@ -4305,6 +4821,10 @@
       <c r="W128" s="11" t="n"/>
       <c r="X128" s="11" t="n"/>
       <c r="Y128" s="11" t="n"/>
+      <c r="Z128" s="11" t="n"/>
+      <c r="AA128" s="11" t="n"/>
+      <c r="AB128" s="11" t="n"/>
+      <c r="AC128" s="11" t="n"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
       <c r="B129" s="14" t="inlineStr">
@@ -4323,8 +4843,8 @@
       <c r="K129" s="13" t="n"/>
       <c r="L129" s="13" t="n"/>
       <c r="M129" s="13" t="n"/>
-      <c r="O129" s="11" t="n"/>
-      <c r="P129" s="11" t="n"/>
+      <c r="N129" s="13" t="n"/>
+      <c r="O129" s="13" t="n"/>
       <c r="Q129" s="11" t="n"/>
       <c r="R129" s="11" t="n"/>
       <c r="S129" s="11" t="n"/>
@@ -4334,6 +4854,10 @@
       <c r="W129" s="11" t="n"/>
       <c r="X129" s="11" t="n"/>
       <c r="Y129" s="11" t="n"/>
+      <c r="Z129" s="11" t="n"/>
+      <c r="AA129" s="11" t="n"/>
+      <c r="AB129" s="11" t="n"/>
+      <c r="AC129" s="11" t="n"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
       <c r="B130" s="14" t="inlineStr">
@@ -4352,8 +4876,8 @@
       <c r="K130" s="13" t="n"/>
       <c r="L130" s="13" t="n"/>
       <c r="M130" s="13" t="n"/>
-      <c r="O130" s="11" t="n"/>
-      <c r="P130" s="11" t="n"/>
+      <c r="N130" s="13" t="n"/>
+      <c r="O130" s="13" t="n"/>
       <c r="Q130" s="11" t="n"/>
       <c r="R130" s="11" t="n"/>
       <c r="S130" s="11" t="n"/>
@@ -4363,6 +4887,10 @@
       <c r="W130" s="11" t="n"/>
       <c r="X130" s="11" t="n"/>
       <c r="Y130" s="11" t="n"/>
+      <c r="Z130" s="11" t="n"/>
+      <c r="AA130" s="11" t="n"/>
+      <c r="AB130" s="11" t="n"/>
+      <c r="AC130" s="11" t="n"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
       <c r="B131" s="9" t="inlineStr">
@@ -4381,8 +4909,8 @@
       <c r="K131" s="10" t="n"/>
       <c r="L131" s="10" t="n"/>
       <c r="M131" s="10" t="n"/>
-      <c r="O131" s="11" t="n"/>
-      <c r="P131" s="11" t="n"/>
+      <c r="N131" s="10" t="n"/>
+      <c r="O131" s="10" t="n"/>
       <c r="Q131" s="11" t="n"/>
       <c r="R131" s="11" t="n"/>
       <c r="S131" s="11" t="n"/>
@@ -4392,6 +4920,10 @@
       <c r="W131" s="11" t="n"/>
       <c r="X131" s="11" t="n"/>
       <c r="Y131" s="11" t="n"/>
+      <c r="Z131" s="11" t="n"/>
+      <c r="AA131" s="11" t="n"/>
+      <c r="AB131" s="11" t="n"/>
+      <c r="AC131" s="11" t="n"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
       <c r="B132" s="12" t="inlineStr">
@@ -4410,8 +4942,8 @@
       <c r="K132" s="13" t="n"/>
       <c r="L132" s="13" t="n"/>
       <c r="M132" s="13" t="n"/>
-      <c r="O132" s="11" t="n"/>
-      <c r="P132" s="11" t="n"/>
+      <c r="N132" s="13" t="n"/>
+      <c r="O132" s="13" t="n"/>
       <c r="Q132" s="11" t="n"/>
       <c r="R132" s="11" t="n"/>
       <c r="S132" s="11" t="n"/>
@@ -4421,6 +4953,10 @@
       <c r="W132" s="11" t="n"/>
       <c r="X132" s="11" t="n"/>
       <c r="Y132" s="11" t="n"/>
+      <c r="Z132" s="11" t="n"/>
+      <c r="AA132" s="11" t="n"/>
+      <c r="AB132" s="11" t="n"/>
+      <c r="AC132" s="11" t="n"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
       <c r="B133" s="12" t="inlineStr">
@@ -4439,8 +4975,8 @@
       <c r="K133" s="13" t="n"/>
       <c r="L133" s="13" t="n"/>
       <c r="M133" s="13" t="n"/>
-      <c r="O133" s="11" t="n"/>
-      <c r="P133" s="11" t="n"/>
+      <c r="N133" s="13" t="n"/>
+      <c r="O133" s="13" t="n"/>
       <c r="Q133" s="11" t="n"/>
       <c r="R133" s="11" t="n"/>
       <c r="S133" s="11" t="n"/>
@@ -4450,6 +4986,10 @@
       <c r="W133" s="11" t="n"/>
       <c r="X133" s="11" t="n"/>
       <c r="Y133" s="11" t="n"/>
+      <c r="Z133" s="11" t="n"/>
+      <c r="AA133" s="11" t="n"/>
+      <c r="AB133" s="11" t="n"/>
+      <c r="AC133" s="11" t="n"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
       <c r="B134" s="12" t="inlineStr">
@@ -4468,8 +5008,8 @@
       <c r="K134" s="13" t="n"/>
       <c r="L134" s="13" t="n"/>
       <c r="M134" s="13" t="n"/>
-      <c r="O134" s="11" t="n"/>
-      <c r="P134" s="11" t="n"/>
+      <c r="N134" s="13" t="n"/>
+      <c r="O134" s="13" t="n"/>
       <c r="Q134" s="11" t="n"/>
       <c r="R134" s="11" t="n"/>
       <c r="S134" s="11" t="n"/>
@@ -4479,6 +5019,10 @@
       <c r="W134" s="11" t="n"/>
       <c r="X134" s="11" t="n"/>
       <c r="Y134" s="11" t="n"/>
+      <c r="Z134" s="11" t="n"/>
+      <c r="AA134" s="11" t="n"/>
+      <c r="AB134" s="11" t="n"/>
+      <c r="AC134" s="11" t="n"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
       <c r="B135" s="12" t="inlineStr">
@@ -4497,8 +5041,8 @@
       <c r="K135" s="13" t="n"/>
       <c r="L135" s="13" t="n"/>
       <c r="M135" s="13" t="n"/>
-      <c r="O135" s="11" t="n"/>
-      <c r="P135" s="11" t="n"/>
+      <c r="N135" s="13" t="n"/>
+      <c r="O135" s="13" t="n"/>
       <c r="Q135" s="11" t="n"/>
       <c r="R135" s="11" t="n"/>
       <c r="S135" s="11" t="n"/>
@@ -4508,6 +5052,10 @@
       <c r="W135" s="11" t="n"/>
       <c r="X135" s="11" t="n"/>
       <c r="Y135" s="11" t="n"/>
+      <c r="Z135" s="11" t="n"/>
+      <c r="AA135" s="11" t="n"/>
+      <c r="AB135" s="11" t="n"/>
+      <c r="AC135" s="11" t="n"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
       <c r="B136" s="9" t="inlineStr">
@@ -4526,8 +5074,8 @@
       <c r="K136" s="10" t="n"/>
       <c r="L136" s="10" t="n"/>
       <c r="M136" s="10" t="n"/>
-      <c r="O136" s="11" t="n"/>
-      <c r="P136" s="11" t="n"/>
+      <c r="N136" s="10" t="n"/>
+      <c r="O136" s="10" t="n"/>
       <c r="Q136" s="11" t="n"/>
       <c r="R136" s="11" t="n"/>
       <c r="S136" s="11" t="n"/>
@@ -4537,6 +5085,10 @@
       <c r="W136" s="11" t="n"/>
       <c r="X136" s="11" t="n"/>
       <c r="Y136" s="11" t="n"/>
+      <c r="Z136" s="11" t="n"/>
+      <c r="AA136" s="11" t="n"/>
+      <c r="AB136" s="11" t="n"/>
+      <c r="AC136" s="11" t="n"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
       <c r="B137" s="12" t="inlineStr">
@@ -4555,8 +5107,8 @@
       <c r="K137" s="13" t="n"/>
       <c r="L137" s="13" t="n"/>
       <c r="M137" s="13" t="n"/>
-      <c r="O137" s="11" t="n"/>
-      <c r="P137" s="11" t="n"/>
+      <c r="N137" s="13" t="n"/>
+      <c r="O137" s="13" t="n"/>
       <c r="Q137" s="11" t="n"/>
       <c r="R137" s="11" t="n"/>
       <c r="S137" s="11" t="n"/>
@@ -4566,6 +5118,10 @@
       <c r="W137" s="11" t="n"/>
       <c r="X137" s="11" t="n"/>
       <c r="Y137" s="11" t="n"/>
+      <c r="Z137" s="11" t="n"/>
+      <c r="AA137" s="11" t="n"/>
+      <c r="AB137" s="11" t="n"/>
+      <c r="AC137" s="11" t="n"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
       <c r="B138" s="12" t="inlineStr">
@@ -4584,8 +5140,8 @@
       <c r="K138" s="13" t="n"/>
       <c r="L138" s="13" t="n"/>
       <c r="M138" s="13" t="n"/>
-      <c r="O138" s="11" t="n"/>
-      <c r="P138" s="11" t="n"/>
+      <c r="N138" s="13" t="n"/>
+      <c r="O138" s="13" t="n"/>
       <c r="Q138" s="11" t="n"/>
       <c r="R138" s="11" t="n"/>
       <c r="S138" s="11" t="n"/>
@@ -4595,6 +5151,10 @@
       <c r="W138" s="11" t="n"/>
       <c r="X138" s="11" t="n"/>
       <c r="Y138" s="11" t="n"/>
+      <c r="Z138" s="11" t="n"/>
+      <c r="AA138" s="11" t="n"/>
+      <c r="AB138" s="11" t="n"/>
+      <c r="AC138" s="11" t="n"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
       <c r="B139" s="12" t="inlineStr">
@@ -4613,8 +5173,8 @@
       <c r="K139" s="13" t="n"/>
       <c r="L139" s="13" t="n"/>
       <c r="M139" s="13" t="n"/>
-      <c r="O139" s="11" t="n"/>
-      <c r="P139" s="11" t="n"/>
+      <c r="N139" s="13" t="n"/>
+      <c r="O139" s="13" t="n"/>
       <c r="Q139" s="11" t="n"/>
       <c r="R139" s="11" t="n"/>
       <c r="S139" s="11" t="n"/>
@@ -4624,6 +5184,10 @@
       <c r="W139" s="11" t="n"/>
       <c r="X139" s="11" t="n"/>
       <c r="Y139" s="11" t="n"/>
+      <c r="Z139" s="11" t="n"/>
+      <c r="AA139" s="11" t="n"/>
+      <c r="AB139" s="11" t="n"/>
+      <c r="AC139" s="11" t="n"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
       <c r="B140" s="14" t="inlineStr">
@@ -4642,8 +5206,8 @@
       <c r="K140" s="13" t="n"/>
       <c r="L140" s="13" t="n"/>
       <c r="M140" s="13" t="n"/>
-      <c r="O140" s="11" t="n"/>
-      <c r="P140" s="11" t="n"/>
+      <c r="N140" s="13" t="n"/>
+      <c r="O140" s="13" t="n"/>
       <c r="Q140" s="11" t="n"/>
       <c r="R140" s="11" t="n"/>
       <c r="S140" s="11" t="n"/>
@@ -4653,26 +5217,30 @@
       <c r="W140" s="11" t="n"/>
       <c r="X140" s="11" t="n"/>
       <c r="Y140" s="11" t="n"/>
+      <c r="Z140" s="11" t="n"/>
+      <c r="AA140" s="11" t="n"/>
+      <c r="AB140" s="11" t="n"/>
+      <c r="AC140" s="11" t="n"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="B141" s="9" t="inlineStr">
+      <c r="B141" s="12" t="inlineStr">
         <is>
           <t>Season Pass (Free)</t>
         </is>
       </c>
-      <c r="C141" s="10" t="n"/>
-      <c r="D141" s="10" t="n"/>
-      <c r="E141" s="10" t="n"/>
-      <c r="F141" s="10" t="n"/>
-      <c r="G141" s="10" t="n"/>
-      <c r="H141" s="10" t="n"/>
-      <c r="I141" s="10" t="n"/>
-      <c r="J141" s="10" t="n"/>
-      <c r="K141" s="10" t="n"/>
-      <c r="L141" s="10" t="n"/>
-      <c r="M141" s="10" t="n"/>
-      <c r="O141" s="11" t="n"/>
-      <c r="P141" s="11" t="n"/>
+      <c r="C141" s="13" t="n"/>
+      <c r="D141" s="13" t="n"/>
+      <c r="E141" s="13" t="n"/>
+      <c r="F141" s="13" t="n"/>
+      <c r="G141" s="13" t="n"/>
+      <c r="H141" s="13" t="n"/>
+      <c r="I141" s="13" t="n"/>
+      <c r="J141" s="13" t="n"/>
+      <c r="K141" s="13" t="n"/>
+      <c r="L141" s="13" t="n"/>
+      <c r="M141" s="13" t="n"/>
+      <c r="N141" s="13" t="n"/>
+      <c r="O141" s="13" t="n"/>
       <c r="Q141" s="11" t="n"/>
       <c r="R141" s="11" t="n"/>
       <c r="S141" s="11" t="n"/>
@@ -4682,6 +5250,10 @@
       <c r="W141" s="11" t="n"/>
       <c r="X141" s="11" t="n"/>
       <c r="Y141" s="11" t="n"/>
+      <c r="Z141" s="11" t="n"/>
+      <c r="AA141" s="11" t="n"/>
+      <c r="AB141" s="11" t="n"/>
+      <c r="AC141" s="11" t="n"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
       <c r="B142" s="12" t="inlineStr">
@@ -4700,8 +5272,8 @@
       <c r="K142" s="13" t="n"/>
       <c r="L142" s="13" t="n"/>
       <c r="M142" s="13" t="n"/>
-      <c r="O142" s="11" t="n"/>
-      <c r="P142" s="11" t="n"/>
+      <c r="N142" s="13" t="n"/>
+      <c r="O142" s="13" t="n"/>
       <c r="Q142" s="11" t="n"/>
       <c r="R142" s="11" t="n"/>
       <c r="S142" s="11" t="n"/>
@@ -4711,6 +5283,10 @@
       <c r="W142" s="11" t="n"/>
       <c r="X142" s="11" t="n"/>
       <c r="Y142" s="11" t="n"/>
+      <c r="Z142" s="11" t="n"/>
+      <c r="AA142" s="11" t="n"/>
+      <c r="AB142" s="11" t="n"/>
+      <c r="AC142" s="11" t="n"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
       <c r="B143" s="9" t="inlineStr">
@@ -4729,8 +5305,8 @@
       <c r="K143" s="10" t="n"/>
       <c r="L143" s="10" t="n"/>
       <c r="M143" s="10" t="n"/>
-      <c r="O143" s="11" t="n"/>
-      <c r="P143" s="11" t="n"/>
+      <c r="N143" s="10" t="n"/>
+      <c r="O143" s="10" t="n"/>
       <c r="Q143" s="11" t="n"/>
       <c r="R143" s="11" t="n"/>
       <c r="S143" s="11" t="n"/>
@@ -4740,6 +5316,10 @@
       <c r="W143" s="11" t="n"/>
       <c r="X143" s="11" t="n"/>
       <c r="Y143" s="11" t="n"/>
+      <c r="Z143" s="11" t="n"/>
+      <c r="AA143" s="11" t="n"/>
+      <c r="AB143" s="11" t="n"/>
+      <c r="AC143" s="11" t="n"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
       <c r="B144" s="9" t="inlineStr">
@@ -4758,8 +5338,8 @@
       <c r="K144" s="10" t="n"/>
       <c r="L144" s="10" t="n"/>
       <c r="M144" s="10" t="n"/>
-      <c r="O144" s="11" t="n"/>
-      <c r="P144" s="11" t="n"/>
+      <c r="N144" s="10" t="n"/>
+      <c r="O144" s="10" t="n"/>
       <c r="Q144" s="11" t="n"/>
       <c r="R144" s="11" t="n"/>
       <c r="S144" s="11" t="n"/>
@@ -4769,6 +5349,10 @@
       <c r="W144" s="11" t="n"/>
       <c r="X144" s="11" t="n"/>
       <c r="Y144" s="11" t="n"/>
+      <c r="Z144" s="11" t="n"/>
+      <c r="AA144" s="11" t="n"/>
+      <c r="AB144" s="11" t="n"/>
+      <c r="AC144" s="11" t="n"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
       <c r="B145" s="12" t="inlineStr">
@@ -4787,8 +5371,8 @@
       <c r="K145" s="13" t="n"/>
       <c r="L145" s="13" t="n"/>
       <c r="M145" s="13" t="n"/>
-      <c r="O145" s="11" t="n"/>
-      <c r="P145" s="11" t="n"/>
+      <c r="N145" s="13" t="n"/>
+      <c r="O145" s="13" t="n"/>
       <c r="Q145" s="11" t="n"/>
       <c r="R145" s="11" t="n"/>
       <c r="S145" s="11" t="n"/>
@@ -4798,6 +5382,10 @@
       <c r="W145" s="11" t="n"/>
       <c r="X145" s="11" t="n"/>
       <c r="Y145" s="11" t="n"/>
+      <c r="Z145" s="11" t="n"/>
+      <c r="AA145" s="11" t="n"/>
+      <c r="AB145" s="11" t="n"/>
+      <c r="AC145" s="11" t="n"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
       <c r="B146" s="9" t="inlineStr">
@@ -4816,8 +5404,8 @@
       <c r="K146" s="10" t="n"/>
       <c r="L146" s="10" t="n"/>
       <c r="M146" s="10" t="n"/>
-      <c r="O146" s="11" t="n"/>
-      <c r="P146" s="11" t="n"/>
+      <c r="N146" s="10" t="n"/>
+      <c r="O146" s="10" t="n"/>
       <c r="Q146" s="11" t="n"/>
       <c r="R146" s="11" t="n"/>
       <c r="S146" s="11" t="n"/>
@@ -4827,6 +5415,10 @@
       <c r="W146" s="11" t="n"/>
       <c r="X146" s="11" t="n"/>
       <c r="Y146" s="11" t="n"/>
+      <c r="Z146" s="11" t="n"/>
+      <c r="AA146" s="11" t="n"/>
+      <c r="AB146" s="11" t="n"/>
+      <c r="AC146" s="11" t="n"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
       <c r="B147" s="12" t="inlineStr">
@@ -4845,8 +5437,8 @@
       <c r="K147" s="13" t="n"/>
       <c r="L147" s="13" t="n"/>
       <c r="M147" s="13" t="n"/>
-      <c r="O147" s="11" t="n"/>
-      <c r="P147" s="11" t="n"/>
+      <c r="N147" s="13" t="n"/>
+      <c r="O147" s="13" t="n"/>
       <c r="Q147" s="11" t="n"/>
       <c r="R147" s="11" t="n"/>
       <c r="S147" s="11" t="n"/>
@@ -4856,6 +5448,10 @@
       <c r="W147" s="11" t="n"/>
       <c r="X147" s="11" t="n"/>
       <c r="Y147" s="11" t="n"/>
+      <c r="Z147" s="11" t="n"/>
+      <c r="AA147" s="11" t="n"/>
+      <c r="AB147" s="11" t="n"/>
+      <c r="AC147" s="11" t="n"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
       <c r="B148" s="9" t="inlineStr">
@@ -4874,8 +5470,8 @@
       <c r="K148" s="10" t="n"/>
       <c r="L148" s="10" t="n"/>
       <c r="M148" s="10" t="n"/>
-      <c r="O148" s="11" t="n"/>
-      <c r="P148" s="11" t="n"/>
+      <c r="N148" s="10" t="n"/>
+      <c r="O148" s="10" t="n"/>
       <c r="Q148" s="11" t="n"/>
       <c r="R148" s="11" t="n"/>
       <c r="S148" s="11" t="n"/>
@@ -4885,6 +5481,10 @@
       <c r="W148" s="11" t="n"/>
       <c r="X148" s="11" t="n"/>
       <c r="Y148" s="11" t="n"/>
+      <c r="Z148" s="11" t="n"/>
+      <c r="AA148" s="11" t="n"/>
+      <c r="AB148" s="11" t="n"/>
+      <c r="AC148" s="11" t="n"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
       <c r="B151" s="5" t="inlineStr">
@@ -4897,7 +5497,7 @@
           <t>A. 0 Appendix - carried &amp; annotated (not simulated)</t>
         </is>
       </c>
-      <c r="O151" s="6" t="inlineStr">
+      <c r="Q151" s="6" t="inlineStr">
         <is>
           <t>A. 0 Appendix - Difference (config-only changes)</t>
         </is>
@@ -4964,59 +5564,79 @@
           <t>Unlimited Lives</t>
         </is>
       </c>
+      <c r="N152" s="8" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
       <c r="O152" s="8" t="inlineStr">
         <is>
+          <t>SPTx2</t>
+        </is>
+      </c>
+      <c r="Q152" s="8" t="inlineStr">
+        <is>
           <t>HC</t>
         </is>
       </c>
-      <c r="P152" s="8" t="inlineStr">
+      <c r="R152" s="8" t="inlineStr">
         <is>
           <t>Slingshot</t>
         </is>
       </c>
-      <c r="Q152" s="8" t="inlineStr">
+      <c r="S152" s="8" t="inlineStr">
         <is>
           <t>Shuffle</t>
         </is>
       </c>
-      <c r="R152" s="8" t="inlineStr">
+      <c r="T152" s="8" t="inlineStr">
         <is>
           <t>Comet</t>
         </is>
       </c>
-      <c r="S152" s="8" t="inlineStr">
+      <c r="U152" s="8" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="T152" s="8" t="inlineStr">
+      <c r="V152" s="8" t="inlineStr">
         <is>
           <t>Chuck</t>
         </is>
       </c>
-      <c r="U152" s="8" t="inlineStr">
+      <c r="W152" s="8" t="inlineStr">
         <is>
           <t>Bomb</t>
         </is>
       </c>
-      <c r="V152" s="8" t="inlineStr">
+      <c r="X152" s="8" t="inlineStr">
         <is>
           <t>UL Bomb</t>
         </is>
       </c>
-      <c r="W152" s="8" t="inlineStr">
+      <c r="Y152" s="8" t="inlineStr">
         <is>
           <t>UL Chuck</t>
         </is>
       </c>
-      <c r="X152" s="8" t="inlineStr">
+      <c r="Z152" s="8" t="inlineStr">
         <is>
           <t>UL Red</t>
         </is>
       </c>
-      <c r="Y152" s="8" t="inlineStr">
+      <c r="AA152" s="8" t="inlineStr">
         <is>
           <t>Unlimited Lives</t>
+        </is>
+      </c>
+      <c r="AB152" s="8" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
+      <c r="AC152" s="8" t="inlineStr">
+        <is>
+          <t>SPTx2</t>
         </is>
       </c>
     </row>
@@ -5040,12 +5660,12 @@
       <c r="K153" s="10" t="n"/>
       <c r="L153" s="10" t="n"/>
       <c r="M153" s="10" t="n"/>
-      <c r="O153" s="11">
+      <c r="N153" s="10" t="n"/>
+      <c r="O153" s="10" t="n"/>
+      <c r="Q153" s="11">
         <f>LET(payer, $C$3, segment, $B$151, ECOGAINS_DIFF(payer, segment, sim_refresh!$A$1))</f>
         <v/>
       </c>
-      <c r="P153" s="11" t="n"/>
-      <c r="Q153" s="11" t="n"/>
       <c r="R153" s="11" t="n"/>
       <c r="S153" s="11" t="n"/>
       <c r="T153" s="11" t="n"/>
@@ -5054,6 +5674,10 @@
       <c r="W153" s="11" t="n"/>
       <c r="X153" s="11" t="n"/>
       <c r="Y153" s="11" t="n"/>
+      <c r="Z153" s="11" t="n"/>
+      <c r="AA153" s="11" t="n"/>
+      <c r="AB153" s="11" t="n"/>
+      <c r="AC153" s="11" t="n"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
       <c r="B154" s="9" t="inlineStr">
@@ -5072,8 +5696,8 @@
       <c r="K154" s="10" t="n"/>
       <c r="L154" s="10" t="n"/>
       <c r="M154" s="10" t="n"/>
-      <c r="O154" s="11" t="n"/>
-      <c r="P154" s="11" t="n"/>
+      <c r="N154" s="10" t="n"/>
+      <c r="O154" s="10" t="n"/>
       <c r="Q154" s="11" t="n"/>
       <c r="R154" s="11" t="n"/>
       <c r="S154" s="11" t="n"/>
@@ -5083,6 +5707,10 @@
       <c r="W154" s="11" t="n"/>
       <c r="X154" s="11" t="n"/>
       <c r="Y154" s="11" t="n"/>
+      <c r="Z154" s="11" t="n"/>
+      <c r="AA154" s="11" t="n"/>
+      <c r="AB154" s="11" t="n"/>
+      <c r="AC154" s="11" t="n"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
       <c r="B155" s="9" t="inlineStr">
@@ -5101,8 +5729,8 @@
       <c r="K155" s="10" t="n"/>
       <c r="L155" s="10" t="n"/>
       <c r="M155" s="10" t="n"/>
-      <c r="O155" s="11" t="n"/>
-      <c r="P155" s="11" t="n"/>
+      <c r="N155" s="10" t="n"/>
+      <c r="O155" s="10" t="n"/>
       <c r="Q155" s="11" t="n"/>
       <c r="R155" s="11" t="n"/>
       <c r="S155" s="11" t="n"/>
@@ -5112,6 +5740,10 @@
       <c r="W155" s="11" t="n"/>
       <c r="X155" s="11" t="n"/>
       <c r="Y155" s="11" t="n"/>
+      <c r="Z155" s="11" t="n"/>
+      <c r="AA155" s="11" t="n"/>
+      <c r="AB155" s="11" t="n"/>
+      <c r="AC155" s="11" t="n"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
       <c r="B156" s="9" t="inlineStr">
@@ -5130,8 +5762,8 @@
       <c r="K156" s="10" t="n"/>
       <c r="L156" s="10" t="n"/>
       <c r="M156" s="10" t="n"/>
-      <c r="O156" s="11" t="n"/>
-      <c r="P156" s="11" t="n"/>
+      <c r="N156" s="10" t="n"/>
+      <c r="O156" s="10" t="n"/>
       <c r="Q156" s="11" t="n"/>
       <c r="R156" s="11" t="n"/>
       <c r="S156" s="11" t="n"/>
@@ -5141,6 +5773,10 @@
       <c r="W156" s="11" t="n"/>
       <c r="X156" s="11" t="n"/>
       <c r="Y156" s="11" t="n"/>
+      <c r="Z156" s="11" t="n"/>
+      <c r="AA156" s="11" t="n"/>
+      <c r="AB156" s="11" t="n"/>
+      <c r="AC156" s="11" t="n"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
       <c r="B157" s="9" t="inlineStr">
@@ -5159,8 +5795,8 @@
       <c r="K157" s="10" t="n"/>
       <c r="L157" s="10" t="n"/>
       <c r="M157" s="10" t="n"/>
-      <c r="O157" s="11" t="n"/>
-      <c r="P157" s="11" t="n"/>
+      <c r="N157" s="10" t="n"/>
+      <c r="O157" s="10" t="n"/>
       <c r="Q157" s="11" t="n"/>
       <c r="R157" s="11" t="n"/>
       <c r="S157" s="11" t="n"/>
@@ -5170,6 +5806,10 @@
       <c r="W157" s="11" t="n"/>
       <c r="X157" s="11" t="n"/>
       <c r="Y157" s="11" t="n"/>
+      <c r="Z157" s="11" t="n"/>
+      <c r="AA157" s="11" t="n"/>
+      <c r="AB157" s="11" t="n"/>
+      <c r="AC157" s="11" t="n"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
       <c r="B158" s="14" t="inlineStr">
@@ -5188,8 +5828,8 @@
       <c r="K158" s="13" t="n"/>
       <c r="L158" s="13" t="n"/>
       <c r="M158" s="13" t="n"/>
-      <c r="O158" s="11" t="n"/>
-      <c r="P158" s="11" t="n"/>
+      <c r="N158" s="13" t="n"/>
+      <c r="O158" s="13" t="n"/>
       <c r="Q158" s="11" t="n"/>
       <c r="R158" s="11" t="n"/>
       <c r="S158" s="11" t="n"/>
@@ -5199,6 +5839,10 @@
       <c r="W158" s="11" t="n"/>
       <c r="X158" s="11" t="n"/>
       <c r="Y158" s="11" t="n"/>
+      <c r="Z158" s="11" t="n"/>
+      <c r="AA158" s="11" t="n"/>
+      <c r="AB158" s="11" t="n"/>
+      <c r="AC158" s="11" t="n"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
       <c r="B159" s="9" t="inlineStr">
@@ -5217,8 +5861,8 @@
       <c r="K159" s="10" t="n"/>
       <c r="L159" s="10" t="n"/>
       <c r="M159" s="10" t="n"/>
-      <c r="O159" s="11" t="n"/>
-      <c r="P159" s="11" t="n"/>
+      <c r="N159" s="10" t="n"/>
+      <c r="O159" s="10" t="n"/>
       <c r="Q159" s="11" t="n"/>
       <c r="R159" s="11" t="n"/>
       <c r="S159" s="11" t="n"/>
@@ -5228,6 +5872,10 @@
       <c r="W159" s="11" t="n"/>
       <c r="X159" s="11" t="n"/>
       <c r="Y159" s="11" t="n"/>
+      <c r="Z159" s="11" t="n"/>
+      <c r="AA159" s="11" t="n"/>
+      <c r="AB159" s="11" t="n"/>
+      <c r="AC159" s="11" t="n"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
       <c r="B160" s="9" t="inlineStr">
@@ -5246,8 +5894,8 @@
       <c r="K160" s="10" t="n"/>
       <c r="L160" s="10" t="n"/>
       <c r="M160" s="10" t="n"/>
-      <c r="O160" s="11" t="n"/>
-      <c r="P160" s="11" t="n"/>
+      <c r="N160" s="10" t="n"/>
+      <c r="O160" s="10" t="n"/>
       <c r="Q160" s="11" t="n"/>
       <c r="R160" s="11" t="n"/>
       <c r="S160" s="11" t="n"/>
@@ -5257,6 +5905,10 @@
       <c r="W160" s="11" t="n"/>
       <c r="X160" s="11" t="n"/>
       <c r="Y160" s="11" t="n"/>
+      <c r="Z160" s="11" t="n"/>
+      <c r="AA160" s="11" t="n"/>
+      <c r="AB160" s="11" t="n"/>
+      <c r="AC160" s="11" t="n"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
       <c r="B161" s="9" t="inlineStr">
@@ -5275,8 +5927,8 @@
       <c r="K161" s="10" t="n"/>
       <c r="L161" s="10" t="n"/>
       <c r="M161" s="10" t="n"/>
-      <c r="O161" s="11" t="n"/>
-      <c r="P161" s="11" t="n"/>
+      <c r="N161" s="10" t="n"/>
+      <c r="O161" s="10" t="n"/>
       <c r="Q161" s="11" t="n"/>
       <c r="R161" s="11" t="n"/>
       <c r="S161" s="11" t="n"/>
@@ -5286,6 +5938,10 @@
       <c r="W161" s="11" t="n"/>
       <c r="X161" s="11" t="n"/>
       <c r="Y161" s="11" t="n"/>
+      <c r="Z161" s="11" t="n"/>
+      <c r="AA161" s="11" t="n"/>
+      <c r="AB161" s="11" t="n"/>
+      <c r="AC161" s="11" t="n"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
       <c r="B162" s="9" t="inlineStr">
@@ -5304,8 +5960,8 @@
       <c r="K162" s="10" t="n"/>
       <c r="L162" s="10" t="n"/>
       <c r="M162" s="10" t="n"/>
-      <c r="O162" s="11" t="n"/>
-      <c r="P162" s="11" t="n"/>
+      <c r="N162" s="10" t="n"/>
+      <c r="O162" s="10" t="n"/>
       <c r="Q162" s="11" t="n"/>
       <c r="R162" s="11" t="n"/>
       <c r="S162" s="11" t="n"/>
@@ -5315,6 +5971,10 @@
       <c r="W162" s="11" t="n"/>
       <c r="X162" s="11" t="n"/>
       <c r="Y162" s="11" t="n"/>
+      <c r="Z162" s="11" t="n"/>
+      <c r="AA162" s="11" t="n"/>
+      <c r="AB162" s="11" t="n"/>
+      <c r="AC162" s="11" t="n"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
       <c r="B163" s="9" t="inlineStr">
@@ -5333,8 +5993,8 @@
       <c r="K163" s="10" t="n"/>
       <c r="L163" s="10" t="n"/>
       <c r="M163" s="10" t="n"/>
-      <c r="O163" s="11" t="n"/>
-      <c r="P163" s="11" t="n"/>
+      <c r="N163" s="10" t="n"/>
+      <c r="O163" s="10" t="n"/>
       <c r="Q163" s="11" t="n"/>
       <c r="R163" s="11" t="n"/>
       <c r="S163" s="11" t="n"/>
@@ -5344,6 +6004,10 @@
       <c r="W163" s="11" t="n"/>
       <c r="X163" s="11" t="n"/>
       <c r="Y163" s="11" t="n"/>
+      <c r="Z163" s="11" t="n"/>
+      <c r="AA163" s="11" t="n"/>
+      <c r="AB163" s="11" t="n"/>
+      <c r="AC163" s="11" t="n"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
       <c r="B164" s="9" t="inlineStr">
@@ -5362,8 +6026,8 @@
       <c r="K164" s="10" t="n"/>
       <c r="L164" s="10" t="n"/>
       <c r="M164" s="10" t="n"/>
-      <c r="O164" s="11" t="n"/>
-      <c r="P164" s="11" t="n"/>
+      <c r="N164" s="10" t="n"/>
+      <c r="O164" s="10" t="n"/>
       <c r="Q164" s="11" t="n"/>
       <c r="R164" s="11" t="n"/>
       <c r="S164" s="11" t="n"/>
@@ -5373,6 +6037,10 @@
       <c r="W164" s="11" t="n"/>
       <c r="X164" s="11" t="n"/>
       <c r="Y164" s="11" t="n"/>
+      <c r="Z164" s="11" t="n"/>
+      <c r="AA164" s="11" t="n"/>
+      <c r="AB164" s="11" t="n"/>
+      <c r="AC164" s="11" t="n"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
       <c r="B165" s="9" t="inlineStr">
@@ -5391,8 +6059,8 @@
       <c r="K165" s="10" t="n"/>
       <c r="L165" s="10" t="n"/>
       <c r="M165" s="10" t="n"/>
-      <c r="O165" s="11" t="n"/>
-      <c r="P165" s="11" t="n"/>
+      <c r="N165" s="10" t="n"/>
+      <c r="O165" s="10" t="n"/>
       <c r="Q165" s="11" t="n"/>
       <c r="R165" s="11" t="n"/>
       <c r="S165" s="11" t="n"/>
@@ -5402,6 +6070,10 @@
       <c r="W165" s="11" t="n"/>
       <c r="X165" s="11" t="n"/>
       <c r="Y165" s="11" t="n"/>
+      <c r="Z165" s="11" t="n"/>
+      <c r="AA165" s="11" t="n"/>
+      <c r="AB165" s="11" t="n"/>
+      <c r="AC165" s="11" t="n"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
       <c r="B166" s="9" t="inlineStr">
@@ -5420,8 +6092,8 @@
       <c r="K166" s="10" t="n"/>
       <c r="L166" s="10" t="n"/>
       <c r="M166" s="10" t="n"/>
-      <c r="O166" s="11" t="n"/>
-      <c r="P166" s="11" t="n"/>
+      <c r="N166" s="10" t="n"/>
+      <c r="O166" s="10" t="n"/>
       <c r="Q166" s="11" t="n"/>
       <c r="R166" s="11" t="n"/>
       <c r="S166" s="11" t="n"/>
@@ -5431,6 +6103,10 @@
       <c r="W166" s="11" t="n"/>
       <c r="X166" s="11" t="n"/>
       <c r="Y166" s="11" t="n"/>
+      <c r="Z166" s="11" t="n"/>
+      <c r="AA166" s="11" t="n"/>
+      <c r="AB166" s="11" t="n"/>
+      <c r="AC166" s="11" t="n"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
       <c r="B167" s="9" t="inlineStr">
@@ -5449,8 +6125,8 @@
       <c r="K167" s="10" t="n"/>
       <c r="L167" s="10" t="n"/>
       <c r="M167" s="10" t="n"/>
-      <c r="O167" s="11" t="n"/>
-      <c r="P167" s="11" t="n"/>
+      <c r="N167" s="10" t="n"/>
+      <c r="O167" s="10" t="n"/>
       <c r="Q167" s="11" t="n"/>
       <c r="R167" s="11" t="n"/>
       <c r="S167" s="11" t="n"/>
@@ -5460,6 +6136,10 @@
       <c r="W167" s="11" t="n"/>
       <c r="X167" s="11" t="n"/>
       <c r="Y167" s="11" t="n"/>
+      <c r="Z167" s="11" t="n"/>
+      <c r="AA167" s="11" t="n"/>
+      <c r="AB167" s="11" t="n"/>
+      <c r="AC167" s="11" t="n"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
       <c r="B168" s="12" t="inlineStr">
@@ -5478,8 +6158,8 @@
       <c r="K168" s="13" t="n"/>
       <c r="L168" s="13" t="n"/>
       <c r="M168" s="13" t="n"/>
-      <c r="O168" s="11" t="n"/>
-      <c r="P168" s="11" t="n"/>
+      <c r="N168" s="13" t="n"/>
+      <c r="O168" s="13" t="n"/>
       <c r="Q168" s="11" t="n"/>
       <c r="R168" s="11" t="n"/>
       <c r="S168" s="11" t="n"/>
@@ -5489,6 +6169,10 @@
       <c r="W168" s="11" t="n"/>
       <c r="X168" s="11" t="n"/>
       <c r="Y168" s="11" t="n"/>
+      <c r="Z168" s="11" t="n"/>
+      <c r="AA168" s="11" t="n"/>
+      <c r="AB168" s="11" t="n"/>
+      <c r="AC168" s="11" t="n"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
       <c r="B169" s="14" t="inlineStr">
@@ -5507,8 +6191,8 @@
       <c r="K169" s="13" t="n"/>
       <c r="L169" s="13" t="n"/>
       <c r="M169" s="13" t="n"/>
-      <c r="O169" s="11" t="n"/>
-      <c r="P169" s="11" t="n"/>
+      <c r="N169" s="13" t="n"/>
+      <c r="O169" s="13" t="n"/>
       <c r="Q169" s="11" t="n"/>
       <c r="R169" s="11" t="n"/>
       <c r="S169" s="11" t="n"/>
@@ -5518,6 +6202,10 @@
       <c r="W169" s="11" t="n"/>
       <c r="X169" s="11" t="n"/>
       <c r="Y169" s="11" t="n"/>
+      <c r="Z169" s="11" t="n"/>
+      <c r="AA169" s="11" t="n"/>
+      <c r="AB169" s="11" t="n"/>
+      <c r="AC169" s="11" t="n"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
       <c r="B170" s="9" t="inlineStr">
@@ -5536,8 +6224,8 @@
       <c r="K170" s="10" t="n"/>
       <c r="L170" s="10" t="n"/>
       <c r="M170" s="10" t="n"/>
-      <c r="O170" s="11" t="n"/>
-      <c r="P170" s="11" t="n"/>
+      <c r="N170" s="10" t="n"/>
+      <c r="O170" s="10" t="n"/>
       <c r="Q170" s="11" t="n"/>
       <c r="R170" s="11" t="n"/>
       <c r="S170" s="11" t="n"/>
@@ -5547,6 +6235,10 @@
       <c r="W170" s="11" t="n"/>
       <c r="X170" s="11" t="n"/>
       <c r="Y170" s="11" t="n"/>
+      <c r="Z170" s="11" t="n"/>
+      <c r="AA170" s="11" t="n"/>
+      <c r="AB170" s="11" t="n"/>
+      <c r="AC170" s="11" t="n"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
       <c r="B171" s="9" t="inlineStr">
@@ -5565,8 +6257,8 @@
       <c r="K171" s="10" t="n"/>
       <c r="L171" s="10" t="n"/>
       <c r="M171" s="10" t="n"/>
-      <c r="O171" s="11" t="n"/>
-      <c r="P171" s="11" t="n"/>
+      <c r="N171" s="10" t="n"/>
+      <c r="O171" s="10" t="n"/>
       <c r="Q171" s="11" t="n"/>
       <c r="R171" s="11" t="n"/>
       <c r="S171" s="11" t="n"/>
@@ -5576,6 +6268,10 @@
       <c r="W171" s="11" t="n"/>
       <c r="X171" s="11" t="n"/>
       <c r="Y171" s="11" t="n"/>
+      <c r="Z171" s="11" t="n"/>
+      <c r="AA171" s="11" t="n"/>
+      <c r="AB171" s="11" t="n"/>
+      <c r="AC171" s="11" t="n"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
       <c r="B172" s="9" t="inlineStr">
@@ -5594,8 +6290,8 @@
       <c r="K172" s="10" t="n"/>
       <c r="L172" s="10" t="n"/>
       <c r="M172" s="10" t="n"/>
-      <c r="O172" s="11" t="n"/>
-      <c r="P172" s="11" t="n"/>
+      <c r="N172" s="10" t="n"/>
+      <c r="O172" s="10" t="n"/>
       <c r="Q172" s="11" t="n"/>
       <c r="R172" s="11" t="n"/>
       <c r="S172" s="11" t="n"/>
@@ -5605,6 +6301,10 @@
       <c r="W172" s="11" t="n"/>
       <c r="X172" s="11" t="n"/>
       <c r="Y172" s="11" t="n"/>
+      <c r="Z172" s="11" t="n"/>
+      <c r="AA172" s="11" t="n"/>
+      <c r="AB172" s="11" t="n"/>
+      <c r="AC172" s="11" t="n"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
       <c r="B173" s="9" t="inlineStr">
@@ -5623,8 +6323,8 @@
       <c r="K173" s="10" t="n"/>
       <c r="L173" s="10" t="n"/>
       <c r="M173" s="10" t="n"/>
-      <c r="O173" s="11" t="n"/>
-      <c r="P173" s="11" t="n"/>
+      <c r="N173" s="10" t="n"/>
+      <c r="O173" s="10" t="n"/>
       <c r="Q173" s="11" t="n"/>
       <c r="R173" s="11" t="n"/>
       <c r="S173" s="11" t="n"/>
@@ -5634,6 +6334,10 @@
       <c r="W173" s="11" t="n"/>
       <c r="X173" s="11" t="n"/>
       <c r="Y173" s="11" t="n"/>
+      <c r="Z173" s="11" t="n"/>
+      <c r="AA173" s="11" t="n"/>
+      <c r="AB173" s="11" t="n"/>
+      <c r="AC173" s="11" t="n"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
       <c r="B174" s="9" t="inlineStr">
@@ -5652,8 +6356,8 @@
       <c r="K174" s="10" t="n"/>
       <c r="L174" s="10" t="n"/>
       <c r="M174" s="10" t="n"/>
-      <c r="O174" s="11" t="n"/>
-      <c r="P174" s="11" t="n"/>
+      <c r="N174" s="10" t="n"/>
+      <c r="O174" s="10" t="n"/>
       <c r="Q174" s="11" t="n"/>
       <c r="R174" s="11" t="n"/>
       <c r="S174" s="11" t="n"/>
@@ -5663,6 +6367,10 @@
       <c r="W174" s="11" t="n"/>
       <c r="X174" s="11" t="n"/>
       <c r="Y174" s="11" t="n"/>
+      <c r="Z174" s="11" t="n"/>
+      <c r="AA174" s="11" t="n"/>
+      <c r="AB174" s="11" t="n"/>
+      <c r="AC174" s="11" t="n"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
       <c r="B175" s="9" t="inlineStr">
@@ -5681,8 +6389,8 @@
       <c r="K175" s="10" t="n"/>
       <c r="L175" s="10" t="n"/>
       <c r="M175" s="10" t="n"/>
-      <c r="O175" s="11" t="n"/>
-      <c r="P175" s="11" t="n"/>
+      <c r="N175" s="10" t="n"/>
+      <c r="O175" s="10" t="n"/>
       <c r="Q175" s="11" t="n"/>
       <c r="R175" s="11" t="n"/>
       <c r="S175" s="11" t="n"/>
@@ -5692,6 +6400,10 @@
       <c r="W175" s="11" t="n"/>
       <c r="X175" s="11" t="n"/>
       <c r="Y175" s="11" t="n"/>
+      <c r="Z175" s="11" t="n"/>
+      <c r="AA175" s="11" t="n"/>
+      <c r="AB175" s="11" t="n"/>
+      <c r="AC175" s="11" t="n"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
       <c r="B176" s="9" t="inlineStr">
@@ -5710,8 +6422,8 @@
       <c r="K176" s="10" t="n"/>
       <c r="L176" s="10" t="n"/>
       <c r="M176" s="10" t="n"/>
-      <c r="O176" s="11" t="n"/>
-      <c r="P176" s="11" t="n"/>
+      <c r="N176" s="10" t="n"/>
+      <c r="O176" s="10" t="n"/>
       <c r="Q176" s="11" t="n"/>
       <c r="R176" s="11" t="n"/>
       <c r="S176" s="11" t="n"/>
@@ -5721,6 +6433,10 @@
       <c r="W176" s="11" t="n"/>
       <c r="X176" s="11" t="n"/>
       <c r="Y176" s="11" t="n"/>
+      <c r="Z176" s="11" t="n"/>
+      <c r="AA176" s="11" t="n"/>
+      <c r="AB176" s="11" t="n"/>
+      <c r="AC176" s="11" t="n"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
       <c r="B177" s="9" t="inlineStr">
@@ -5739,8 +6455,8 @@
       <c r="K177" s="10" t="n"/>
       <c r="L177" s="10" t="n"/>
       <c r="M177" s="10" t="n"/>
-      <c r="O177" s="11" t="n"/>
-      <c r="P177" s="11" t="n"/>
+      <c r="N177" s="10" t="n"/>
+      <c r="O177" s="10" t="n"/>
       <c r="Q177" s="11" t="n"/>
       <c r="R177" s="11" t="n"/>
       <c r="S177" s="11" t="n"/>
@@ -5750,6 +6466,10 @@
       <c r="W177" s="11" t="n"/>
       <c r="X177" s="11" t="n"/>
       <c r="Y177" s="11" t="n"/>
+      <c r="Z177" s="11" t="n"/>
+      <c r="AA177" s="11" t="n"/>
+      <c r="AB177" s="11" t="n"/>
+      <c r="AC177" s="11" t="n"/>
     </row>
     <row r="181">
       <c r="B181" s="15" t="inlineStr">
@@ -5817,12 +6537,26 @@
     <row r="190">
       <c r="B190" s="4" t="inlineStr">
         <is>
+          <t>SPT / SPTx2 (13-resource universe since 2026-07-10, D16): season pass tokens, appended as the last two columns; SPTx2 counts DOUBLE toward season-pass tier progression but displays separately. Every simulated source moves its SPT via the same R x D x T as its other resources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" s="4" t="inlineStr">
+        <is>
+          <t>Season Pass (Free) is SIMULATED via SPT tier coupling: per-earner SPT+2xSPTx2 window totals (measured vs simulated, summed over all sources - additive-projection convention) x seasonDays/33 land on the SP / SP_v2 'Cumul' ladder; the row scales by cum-reward ratio through the reached tier (FREE track for nonpayers, FREE+PAID for payers - ASSUMPTION: the measured '(Free)' row contains payers' paid-track claims) x SP_lb_v2/SP_lb challenge pot ratio (zero-sum; Dream Pass telemetry is empty) x calendar T (D=1). No anchor (measured 0 or base cum 0): tiers GAINED add absolute SP_v2 rewards (HYBRID, flagged); otherwise carried. SP_v2 / SP_lb_v2 missing -&gt; base sheets serve both sides (ratios 1). Not applied to A. 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" s="4" t="inlineStr">
+        <is>
           <t>After editing a calendar: menu EcoGainsSim ▸ Precompute calendars (writes hidden cal_parsed; engine prefers it). Sanity canary: the Kite Festival row must GROW ~x1.3 vs measured. If every event row equals measured, the calendar read failed.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="O8:Y32">
+  <conditionalFormatting sqref="Q8:AC32">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -5830,7 +6564,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O37:Y61">
+  <conditionalFormatting sqref="Q37:AC61">
     <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -5838,7 +6572,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O66:Y90">
+  <conditionalFormatting sqref="Q66:AC90">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -5846,7 +6580,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O95:Y119">
+  <conditionalFormatting sqref="Q95:AC119">
     <cfRule type="cellIs" priority="7" operator="lessThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -5854,7 +6588,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O124:Y148">
+  <conditionalFormatting sqref="Q124:AC148">
     <cfRule type="cellIs" priority="9" operator="lessThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -5862,7 +6596,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O153:Y177">
+  <conditionalFormatting sqref="Q153:AC177">
     <cfRule type="cellIs" priority="11" operator="lessThan" dxfId="0">
       <formula>0</formula>
     </cfRule>

--- a/display/EcoGainsSim_HC_v4.xlsx
+++ b/display/EcoGainsSim_HC_v4.xlsx
@@ -524,13 +524,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:AC192"/>
+  <dimension ref="B2:AT195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.75" customWidth="1" min="1" max="1"/>
     <col width="19.25" customWidth="1" min="2" max="2"/>
     <col width="8.25" customWidth="1" min="3" max="3"/>
-    <col width="7.63" customWidth="1" min="30" max="30"/>
+    <col width="7.63" customWidth="1" min="42" max="42"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -572,7 +572,7 @@
           <t>0-9 Segment - Over Time Period  (uses 1-9 gains data)</t>
         </is>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
+      <c r="W6" s="6" t="inlineStr">
         <is>
           <t>0-9 Segment - Over Time Period - Difference</t>
         </is>
@@ -649,69 +649,129 @@
           <t>SPTx2</t>
         </is>
       </c>
+      <c r="P7" s="8" t="inlineStr">
+        <is>
+          <t>1-star Pack</t>
+        </is>
+      </c>
       <c r="Q7" s="8" t="inlineStr">
         <is>
+          <t>2-star Pack</t>
+        </is>
+      </c>
+      <c r="R7" s="8" t="inlineStr">
+        <is>
+          <t>3-star Pack</t>
+        </is>
+      </c>
+      <c r="S7" s="8" t="inlineStr">
+        <is>
+          <t>4-star Pack</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>5-star Pack</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>6-star Pack</t>
+        </is>
+      </c>
+      <c r="W7" s="8" t="inlineStr">
+        <is>
           <t>HC</t>
         </is>
       </c>
-      <c r="R7" s="8" t="inlineStr">
+      <c r="X7" s="8" t="inlineStr">
         <is>
           <t>Slingshot</t>
         </is>
       </c>
-      <c r="S7" s="8" t="inlineStr">
+      <c r="Y7" s="8" t="inlineStr">
         <is>
           <t>Shuffle</t>
         </is>
       </c>
-      <c r="T7" s="8" t="inlineStr">
+      <c r="Z7" s="8" t="inlineStr">
         <is>
           <t>Comet</t>
         </is>
       </c>
-      <c r="U7" s="8" t="inlineStr">
+      <c r="AA7" s="8" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="V7" s="8" t="inlineStr">
+      <c r="AB7" s="8" t="inlineStr">
         <is>
           <t>Chuck</t>
         </is>
       </c>
-      <c r="W7" s="8" t="inlineStr">
+      <c r="AC7" s="8" t="inlineStr">
         <is>
           <t>Bomb</t>
         </is>
       </c>
-      <c r="X7" s="8" t="inlineStr">
+      <c r="AD7" s="8" t="inlineStr">
         <is>
           <t>UL Bomb</t>
         </is>
       </c>
-      <c r="Y7" s="8" t="inlineStr">
+      <c r="AE7" s="8" t="inlineStr">
         <is>
           <t>UL Chuck</t>
         </is>
       </c>
-      <c r="Z7" s="8" t="inlineStr">
+      <c r="AF7" s="8" t="inlineStr">
         <is>
           <t>UL Red</t>
         </is>
       </c>
-      <c r="AA7" s="8" t="inlineStr">
+      <c r="AG7" s="8" t="inlineStr">
         <is>
           <t>Unlimited Lives</t>
         </is>
       </c>
-      <c r="AB7" s="8" t="inlineStr">
+      <c r="AH7" s="8" t="inlineStr">
         <is>
           <t>SPT</t>
         </is>
       </c>
-      <c r="AC7" s="8" t="inlineStr">
+      <c r="AI7" s="8" t="inlineStr">
         <is>
           <t>SPTx2</t>
+        </is>
+      </c>
+      <c r="AJ7" s="8" t="inlineStr">
+        <is>
+          <t>1-star Pack</t>
+        </is>
+      </c>
+      <c r="AK7" s="8" t="inlineStr">
+        <is>
+          <t>2-star Pack</t>
+        </is>
+      </c>
+      <c r="AL7" s="8" t="inlineStr">
+        <is>
+          <t>3-star Pack</t>
+        </is>
+      </c>
+      <c r="AM7" s="8" t="inlineStr">
+        <is>
+          <t>4-star Pack</t>
+        </is>
+      </c>
+      <c r="AN7" s="8" t="inlineStr">
+        <is>
+          <t>5-star Pack</t>
+        </is>
+      </c>
+      <c r="AO7" s="8" t="inlineStr">
+        <is>
+          <t>6-star Pack</t>
         </is>
       </c>
     </row>
@@ -737,22 +797,42 @@
       <c r="M8" s="10" t="n"/>
       <c r="N8" s="10" t="n"/>
       <c r="O8" s="10" t="n"/>
-      <c r="Q8" s="11">
+      <c r="P8" s="10" t="n"/>
+      <c r="Q8" s="10" t="n"/>
+      <c r="R8" s="10" t="n"/>
+      <c r="S8" s="10" t="n"/>
+      <c r="T8" s="10" t="n"/>
+      <c r="U8" s="10" t="n"/>
+      <c r="W8" s="11">
         <f>LET(payer, $C$3, segment, $B$6, ECOGAINS_DIFF(payer, segment, sim_refresh!$A$1))</f>
         <v/>
       </c>
-      <c r="R8" s="11" t="n"/>
-      <c r="S8" s="11" t="n"/>
-      <c r="T8" s="11" t="n"/>
-      <c r="U8" s="11" t="n"/>
-      <c r="V8" s="11" t="n"/>
-      <c r="W8" s="11" t="n"/>
       <c r="X8" s="11" t="n"/>
       <c r="Y8" s="11" t="n"/>
       <c r="Z8" s="11" t="n"/>
       <c r="AA8" s="11" t="n"/>
       <c r="AB8" s="11" t="n"/>
       <c r="AC8" s="11" t="n"/>
+      <c r="AD8" s="11" t="n"/>
+      <c r="AE8" s="11" t="n"/>
+      <c r="AF8" s="11" t="n"/>
+      <c r="AG8" s="11" t="n"/>
+      <c r="AH8" s="11" t="n"/>
+      <c r="AI8" s="11" t="n"/>
+      <c r="AJ8" s="11" t="n"/>
+      <c r="AK8" s="11" t="n"/>
+      <c r="AL8" s="11" t="n"/>
+      <c r="AM8" s="11" t="n"/>
+      <c r="AN8" s="11" t="n"/>
+      <c r="AO8" s="11" t="n"/>
+      <c r="AQ8">
+        <f>ECOGAINS_CAL_STATS("cal_curr", sim_refresh!$A$1)</f>
+        <v/>
+      </c>
+      <c r="AT8">
+        <f>ECOGAINS_CAL_STATS("cal_new", sim_refresh!$A$1)</f>
+        <v/>
+      </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="B9" s="12" t="inlineStr">
@@ -773,12 +853,12 @@
       <c r="M9" s="13" t="n"/>
       <c r="N9" s="13" t="n"/>
       <c r="O9" s="13" t="n"/>
-      <c r="Q9" s="11" t="n"/>
-      <c r="R9" s="11" t="n"/>
-      <c r="S9" s="11" t="n"/>
-      <c r="T9" s="11" t="n"/>
-      <c r="U9" s="11" t="n"/>
-      <c r="V9" s="11" t="n"/>
+      <c r="P9" s="13" t="n"/>
+      <c r="Q9" s="13" t="n"/>
+      <c r="R9" s="13" t="n"/>
+      <c r="S9" s="13" t="n"/>
+      <c r="T9" s="13" t="n"/>
+      <c r="U9" s="13" t="n"/>
       <c r="W9" s="11" t="n"/>
       <c r="X9" s="11" t="n"/>
       <c r="Y9" s="11" t="n"/>
@@ -786,6 +866,18 @@
       <c r="AA9" s="11" t="n"/>
       <c r="AB9" s="11" t="n"/>
       <c r="AC9" s="11" t="n"/>
+      <c r="AD9" s="11" t="n"/>
+      <c r="AE9" s="11" t="n"/>
+      <c r="AF9" s="11" t="n"/>
+      <c r="AG9" s="11" t="n"/>
+      <c r="AH9" s="11" t="n"/>
+      <c r="AI9" s="11" t="n"/>
+      <c r="AJ9" s="11" t="n"/>
+      <c r="AK9" s="11" t="n"/>
+      <c r="AL9" s="11" t="n"/>
+      <c r="AM9" s="11" t="n"/>
+      <c r="AN9" s="11" t="n"/>
+      <c r="AO9" s="11" t="n"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="B10" s="12" t="inlineStr">
@@ -806,12 +898,12 @@
       <c r="M10" s="13" t="n"/>
       <c r="N10" s="13" t="n"/>
       <c r="O10" s="13" t="n"/>
-      <c r="Q10" s="11" t="n"/>
-      <c r="R10" s="11" t="n"/>
-      <c r="S10" s="11" t="n"/>
-      <c r="T10" s="11" t="n"/>
-      <c r="U10" s="11" t="n"/>
-      <c r="V10" s="11" t="n"/>
+      <c r="P10" s="13" t="n"/>
+      <c r="Q10" s="13" t="n"/>
+      <c r="R10" s="13" t="n"/>
+      <c r="S10" s="13" t="n"/>
+      <c r="T10" s="13" t="n"/>
+      <c r="U10" s="13" t="n"/>
       <c r="W10" s="11" t="n"/>
       <c r="X10" s="11" t="n"/>
       <c r="Y10" s="11" t="n"/>
@@ -819,6 +911,18 @@
       <c r="AA10" s="11" t="n"/>
       <c r="AB10" s="11" t="n"/>
       <c r="AC10" s="11" t="n"/>
+      <c r="AD10" s="11" t="n"/>
+      <c r="AE10" s="11" t="n"/>
+      <c r="AF10" s="11" t="n"/>
+      <c r="AG10" s="11" t="n"/>
+      <c r="AH10" s="11" t="n"/>
+      <c r="AI10" s="11" t="n"/>
+      <c r="AJ10" s="11" t="n"/>
+      <c r="AK10" s="11" t="n"/>
+      <c r="AL10" s="11" t="n"/>
+      <c r="AM10" s="11" t="n"/>
+      <c r="AN10" s="11" t="n"/>
+      <c r="AO10" s="11" t="n"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="B11" s="12" t="inlineStr">
@@ -839,12 +943,12 @@
       <c r="M11" s="13" t="n"/>
       <c r="N11" s="13" t="n"/>
       <c r="O11" s="13" t="n"/>
-      <c r="Q11" s="11" t="n"/>
-      <c r="R11" s="11" t="n"/>
-      <c r="S11" s="11" t="n"/>
-      <c r="T11" s="11" t="n"/>
-      <c r="U11" s="11" t="n"/>
-      <c r="V11" s="11" t="n"/>
+      <c r="P11" s="13" t="n"/>
+      <c r="Q11" s="13" t="n"/>
+      <c r="R11" s="13" t="n"/>
+      <c r="S11" s="13" t="n"/>
+      <c r="T11" s="13" t="n"/>
+      <c r="U11" s="13" t="n"/>
       <c r="W11" s="11" t="n"/>
       <c r="X11" s="11" t="n"/>
       <c r="Y11" s="11" t="n"/>
@@ -852,6 +956,18 @@
       <c r="AA11" s="11" t="n"/>
       <c r="AB11" s="11" t="n"/>
       <c r="AC11" s="11" t="n"/>
+      <c r="AD11" s="11" t="n"/>
+      <c r="AE11" s="11" t="n"/>
+      <c r="AF11" s="11" t="n"/>
+      <c r="AG11" s="11" t="n"/>
+      <c r="AH11" s="11" t="n"/>
+      <c r="AI11" s="11" t="n"/>
+      <c r="AJ11" s="11" t="n"/>
+      <c r="AK11" s="11" t="n"/>
+      <c r="AL11" s="11" t="n"/>
+      <c r="AM11" s="11" t="n"/>
+      <c r="AN11" s="11" t="n"/>
+      <c r="AO11" s="11" t="n"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="B12" s="9" t="inlineStr">
@@ -872,12 +988,12 @@
       <c r="M12" s="10" t="n"/>
       <c r="N12" s="10" t="n"/>
       <c r="O12" s="10" t="n"/>
-      <c r="Q12" s="11" t="n"/>
-      <c r="R12" s="11" t="n"/>
-      <c r="S12" s="11" t="n"/>
-      <c r="T12" s="11" t="n"/>
-      <c r="U12" s="11" t="n"/>
-      <c r="V12" s="11" t="n"/>
+      <c r="P12" s="10" t="n"/>
+      <c r="Q12" s="10" t="n"/>
+      <c r="R12" s="10" t="n"/>
+      <c r="S12" s="10" t="n"/>
+      <c r="T12" s="10" t="n"/>
+      <c r="U12" s="10" t="n"/>
       <c r="W12" s="11" t="n"/>
       <c r="X12" s="11" t="n"/>
       <c r="Y12" s="11" t="n"/>
@@ -885,6 +1001,18 @@
       <c r="AA12" s="11" t="n"/>
       <c r="AB12" s="11" t="n"/>
       <c r="AC12" s="11" t="n"/>
+      <c r="AD12" s="11" t="n"/>
+      <c r="AE12" s="11" t="n"/>
+      <c r="AF12" s="11" t="n"/>
+      <c r="AG12" s="11" t="n"/>
+      <c r="AH12" s="11" t="n"/>
+      <c r="AI12" s="11" t="n"/>
+      <c r="AJ12" s="11" t="n"/>
+      <c r="AK12" s="11" t="n"/>
+      <c r="AL12" s="11" t="n"/>
+      <c r="AM12" s="11" t="n"/>
+      <c r="AN12" s="11" t="n"/>
+      <c r="AO12" s="11" t="n"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="B13" s="14" t="inlineStr">
@@ -905,12 +1033,12 @@
       <c r="M13" s="13" t="n"/>
       <c r="N13" s="13" t="n"/>
       <c r="O13" s="13" t="n"/>
-      <c r="Q13" s="11" t="n"/>
-      <c r="R13" s="11" t="n"/>
-      <c r="S13" s="11" t="n"/>
-      <c r="T13" s="11" t="n"/>
-      <c r="U13" s="11" t="n"/>
-      <c r="V13" s="11" t="n"/>
+      <c r="P13" s="13" t="n"/>
+      <c r="Q13" s="13" t="n"/>
+      <c r="R13" s="13" t="n"/>
+      <c r="S13" s="13" t="n"/>
+      <c r="T13" s="13" t="n"/>
+      <c r="U13" s="13" t="n"/>
       <c r="W13" s="11" t="n"/>
       <c r="X13" s="11" t="n"/>
       <c r="Y13" s="11" t="n"/>
@@ -918,6 +1046,18 @@
       <c r="AA13" s="11" t="n"/>
       <c r="AB13" s="11" t="n"/>
       <c r="AC13" s="11" t="n"/>
+      <c r="AD13" s="11" t="n"/>
+      <c r="AE13" s="11" t="n"/>
+      <c r="AF13" s="11" t="n"/>
+      <c r="AG13" s="11" t="n"/>
+      <c r="AH13" s="11" t="n"/>
+      <c r="AI13" s="11" t="n"/>
+      <c r="AJ13" s="11" t="n"/>
+      <c r="AK13" s="11" t="n"/>
+      <c r="AL13" s="11" t="n"/>
+      <c r="AM13" s="11" t="n"/>
+      <c r="AN13" s="11" t="n"/>
+      <c r="AO13" s="11" t="n"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="B14" s="14" t="inlineStr">
@@ -938,12 +1078,12 @@
       <c r="M14" s="13" t="n"/>
       <c r="N14" s="13" t="n"/>
       <c r="O14" s="13" t="n"/>
-      <c r="Q14" s="11" t="n"/>
-      <c r="R14" s="11" t="n"/>
-      <c r="S14" s="11" t="n"/>
-      <c r="T14" s="11" t="n"/>
-      <c r="U14" s="11" t="n"/>
-      <c r="V14" s="11" t="n"/>
+      <c r="P14" s="13" t="n"/>
+      <c r="Q14" s="13" t="n"/>
+      <c r="R14" s="13" t="n"/>
+      <c r="S14" s="13" t="n"/>
+      <c r="T14" s="13" t="n"/>
+      <c r="U14" s="13" t="n"/>
       <c r="W14" s="11" t="n"/>
       <c r="X14" s="11" t="n"/>
       <c r="Y14" s="11" t="n"/>
@@ -951,6 +1091,18 @@
       <c r="AA14" s="11" t="n"/>
       <c r="AB14" s="11" t="n"/>
       <c r="AC14" s="11" t="n"/>
+      <c r="AD14" s="11" t="n"/>
+      <c r="AE14" s="11" t="n"/>
+      <c r="AF14" s="11" t="n"/>
+      <c r="AG14" s="11" t="n"/>
+      <c r="AH14" s="11" t="n"/>
+      <c r="AI14" s="11" t="n"/>
+      <c r="AJ14" s="11" t="n"/>
+      <c r="AK14" s="11" t="n"/>
+      <c r="AL14" s="11" t="n"/>
+      <c r="AM14" s="11" t="n"/>
+      <c r="AN14" s="11" t="n"/>
+      <c r="AO14" s="11" t="n"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="B15" s="9" t="inlineStr">
@@ -971,12 +1123,12 @@
       <c r="M15" s="10" t="n"/>
       <c r="N15" s="10" t="n"/>
       <c r="O15" s="10" t="n"/>
-      <c r="Q15" s="11" t="n"/>
-      <c r="R15" s="11" t="n"/>
-      <c r="S15" s="11" t="n"/>
-      <c r="T15" s="11" t="n"/>
-      <c r="U15" s="11" t="n"/>
-      <c r="V15" s="11" t="n"/>
+      <c r="P15" s="10" t="n"/>
+      <c r="Q15" s="10" t="n"/>
+      <c r="R15" s="10" t="n"/>
+      <c r="S15" s="10" t="n"/>
+      <c r="T15" s="10" t="n"/>
+      <c r="U15" s="10" t="n"/>
       <c r="W15" s="11" t="n"/>
       <c r="X15" s="11" t="n"/>
       <c r="Y15" s="11" t="n"/>
@@ -984,6 +1136,18 @@
       <c r="AA15" s="11" t="n"/>
       <c r="AB15" s="11" t="n"/>
       <c r="AC15" s="11" t="n"/>
+      <c r="AD15" s="11" t="n"/>
+      <c r="AE15" s="11" t="n"/>
+      <c r="AF15" s="11" t="n"/>
+      <c r="AG15" s="11" t="n"/>
+      <c r="AH15" s="11" t="n"/>
+      <c r="AI15" s="11" t="n"/>
+      <c r="AJ15" s="11" t="n"/>
+      <c r="AK15" s="11" t="n"/>
+      <c r="AL15" s="11" t="n"/>
+      <c r="AM15" s="11" t="n"/>
+      <c r="AN15" s="11" t="n"/>
+      <c r="AO15" s="11" t="n"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="B16" s="12" t="inlineStr">
@@ -1004,12 +1168,12 @@
       <c r="M16" s="13" t="n"/>
       <c r="N16" s="13" t="n"/>
       <c r="O16" s="13" t="n"/>
-      <c r="Q16" s="11" t="n"/>
-      <c r="R16" s="11" t="n"/>
-      <c r="S16" s="11" t="n"/>
-      <c r="T16" s="11" t="n"/>
-      <c r="U16" s="11" t="n"/>
-      <c r="V16" s="11" t="n"/>
+      <c r="P16" s="13" t="n"/>
+      <c r="Q16" s="13" t="n"/>
+      <c r="R16" s="13" t="n"/>
+      <c r="S16" s="13" t="n"/>
+      <c r="T16" s="13" t="n"/>
+      <c r="U16" s="13" t="n"/>
       <c r="W16" s="11" t="n"/>
       <c r="X16" s="11" t="n"/>
       <c r="Y16" s="11" t="n"/>
@@ -1017,6 +1181,18 @@
       <c r="AA16" s="11" t="n"/>
       <c r="AB16" s="11" t="n"/>
       <c r="AC16" s="11" t="n"/>
+      <c r="AD16" s="11" t="n"/>
+      <c r="AE16" s="11" t="n"/>
+      <c r="AF16" s="11" t="n"/>
+      <c r="AG16" s="11" t="n"/>
+      <c r="AH16" s="11" t="n"/>
+      <c r="AI16" s="11" t="n"/>
+      <c r="AJ16" s="11" t="n"/>
+      <c r="AK16" s="11" t="n"/>
+      <c r="AL16" s="11" t="n"/>
+      <c r="AM16" s="11" t="n"/>
+      <c r="AN16" s="11" t="n"/>
+      <c r="AO16" s="11" t="n"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="B17" s="12" t="inlineStr">
@@ -1037,12 +1213,12 @@
       <c r="M17" s="13" t="n"/>
       <c r="N17" s="13" t="n"/>
       <c r="O17" s="13" t="n"/>
-      <c r="Q17" s="11" t="n"/>
-      <c r="R17" s="11" t="n"/>
-      <c r="S17" s="11" t="n"/>
-      <c r="T17" s="11" t="n"/>
-      <c r="U17" s="11" t="n"/>
-      <c r="V17" s="11" t="n"/>
+      <c r="P17" s="13" t="n"/>
+      <c r="Q17" s="13" t="n"/>
+      <c r="R17" s="13" t="n"/>
+      <c r="S17" s="13" t="n"/>
+      <c r="T17" s="13" t="n"/>
+      <c r="U17" s="13" t="n"/>
       <c r="W17" s="11" t="n"/>
       <c r="X17" s="11" t="n"/>
       <c r="Y17" s="11" t="n"/>
@@ -1050,6 +1226,18 @@
       <c r="AA17" s="11" t="n"/>
       <c r="AB17" s="11" t="n"/>
       <c r="AC17" s="11" t="n"/>
+      <c r="AD17" s="11" t="n"/>
+      <c r="AE17" s="11" t="n"/>
+      <c r="AF17" s="11" t="n"/>
+      <c r="AG17" s="11" t="n"/>
+      <c r="AH17" s="11" t="n"/>
+      <c r="AI17" s="11" t="n"/>
+      <c r="AJ17" s="11" t="n"/>
+      <c r="AK17" s="11" t="n"/>
+      <c r="AL17" s="11" t="n"/>
+      <c r="AM17" s="11" t="n"/>
+      <c r="AN17" s="11" t="n"/>
+      <c r="AO17" s="11" t="n"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="B18" s="12" t="inlineStr">
@@ -1070,12 +1258,12 @@
       <c r="M18" s="13" t="n"/>
       <c r="N18" s="13" t="n"/>
       <c r="O18" s="13" t="n"/>
-      <c r="Q18" s="11" t="n"/>
-      <c r="R18" s="11" t="n"/>
-      <c r="S18" s="11" t="n"/>
-      <c r="T18" s="11" t="n"/>
-      <c r="U18" s="11" t="n"/>
-      <c r="V18" s="11" t="n"/>
+      <c r="P18" s="13" t="n"/>
+      <c r="Q18" s="13" t="n"/>
+      <c r="R18" s="13" t="n"/>
+      <c r="S18" s="13" t="n"/>
+      <c r="T18" s="13" t="n"/>
+      <c r="U18" s="13" t="n"/>
       <c r="W18" s="11" t="n"/>
       <c r="X18" s="11" t="n"/>
       <c r="Y18" s="11" t="n"/>
@@ -1083,6 +1271,18 @@
       <c r="AA18" s="11" t="n"/>
       <c r="AB18" s="11" t="n"/>
       <c r="AC18" s="11" t="n"/>
+      <c r="AD18" s="11" t="n"/>
+      <c r="AE18" s="11" t="n"/>
+      <c r="AF18" s="11" t="n"/>
+      <c r="AG18" s="11" t="n"/>
+      <c r="AH18" s="11" t="n"/>
+      <c r="AI18" s="11" t="n"/>
+      <c r="AJ18" s="11" t="n"/>
+      <c r="AK18" s="11" t="n"/>
+      <c r="AL18" s="11" t="n"/>
+      <c r="AM18" s="11" t="n"/>
+      <c r="AN18" s="11" t="n"/>
+      <c r="AO18" s="11" t="n"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="B19" s="12" t="inlineStr">
@@ -1103,12 +1303,12 @@
       <c r="M19" s="13" t="n"/>
       <c r="N19" s="13" t="n"/>
       <c r="O19" s="13" t="n"/>
-      <c r="Q19" s="11" t="n"/>
-      <c r="R19" s="11" t="n"/>
-      <c r="S19" s="11" t="n"/>
-      <c r="T19" s="11" t="n"/>
-      <c r="U19" s="11" t="n"/>
-      <c r="V19" s="11" t="n"/>
+      <c r="P19" s="13" t="n"/>
+      <c r="Q19" s="13" t="n"/>
+      <c r="R19" s="13" t="n"/>
+      <c r="S19" s="13" t="n"/>
+      <c r="T19" s="13" t="n"/>
+      <c r="U19" s="13" t="n"/>
       <c r="W19" s="11" t="n"/>
       <c r="X19" s="11" t="n"/>
       <c r="Y19" s="11" t="n"/>
@@ -1116,6 +1316,18 @@
       <c r="AA19" s="11" t="n"/>
       <c r="AB19" s="11" t="n"/>
       <c r="AC19" s="11" t="n"/>
+      <c r="AD19" s="11" t="n"/>
+      <c r="AE19" s="11" t="n"/>
+      <c r="AF19" s="11" t="n"/>
+      <c r="AG19" s="11" t="n"/>
+      <c r="AH19" s="11" t="n"/>
+      <c r="AI19" s="11" t="n"/>
+      <c r="AJ19" s="11" t="n"/>
+      <c r="AK19" s="11" t="n"/>
+      <c r="AL19" s="11" t="n"/>
+      <c r="AM19" s="11" t="n"/>
+      <c r="AN19" s="11" t="n"/>
+      <c r="AO19" s="11" t="n"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="B20" s="9" t="inlineStr">
@@ -1136,12 +1348,12 @@
       <c r="M20" s="10" t="n"/>
       <c r="N20" s="10" t="n"/>
       <c r="O20" s="10" t="n"/>
-      <c r="Q20" s="11" t="n"/>
-      <c r="R20" s="11" t="n"/>
-      <c r="S20" s="11" t="n"/>
-      <c r="T20" s="11" t="n"/>
-      <c r="U20" s="11" t="n"/>
-      <c r="V20" s="11" t="n"/>
+      <c r="P20" s="10" t="n"/>
+      <c r="Q20" s="10" t="n"/>
+      <c r="R20" s="10" t="n"/>
+      <c r="S20" s="10" t="n"/>
+      <c r="T20" s="10" t="n"/>
+      <c r="U20" s="10" t="n"/>
       <c r="W20" s="11" t="n"/>
       <c r="X20" s="11" t="n"/>
       <c r="Y20" s="11" t="n"/>
@@ -1149,6 +1361,18 @@
       <c r="AA20" s="11" t="n"/>
       <c r="AB20" s="11" t="n"/>
       <c r="AC20" s="11" t="n"/>
+      <c r="AD20" s="11" t="n"/>
+      <c r="AE20" s="11" t="n"/>
+      <c r="AF20" s="11" t="n"/>
+      <c r="AG20" s="11" t="n"/>
+      <c r="AH20" s="11" t="n"/>
+      <c r="AI20" s="11" t="n"/>
+      <c r="AJ20" s="11" t="n"/>
+      <c r="AK20" s="11" t="n"/>
+      <c r="AL20" s="11" t="n"/>
+      <c r="AM20" s="11" t="n"/>
+      <c r="AN20" s="11" t="n"/>
+      <c r="AO20" s="11" t="n"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="B21" s="12" t="inlineStr">
@@ -1169,12 +1393,12 @@
       <c r="M21" s="13" t="n"/>
       <c r="N21" s="13" t="n"/>
       <c r="O21" s="13" t="n"/>
-      <c r="Q21" s="11" t="n"/>
-      <c r="R21" s="11" t="n"/>
-      <c r="S21" s="11" t="n"/>
-      <c r="T21" s="11" t="n"/>
-      <c r="U21" s="11" t="n"/>
-      <c r="V21" s="11" t="n"/>
+      <c r="P21" s="13" t="n"/>
+      <c r="Q21" s="13" t="n"/>
+      <c r="R21" s="13" t="n"/>
+      <c r="S21" s="13" t="n"/>
+      <c r="T21" s="13" t="n"/>
+      <c r="U21" s="13" t="n"/>
       <c r="W21" s="11" t="n"/>
       <c r="X21" s="11" t="n"/>
       <c r="Y21" s="11" t="n"/>
@@ -1182,6 +1406,18 @@
       <c r="AA21" s="11" t="n"/>
       <c r="AB21" s="11" t="n"/>
       <c r="AC21" s="11" t="n"/>
+      <c r="AD21" s="11" t="n"/>
+      <c r="AE21" s="11" t="n"/>
+      <c r="AF21" s="11" t="n"/>
+      <c r="AG21" s="11" t="n"/>
+      <c r="AH21" s="11" t="n"/>
+      <c r="AI21" s="11" t="n"/>
+      <c r="AJ21" s="11" t="n"/>
+      <c r="AK21" s="11" t="n"/>
+      <c r="AL21" s="11" t="n"/>
+      <c r="AM21" s="11" t="n"/>
+      <c r="AN21" s="11" t="n"/>
+      <c r="AO21" s="11" t="n"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="B22" s="12" t="inlineStr">
@@ -1202,12 +1438,12 @@
       <c r="M22" s="13" t="n"/>
       <c r="N22" s="13" t="n"/>
       <c r="O22" s="13" t="n"/>
-      <c r="Q22" s="11" t="n"/>
-      <c r="R22" s="11" t="n"/>
-      <c r="S22" s="11" t="n"/>
-      <c r="T22" s="11" t="n"/>
-      <c r="U22" s="11" t="n"/>
-      <c r="V22" s="11" t="n"/>
+      <c r="P22" s="13" t="n"/>
+      <c r="Q22" s="13" t="n"/>
+      <c r="R22" s="13" t="n"/>
+      <c r="S22" s="13" t="n"/>
+      <c r="T22" s="13" t="n"/>
+      <c r="U22" s="13" t="n"/>
       <c r="W22" s="11" t="n"/>
       <c r="X22" s="11" t="n"/>
       <c r="Y22" s="11" t="n"/>
@@ -1215,6 +1451,18 @@
       <c r="AA22" s="11" t="n"/>
       <c r="AB22" s="11" t="n"/>
       <c r="AC22" s="11" t="n"/>
+      <c r="AD22" s="11" t="n"/>
+      <c r="AE22" s="11" t="n"/>
+      <c r="AF22" s="11" t="n"/>
+      <c r="AG22" s="11" t="n"/>
+      <c r="AH22" s="11" t="n"/>
+      <c r="AI22" s="11" t="n"/>
+      <c r="AJ22" s="11" t="n"/>
+      <c r="AK22" s="11" t="n"/>
+      <c r="AL22" s="11" t="n"/>
+      <c r="AM22" s="11" t="n"/>
+      <c r="AN22" s="11" t="n"/>
+      <c r="AO22" s="11" t="n"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="B23" s="12" t="inlineStr">
@@ -1235,12 +1483,12 @@
       <c r="M23" s="13" t="n"/>
       <c r="N23" s="13" t="n"/>
       <c r="O23" s="13" t="n"/>
-      <c r="Q23" s="11" t="n"/>
-      <c r="R23" s="11" t="n"/>
-      <c r="S23" s="11" t="n"/>
-      <c r="T23" s="11" t="n"/>
-      <c r="U23" s="11" t="n"/>
-      <c r="V23" s="11" t="n"/>
+      <c r="P23" s="13" t="n"/>
+      <c r="Q23" s="13" t="n"/>
+      <c r="R23" s="13" t="n"/>
+      <c r="S23" s="13" t="n"/>
+      <c r="T23" s="13" t="n"/>
+      <c r="U23" s="13" t="n"/>
       <c r="W23" s="11" t="n"/>
       <c r="X23" s="11" t="n"/>
       <c r="Y23" s="11" t="n"/>
@@ -1248,6 +1496,18 @@
       <c r="AA23" s="11" t="n"/>
       <c r="AB23" s="11" t="n"/>
       <c r="AC23" s="11" t="n"/>
+      <c r="AD23" s="11" t="n"/>
+      <c r="AE23" s="11" t="n"/>
+      <c r="AF23" s="11" t="n"/>
+      <c r="AG23" s="11" t="n"/>
+      <c r="AH23" s="11" t="n"/>
+      <c r="AI23" s="11" t="n"/>
+      <c r="AJ23" s="11" t="n"/>
+      <c r="AK23" s="11" t="n"/>
+      <c r="AL23" s="11" t="n"/>
+      <c r="AM23" s="11" t="n"/>
+      <c r="AN23" s="11" t="n"/>
+      <c r="AO23" s="11" t="n"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="B24" s="14" t="inlineStr">
@@ -1268,12 +1528,12 @@
       <c r="M24" s="13" t="n"/>
       <c r="N24" s="13" t="n"/>
       <c r="O24" s="13" t="n"/>
-      <c r="Q24" s="11" t="n"/>
-      <c r="R24" s="11" t="n"/>
-      <c r="S24" s="11" t="n"/>
-      <c r="T24" s="11" t="n"/>
-      <c r="U24" s="11" t="n"/>
-      <c r="V24" s="11" t="n"/>
+      <c r="P24" s="13" t="n"/>
+      <c r="Q24" s="13" t="n"/>
+      <c r="R24" s="13" t="n"/>
+      <c r="S24" s="13" t="n"/>
+      <c r="T24" s="13" t="n"/>
+      <c r="U24" s="13" t="n"/>
       <c r="W24" s="11" t="n"/>
       <c r="X24" s="11" t="n"/>
       <c r="Y24" s="11" t="n"/>
@@ -1281,6 +1541,18 @@
       <c r="AA24" s="11" t="n"/>
       <c r="AB24" s="11" t="n"/>
       <c r="AC24" s="11" t="n"/>
+      <c r="AD24" s="11" t="n"/>
+      <c r="AE24" s="11" t="n"/>
+      <c r="AF24" s="11" t="n"/>
+      <c r="AG24" s="11" t="n"/>
+      <c r="AH24" s="11" t="n"/>
+      <c r="AI24" s="11" t="n"/>
+      <c r="AJ24" s="11" t="n"/>
+      <c r="AK24" s="11" t="n"/>
+      <c r="AL24" s="11" t="n"/>
+      <c r="AM24" s="11" t="n"/>
+      <c r="AN24" s="11" t="n"/>
+      <c r="AO24" s="11" t="n"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="B25" s="12" t="inlineStr">
@@ -1301,12 +1573,12 @@
       <c r="M25" s="13" t="n"/>
       <c r="N25" s="13" t="n"/>
       <c r="O25" s="13" t="n"/>
-      <c r="Q25" s="11" t="n"/>
-      <c r="R25" s="11" t="n"/>
-      <c r="S25" s="11" t="n"/>
-      <c r="T25" s="11" t="n"/>
-      <c r="U25" s="11" t="n"/>
-      <c r="V25" s="11" t="n"/>
+      <c r="P25" s="13" t="n"/>
+      <c r="Q25" s="13" t="n"/>
+      <c r="R25" s="13" t="n"/>
+      <c r="S25" s="13" t="n"/>
+      <c r="T25" s="13" t="n"/>
+      <c r="U25" s="13" t="n"/>
       <c r="W25" s="11" t="n"/>
       <c r="X25" s="11" t="n"/>
       <c r="Y25" s="11" t="n"/>
@@ -1314,6 +1586,18 @@
       <c r="AA25" s="11" t="n"/>
       <c r="AB25" s="11" t="n"/>
       <c r="AC25" s="11" t="n"/>
+      <c r="AD25" s="11" t="n"/>
+      <c r="AE25" s="11" t="n"/>
+      <c r="AF25" s="11" t="n"/>
+      <c r="AG25" s="11" t="n"/>
+      <c r="AH25" s="11" t="n"/>
+      <c r="AI25" s="11" t="n"/>
+      <c r="AJ25" s="11" t="n"/>
+      <c r="AK25" s="11" t="n"/>
+      <c r="AL25" s="11" t="n"/>
+      <c r="AM25" s="11" t="n"/>
+      <c r="AN25" s="11" t="n"/>
+      <c r="AO25" s="11" t="n"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="B26" s="12" t="inlineStr">
@@ -1334,12 +1618,12 @@
       <c r="M26" s="13" t="n"/>
       <c r="N26" s="13" t="n"/>
       <c r="O26" s="13" t="n"/>
-      <c r="Q26" s="11" t="n"/>
-      <c r="R26" s="11" t="n"/>
-      <c r="S26" s="11" t="n"/>
-      <c r="T26" s="11" t="n"/>
-      <c r="U26" s="11" t="n"/>
-      <c r="V26" s="11" t="n"/>
+      <c r="P26" s="13" t="n"/>
+      <c r="Q26" s="13" t="n"/>
+      <c r="R26" s="13" t="n"/>
+      <c r="S26" s="13" t="n"/>
+      <c r="T26" s="13" t="n"/>
+      <c r="U26" s="13" t="n"/>
       <c r="W26" s="11" t="n"/>
       <c r="X26" s="11" t="n"/>
       <c r="Y26" s="11" t="n"/>
@@ -1347,6 +1631,18 @@
       <c r="AA26" s="11" t="n"/>
       <c r="AB26" s="11" t="n"/>
       <c r="AC26" s="11" t="n"/>
+      <c r="AD26" s="11" t="n"/>
+      <c r="AE26" s="11" t="n"/>
+      <c r="AF26" s="11" t="n"/>
+      <c r="AG26" s="11" t="n"/>
+      <c r="AH26" s="11" t="n"/>
+      <c r="AI26" s="11" t="n"/>
+      <c r="AJ26" s="11" t="n"/>
+      <c r="AK26" s="11" t="n"/>
+      <c r="AL26" s="11" t="n"/>
+      <c r="AM26" s="11" t="n"/>
+      <c r="AN26" s="11" t="n"/>
+      <c r="AO26" s="11" t="n"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="B27" s="9" t="inlineStr">
@@ -1367,12 +1663,12 @@
       <c r="M27" s="10" t="n"/>
       <c r="N27" s="10" t="n"/>
       <c r="O27" s="10" t="n"/>
-      <c r="Q27" s="11" t="n"/>
-      <c r="R27" s="11" t="n"/>
-      <c r="S27" s="11" t="n"/>
-      <c r="T27" s="11" t="n"/>
-      <c r="U27" s="11" t="n"/>
-      <c r="V27" s="11" t="n"/>
+      <c r="P27" s="10" t="n"/>
+      <c r="Q27" s="10" t="n"/>
+      <c r="R27" s="10" t="n"/>
+      <c r="S27" s="10" t="n"/>
+      <c r="T27" s="10" t="n"/>
+      <c r="U27" s="10" t="n"/>
       <c r="W27" s="11" t="n"/>
       <c r="X27" s="11" t="n"/>
       <c r="Y27" s="11" t="n"/>
@@ -1380,6 +1676,18 @@
       <c r="AA27" s="11" t="n"/>
       <c r="AB27" s="11" t="n"/>
       <c r="AC27" s="11" t="n"/>
+      <c r="AD27" s="11" t="n"/>
+      <c r="AE27" s="11" t="n"/>
+      <c r="AF27" s="11" t="n"/>
+      <c r="AG27" s="11" t="n"/>
+      <c r="AH27" s="11" t="n"/>
+      <c r="AI27" s="11" t="n"/>
+      <c r="AJ27" s="11" t="n"/>
+      <c r="AK27" s="11" t="n"/>
+      <c r="AL27" s="11" t="n"/>
+      <c r="AM27" s="11" t="n"/>
+      <c r="AN27" s="11" t="n"/>
+      <c r="AO27" s="11" t="n"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="B28" s="9" t="inlineStr">
@@ -1400,12 +1708,12 @@
       <c r="M28" s="10" t="n"/>
       <c r="N28" s="10" t="n"/>
       <c r="O28" s="10" t="n"/>
-      <c r="Q28" s="11" t="n"/>
-      <c r="R28" s="11" t="n"/>
-      <c r="S28" s="11" t="n"/>
-      <c r="T28" s="11" t="n"/>
-      <c r="U28" s="11" t="n"/>
-      <c r="V28" s="11" t="n"/>
+      <c r="P28" s="10" t="n"/>
+      <c r="Q28" s="10" t="n"/>
+      <c r="R28" s="10" t="n"/>
+      <c r="S28" s="10" t="n"/>
+      <c r="T28" s="10" t="n"/>
+      <c r="U28" s="10" t="n"/>
       <c r="W28" s="11" t="n"/>
       <c r="X28" s="11" t="n"/>
       <c r="Y28" s="11" t="n"/>
@@ -1413,6 +1721,18 @@
       <c r="AA28" s="11" t="n"/>
       <c r="AB28" s="11" t="n"/>
       <c r="AC28" s="11" t="n"/>
+      <c r="AD28" s="11" t="n"/>
+      <c r="AE28" s="11" t="n"/>
+      <c r="AF28" s="11" t="n"/>
+      <c r="AG28" s="11" t="n"/>
+      <c r="AH28" s="11" t="n"/>
+      <c r="AI28" s="11" t="n"/>
+      <c r="AJ28" s="11" t="n"/>
+      <c r="AK28" s="11" t="n"/>
+      <c r="AL28" s="11" t="n"/>
+      <c r="AM28" s="11" t="n"/>
+      <c r="AN28" s="11" t="n"/>
+      <c r="AO28" s="11" t="n"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="B29" s="12" t="inlineStr">
@@ -1433,12 +1753,12 @@
       <c r="M29" s="13" t="n"/>
       <c r="N29" s="13" t="n"/>
       <c r="O29" s="13" t="n"/>
-      <c r="Q29" s="11" t="n"/>
-      <c r="R29" s="11" t="n"/>
-      <c r="S29" s="11" t="n"/>
-      <c r="T29" s="11" t="n"/>
-      <c r="U29" s="11" t="n"/>
-      <c r="V29" s="11" t="n"/>
+      <c r="P29" s="13" t="n"/>
+      <c r="Q29" s="13" t="n"/>
+      <c r="R29" s="13" t="n"/>
+      <c r="S29" s="13" t="n"/>
+      <c r="T29" s="13" t="n"/>
+      <c r="U29" s="13" t="n"/>
       <c r="W29" s="11" t="n"/>
       <c r="X29" s="11" t="n"/>
       <c r="Y29" s="11" t="n"/>
@@ -1446,6 +1766,18 @@
       <c r="AA29" s="11" t="n"/>
       <c r="AB29" s="11" t="n"/>
       <c r="AC29" s="11" t="n"/>
+      <c r="AD29" s="11" t="n"/>
+      <c r="AE29" s="11" t="n"/>
+      <c r="AF29" s="11" t="n"/>
+      <c r="AG29" s="11" t="n"/>
+      <c r="AH29" s="11" t="n"/>
+      <c r="AI29" s="11" t="n"/>
+      <c r="AJ29" s="11" t="n"/>
+      <c r="AK29" s="11" t="n"/>
+      <c r="AL29" s="11" t="n"/>
+      <c r="AM29" s="11" t="n"/>
+      <c r="AN29" s="11" t="n"/>
+      <c r="AO29" s="11" t="n"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="B30" s="9" t="inlineStr">
@@ -1466,12 +1798,12 @@
       <c r="M30" s="10" t="n"/>
       <c r="N30" s="10" t="n"/>
       <c r="O30" s="10" t="n"/>
-      <c r="Q30" s="11" t="n"/>
-      <c r="R30" s="11" t="n"/>
-      <c r="S30" s="11" t="n"/>
-      <c r="T30" s="11" t="n"/>
-      <c r="U30" s="11" t="n"/>
-      <c r="V30" s="11" t="n"/>
+      <c r="P30" s="10" t="n"/>
+      <c r="Q30" s="10" t="n"/>
+      <c r="R30" s="10" t="n"/>
+      <c r="S30" s="10" t="n"/>
+      <c r="T30" s="10" t="n"/>
+      <c r="U30" s="10" t="n"/>
       <c r="W30" s="11" t="n"/>
       <c r="X30" s="11" t="n"/>
       <c r="Y30" s="11" t="n"/>
@@ -1479,6 +1811,18 @@
       <c r="AA30" s="11" t="n"/>
       <c r="AB30" s="11" t="n"/>
       <c r="AC30" s="11" t="n"/>
+      <c r="AD30" s="11" t="n"/>
+      <c r="AE30" s="11" t="n"/>
+      <c r="AF30" s="11" t="n"/>
+      <c r="AG30" s="11" t="n"/>
+      <c r="AH30" s="11" t="n"/>
+      <c r="AI30" s="11" t="n"/>
+      <c r="AJ30" s="11" t="n"/>
+      <c r="AK30" s="11" t="n"/>
+      <c r="AL30" s="11" t="n"/>
+      <c r="AM30" s="11" t="n"/>
+      <c r="AN30" s="11" t="n"/>
+      <c r="AO30" s="11" t="n"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="B31" s="12" t="inlineStr">
@@ -1499,12 +1843,12 @@
       <c r="M31" s="13" t="n"/>
       <c r="N31" s="13" t="n"/>
       <c r="O31" s="13" t="n"/>
-      <c r="Q31" s="11" t="n"/>
-      <c r="R31" s="11" t="n"/>
-      <c r="S31" s="11" t="n"/>
-      <c r="T31" s="11" t="n"/>
-      <c r="U31" s="11" t="n"/>
-      <c r="V31" s="11" t="n"/>
+      <c r="P31" s="13" t="n"/>
+      <c r="Q31" s="13" t="n"/>
+      <c r="R31" s="13" t="n"/>
+      <c r="S31" s="13" t="n"/>
+      <c r="T31" s="13" t="n"/>
+      <c r="U31" s="13" t="n"/>
       <c r="W31" s="11" t="n"/>
       <c r="X31" s="11" t="n"/>
       <c r="Y31" s="11" t="n"/>
@@ -1512,6 +1856,18 @@
       <c r="AA31" s="11" t="n"/>
       <c r="AB31" s="11" t="n"/>
       <c r="AC31" s="11" t="n"/>
+      <c r="AD31" s="11" t="n"/>
+      <c r="AE31" s="11" t="n"/>
+      <c r="AF31" s="11" t="n"/>
+      <c r="AG31" s="11" t="n"/>
+      <c r="AH31" s="11" t="n"/>
+      <c r="AI31" s="11" t="n"/>
+      <c r="AJ31" s="11" t="n"/>
+      <c r="AK31" s="11" t="n"/>
+      <c r="AL31" s="11" t="n"/>
+      <c r="AM31" s="11" t="n"/>
+      <c r="AN31" s="11" t="n"/>
+      <c r="AO31" s="11" t="n"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="B32" s="9" t="inlineStr">
@@ -1532,12 +1888,12 @@
       <c r="M32" s="10" t="n"/>
       <c r="N32" s="10" t="n"/>
       <c r="O32" s="10" t="n"/>
-      <c r="Q32" s="11" t="n"/>
-      <c r="R32" s="11" t="n"/>
-      <c r="S32" s="11" t="n"/>
-      <c r="T32" s="11" t="n"/>
-      <c r="U32" s="11" t="n"/>
-      <c r="V32" s="11" t="n"/>
+      <c r="P32" s="10" t="n"/>
+      <c r="Q32" s="10" t="n"/>
+      <c r="R32" s="10" t="n"/>
+      <c r="S32" s="10" t="n"/>
+      <c r="T32" s="10" t="n"/>
+      <c r="U32" s="10" t="n"/>
       <c r="W32" s="11" t="n"/>
       <c r="X32" s="11" t="n"/>
       <c r="Y32" s="11" t="n"/>
@@ -1545,6 +1901,18 @@
       <c r="AA32" s="11" t="n"/>
       <c r="AB32" s="11" t="n"/>
       <c r="AC32" s="11" t="n"/>
+      <c r="AD32" s="11" t="n"/>
+      <c r="AE32" s="11" t="n"/>
+      <c r="AF32" s="11" t="n"/>
+      <c r="AG32" s="11" t="n"/>
+      <c r="AH32" s="11" t="n"/>
+      <c r="AI32" s="11" t="n"/>
+      <c r="AJ32" s="11" t="n"/>
+      <c r="AK32" s="11" t="n"/>
+      <c r="AL32" s="11" t="n"/>
+      <c r="AM32" s="11" t="n"/>
+      <c r="AN32" s="11" t="n"/>
+      <c r="AO32" s="11" t="n"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="B35" s="5" t="inlineStr">
@@ -1557,7 +1925,7 @@
           <t>10-19 Segment - Over Time Period</t>
         </is>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
+      <c r="W35" s="6" t="inlineStr">
         <is>
           <t>10-19 Segment - Over Time Period - Difference</t>
         </is>
@@ -1634,69 +2002,129 @@
           <t>SPTx2</t>
         </is>
       </c>
+      <c r="P36" s="8" t="inlineStr">
+        <is>
+          <t>1-star Pack</t>
+        </is>
+      </c>
       <c r="Q36" s="8" t="inlineStr">
         <is>
+          <t>2-star Pack</t>
+        </is>
+      </c>
+      <c r="R36" s="8" t="inlineStr">
+        <is>
+          <t>3-star Pack</t>
+        </is>
+      </c>
+      <c r="S36" s="8" t="inlineStr">
+        <is>
+          <t>4-star Pack</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>5-star Pack</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>6-star Pack</t>
+        </is>
+      </c>
+      <c r="W36" s="8" t="inlineStr">
+        <is>
           <t>HC</t>
         </is>
       </c>
-      <c r="R36" s="8" t="inlineStr">
+      <c r="X36" s="8" t="inlineStr">
         <is>
           <t>Slingshot</t>
         </is>
       </c>
-      <c r="S36" s="8" t="inlineStr">
+      <c r="Y36" s="8" t="inlineStr">
         <is>
           <t>Shuffle</t>
         </is>
       </c>
-      <c r="T36" s="8" t="inlineStr">
+      <c r="Z36" s="8" t="inlineStr">
         <is>
           <t>Comet</t>
         </is>
       </c>
-      <c r="U36" s="8" t="inlineStr">
+      <c r="AA36" s="8" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="V36" s="8" t="inlineStr">
+      <c r="AB36" s="8" t="inlineStr">
         <is>
           <t>Chuck</t>
         </is>
       </c>
-      <c r="W36" s="8" t="inlineStr">
+      <c r="AC36" s="8" t="inlineStr">
         <is>
           <t>Bomb</t>
         </is>
       </c>
-      <c r="X36" s="8" t="inlineStr">
+      <c r="AD36" s="8" t="inlineStr">
         <is>
           <t>UL Bomb</t>
         </is>
       </c>
-      <c r="Y36" s="8" t="inlineStr">
+      <c r="AE36" s="8" t="inlineStr">
         <is>
           <t>UL Chuck</t>
         </is>
       </c>
-      <c r="Z36" s="8" t="inlineStr">
+      <c r="AF36" s="8" t="inlineStr">
         <is>
           <t>UL Red</t>
         </is>
       </c>
-      <c r="AA36" s="8" t="inlineStr">
+      <c r="AG36" s="8" t="inlineStr">
         <is>
           <t>Unlimited Lives</t>
         </is>
       </c>
-      <c r="AB36" s="8" t="inlineStr">
+      <c r="AH36" s="8" t="inlineStr">
         <is>
           <t>SPT</t>
         </is>
       </c>
-      <c r="AC36" s="8" t="inlineStr">
+      <c r="AI36" s="8" t="inlineStr">
         <is>
           <t>SPTx2</t>
+        </is>
+      </c>
+      <c r="AJ36" s="8" t="inlineStr">
+        <is>
+          <t>1-star Pack</t>
+        </is>
+      </c>
+      <c r="AK36" s="8" t="inlineStr">
+        <is>
+          <t>2-star Pack</t>
+        </is>
+      </c>
+      <c r="AL36" s="8" t="inlineStr">
+        <is>
+          <t>3-star Pack</t>
+        </is>
+      </c>
+      <c r="AM36" s="8" t="inlineStr">
+        <is>
+          <t>4-star Pack</t>
+        </is>
+      </c>
+      <c r="AN36" s="8" t="inlineStr">
+        <is>
+          <t>5-star Pack</t>
+        </is>
+      </c>
+      <c r="AO36" s="8" t="inlineStr">
+        <is>
+          <t>6-star Pack</t>
         </is>
       </c>
     </row>
@@ -1722,22 +2150,34 @@
       <c r="M37" s="10" t="n"/>
       <c r="N37" s="10" t="n"/>
       <c r="O37" s="10" t="n"/>
-      <c r="Q37" s="11">
+      <c r="P37" s="10" t="n"/>
+      <c r="Q37" s="10" t="n"/>
+      <c r="R37" s="10" t="n"/>
+      <c r="S37" s="10" t="n"/>
+      <c r="T37" s="10" t="n"/>
+      <c r="U37" s="10" t="n"/>
+      <c r="W37" s="11">
         <f>LET(payer, $C$3, segment, $B$35, ECOGAINS_DIFF(payer, segment, sim_refresh!$A$1))</f>
         <v/>
       </c>
-      <c r="R37" s="11" t="n"/>
-      <c r="S37" s="11" t="n"/>
-      <c r="T37" s="11" t="n"/>
-      <c r="U37" s="11" t="n"/>
-      <c r="V37" s="11" t="n"/>
-      <c r="W37" s="11" t="n"/>
       <c r="X37" s="11" t="n"/>
       <c r="Y37" s="11" t="n"/>
       <c r="Z37" s="11" t="n"/>
       <c r="AA37" s="11" t="n"/>
       <c r="AB37" s="11" t="n"/>
       <c r="AC37" s="11" t="n"/>
+      <c r="AD37" s="11" t="n"/>
+      <c r="AE37" s="11" t="n"/>
+      <c r="AF37" s="11" t="n"/>
+      <c r="AG37" s="11" t="n"/>
+      <c r="AH37" s="11" t="n"/>
+      <c r="AI37" s="11" t="n"/>
+      <c r="AJ37" s="11" t="n"/>
+      <c r="AK37" s="11" t="n"/>
+      <c r="AL37" s="11" t="n"/>
+      <c r="AM37" s="11" t="n"/>
+      <c r="AN37" s="11" t="n"/>
+      <c r="AO37" s="11" t="n"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="B38" s="12" t="inlineStr">
@@ -1758,12 +2198,12 @@
       <c r="M38" s="13" t="n"/>
       <c r="N38" s="13" t="n"/>
       <c r="O38" s="13" t="n"/>
-      <c r="Q38" s="11" t="n"/>
-      <c r="R38" s="11" t="n"/>
-      <c r="S38" s="11" t="n"/>
-      <c r="T38" s="11" t="n"/>
-      <c r="U38" s="11" t="n"/>
-      <c r="V38" s="11" t="n"/>
+      <c r="P38" s="13" t="n"/>
+      <c r="Q38" s="13" t="n"/>
+      <c r="R38" s="13" t="n"/>
+      <c r="S38" s="13" t="n"/>
+      <c r="T38" s="13" t="n"/>
+      <c r="U38" s="13" t="n"/>
       <c r="W38" s="11" t="n"/>
       <c r="X38" s="11" t="n"/>
       <c r="Y38" s="11" t="n"/>
@@ -1771,6 +2211,18 @@
       <c r="AA38" s="11" t="n"/>
       <c r="AB38" s="11" t="n"/>
       <c r="AC38" s="11" t="n"/>
+      <c r="AD38" s="11" t="n"/>
+      <c r="AE38" s="11" t="n"/>
+      <c r="AF38" s="11" t="n"/>
+      <c r="AG38" s="11" t="n"/>
+      <c r="AH38" s="11" t="n"/>
+      <c r="AI38" s="11" t="n"/>
+      <c r="AJ38" s="11" t="n"/>
+      <c r="AK38" s="11" t="n"/>
+      <c r="AL38" s="11" t="n"/>
+      <c r="AM38" s="11" t="n"/>
+      <c r="AN38" s="11" t="n"/>
+      <c r="AO38" s="11" t="n"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="B39" s="12" t="inlineStr">
@@ -1791,12 +2243,12 @@
       <c r="M39" s="13" t="n"/>
       <c r="N39" s="13" t="n"/>
       <c r="O39" s="13" t="n"/>
-      <c r="Q39" s="11" t="n"/>
-      <c r="R39" s="11" t="n"/>
-      <c r="S39" s="11" t="n"/>
-      <c r="T39" s="11" t="n"/>
-      <c r="U39" s="11" t="n"/>
-      <c r="V39" s="11" t="n"/>
+      <c r="P39" s="13" t="n"/>
+      <c r="Q39" s="13" t="n"/>
+      <c r="R39" s="13" t="n"/>
+      <c r="S39" s="13" t="n"/>
+      <c r="T39" s="13" t="n"/>
+      <c r="U39" s="13" t="n"/>
       <c r="W39" s="11" t="n"/>
       <c r="X39" s="11" t="n"/>
       <c r="Y39" s="11" t="n"/>
@@ -1804,6 +2256,18 @@
       <c r="AA39" s="11" t="n"/>
       <c r="AB39" s="11" t="n"/>
       <c r="AC39" s="11" t="n"/>
+      <c r="AD39" s="11" t="n"/>
+      <c r="AE39" s="11" t="n"/>
+      <c r="AF39" s="11" t="n"/>
+      <c r="AG39" s="11" t="n"/>
+      <c r="AH39" s="11" t="n"/>
+      <c r="AI39" s="11" t="n"/>
+      <c r="AJ39" s="11" t="n"/>
+      <c r="AK39" s="11" t="n"/>
+      <c r="AL39" s="11" t="n"/>
+      <c r="AM39" s="11" t="n"/>
+      <c r="AN39" s="11" t="n"/>
+      <c r="AO39" s="11" t="n"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="B40" s="12" t="inlineStr">
@@ -1824,12 +2288,12 @@
       <c r="M40" s="13" t="n"/>
       <c r="N40" s="13" t="n"/>
       <c r="O40" s="13" t="n"/>
-      <c r="Q40" s="11" t="n"/>
-      <c r="R40" s="11" t="n"/>
-      <c r="S40" s="11" t="n"/>
-      <c r="T40" s="11" t="n"/>
-      <c r="U40" s="11" t="n"/>
-      <c r="V40" s="11" t="n"/>
+      <c r="P40" s="13" t="n"/>
+      <c r="Q40" s="13" t="n"/>
+      <c r="R40" s="13" t="n"/>
+      <c r="S40" s="13" t="n"/>
+      <c r="T40" s="13" t="n"/>
+      <c r="U40" s="13" t="n"/>
       <c r="W40" s="11" t="n"/>
       <c r="X40" s="11" t="n"/>
       <c r="Y40" s="11" t="n"/>
@@ -1837,6 +2301,18 @@
       <c r="AA40" s="11" t="n"/>
       <c r="AB40" s="11" t="n"/>
       <c r="AC40" s="11" t="n"/>
+      <c r="AD40" s="11" t="n"/>
+      <c r="AE40" s="11" t="n"/>
+      <c r="AF40" s="11" t="n"/>
+      <c r="AG40" s="11" t="n"/>
+      <c r="AH40" s="11" t="n"/>
+      <c r="AI40" s="11" t="n"/>
+      <c r="AJ40" s="11" t="n"/>
+      <c r="AK40" s="11" t="n"/>
+      <c r="AL40" s="11" t="n"/>
+      <c r="AM40" s="11" t="n"/>
+      <c r="AN40" s="11" t="n"/>
+      <c r="AO40" s="11" t="n"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="B41" s="9" t="inlineStr">
@@ -1857,12 +2333,12 @@
       <c r="M41" s="10" t="n"/>
       <c r="N41" s="10" t="n"/>
       <c r="O41" s="10" t="n"/>
-      <c r="Q41" s="11" t="n"/>
-      <c r="R41" s="11" t="n"/>
-      <c r="S41" s="11" t="n"/>
-      <c r="T41" s="11" t="n"/>
-      <c r="U41" s="11" t="n"/>
-      <c r="V41" s="11" t="n"/>
+      <c r="P41" s="10" t="n"/>
+      <c r="Q41" s="10" t="n"/>
+      <c r="R41" s="10" t="n"/>
+      <c r="S41" s="10" t="n"/>
+      <c r="T41" s="10" t="n"/>
+      <c r="U41" s="10" t="n"/>
       <c r="W41" s="11" t="n"/>
       <c r="X41" s="11" t="n"/>
       <c r="Y41" s="11" t="n"/>
@@ -1870,6 +2346,18 @@
       <c r="AA41" s="11" t="n"/>
       <c r="AB41" s="11" t="n"/>
       <c r="AC41" s="11" t="n"/>
+      <c r="AD41" s="11" t="n"/>
+      <c r="AE41" s="11" t="n"/>
+      <c r="AF41" s="11" t="n"/>
+      <c r="AG41" s="11" t="n"/>
+      <c r="AH41" s="11" t="n"/>
+      <c r="AI41" s="11" t="n"/>
+      <c r="AJ41" s="11" t="n"/>
+      <c r="AK41" s="11" t="n"/>
+      <c r="AL41" s="11" t="n"/>
+      <c r="AM41" s="11" t="n"/>
+      <c r="AN41" s="11" t="n"/>
+      <c r="AO41" s="11" t="n"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="B42" s="14" t="inlineStr">
@@ -1890,12 +2378,12 @@
       <c r="M42" s="13" t="n"/>
       <c r="N42" s="13" t="n"/>
       <c r="O42" s="13" t="n"/>
-      <c r="Q42" s="11" t="n"/>
-      <c r="R42" s="11" t="n"/>
-      <c r="S42" s="11" t="n"/>
-      <c r="T42" s="11" t="n"/>
-      <c r="U42" s="11" t="n"/>
-      <c r="V42" s="11" t="n"/>
+      <c r="P42" s="13" t="n"/>
+      <c r="Q42" s="13" t="n"/>
+      <c r="R42" s="13" t="n"/>
+      <c r="S42" s="13" t="n"/>
+      <c r="T42" s="13" t="n"/>
+      <c r="U42" s="13" t="n"/>
       <c r="W42" s="11" t="n"/>
       <c r="X42" s="11" t="n"/>
       <c r="Y42" s="11" t="n"/>
@@ -1903,6 +2391,18 @@
       <c r="AA42" s="11" t="n"/>
       <c r="AB42" s="11" t="n"/>
       <c r="AC42" s="11" t="n"/>
+      <c r="AD42" s="11" t="n"/>
+      <c r="AE42" s="11" t="n"/>
+      <c r="AF42" s="11" t="n"/>
+      <c r="AG42" s="11" t="n"/>
+      <c r="AH42" s="11" t="n"/>
+      <c r="AI42" s="11" t="n"/>
+      <c r="AJ42" s="11" t="n"/>
+      <c r="AK42" s="11" t="n"/>
+      <c r="AL42" s="11" t="n"/>
+      <c r="AM42" s="11" t="n"/>
+      <c r="AN42" s="11" t="n"/>
+      <c r="AO42" s="11" t="n"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="B43" s="14" t="inlineStr">
@@ -1923,12 +2423,12 @@
       <c r="M43" s="13" t="n"/>
       <c r="N43" s="13" t="n"/>
       <c r="O43" s="13" t="n"/>
-      <c r="Q43" s="11" t="n"/>
-      <c r="R43" s="11" t="n"/>
-      <c r="S43" s="11" t="n"/>
-      <c r="T43" s="11" t="n"/>
-      <c r="U43" s="11" t="n"/>
-      <c r="V43" s="11" t="n"/>
+      <c r="P43" s="13" t="n"/>
+      <c r="Q43" s="13" t="n"/>
+      <c r="R43" s="13" t="n"/>
+      <c r="S43" s="13" t="n"/>
+      <c r="T43" s="13" t="n"/>
+      <c r="U43" s="13" t="n"/>
       <c r="W43" s="11" t="n"/>
       <c r="X43" s="11" t="n"/>
       <c r="Y43" s="11" t="n"/>
@@ -1936,6 +2436,18 @@
       <c r="AA43" s="11" t="n"/>
       <c r="AB43" s="11" t="n"/>
       <c r="AC43" s="11" t="n"/>
+      <c r="AD43" s="11" t="n"/>
+      <c r="AE43" s="11" t="n"/>
+      <c r="AF43" s="11" t="n"/>
+      <c r="AG43" s="11" t="n"/>
+      <c r="AH43" s="11" t="n"/>
+      <c r="AI43" s="11" t="n"/>
+      <c r="AJ43" s="11" t="n"/>
+      <c r="AK43" s="11" t="n"/>
+      <c r="AL43" s="11" t="n"/>
+      <c r="AM43" s="11" t="n"/>
+      <c r="AN43" s="11" t="n"/>
+      <c r="AO43" s="11" t="n"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="B44" s="9" t="inlineStr">
@@ -1956,12 +2468,12 @@
       <c r="M44" s="10" t="n"/>
       <c r="N44" s="10" t="n"/>
       <c r="O44" s="10" t="n"/>
-      <c r="Q44" s="11" t="n"/>
-      <c r="R44" s="11" t="n"/>
-      <c r="S44" s="11" t="n"/>
-      <c r="T44" s="11" t="n"/>
-      <c r="U44" s="11" t="n"/>
-      <c r="V44" s="11" t="n"/>
+      <c r="P44" s="10" t="n"/>
+      <c r="Q44" s="10" t="n"/>
+      <c r="R44" s="10" t="n"/>
+      <c r="S44" s="10" t="n"/>
+      <c r="T44" s="10" t="n"/>
+      <c r="U44" s="10" t="n"/>
       <c r="W44" s="11" t="n"/>
       <c r="X44" s="11" t="n"/>
       <c r="Y44" s="11" t="n"/>
@@ -1969,6 +2481,18 @@
       <c r="AA44" s="11" t="n"/>
       <c r="AB44" s="11" t="n"/>
       <c r="AC44" s="11" t="n"/>
+      <c r="AD44" s="11" t="n"/>
+      <c r="AE44" s="11" t="n"/>
+      <c r="AF44" s="11" t="n"/>
+      <c r="AG44" s="11" t="n"/>
+      <c r="AH44" s="11" t="n"/>
+      <c r="AI44" s="11" t="n"/>
+      <c r="AJ44" s="11" t="n"/>
+      <c r="AK44" s="11" t="n"/>
+      <c r="AL44" s="11" t="n"/>
+      <c r="AM44" s="11" t="n"/>
+      <c r="AN44" s="11" t="n"/>
+      <c r="AO44" s="11" t="n"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="B45" s="12" t="inlineStr">
@@ -1989,12 +2513,12 @@
       <c r="M45" s="13" t="n"/>
       <c r="N45" s="13" t="n"/>
       <c r="O45" s="13" t="n"/>
-      <c r="Q45" s="11" t="n"/>
-      <c r="R45" s="11" t="n"/>
-      <c r="S45" s="11" t="n"/>
-      <c r="T45" s="11" t="n"/>
-      <c r="U45" s="11" t="n"/>
-      <c r="V45" s="11" t="n"/>
+      <c r="P45" s="13" t="n"/>
+      <c r="Q45" s="13" t="n"/>
+      <c r="R45" s="13" t="n"/>
+      <c r="S45" s="13" t="n"/>
+      <c r="T45" s="13" t="n"/>
+      <c r="U45" s="13" t="n"/>
       <c r="W45" s="11" t="n"/>
       <c r="X45" s="11" t="n"/>
       <c r="Y45" s="11" t="n"/>
@@ -2002,6 +2526,18 @@
       <c r="AA45" s="11" t="n"/>
       <c r="AB45" s="11" t="n"/>
       <c r="AC45" s="11" t="n"/>
+      <c r="AD45" s="11" t="n"/>
+      <c r="AE45" s="11" t="n"/>
+      <c r="AF45" s="11" t="n"/>
+      <c r="AG45" s="11" t="n"/>
+      <c r="AH45" s="11" t="n"/>
+      <c r="AI45" s="11" t="n"/>
+      <c r="AJ45" s="11" t="n"/>
+      <c r="AK45" s="11" t="n"/>
+      <c r="AL45" s="11" t="n"/>
+      <c r="AM45" s="11" t="n"/>
+      <c r="AN45" s="11" t="n"/>
+      <c r="AO45" s="11" t="n"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="B46" s="12" t="inlineStr">
@@ -2022,12 +2558,12 @@
       <c r="M46" s="13" t="n"/>
       <c r="N46" s="13" t="n"/>
       <c r="O46" s="13" t="n"/>
-      <c r="Q46" s="11" t="n"/>
-      <c r="R46" s="11" t="n"/>
-      <c r="S46" s="11" t="n"/>
-      <c r="T46" s="11" t="n"/>
-      <c r="U46" s="11" t="n"/>
-      <c r="V46" s="11" t="n"/>
+      <c r="P46" s="13" t="n"/>
+      <c r="Q46" s="13" t="n"/>
+      <c r="R46" s="13" t="n"/>
+      <c r="S46" s="13" t="n"/>
+      <c r="T46" s="13" t="n"/>
+      <c r="U46" s="13" t="n"/>
       <c r="W46" s="11" t="n"/>
       <c r="X46" s="11" t="n"/>
       <c r="Y46" s="11" t="n"/>
@@ -2035,6 +2571,18 @@
       <c r="AA46" s="11" t="n"/>
       <c r="AB46" s="11" t="n"/>
       <c r="AC46" s="11" t="n"/>
+      <c r="AD46" s="11" t="n"/>
+      <c r="AE46" s="11" t="n"/>
+      <c r="AF46" s="11" t="n"/>
+      <c r="AG46" s="11" t="n"/>
+      <c r="AH46" s="11" t="n"/>
+      <c r="AI46" s="11" t="n"/>
+      <c r="AJ46" s="11" t="n"/>
+      <c r="AK46" s="11" t="n"/>
+      <c r="AL46" s="11" t="n"/>
+      <c r="AM46" s="11" t="n"/>
+      <c r="AN46" s="11" t="n"/>
+      <c r="AO46" s="11" t="n"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="B47" s="12" t="inlineStr">
@@ -2055,12 +2603,12 @@
       <c r="M47" s="13" t="n"/>
       <c r="N47" s="13" t="n"/>
       <c r="O47" s="13" t="n"/>
-      <c r="Q47" s="11" t="n"/>
-      <c r="R47" s="11" t="n"/>
-      <c r="S47" s="11" t="n"/>
-      <c r="T47" s="11" t="n"/>
-      <c r="U47" s="11" t="n"/>
-      <c r="V47" s="11" t="n"/>
+      <c r="P47" s="13" t="n"/>
+      <c r="Q47" s="13" t="n"/>
+      <c r="R47" s="13" t="n"/>
+      <c r="S47" s="13" t="n"/>
+      <c r="T47" s="13" t="n"/>
+      <c r="U47" s="13" t="n"/>
       <c r="W47" s="11" t="n"/>
       <c r="X47" s="11" t="n"/>
       <c r="Y47" s="11" t="n"/>
@@ -2068,6 +2616,18 @@
       <c r="AA47" s="11" t="n"/>
       <c r="AB47" s="11" t="n"/>
       <c r="AC47" s="11" t="n"/>
+      <c r="AD47" s="11" t="n"/>
+      <c r="AE47" s="11" t="n"/>
+      <c r="AF47" s="11" t="n"/>
+      <c r="AG47" s="11" t="n"/>
+      <c r="AH47" s="11" t="n"/>
+      <c r="AI47" s="11" t="n"/>
+      <c r="AJ47" s="11" t="n"/>
+      <c r="AK47" s="11" t="n"/>
+      <c r="AL47" s="11" t="n"/>
+      <c r="AM47" s="11" t="n"/>
+      <c r="AN47" s="11" t="n"/>
+      <c r="AO47" s="11" t="n"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="B48" s="12" t="inlineStr">
@@ -2088,12 +2648,12 @@
       <c r="M48" s="13" t="n"/>
       <c r="N48" s="13" t="n"/>
       <c r="O48" s="13" t="n"/>
-      <c r="Q48" s="11" t="n"/>
-      <c r="R48" s="11" t="n"/>
-      <c r="S48" s="11" t="n"/>
-      <c r="T48" s="11" t="n"/>
-      <c r="U48" s="11" t="n"/>
-      <c r="V48" s="11" t="n"/>
+      <c r="P48" s="13" t="n"/>
+      <c r="Q48" s="13" t="n"/>
+      <c r="R48" s="13" t="n"/>
+      <c r="S48" s="13" t="n"/>
+      <c r="T48" s="13" t="n"/>
+      <c r="U48" s="13" t="n"/>
       <c r="W48" s="11" t="n"/>
       <c r="X48" s="11" t="n"/>
       <c r="Y48" s="11" t="n"/>
@@ -2101,6 +2661,18 @@
       <c r="AA48" s="11" t="n"/>
       <c r="AB48" s="11" t="n"/>
       <c r="AC48" s="11" t="n"/>
+      <c r="AD48" s="11" t="n"/>
+      <c r="AE48" s="11" t="n"/>
+      <c r="AF48" s="11" t="n"/>
+      <c r="AG48" s="11" t="n"/>
+      <c r="AH48" s="11" t="n"/>
+      <c r="AI48" s="11" t="n"/>
+      <c r="AJ48" s="11" t="n"/>
+      <c r="AK48" s="11" t="n"/>
+      <c r="AL48" s="11" t="n"/>
+      <c r="AM48" s="11" t="n"/>
+      <c r="AN48" s="11" t="n"/>
+      <c r="AO48" s="11" t="n"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="B49" s="9" t="inlineStr">
@@ -2121,12 +2693,12 @@
       <c r="M49" s="10" t="n"/>
       <c r="N49" s="10" t="n"/>
       <c r="O49" s="10" t="n"/>
-      <c r="Q49" s="11" t="n"/>
-      <c r="R49" s="11" t="n"/>
-      <c r="S49" s="11" t="n"/>
-      <c r="T49" s="11" t="n"/>
-      <c r="U49" s="11" t="n"/>
-      <c r="V49" s="11" t="n"/>
+      <c r="P49" s="10" t="n"/>
+      <c r="Q49" s="10" t="n"/>
+      <c r="R49" s="10" t="n"/>
+      <c r="S49" s="10" t="n"/>
+      <c r="T49" s="10" t="n"/>
+      <c r="U49" s="10" t="n"/>
       <c r="W49" s="11" t="n"/>
       <c r="X49" s="11" t="n"/>
       <c r="Y49" s="11" t="n"/>
@@ -2134,6 +2706,18 @@
       <c r="AA49" s="11" t="n"/>
       <c r="AB49" s="11" t="n"/>
       <c r="AC49" s="11" t="n"/>
+      <c r="AD49" s="11" t="n"/>
+      <c r="AE49" s="11" t="n"/>
+      <c r="AF49" s="11" t="n"/>
+      <c r="AG49" s="11" t="n"/>
+      <c r="AH49" s="11" t="n"/>
+      <c r="AI49" s="11" t="n"/>
+      <c r="AJ49" s="11" t="n"/>
+      <c r="AK49" s="11" t="n"/>
+      <c r="AL49" s="11" t="n"/>
+      <c r="AM49" s="11" t="n"/>
+      <c r="AN49" s="11" t="n"/>
+      <c r="AO49" s="11" t="n"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="B50" s="12" t="inlineStr">
@@ -2154,12 +2738,12 @@
       <c r="M50" s="13" t="n"/>
       <c r="N50" s="13" t="n"/>
       <c r="O50" s="13" t="n"/>
-      <c r="Q50" s="11" t="n"/>
-      <c r="R50" s="11" t="n"/>
-      <c r="S50" s="11" t="n"/>
-      <c r="T50" s="11" t="n"/>
-      <c r="U50" s="11" t="n"/>
-      <c r="V50" s="11" t="n"/>
+      <c r="P50" s="13" t="n"/>
+      <c r="Q50" s="13" t="n"/>
+      <c r="R50" s="13" t="n"/>
+      <c r="S50" s="13" t="n"/>
+      <c r="T50" s="13" t="n"/>
+      <c r="U50" s="13" t="n"/>
       <c r="W50" s="11" t="n"/>
       <c r="X50" s="11" t="n"/>
       <c r="Y50" s="11" t="n"/>
@@ -2167,6 +2751,18 @@
       <c r="AA50" s="11" t="n"/>
       <c r="AB50" s="11" t="n"/>
       <c r="AC50" s="11" t="n"/>
+      <c r="AD50" s="11" t="n"/>
+      <c r="AE50" s="11" t="n"/>
+      <c r="AF50" s="11" t="n"/>
+      <c r="AG50" s="11" t="n"/>
+      <c r="AH50" s="11" t="n"/>
+      <c r="AI50" s="11" t="n"/>
+      <c r="AJ50" s="11" t="n"/>
+      <c r="AK50" s="11" t="n"/>
+      <c r="AL50" s="11" t="n"/>
+      <c r="AM50" s="11" t="n"/>
+      <c r="AN50" s="11" t="n"/>
+      <c r="AO50" s="11" t="n"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="B51" s="12" t="inlineStr">
@@ -2187,12 +2783,12 @@
       <c r="M51" s="13" t="n"/>
       <c r="N51" s="13" t="n"/>
       <c r="O51" s="13" t="n"/>
-      <c r="Q51" s="11" t="n"/>
-      <c r="R51" s="11" t="n"/>
-      <c r="S51" s="11" t="n"/>
-      <c r="T51" s="11" t="n"/>
-      <c r="U51" s="11" t="n"/>
-      <c r="V51" s="11" t="n"/>
+      <c r="P51" s="13" t="n"/>
+      <c r="Q51" s="13" t="n"/>
+      <c r="R51" s="13" t="n"/>
+      <c r="S51" s="13" t="n"/>
+      <c r="T51" s="13" t="n"/>
+      <c r="U51" s="13" t="n"/>
       <c r="W51" s="11" t="n"/>
       <c r="X51" s="11" t="n"/>
       <c r="Y51" s="11" t="n"/>
@@ -2200,6 +2796,18 @@
       <c r="AA51" s="11" t="n"/>
       <c r="AB51" s="11" t="n"/>
       <c r="AC51" s="11" t="n"/>
+      <c r="AD51" s="11" t="n"/>
+      <c r="AE51" s="11" t="n"/>
+      <c r="AF51" s="11" t="n"/>
+      <c r="AG51" s="11" t="n"/>
+      <c r="AH51" s="11" t="n"/>
+      <c r="AI51" s="11" t="n"/>
+      <c r="AJ51" s="11" t="n"/>
+      <c r="AK51" s="11" t="n"/>
+      <c r="AL51" s="11" t="n"/>
+      <c r="AM51" s="11" t="n"/>
+      <c r="AN51" s="11" t="n"/>
+      <c r="AO51" s="11" t="n"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="B52" s="12" t="inlineStr">
@@ -2220,12 +2828,12 @@
       <c r="M52" s="13" t="n"/>
       <c r="N52" s="13" t="n"/>
       <c r="O52" s="13" t="n"/>
-      <c r="Q52" s="11" t="n"/>
-      <c r="R52" s="11" t="n"/>
-      <c r="S52" s="11" t="n"/>
-      <c r="T52" s="11" t="n"/>
-      <c r="U52" s="11" t="n"/>
-      <c r="V52" s="11" t="n"/>
+      <c r="P52" s="13" t="n"/>
+      <c r="Q52" s="13" t="n"/>
+      <c r="R52" s="13" t="n"/>
+      <c r="S52" s="13" t="n"/>
+      <c r="T52" s="13" t="n"/>
+      <c r="U52" s="13" t="n"/>
       <c r="W52" s="11" t="n"/>
       <c r="X52" s="11" t="n"/>
       <c r="Y52" s="11" t="n"/>
@@ -2233,6 +2841,18 @@
       <c r="AA52" s="11" t="n"/>
       <c r="AB52" s="11" t="n"/>
       <c r="AC52" s="11" t="n"/>
+      <c r="AD52" s="11" t="n"/>
+      <c r="AE52" s="11" t="n"/>
+      <c r="AF52" s="11" t="n"/>
+      <c r="AG52" s="11" t="n"/>
+      <c r="AH52" s="11" t="n"/>
+      <c r="AI52" s="11" t="n"/>
+      <c r="AJ52" s="11" t="n"/>
+      <c r="AK52" s="11" t="n"/>
+      <c r="AL52" s="11" t="n"/>
+      <c r="AM52" s="11" t="n"/>
+      <c r="AN52" s="11" t="n"/>
+      <c r="AO52" s="11" t="n"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="B53" s="14" t="inlineStr">
@@ -2253,12 +2873,12 @@
       <c r="M53" s="13" t="n"/>
       <c r="N53" s="13" t="n"/>
       <c r="O53" s="13" t="n"/>
-      <c r="Q53" s="11" t="n"/>
-      <c r="R53" s="11" t="n"/>
-      <c r="S53" s="11" t="n"/>
-      <c r="T53" s="11" t="n"/>
-      <c r="U53" s="11" t="n"/>
-      <c r="V53" s="11" t="n"/>
+      <c r="P53" s="13" t="n"/>
+      <c r="Q53" s="13" t="n"/>
+      <c r="R53" s="13" t="n"/>
+      <c r="S53" s="13" t="n"/>
+      <c r="T53" s="13" t="n"/>
+      <c r="U53" s="13" t="n"/>
       <c r="W53" s="11" t="n"/>
       <c r="X53" s="11" t="n"/>
       <c r="Y53" s="11" t="n"/>
@@ -2266,6 +2886,18 @@
       <c r="AA53" s="11" t="n"/>
       <c r="AB53" s="11" t="n"/>
       <c r="AC53" s="11" t="n"/>
+      <c r="AD53" s="11" t="n"/>
+      <c r="AE53" s="11" t="n"/>
+      <c r="AF53" s="11" t="n"/>
+      <c r="AG53" s="11" t="n"/>
+      <c r="AH53" s="11" t="n"/>
+      <c r="AI53" s="11" t="n"/>
+      <c r="AJ53" s="11" t="n"/>
+      <c r="AK53" s="11" t="n"/>
+      <c r="AL53" s="11" t="n"/>
+      <c r="AM53" s="11" t="n"/>
+      <c r="AN53" s="11" t="n"/>
+      <c r="AO53" s="11" t="n"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="B54" s="12" t="inlineStr">
@@ -2286,12 +2918,12 @@
       <c r="M54" s="13" t="n"/>
       <c r="N54" s="13" t="n"/>
       <c r="O54" s="13" t="n"/>
-      <c r="Q54" s="11" t="n"/>
-      <c r="R54" s="11" t="n"/>
-      <c r="S54" s="11" t="n"/>
-      <c r="T54" s="11" t="n"/>
-      <c r="U54" s="11" t="n"/>
-      <c r="V54" s="11" t="n"/>
+      <c r="P54" s="13" t="n"/>
+      <c r="Q54" s="13" t="n"/>
+      <c r="R54" s="13" t="n"/>
+      <c r="S54" s="13" t="n"/>
+      <c r="T54" s="13" t="n"/>
+      <c r="U54" s="13" t="n"/>
       <c r="W54" s="11" t="n"/>
       <c r="X54" s="11" t="n"/>
       <c r="Y54" s="11" t="n"/>
@@ -2299,6 +2931,18 @@
       <c r="AA54" s="11" t="n"/>
       <c r="AB54" s="11" t="n"/>
       <c r="AC54" s="11" t="n"/>
+      <c r="AD54" s="11" t="n"/>
+      <c r="AE54" s="11" t="n"/>
+      <c r="AF54" s="11" t="n"/>
+      <c r="AG54" s="11" t="n"/>
+      <c r="AH54" s="11" t="n"/>
+      <c r="AI54" s="11" t="n"/>
+      <c r="AJ54" s="11" t="n"/>
+      <c r="AK54" s="11" t="n"/>
+      <c r="AL54" s="11" t="n"/>
+      <c r="AM54" s="11" t="n"/>
+      <c r="AN54" s="11" t="n"/>
+      <c r="AO54" s="11" t="n"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="B55" s="12" t="inlineStr">
@@ -2319,12 +2963,12 @@
       <c r="M55" s="13" t="n"/>
       <c r="N55" s="13" t="n"/>
       <c r="O55" s="13" t="n"/>
-      <c r="Q55" s="11" t="n"/>
-      <c r="R55" s="11" t="n"/>
-      <c r="S55" s="11" t="n"/>
-      <c r="T55" s="11" t="n"/>
-      <c r="U55" s="11" t="n"/>
-      <c r="V55" s="11" t="n"/>
+      <c r="P55" s="13" t="n"/>
+      <c r="Q55" s="13" t="n"/>
+      <c r="R55" s="13" t="n"/>
+      <c r="S55" s="13" t="n"/>
+      <c r="T55" s="13" t="n"/>
+      <c r="U55" s="13" t="n"/>
       <c r="W55" s="11" t="n"/>
       <c r="X55" s="11" t="n"/>
       <c r="Y55" s="11" t="n"/>
@@ -2332,6 +2976,18 @@
       <c r="AA55" s="11" t="n"/>
       <c r="AB55" s="11" t="n"/>
       <c r="AC55" s="11" t="n"/>
+      <c r="AD55" s="11" t="n"/>
+      <c r="AE55" s="11" t="n"/>
+      <c r="AF55" s="11" t="n"/>
+      <c r="AG55" s="11" t="n"/>
+      <c r="AH55" s="11" t="n"/>
+      <c r="AI55" s="11" t="n"/>
+      <c r="AJ55" s="11" t="n"/>
+      <c r="AK55" s="11" t="n"/>
+      <c r="AL55" s="11" t="n"/>
+      <c r="AM55" s="11" t="n"/>
+      <c r="AN55" s="11" t="n"/>
+      <c r="AO55" s="11" t="n"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="B56" s="9" t="inlineStr">
@@ -2352,12 +3008,12 @@
       <c r="M56" s="10" t="n"/>
       <c r="N56" s="10" t="n"/>
       <c r="O56" s="10" t="n"/>
-      <c r="Q56" s="11" t="n"/>
-      <c r="R56" s="11" t="n"/>
-      <c r="S56" s="11" t="n"/>
-      <c r="T56" s="11" t="n"/>
-      <c r="U56" s="11" t="n"/>
-      <c r="V56" s="11" t="n"/>
+      <c r="P56" s="10" t="n"/>
+      <c r="Q56" s="10" t="n"/>
+      <c r="R56" s="10" t="n"/>
+      <c r="S56" s="10" t="n"/>
+      <c r="T56" s="10" t="n"/>
+      <c r="U56" s="10" t="n"/>
       <c r="W56" s="11" t="n"/>
       <c r="X56" s="11" t="n"/>
       <c r="Y56" s="11" t="n"/>
@@ -2365,6 +3021,18 @@
       <c r="AA56" s="11" t="n"/>
       <c r="AB56" s="11" t="n"/>
       <c r="AC56" s="11" t="n"/>
+      <c r="AD56" s="11" t="n"/>
+      <c r="AE56" s="11" t="n"/>
+      <c r="AF56" s="11" t="n"/>
+      <c r="AG56" s="11" t="n"/>
+      <c r="AH56" s="11" t="n"/>
+      <c r="AI56" s="11" t="n"/>
+      <c r="AJ56" s="11" t="n"/>
+      <c r="AK56" s="11" t="n"/>
+      <c r="AL56" s="11" t="n"/>
+      <c r="AM56" s="11" t="n"/>
+      <c r="AN56" s="11" t="n"/>
+      <c r="AO56" s="11" t="n"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="B57" s="9" t="inlineStr">
@@ -2385,12 +3053,12 @@
       <c r="M57" s="10" t="n"/>
       <c r="N57" s="10" t="n"/>
       <c r="O57" s="10" t="n"/>
-      <c r="Q57" s="11" t="n"/>
-      <c r="R57" s="11" t="n"/>
-      <c r="S57" s="11" t="n"/>
-      <c r="T57" s="11" t="n"/>
-      <c r="U57" s="11" t="n"/>
-      <c r="V57" s="11" t="n"/>
+      <c r="P57" s="10" t="n"/>
+      <c r="Q57" s="10" t="n"/>
+      <c r="R57" s="10" t="n"/>
+      <c r="S57" s="10" t="n"/>
+      <c r="T57" s="10" t="n"/>
+      <c r="U57" s="10" t="n"/>
       <c r="W57" s="11" t="n"/>
       <c r="X57" s="11" t="n"/>
       <c r="Y57" s="11" t="n"/>
@@ -2398,6 +3066,18 @@
       <c r="AA57" s="11" t="n"/>
       <c r="AB57" s="11" t="n"/>
       <c r="AC57" s="11" t="n"/>
+      <c r="AD57" s="11" t="n"/>
+      <c r="AE57" s="11" t="n"/>
+      <c r="AF57" s="11" t="n"/>
+      <c r="AG57" s="11" t="n"/>
+      <c r="AH57" s="11" t="n"/>
+      <c r="AI57" s="11" t="n"/>
+      <c r="AJ57" s="11" t="n"/>
+      <c r="AK57" s="11" t="n"/>
+      <c r="AL57" s="11" t="n"/>
+      <c r="AM57" s="11" t="n"/>
+      <c r="AN57" s="11" t="n"/>
+      <c r="AO57" s="11" t="n"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="B58" s="12" t="inlineStr">
@@ -2418,12 +3098,12 @@
       <c r="M58" s="13" t="n"/>
       <c r="N58" s="13" t="n"/>
       <c r="O58" s="13" t="n"/>
-      <c r="Q58" s="11" t="n"/>
-      <c r="R58" s="11" t="n"/>
-      <c r="S58" s="11" t="n"/>
-      <c r="T58" s="11" t="n"/>
-      <c r="U58" s="11" t="n"/>
-      <c r="V58" s="11" t="n"/>
+      <c r="P58" s="13" t="n"/>
+      <c r="Q58" s="13" t="n"/>
+      <c r="R58" s="13" t="n"/>
+      <c r="S58" s="13" t="n"/>
+      <c r="T58" s="13" t="n"/>
+      <c r="U58" s="13" t="n"/>
       <c r="W58" s="11" t="n"/>
       <c r="X58" s="11" t="n"/>
       <c r="Y58" s="11" t="n"/>
@@ -2431,6 +3111,18 @@
       <c r="AA58" s="11" t="n"/>
       <c r="AB58" s="11" t="n"/>
       <c r="AC58" s="11" t="n"/>
+      <c r="AD58" s="11" t="n"/>
+      <c r="AE58" s="11" t="n"/>
+      <c r="AF58" s="11" t="n"/>
+      <c r="AG58" s="11" t="n"/>
+      <c r="AH58" s="11" t="n"/>
+      <c r="AI58" s="11" t="n"/>
+      <c r="AJ58" s="11" t="n"/>
+      <c r="AK58" s="11" t="n"/>
+      <c r="AL58" s="11" t="n"/>
+      <c r="AM58" s="11" t="n"/>
+      <c r="AN58" s="11" t="n"/>
+      <c r="AO58" s="11" t="n"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="B59" s="9" t="inlineStr">
@@ -2451,12 +3143,12 @@
       <c r="M59" s="10" t="n"/>
       <c r="N59" s="10" t="n"/>
       <c r="O59" s="10" t="n"/>
-      <c r="Q59" s="11" t="n"/>
-      <c r="R59" s="11" t="n"/>
-      <c r="S59" s="11" t="n"/>
-      <c r="T59" s="11" t="n"/>
-      <c r="U59" s="11" t="n"/>
-      <c r="V59" s="11" t="n"/>
+      <c r="P59" s="10" t="n"/>
+      <c r="Q59" s="10" t="n"/>
+      <c r="R59" s="10" t="n"/>
+      <c r="S59" s="10" t="n"/>
+      <c r="T59" s="10" t="n"/>
+      <c r="U59" s="10" t="n"/>
       <c r="W59" s="11" t="n"/>
       <c r="X59" s="11" t="n"/>
       <c r="Y59" s="11" t="n"/>
@@ -2464,6 +3156,18 @@
       <c r="AA59" s="11" t="n"/>
       <c r="AB59" s="11" t="n"/>
       <c r="AC59" s="11" t="n"/>
+      <c r="AD59" s="11" t="n"/>
+      <c r="AE59" s="11" t="n"/>
+      <c r="AF59" s="11" t="n"/>
+      <c r="AG59" s="11" t="n"/>
+      <c r="AH59" s="11" t="n"/>
+      <c r="AI59" s="11" t="n"/>
+      <c r="AJ59" s="11" t="n"/>
+      <c r="AK59" s="11" t="n"/>
+      <c r="AL59" s="11" t="n"/>
+      <c r="AM59" s="11" t="n"/>
+      <c r="AN59" s="11" t="n"/>
+      <c r="AO59" s="11" t="n"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="B60" s="12" t="inlineStr">
@@ -2484,12 +3188,12 @@
       <c r="M60" s="13" t="n"/>
       <c r="N60" s="13" t="n"/>
       <c r="O60" s="13" t="n"/>
-      <c r="Q60" s="11" t="n"/>
-      <c r="R60" s="11" t="n"/>
-      <c r="S60" s="11" t="n"/>
-      <c r="T60" s="11" t="n"/>
-      <c r="U60" s="11" t="n"/>
-      <c r="V60" s="11" t="n"/>
+      <c r="P60" s="13" t="n"/>
+      <c r="Q60" s="13" t="n"/>
+      <c r="R60" s="13" t="n"/>
+      <c r="S60" s="13" t="n"/>
+      <c r="T60" s="13" t="n"/>
+      <c r="U60" s="13" t="n"/>
       <c r="W60" s="11" t="n"/>
       <c r="X60" s="11" t="n"/>
       <c r="Y60" s="11" t="n"/>
@@ -2497,6 +3201,18 @@
       <c r="AA60" s="11" t="n"/>
       <c r="AB60" s="11" t="n"/>
       <c r="AC60" s="11" t="n"/>
+      <c r="AD60" s="11" t="n"/>
+      <c r="AE60" s="11" t="n"/>
+      <c r="AF60" s="11" t="n"/>
+      <c r="AG60" s="11" t="n"/>
+      <c r="AH60" s="11" t="n"/>
+      <c r="AI60" s="11" t="n"/>
+      <c r="AJ60" s="11" t="n"/>
+      <c r="AK60" s="11" t="n"/>
+      <c r="AL60" s="11" t="n"/>
+      <c r="AM60" s="11" t="n"/>
+      <c r="AN60" s="11" t="n"/>
+      <c r="AO60" s="11" t="n"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="B61" s="9" t="inlineStr">
@@ -2517,12 +3233,12 @@
       <c r="M61" s="10" t="n"/>
       <c r="N61" s="10" t="n"/>
       <c r="O61" s="10" t="n"/>
-      <c r="Q61" s="11" t="n"/>
-      <c r="R61" s="11" t="n"/>
-      <c r="S61" s="11" t="n"/>
-      <c r="T61" s="11" t="n"/>
-      <c r="U61" s="11" t="n"/>
-      <c r="V61" s="11" t="n"/>
+      <c r="P61" s="10" t="n"/>
+      <c r="Q61" s="10" t="n"/>
+      <c r="R61" s="10" t="n"/>
+      <c r="S61" s="10" t="n"/>
+      <c r="T61" s="10" t="n"/>
+      <c r="U61" s="10" t="n"/>
       <c r="W61" s="11" t="n"/>
       <c r="X61" s="11" t="n"/>
       <c r="Y61" s="11" t="n"/>
@@ -2530,6 +3246,18 @@
       <c r="AA61" s="11" t="n"/>
       <c r="AB61" s="11" t="n"/>
       <c r="AC61" s="11" t="n"/>
+      <c r="AD61" s="11" t="n"/>
+      <c r="AE61" s="11" t="n"/>
+      <c r="AF61" s="11" t="n"/>
+      <c r="AG61" s="11" t="n"/>
+      <c r="AH61" s="11" t="n"/>
+      <c r="AI61" s="11" t="n"/>
+      <c r="AJ61" s="11" t="n"/>
+      <c r="AK61" s="11" t="n"/>
+      <c r="AL61" s="11" t="n"/>
+      <c r="AM61" s="11" t="n"/>
+      <c r="AN61" s="11" t="n"/>
+      <c r="AO61" s="11" t="n"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="B64" s="5" t="inlineStr">
@@ -2542,7 +3270,7 @@
           <t>20-39 Segment - Over Time Period</t>
         </is>
       </c>
-      <c r="Q64" s="6" t="inlineStr">
+      <c r="W64" s="6" t="inlineStr">
         <is>
           <t>20-39 Segment - Over Time Period - Difference</t>
         </is>
@@ -2619,69 +3347,129 @@
           <t>SPTx2</t>
         </is>
       </c>
+      <c r="P65" s="8" t="inlineStr">
+        <is>
+          <t>1-star Pack</t>
+        </is>
+      </c>
       <c r="Q65" s="8" t="inlineStr">
         <is>
+          <t>2-star Pack</t>
+        </is>
+      </c>
+      <c r="R65" s="8" t="inlineStr">
+        <is>
+          <t>3-star Pack</t>
+        </is>
+      </c>
+      <c r="S65" s="8" t="inlineStr">
+        <is>
+          <t>4-star Pack</t>
+        </is>
+      </c>
+      <c r="T65" s="8" t="inlineStr">
+        <is>
+          <t>5-star Pack</t>
+        </is>
+      </c>
+      <c r="U65" s="8" t="inlineStr">
+        <is>
+          <t>6-star Pack</t>
+        </is>
+      </c>
+      <c r="W65" s="8" t="inlineStr">
+        <is>
           <t>HC</t>
         </is>
       </c>
-      <c r="R65" s="8" t="inlineStr">
+      <c r="X65" s="8" t="inlineStr">
         <is>
           <t>Slingshot</t>
         </is>
       </c>
-      <c r="S65" s="8" t="inlineStr">
+      <c r="Y65" s="8" t="inlineStr">
         <is>
           <t>Shuffle</t>
         </is>
       </c>
-      <c r="T65" s="8" t="inlineStr">
+      <c r="Z65" s="8" t="inlineStr">
         <is>
           <t>Comet</t>
         </is>
       </c>
-      <c r="U65" s="8" t="inlineStr">
+      <c r="AA65" s="8" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="V65" s="8" t="inlineStr">
+      <c r="AB65" s="8" t="inlineStr">
         <is>
           <t>Chuck</t>
         </is>
       </c>
-      <c r="W65" s="8" t="inlineStr">
+      <c r="AC65" s="8" t="inlineStr">
         <is>
           <t>Bomb</t>
         </is>
       </c>
-      <c r="X65" s="8" t="inlineStr">
+      <c r="AD65" s="8" t="inlineStr">
         <is>
           <t>UL Bomb</t>
         </is>
       </c>
-      <c r="Y65" s="8" t="inlineStr">
+      <c r="AE65" s="8" t="inlineStr">
         <is>
           <t>UL Chuck</t>
         </is>
       </c>
-      <c r="Z65" s="8" t="inlineStr">
+      <c r="AF65" s="8" t="inlineStr">
         <is>
           <t>UL Red</t>
         </is>
       </c>
-      <c r="AA65" s="8" t="inlineStr">
+      <c r="AG65" s="8" t="inlineStr">
         <is>
           <t>Unlimited Lives</t>
         </is>
       </c>
-      <c r="AB65" s="8" t="inlineStr">
+      <c r="AH65" s="8" t="inlineStr">
         <is>
           <t>SPT</t>
         </is>
       </c>
-      <c r="AC65" s="8" t="inlineStr">
+      <c r="AI65" s="8" t="inlineStr">
         <is>
           <t>SPTx2</t>
+        </is>
+      </c>
+      <c r="AJ65" s="8" t="inlineStr">
+        <is>
+          <t>1-star Pack</t>
+        </is>
+      </c>
+      <c r="AK65" s="8" t="inlineStr">
+        <is>
+          <t>2-star Pack</t>
+        </is>
+      </c>
+      <c r="AL65" s="8" t="inlineStr">
+        <is>
+          <t>3-star Pack</t>
+        </is>
+      </c>
+      <c r="AM65" s="8" t="inlineStr">
+        <is>
+          <t>4-star Pack</t>
+        </is>
+      </c>
+      <c r="AN65" s="8" t="inlineStr">
+        <is>
+          <t>5-star Pack</t>
+        </is>
+      </c>
+      <c r="AO65" s="8" t="inlineStr">
+        <is>
+          <t>6-star Pack</t>
         </is>
       </c>
     </row>
@@ -2707,22 +3495,34 @@
       <c r="M66" s="10" t="n"/>
       <c r="N66" s="10" t="n"/>
       <c r="O66" s="10" t="n"/>
-      <c r="Q66" s="11">
+      <c r="P66" s="10" t="n"/>
+      <c r="Q66" s="10" t="n"/>
+      <c r="R66" s="10" t="n"/>
+      <c r="S66" s="10" t="n"/>
+      <c r="T66" s="10" t="n"/>
+      <c r="U66" s="10" t="n"/>
+      <c r="W66" s="11">
         <f>LET(payer, $C$3, segment, $B$64, ECOGAINS_DIFF(payer, segment, sim_refresh!$A$1))</f>
         <v/>
       </c>
-      <c r="R66" s="11" t="n"/>
-      <c r="S66" s="11" t="n"/>
-      <c r="T66" s="11" t="n"/>
-      <c r="U66" s="11" t="n"/>
-      <c r="V66" s="11" t="n"/>
-      <c r="W66" s="11" t="n"/>
       <c r="X66" s="11" t="n"/>
       <c r="Y66" s="11" t="n"/>
       <c r="Z66" s="11" t="n"/>
       <c r="AA66" s="11" t="n"/>
       <c r="AB66" s="11" t="n"/>
       <c r="AC66" s="11" t="n"/>
+      <c r="AD66" s="11" t="n"/>
+      <c r="AE66" s="11" t="n"/>
+      <c r="AF66" s="11" t="n"/>
+      <c r="AG66" s="11" t="n"/>
+      <c r="AH66" s="11" t="n"/>
+      <c r="AI66" s="11" t="n"/>
+      <c r="AJ66" s="11" t="n"/>
+      <c r="AK66" s="11" t="n"/>
+      <c r="AL66" s="11" t="n"/>
+      <c r="AM66" s="11" t="n"/>
+      <c r="AN66" s="11" t="n"/>
+      <c r="AO66" s="11" t="n"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="B67" s="12" t="inlineStr">
@@ -2743,12 +3543,12 @@
       <c r="M67" s="13" t="n"/>
       <c r="N67" s="13" t="n"/>
       <c r="O67" s="13" t="n"/>
-      <c r="Q67" s="11" t="n"/>
-      <c r="R67" s="11" t="n"/>
-      <c r="S67" s="11" t="n"/>
-      <c r="T67" s="11" t="n"/>
-      <c r="U67" s="11" t="n"/>
-      <c r="V67" s="11" t="n"/>
+      <c r="P67" s="13" t="n"/>
+      <c r="Q67" s="13" t="n"/>
+      <c r="R67" s="13" t="n"/>
+      <c r="S67" s="13" t="n"/>
+      <c r="T67" s="13" t="n"/>
+      <c r="U67" s="13" t="n"/>
       <c r="W67" s="11" t="n"/>
       <c r="X67" s="11" t="n"/>
       <c r="Y67" s="11" t="n"/>
@@ -2756,6 +3556,18 @@
       <c r="AA67" s="11" t="n"/>
       <c r="AB67" s="11" t="n"/>
       <c r="AC67" s="11" t="n"/>
+      <c r="AD67" s="11" t="n"/>
+      <c r="AE67" s="11" t="n"/>
+      <c r="AF67" s="11" t="n"/>
+      <c r="AG67" s="11" t="n"/>
+      <c r="AH67" s="11" t="n"/>
+      <c r="AI67" s="11" t="n"/>
+      <c r="AJ67" s="11" t="n"/>
+      <c r="AK67" s="11" t="n"/>
+      <c r="AL67" s="11" t="n"/>
+      <c r="AM67" s="11" t="n"/>
+      <c r="AN67" s="11" t="n"/>
+      <c r="AO67" s="11" t="n"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="B68" s="12" t="inlineStr">
@@ -2776,12 +3588,12 @@
       <c r="M68" s="13" t="n"/>
       <c r="N68" s="13" t="n"/>
       <c r="O68" s="13" t="n"/>
-      <c r="Q68" s="11" t="n"/>
-      <c r="R68" s="11" t="n"/>
-      <c r="S68" s="11" t="n"/>
-      <c r="T68" s="11" t="n"/>
-      <c r="U68" s="11" t="n"/>
-      <c r="V68" s="11" t="n"/>
+      <c r="P68" s="13" t="n"/>
+      <c r="Q68" s="13" t="n"/>
+      <c r="R68" s="13" t="n"/>
+      <c r="S68" s="13" t="n"/>
+      <c r="T68" s="13" t="n"/>
+      <c r="U68" s="13" t="n"/>
       <c r="W68" s="11" t="n"/>
       <c r="X68" s="11" t="n"/>
       <c r="Y68" s="11" t="n"/>
@@ -2789,6 +3601,18 @@
       <c r="AA68" s="11" t="n"/>
       <c r="AB68" s="11" t="n"/>
       <c r="AC68" s="11" t="n"/>
+      <c r="AD68" s="11" t="n"/>
+      <c r="AE68" s="11" t="n"/>
+      <c r="AF68" s="11" t="n"/>
+      <c r="AG68" s="11" t="n"/>
+      <c r="AH68" s="11" t="n"/>
+      <c r="AI68" s="11" t="n"/>
+      <c r="AJ68" s="11" t="n"/>
+      <c r="AK68" s="11" t="n"/>
+      <c r="AL68" s="11" t="n"/>
+      <c r="AM68" s="11" t="n"/>
+      <c r="AN68" s="11" t="n"/>
+      <c r="AO68" s="11" t="n"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="B69" s="12" t="inlineStr">
@@ -2809,12 +3633,12 @@
       <c r="M69" s="13" t="n"/>
       <c r="N69" s="13" t="n"/>
       <c r="O69" s="13" t="n"/>
-      <c r="Q69" s="11" t="n"/>
-      <c r="R69" s="11" t="n"/>
-      <c r="S69" s="11" t="n"/>
-      <c r="T69" s="11" t="n"/>
-      <c r="U69" s="11" t="n"/>
-      <c r="V69" s="11" t="n"/>
+      <c r="P69" s="13" t="n"/>
+      <c r="Q69" s="13" t="n"/>
+      <c r="R69" s="13" t="n"/>
+      <c r="S69" s="13" t="n"/>
+      <c r="T69" s="13" t="n"/>
+      <c r="U69" s="13" t="n"/>
       <c r="W69" s="11" t="n"/>
       <c r="X69" s="11" t="n"/>
       <c r="Y69" s="11" t="n"/>
@@ -2822,6 +3646,18 @@
       <c r="AA69" s="11" t="n"/>
       <c r="AB69" s="11" t="n"/>
       <c r="AC69" s="11" t="n"/>
+      <c r="AD69" s="11" t="n"/>
+      <c r="AE69" s="11" t="n"/>
+      <c r="AF69" s="11" t="n"/>
+      <c r="AG69" s="11" t="n"/>
+      <c r="AH69" s="11" t="n"/>
+      <c r="AI69" s="11" t="n"/>
+      <c r="AJ69" s="11" t="n"/>
+      <c r="AK69" s="11" t="n"/>
+      <c r="AL69" s="11" t="n"/>
+      <c r="AM69" s="11" t="n"/>
+      <c r="AN69" s="11" t="n"/>
+      <c r="AO69" s="11" t="n"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="B70" s="9" t="inlineStr">
@@ -2842,12 +3678,12 @@
       <c r="M70" s="10" t="n"/>
       <c r="N70" s="10" t="n"/>
       <c r="O70" s="10" t="n"/>
-      <c r="Q70" s="11" t="n"/>
-      <c r="R70" s="11" t="n"/>
-      <c r="S70" s="11" t="n"/>
-      <c r="T70" s="11" t="n"/>
-      <c r="U70" s="11" t="n"/>
-      <c r="V70" s="11" t="n"/>
+      <c r="P70" s="10" t="n"/>
+      <c r="Q70" s="10" t="n"/>
+      <c r="R70" s="10" t="n"/>
+      <c r="S70" s="10" t="n"/>
+      <c r="T70" s="10" t="n"/>
+      <c r="U70" s="10" t="n"/>
       <c r="W70" s="11" t="n"/>
       <c r="X70" s="11" t="n"/>
       <c r="Y70" s="11" t="n"/>
@@ -2855,6 +3691,18 @@
       <c r="AA70" s="11" t="n"/>
       <c r="AB70" s="11" t="n"/>
       <c r="AC70" s="11" t="n"/>
+      <c r="AD70" s="11" t="n"/>
+      <c r="AE70" s="11" t="n"/>
+      <c r="AF70" s="11" t="n"/>
+      <c r="AG70" s="11" t="n"/>
+      <c r="AH70" s="11" t="n"/>
+      <c r="AI70" s="11" t="n"/>
+      <c r="AJ70" s="11" t="n"/>
+      <c r="AK70" s="11" t="n"/>
+      <c r="AL70" s="11" t="n"/>
+      <c r="AM70" s="11" t="n"/>
+      <c r="AN70" s="11" t="n"/>
+      <c r="AO70" s="11" t="n"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="B71" s="14" t="inlineStr">
@@ -2875,12 +3723,12 @@
       <c r="M71" s="13" t="n"/>
       <c r="N71" s="13" t="n"/>
       <c r="O71" s="13" t="n"/>
-      <c r="Q71" s="11" t="n"/>
-      <c r="R71" s="11" t="n"/>
-      <c r="S71" s="11" t="n"/>
-      <c r="T71" s="11" t="n"/>
-      <c r="U71" s="11" t="n"/>
-      <c r="V71" s="11" t="n"/>
+      <c r="P71" s="13" t="n"/>
+      <c r="Q71" s="13" t="n"/>
+      <c r="R71" s="13" t="n"/>
+      <c r="S71" s="13" t="n"/>
+      <c r="T71" s="13" t="n"/>
+      <c r="U71" s="13" t="n"/>
       <c r="W71" s="11" t="n"/>
       <c r="X71" s="11" t="n"/>
       <c r="Y71" s="11" t="n"/>
@@ -2888,6 +3736,18 @@
       <c r="AA71" s="11" t="n"/>
       <c r="AB71" s="11" t="n"/>
       <c r="AC71" s="11" t="n"/>
+      <c r="AD71" s="11" t="n"/>
+      <c r="AE71" s="11" t="n"/>
+      <c r="AF71" s="11" t="n"/>
+      <c r="AG71" s="11" t="n"/>
+      <c r="AH71" s="11" t="n"/>
+      <c r="AI71" s="11" t="n"/>
+      <c r="AJ71" s="11" t="n"/>
+      <c r="AK71" s="11" t="n"/>
+      <c r="AL71" s="11" t="n"/>
+      <c r="AM71" s="11" t="n"/>
+      <c r="AN71" s="11" t="n"/>
+      <c r="AO71" s="11" t="n"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="B72" s="14" t="inlineStr">
@@ -2908,12 +3768,12 @@
       <c r="M72" s="13" t="n"/>
       <c r="N72" s="13" t="n"/>
       <c r="O72" s="13" t="n"/>
-      <c r="Q72" s="11" t="n"/>
-      <c r="R72" s="11" t="n"/>
-      <c r="S72" s="11" t="n"/>
-      <c r="T72" s="11" t="n"/>
-      <c r="U72" s="11" t="n"/>
-      <c r="V72" s="11" t="n"/>
+      <c r="P72" s="13" t="n"/>
+      <c r="Q72" s="13" t="n"/>
+      <c r="R72" s="13" t="n"/>
+      <c r="S72" s="13" t="n"/>
+      <c r="T72" s="13" t="n"/>
+      <c r="U72" s="13" t="n"/>
       <c r="W72" s="11" t="n"/>
       <c r="X72" s="11" t="n"/>
       <c r="Y72" s="11" t="n"/>
@@ -2921,6 +3781,18 @@
       <c r="AA72" s="11" t="n"/>
       <c r="AB72" s="11" t="n"/>
       <c r="AC72" s="11" t="n"/>
+      <c r="AD72" s="11" t="n"/>
+      <c r="AE72" s="11" t="n"/>
+      <c r="AF72" s="11" t="n"/>
+      <c r="AG72" s="11" t="n"/>
+      <c r="AH72" s="11" t="n"/>
+      <c r="AI72" s="11" t="n"/>
+      <c r="AJ72" s="11" t="n"/>
+      <c r="AK72" s="11" t="n"/>
+      <c r="AL72" s="11" t="n"/>
+      <c r="AM72" s="11" t="n"/>
+      <c r="AN72" s="11" t="n"/>
+      <c r="AO72" s="11" t="n"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="B73" s="9" t="inlineStr">
@@ -2941,12 +3813,12 @@
       <c r="M73" s="10" t="n"/>
       <c r="N73" s="10" t="n"/>
       <c r="O73" s="10" t="n"/>
-      <c r="Q73" s="11" t="n"/>
-      <c r="R73" s="11" t="n"/>
-      <c r="S73" s="11" t="n"/>
-      <c r="T73" s="11" t="n"/>
-      <c r="U73" s="11" t="n"/>
-      <c r="V73" s="11" t="n"/>
+      <c r="P73" s="10" t="n"/>
+      <c r="Q73" s="10" t="n"/>
+      <c r="R73" s="10" t="n"/>
+      <c r="S73" s="10" t="n"/>
+      <c r="T73" s="10" t="n"/>
+      <c r="U73" s="10" t="n"/>
       <c r="W73" s="11" t="n"/>
       <c r="X73" s="11" t="n"/>
       <c r="Y73" s="11" t="n"/>
@@ -2954,6 +3826,18 @@
       <c r="AA73" s="11" t="n"/>
       <c r="AB73" s="11" t="n"/>
       <c r="AC73" s="11" t="n"/>
+      <c r="AD73" s="11" t="n"/>
+      <c r="AE73" s="11" t="n"/>
+      <c r="AF73" s="11" t="n"/>
+      <c r="AG73" s="11" t="n"/>
+      <c r="AH73" s="11" t="n"/>
+      <c r="AI73" s="11" t="n"/>
+      <c r="AJ73" s="11" t="n"/>
+      <c r="AK73" s="11" t="n"/>
+      <c r="AL73" s="11" t="n"/>
+      <c r="AM73" s="11" t="n"/>
+      <c r="AN73" s="11" t="n"/>
+      <c r="AO73" s="11" t="n"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="B74" s="12" t="inlineStr">
@@ -2974,12 +3858,12 @@
       <c r="M74" s="13" t="n"/>
       <c r="N74" s="13" t="n"/>
       <c r="O74" s="13" t="n"/>
-      <c r="Q74" s="11" t="n"/>
-      <c r="R74" s="11" t="n"/>
-      <c r="S74" s="11" t="n"/>
-      <c r="T74" s="11" t="n"/>
-      <c r="U74" s="11" t="n"/>
-      <c r="V74" s="11" t="n"/>
+      <c r="P74" s="13" t="n"/>
+      <c r="Q74" s="13" t="n"/>
+      <c r="R74" s="13" t="n"/>
+      <c r="S74" s="13" t="n"/>
+      <c r="T74" s="13" t="n"/>
+      <c r="U74" s="13" t="n"/>
       <c r="W74" s="11" t="n"/>
       <c r="X74" s="11" t="n"/>
       <c r="Y74" s="11" t="n"/>
@@ -2987,6 +3871,18 @@
       <c r="AA74" s="11" t="n"/>
       <c r="AB74" s="11" t="n"/>
       <c r="AC74" s="11" t="n"/>
+      <c r="AD74" s="11" t="n"/>
+      <c r="AE74" s="11" t="n"/>
+      <c r="AF74" s="11" t="n"/>
+      <c r="AG74" s="11" t="n"/>
+      <c r="AH74" s="11" t="n"/>
+      <c r="AI74" s="11" t="n"/>
+      <c r="AJ74" s="11" t="n"/>
+      <c r="AK74" s="11" t="n"/>
+      <c r="AL74" s="11" t="n"/>
+      <c r="AM74" s="11" t="n"/>
+      <c r="AN74" s="11" t="n"/>
+      <c r="AO74" s="11" t="n"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="B75" s="12" t="inlineStr">
@@ -3007,12 +3903,12 @@
       <c r="M75" s="13" t="n"/>
       <c r="N75" s="13" t="n"/>
       <c r="O75" s="13" t="n"/>
-      <c r="Q75" s="11" t="n"/>
-      <c r="R75" s="11" t="n"/>
-      <c r="S75" s="11" t="n"/>
-      <c r="T75" s="11" t="n"/>
-      <c r="U75" s="11" t="n"/>
-      <c r="V75" s="11" t="n"/>
+      <c r="P75" s="13" t="n"/>
+      <c r="Q75" s="13" t="n"/>
+      <c r="R75" s="13" t="n"/>
+      <c r="S75" s="13" t="n"/>
+      <c r="T75" s="13" t="n"/>
+      <c r="U75" s="13" t="n"/>
       <c r="W75" s="11" t="n"/>
       <c r="X75" s="11" t="n"/>
       <c r="Y75" s="11" t="n"/>
@@ -3020,6 +3916,18 @@
       <c r="AA75" s="11" t="n"/>
       <c r="AB75" s="11" t="n"/>
       <c r="AC75" s="11" t="n"/>
+      <c r="AD75" s="11" t="n"/>
+      <c r="AE75" s="11" t="n"/>
+      <c r="AF75" s="11" t="n"/>
+      <c r="AG75" s="11" t="n"/>
+      <c r="AH75" s="11" t="n"/>
+      <c r="AI75" s="11" t="n"/>
+      <c r="AJ75" s="11" t="n"/>
+      <c r="AK75" s="11" t="n"/>
+      <c r="AL75" s="11" t="n"/>
+      <c r="AM75" s="11" t="n"/>
+      <c r="AN75" s="11" t="n"/>
+      <c r="AO75" s="11" t="n"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="B76" s="12" t="inlineStr">
@@ -3040,12 +3948,12 @@
       <c r="M76" s="13" t="n"/>
       <c r="N76" s="13" t="n"/>
       <c r="O76" s="13" t="n"/>
-      <c r="Q76" s="11" t="n"/>
-      <c r="R76" s="11" t="n"/>
-      <c r="S76" s="11" t="n"/>
-      <c r="T76" s="11" t="n"/>
-      <c r="U76" s="11" t="n"/>
-      <c r="V76" s="11" t="n"/>
+      <c r="P76" s="13" t="n"/>
+      <c r="Q76" s="13" t="n"/>
+      <c r="R76" s="13" t="n"/>
+      <c r="S76" s="13" t="n"/>
+      <c r="T76" s="13" t="n"/>
+      <c r="U76" s="13" t="n"/>
       <c r="W76" s="11" t="n"/>
       <c r="X76" s="11" t="n"/>
       <c r="Y76" s="11" t="n"/>
@@ -3053,6 +3961,18 @@
       <c r="AA76" s="11" t="n"/>
       <c r="AB76" s="11" t="n"/>
       <c r="AC76" s="11" t="n"/>
+      <c r="AD76" s="11" t="n"/>
+      <c r="AE76" s="11" t="n"/>
+      <c r="AF76" s="11" t="n"/>
+      <c r="AG76" s="11" t="n"/>
+      <c r="AH76" s="11" t="n"/>
+      <c r="AI76" s="11" t="n"/>
+      <c r="AJ76" s="11" t="n"/>
+      <c r="AK76" s="11" t="n"/>
+      <c r="AL76" s="11" t="n"/>
+      <c r="AM76" s="11" t="n"/>
+      <c r="AN76" s="11" t="n"/>
+      <c r="AO76" s="11" t="n"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="B77" s="12" t="inlineStr">
@@ -3073,12 +3993,12 @@
       <c r="M77" s="13" t="n"/>
       <c r="N77" s="13" t="n"/>
       <c r="O77" s="13" t="n"/>
-      <c r="Q77" s="11" t="n"/>
-      <c r="R77" s="11" t="n"/>
-      <c r="S77" s="11" t="n"/>
-      <c r="T77" s="11" t="n"/>
-      <c r="U77" s="11" t="n"/>
-      <c r="V77" s="11" t="n"/>
+      <c r="P77" s="13" t="n"/>
+      <c r="Q77" s="13" t="n"/>
+      <c r="R77" s="13" t="n"/>
+      <c r="S77" s="13" t="n"/>
+      <c r="T77" s="13" t="n"/>
+      <c r="U77" s="13" t="n"/>
       <c r="W77" s="11" t="n"/>
       <c r="X77" s="11" t="n"/>
       <c r="Y77" s="11" t="n"/>
@@ -3086,6 +4006,18 @@
       <c r="AA77" s="11" t="n"/>
       <c r="AB77" s="11" t="n"/>
       <c r="AC77" s="11" t="n"/>
+      <c r="AD77" s="11" t="n"/>
+      <c r="AE77" s="11" t="n"/>
+      <c r="AF77" s="11" t="n"/>
+      <c r="AG77" s="11" t="n"/>
+      <c r="AH77" s="11" t="n"/>
+      <c r="AI77" s="11" t="n"/>
+      <c r="AJ77" s="11" t="n"/>
+      <c r="AK77" s="11" t="n"/>
+      <c r="AL77" s="11" t="n"/>
+      <c r="AM77" s="11" t="n"/>
+      <c r="AN77" s="11" t="n"/>
+      <c r="AO77" s="11" t="n"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="B78" s="9" t="inlineStr">
@@ -3106,12 +4038,12 @@
       <c r="M78" s="10" t="n"/>
       <c r="N78" s="10" t="n"/>
       <c r="O78" s="10" t="n"/>
-      <c r="Q78" s="11" t="n"/>
-      <c r="R78" s="11" t="n"/>
-      <c r="S78" s="11" t="n"/>
-      <c r="T78" s="11" t="n"/>
-      <c r="U78" s="11" t="n"/>
-      <c r="V78" s="11" t="n"/>
+      <c r="P78" s="10" t="n"/>
+      <c r="Q78" s="10" t="n"/>
+      <c r="R78" s="10" t="n"/>
+      <c r="S78" s="10" t="n"/>
+      <c r="T78" s="10" t="n"/>
+      <c r="U78" s="10" t="n"/>
       <c r="W78" s="11" t="n"/>
       <c r="X78" s="11" t="n"/>
       <c r="Y78" s="11" t="n"/>
@@ -3119,6 +4051,18 @@
       <c r="AA78" s="11" t="n"/>
       <c r="AB78" s="11" t="n"/>
       <c r="AC78" s="11" t="n"/>
+      <c r="AD78" s="11" t="n"/>
+      <c r="AE78" s="11" t="n"/>
+      <c r="AF78" s="11" t="n"/>
+      <c r="AG78" s="11" t="n"/>
+      <c r="AH78" s="11" t="n"/>
+      <c r="AI78" s="11" t="n"/>
+      <c r="AJ78" s="11" t="n"/>
+      <c r="AK78" s="11" t="n"/>
+      <c r="AL78" s="11" t="n"/>
+      <c r="AM78" s="11" t="n"/>
+      <c r="AN78" s="11" t="n"/>
+      <c r="AO78" s="11" t="n"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="B79" s="12" t="inlineStr">
@@ -3139,12 +4083,12 @@
       <c r="M79" s="13" t="n"/>
       <c r="N79" s="13" t="n"/>
       <c r="O79" s="13" t="n"/>
-      <c r="Q79" s="11" t="n"/>
-      <c r="R79" s="11" t="n"/>
-      <c r="S79" s="11" t="n"/>
-      <c r="T79" s="11" t="n"/>
-      <c r="U79" s="11" t="n"/>
-      <c r="V79" s="11" t="n"/>
+      <c r="P79" s="13" t="n"/>
+      <c r="Q79" s="13" t="n"/>
+      <c r="R79" s="13" t="n"/>
+      <c r="S79" s="13" t="n"/>
+      <c r="T79" s="13" t="n"/>
+      <c r="U79" s="13" t="n"/>
       <c r="W79" s="11" t="n"/>
       <c r="X79" s="11" t="n"/>
       <c r="Y79" s="11" t="n"/>
@@ -3152,6 +4096,18 @@
       <c r="AA79" s="11" t="n"/>
       <c r="AB79" s="11" t="n"/>
       <c r="AC79" s="11" t="n"/>
+      <c r="AD79" s="11" t="n"/>
+      <c r="AE79" s="11" t="n"/>
+      <c r="AF79" s="11" t="n"/>
+      <c r="AG79" s="11" t="n"/>
+      <c r="AH79" s="11" t="n"/>
+      <c r="AI79" s="11" t="n"/>
+      <c r="AJ79" s="11" t="n"/>
+      <c r="AK79" s="11" t="n"/>
+      <c r="AL79" s="11" t="n"/>
+      <c r="AM79" s="11" t="n"/>
+      <c r="AN79" s="11" t="n"/>
+      <c r="AO79" s="11" t="n"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="B80" s="12" t="inlineStr">
@@ -3172,12 +4128,12 @@
       <c r="M80" s="13" t="n"/>
       <c r="N80" s="13" t="n"/>
       <c r="O80" s="13" t="n"/>
-      <c r="Q80" s="11" t="n"/>
-      <c r="R80" s="11" t="n"/>
-      <c r="S80" s="11" t="n"/>
-      <c r="T80" s="11" t="n"/>
-      <c r="U80" s="11" t="n"/>
-      <c r="V80" s="11" t="n"/>
+      <c r="P80" s="13" t="n"/>
+      <c r="Q80" s="13" t="n"/>
+      <c r="R80" s="13" t="n"/>
+      <c r="S80" s="13" t="n"/>
+      <c r="T80" s="13" t="n"/>
+      <c r="U80" s="13" t="n"/>
       <c r="W80" s="11" t="n"/>
       <c r="X80" s="11" t="n"/>
       <c r="Y80" s="11" t="n"/>
@@ -3185,6 +4141,18 @@
       <c r="AA80" s="11" t="n"/>
       <c r="AB80" s="11" t="n"/>
       <c r="AC80" s="11" t="n"/>
+      <c r="AD80" s="11" t="n"/>
+      <c r="AE80" s="11" t="n"/>
+      <c r="AF80" s="11" t="n"/>
+      <c r="AG80" s="11" t="n"/>
+      <c r="AH80" s="11" t="n"/>
+      <c r="AI80" s="11" t="n"/>
+      <c r="AJ80" s="11" t="n"/>
+      <c r="AK80" s="11" t="n"/>
+      <c r="AL80" s="11" t="n"/>
+      <c r="AM80" s="11" t="n"/>
+      <c r="AN80" s="11" t="n"/>
+      <c r="AO80" s="11" t="n"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="B81" s="12" t="inlineStr">
@@ -3205,12 +4173,12 @@
       <c r="M81" s="13" t="n"/>
       <c r="N81" s="13" t="n"/>
       <c r="O81" s="13" t="n"/>
-      <c r="Q81" s="11" t="n"/>
-      <c r="R81" s="11" t="n"/>
-      <c r="S81" s="11" t="n"/>
-      <c r="T81" s="11" t="n"/>
-      <c r="U81" s="11" t="n"/>
-      <c r="V81" s="11" t="n"/>
+      <c r="P81" s="13" t="n"/>
+      <c r="Q81" s="13" t="n"/>
+      <c r="R81" s="13" t="n"/>
+      <c r="S81" s="13" t="n"/>
+      <c r="T81" s="13" t="n"/>
+      <c r="U81" s="13" t="n"/>
       <c r="W81" s="11" t="n"/>
       <c r="X81" s="11" t="n"/>
       <c r="Y81" s="11" t="n"/>
@@ -3218,6 +4186,18 @@
       <c r="AA81" s="11" t="n"/>
       <c r="AB81" s="11" t="n"/>
       <c r="AC81" s="11" t="n"/>
+      <c r="AD81" s="11" t="n"/>
+      <c r="AE81" s="11" t="n"/>
+      <c r="AF81" s="11" t="n"/>
+      <c r="AG81" s="11" t="n"/>
+      <c r="AH81" s="11" t="n"/>
+      <c r="AI81" s="11" t="n"/>
+      <c r="AJ81" s="11" t="n"/>
+      <c r="AK81" s="11" t="n"/>
+      <c r="AL81" s="11" t="n"/>
+      <c r="AM81" s="11" t="n"/>
+      <c r="AN81" s="11" t="n"/>
+      <c r="AO81" s="11" t="n"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="B82" s="14" t="inlineStr">
@@ -3238,12 +4218,12 @@
       <c r="M82" s="13" t="n"/>
       <c r="N82" s="13" t="n"/>
       <c r="O82" s="13" t="n"/>
-      <c r="Q82" s="11" t="n"/>
-      <c r="R82" s="11" t="n"/>
-      <c r="S82" s="11" t="n"/>
-      <c r="T82" s="11" t="n"/>
-      <c r="U82" s="11" t="n"/>
-      <c r="V82" s="11" t="n"/>
+      <c r="P82" s="13" t="n"/>
+      <c r="Q82" s="13" t="n"/>
+      <c r="R82" s="13" t="n"/>
+      <c r="S82" s="13" t="n"/>
+      <c r="T82" s="13" t="n"/>
+      <c r="U82" s="13" t="n"/>
       <c r="W82" s="11" t="n"/>
       <c r="X82" s="11" t="n"/>
       <c r="Y82" s="11" t="n"/>
@@ -3251,6 +4231,18 @@
       <c r="AA82" s="11" t="n"/>
       <c r="AB82" s="11" t="n"/>
       <c r="AC82" s="11" t="n"/>
+      <c r="AD82" s="11" t="n"/>
+      <c r="AE82" s="11" t="n"/>
+      <c r="AF82" s="11" t="n"/>
+      <c r="AG82" s="11" t="n"/>
+      <c r="AH82" s="11" t="n"/>
+      <c r="AI82" s="11" t="n"/>
+      <c r="AJ82" s="11" t="n"/>
+      <c r="AK82" s="11" t="n"/>
+      <c r="AL82" s="11" t="n"/>
+      <c r="AM82" s="11" t="n"/>
+      <c r="AN82" s="11" t="n"/>
+      <c r="AO82" s="11" t="n"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="B83" s="12" t="inlineStr">
@@ -3271,12 +4263,12 @@
       <c r="M83" s="13" t="n"/>
       <c r="N83" s="13" t="n"/>
       <c r="O83" s="13" t="n"/>
-      <c r="Q83" s="11" t="n"/>
-      <c r="R83" s="11" t="n"/>
-      <c r="S83" s="11" t="n"/>
-      <c r="T83" s="11" t="n"/>
-      <c r="U83" s="11" t="n"/>
-      <c r="V83" s="11" t="n"/>
+      <c r="P83" s="13" t="n"/>
+      <c r="Q83" s="13" t="n"/>
+      <c r="R83" s="13" t="n"/>
+      <c r="S83" s="13" t="n"/>
+      <c r="T83" s="13" t="n"/>
+      <c r="U83" s="13" t="n"/>
       <c r="W83" s="11" t="n"/>
       <c r="X83" s="11" t="n"/>
       <c r="Y83" s="11" t="n"/>
@@ -3284,6 +4276,18 @@
       <c r="AA83" s="11" t="n"/>
       <c r="AB83" s="11" t="n"/>
       <c r="AC83" s="11" t="n"/>
+      <c r="AD83" s="11" t="n"/>
+      <c r="AE83" s="11" t="n"/>
+      <c r="AF83" s="11" t="n"/>
+      <c r="AG83" s="11" t="n"/>
+      <c r="AH83" s="11" t="n"/>
+      <c r="AI83" s="11" t="n"/>
+      <c r="AJ83" s="11" t="n"/>
+      <c r="AK83" s="11" t="n"/>
+      <c r="AL83" s="11" t="n"/>
+      <c r="AM83" s="11" t="n"/>
+      <c r="AN83" s="11" t="n"/>
+      <c r="AO83" s="11" t="n"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="B84" s="12" t="inlineStr">
@@ -3304,12 +4308,12 @@
       <c r="M84" s="13" t="n"/>
       <c r="N84" s="13" t="n"/>
       <c r="O84" s="13" t="n"/>
-      <c r="Q84" s="11" t="n"/>
-      <c r="R84" s="11" t="n"/>
-      <c r="S84" s="11" t="n"/>
-      <c r="T84" s="11" t="n"/>
-      <c r="U84" s="11" t="n"/>
-      <c r="V84" s="11" t="n"/>
+      <c r="P84" s="13" t="n"/>
+      <c r="Q84" s="13" t="n"/>
+      <c r="R84" s="13" t="n"/>
+      <c r="S84" s="13" t="n"/>
+      <c r="T84" s="13" t="n"/>
+      <c r="U84" s="13" t="n"/>
       <c r="W84" s="11" t="n"/>
       <c r="X84" s="11" t="n"/>
       <c r="Y84" s="11" t="n"/>
@@ -3317,6 +4321,18 @@
       <c r="AA84" s="11" t="n"/>
       <c r="AB84" s="11" t="n"/>
       <c r="AC84" s="11" t="n"/>
+      <c r="AD84" s="11" t="n"/>
+      <c r="AE84" s="11" t="n"/>
+      <c r="AF84" s="11" t="n"/>
+      <c r="AG84" s="11" t="n"/>
+      <c r="AH84" s="11" t="n"/>
+      <c r="AI84" s="11" t="n"/>
+      <c r="AJ84" s="11" t="n"/>
+      <c r="AK84" s="11" t="n"/>
+      <c r="AL84" s="11" t="n"/>
+      <c r="AM84" s="11" t="n"/>
+      <c r="AN84" s="11" t="n"/>
+      <c r="AO84" s="11" t="n"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="B85" s="9" t="inlineStr">
@@ -3337,12 +4353,12 @@
       <c r="M85" s="10" t="n"/>
       <c r="N85" s="10" t="n"/>
       <c r="O85" s="10" t="n"/>
-      <c r="Q85" s="11" t="n"/>
-      <c r="R85" s="11" t="n"/>
-      <c r="S85" s="11" t="n"/>
-      <c r="T85" s="11" t="n"/>
-      <c r="U85" s="11" t="n"/>
-      <c r="V85" s="11" t="n"/>
+      <c r="P85" s="10" t="n"/>
+      <c r="Q85" s="10" t="n"/>
+      <c r="R85" s="10" t="n"/>
+      <c r="S85" s="10" t="n"/>
+      <c r="T85" s="10" t="n"/>
+      <c r="U85" s="10" t="n"/>
       <c r="W85" s="11" t="n"/>
       <c r="X85" s="11" t="n"/>
       <c r="Y85" s="11" t="n"/>
@@ -3350,6 +4366,18 @@
       <c r="AA85" s="11" t="n"/>
       <c r="AB85" s="11" t="n"/>
       <c r="AC85" s="11" t="n"/>
+      <c r="AD85" s="11" t="n"/>
+      <c r="AE85" s="11" t="n"/>
+      <c r="AF85" s="11" t="n"/>
+      <c r="AG85" s="11" t="n"/>
+      <c r="AH85" s="11" t="n"/>
+      <c r="AI85" s="11" t="n"/>
+      <c r="AJ85" s="11" t="n"/>
+      <c r="AK85" s="11" t="n"/>
+      <c r="AL85" s="11" t="n"/>
+      <c r="AM85" s="11" t="n"/>
+      <c r="AN85" s="11" t="n"/>
+      <c r="AO85" s="11" t="n"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="B86" s="9" t="inlineStr">
@@ -3370,12 +4398,12 @@
       <c r="M86" s="10" t="n"/>
       <c r="N86" s="10" t="n"/>
       <c r="O86" s="10" t="n"/>
-      <c r="Q86" s="11" t="n"/>
-      <c r="R86" s="11" t="n"/>
-      <c r="S86" s="11" t="n"/>
-      <c r="T86" s="11" t="n"/>
-      <c r="U86" s="11" t="n"/>
-      <c r="V86" s="11" t="n"/>
+      <c r="P86" s="10" t="n"/>
+      <c r="Q86" s="10" t="n"/>
+      <c r="R86" s="10" t="n"/>
+      <c r="S86" s="10" t="n"/>
+      <c r="T86" s="10" t="n"/>
+      <c r="U86" s="10" t="n"/>
       <c r="W86" s="11" t="n"/>
       <c r="X86" s="11" t="n"/>
       <c r="Y86" s="11" t="n"/>
@@ -3383,6 +4411,18 @@
       <c r="AA86" s="11" t="n"/>
       <c r="AB86" s="11" t="n"/>
       <c r="AC86" s="11" t="n"/>
+      <c r="AD86" s="11" t="n"/>
+      <c r="AE86" s="11" t="n"/>
+      <c r="AF86" s="11" t="n"/>
+      <c r="AG86" s="11" t="n"/>
+      <c r="AH86" s="11" t="n"/>
+      <c r="AI86" s="11" t="n"/>
+      <c r="AJ86" s="11" t="n"/>
+      <c r="AK86" s="11" t="n"/>
+      <c r="AL86" s="11" t="n"/>
+      <c r="AM86" s="11" t="n"/>
+      <c r="AN86" s="11" t="n"/>
+      <c r="AO86" s="11" t="n"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="B87" s="12" t="inlineStr">
@@ -3403,12 +4443,12 @@
       <c r="M87" s="13" t="n"/>
       <c r="N87" s="13" t="n"/>
       <c r="O87" s="13" t="n"/>
-      <c r="Q87" s="11" t="n"/>
-      <c r="R87" s="11" t="n"/>
-      <c r="S87" s="11" t="n"/>
-      <c r="T87" s="11" t="n"/>
-      <c r="U87" s="11" t="n"/>
-      <c r="V87" s="11" t="n"/>
+      <c r="P87" s="13" t="n"/>
+      <c r="Q87" s="13" t="n"/>
+      <c r="R87" s="13" t="n"/>
+      <c r="S87" s="13" t="n"/>
+      <c r="T87" s="13" t="n"/>
+      <c r="U87" s="13" t="n"/>
       <c r="W87" s="11" t="n"/>
       <c r="X87" s="11" t="n"/>
       <c r="Y87" s="11" t="n"/>
@@ -3416,6 +4456,18 @@
       <c r="AA87" s="11" t="n"/>
       <c r="AB87" s="11" t="n"/>
       <c r="AC87" s="11" t="n"/>
+      <c r="AD87" s="11" t="n"/>
+      <c r="AE87" s="11" t="n"/>
+      <c r="AF87" s="11" t="n"/>
+      <c r="AG87" s="11" t="n"/>
+      <c r="AH87" s="11" t="n"/>
+      <c r="AI87" s="11" t="n"/>
+      <c r="AJ87" s="11" t="n"/>
+      <c r="AK87" s="11" t="n"/>
+      <c r="AL87" s="11" t="n"/>
+      <c r="AM87" s="11" t="n"/>
+      <c r="AN87" s="11" t="n"/>
+      <c r="AO87" s="11" t="n"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="B88" s="9" t="inlineStr">
@@ -3436,12 +4488,12 @@
       <c r="M88" s="10" t="n"/>
       <c r="N88" s="10" t="n"/>
       <c r="O88" s="10" t="n"/>
-      <c r="Q88" s="11" t="n"/>
-      <c r="R88" s="11" t="n"/>
-      <c r="S88" s="11" t="n"/>
-      <c r="T88" s="11" t="n"/>
-      <c r="U88" s="11" t="n"/>
-      <c r="V88" s="11" t="n"/>
+      <c r="P88" s="10" t="n"/>
+      <c r="Q88" s="10" t="n"/>
+      <c r="R88" s="10" t="n"/>
+      <c r="S88" s="10" t="n"/>
+      <c r="T88" s="10" t="n"/>
+      <c r="U88" s="10" t="n"/>
       <c r="W88" s="11" t="n"/>
       <c r="X88" s="11" t="n"/>
       <c r="Y88" s="11" t="n"/>
@@ -3449,6 +4501,18 @@
       <c r="AA88" s="11" t="n"/>
       <c r="AB88" s="11" t="n"/>
       <c r="AC88" s="11" t="n"/>
+      <c r="AD88" s="11" t="n"/>
+      <c r="AE88" s="11" t="n"/>
+      <c r="AF88" s="11" t="n"/>
+      <c r="AG88" s="11" t="n"/>
+      <c r="AH88" s="11" t="n"/>
+      <c r="AI88" s="11" t="n"/>
+      <c r="AJ88" s="11" t="n"/>
+      <c r="AK88" s="11" t="n"/>
+      <c r="AL88" s="11" t="n"/>
+      <c r="AM88" s="11" t="n"/>
+      <c r="AN88" s="11" t="n"/>
+      <c r="AO88" s="11" t="n"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="B89" s="12" t="inlineStr">
@@ -3469,12 +4533,12 @@
       <c r="M89" s="13" t="n"/>
       <c r="N89" s="13" t="n"/>
       <c r="O89" s="13" t="n"/>
-      <c r="Q89" s="11" t="n"/>
-      <c r="R89" s="11" t="n"/>
-      <c r="S89" s="11" t="n"/>
-      <c r="T89" s="11" t="n"/>
-      <c r="U89" s="11" t="n"/>
-      <c r="V89" s="11" t="n"/>
+      <c r="P89" s="13" t="n"/>
+      <c r="Q89" s="13" t="n"/>
+      <c r="R89" s="13" t="n"/>
+      <c r="S89" s="13" t="n"/>
+      <c r="T89" s="13" t="n"/>
+      <c r="U89" s="13" t="n"/>
       <c r="W89" s="11" t="n"/>
       <c r="X89" s="11" t="n"/>
       <c r="Y89" s="11" t="n"/>
@@ -3482,6 +4546,18 @@
       <c r="AA89" s="11" t="n"/>
       <c r="AB89" s="11" t="n"/>
       <c r="AC89" s="11" t="n"/>
+      <c r="AD89" s="11" t="n"/>
+      <c r="AE89" s="11" t="n"/>
+      <c r="AF89" s="11" t="n"/>
+      <c r="AG89" s="11" t="n"/>
+      <c r="AH89" s="11" t="n"/>
+      <c r="AI89" s="11" t="n"/>
+      <c r="AJ89" s="11" t="n"/>
+      <c r="AK89" s="11" t="n"/>
+      <c r="AL89" s="11" t="n"/>
+      <c r="AM89" s="11" t="n"/>
+      <c r="AN89" s="11" t="n"/>
+      <c r="AO89" s="11" t="n"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="B90" s="9" t="inlineStr">
@@ -3502,12 +4578,12 @@
       <c r="M90" s="10" t="n"/>
       <c r="N90" s="10" t="n"/>
       <c r="O90" s="10" t="n"/>
-      <c r="Q90" s="11" t="n"/>
-      <c r="R90" s="11" t="n"/>
-      <c r="S90" s="11" t="n"/>
-      <c r="T90" s="11" t="n"/>
-      <c r="U90" s="11" t="n"/>
-      <c r="V90" s="11" t="n"/>
+      <c r="P90" s="10" t="n"/>
+      <c r="Q90" s="10" t="n"/>
+      <c r="R90" s="10" t="n"/>
+      <c r="S90" s="10" t="n"/>
+      <c r="T90" s="10" t="n"/>
+      <c r="U90" s="10" t="n"/>
       <c r="W90" s="11" t="n"/>
       <c r="X90" s="11" t="n"/>
       <c r="Y90" s="11" t="n"/>
@@ -3515,6 +4591,18 @@
       <c r="AA90" s="11" t="n"/>
       <c r="AB90" s="11" t="n"/>
       <c r="AC90" s="11" t="n"/>
+      <c r="AD90" s="11" t="n"/>
+      <c r="AE90" s="11" t="n"/>
+      <c r="AF90" s="11" t="n"/>
+      <c r="AG90" s="11" t="n"/>
+      <c r="AH90" s="11" t="n"/>
+      <c r="AI90" s="11" t="n"/>
+      <c r="AJ90" s="11" t="n"/>
+      <c r="AK90" s="11" t="n"/>
+      <c r="AL90" s="11" t="n"/>
+      <c r="AM90" s="11" t="n"/>
+      <c r="AN90" s="11" t="n"/>
+      <c r="AO90" s="11" t="n"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="B93" s="5" t="inlineStr">
@@ -3527,7 +4615,7 @@
           <t>40-99 Segment - Over Time Period</t>
         </is>
       </c>
-      <c r="Q93" s="6" t="inlineStr">
+      <c r="W93" s="6" t="inlineStr">
         <is>
           <t>40-99 Segment - Over Time Period - Difference</t>
         </is>
@@ -3604,69 +4692,129 @@
           <t>SPTx2</t>
         </is>
       </c>
+      <c r="P94" s="8" t="inlineStr">
+        <is>
+          <t>1-star Pack</t>
+        </is>
+      </c>
       <c r="Q94" s="8" t="inlineStr">
         <is>
+          <t>2-star Pack</t>
+        </is>
+      </c>
+      <c r="R94" s="8" t="inlineStr">
+        <is>
+          <t>3-star Pack</t>
+        </is>
+      </c>
+      <c r="S94" s="8" t="inlineStr">
+        <is>
+          <t>4-star Pack</t>
+        </is>
+      </c>
+      <c r="T94" s="8" t="inlineStr">
+        <is>
+          <t>5-star Pack</t>
+        </is>
+      </c>
+      <c r="U94" s="8" t="inlineStr">
+        <is>
+          <t>6-star Pack</t>
+        </is>
+      </c>
+      <c r="W94" s="8" t="inlineStr">
+        <is>
           <t>HC</t>
         </is>
       </c>
-      <c r="R94" s="8" t="inlineStr">
+      <c r="X94" s="8" t="inlineStr">
         <is>
           <t>Slingshot</t>
         </is>
       </c>
-      <c r="S94" s="8" t="inlineStr">
+      <c r="Y94" s="8" t="inlineStr">
         <is>
           <t>Shuffle</t>
         </is>
       </c>
-      <c r="T94" s="8" t="inlineStr">
+      <c r="Z94" s="8" t="inlineStr">
         <is>
           <t>Comet</t>
         </is>
       </c>
-      <c r="U94" s="8" t="inlineStr">
+      <c r="AA94" s="8" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="V94" s="8" t="inlineStr">
+      <c r="AB94" s="8" t="inlineStr">
         <is>
           <t>Chuck</t>
         </is>
       </c>
-      <c r="W94" s="8" t="inlineStr">
+      <c r="AC94" s="8" t="inlineStr">
         <is>
           <t>Bomb</t>
         </is>
       </c>
-      <c r="X94" s="8" t="inlineStr">
+      <c r="AD94" s="8" t="inlineStr">
         <is>
           <t>UL Bomb</t>
         </is>
       </c>
-      <c r="Y94" s="8" t="inlineStr">
+      <c r="AE94" s="8" t="inlineStr">
         <is>
           <t>UL Chuck</t>
         </is>
       </c>
-      <c r="Z94" s="8" t="inlineStr">
+      <c r="AF94" s="8" t="inlineStr">
         <is>
           <t>UL Red</t>
         </is>
       </c>
-      <c r="AA94" s="8" t="inlineStr">
+      <c r="AG94" s="8" t="inlineStr">
         <is>
           <t>Unlimited Lives</t>
         </is>
       </c>
-      <c r="AB94" s="8" t="inlineStr">
+      <c r="AH94" s="8" t="inlineStr">
         <is>
           <t>SPT</t>
         </is>
       </c>
-      <c r="AC94" s="8" t="inlineStr">
+      <c r="AI94" s="8" t="inlineStr">
         <is>
           <t>SPTx2</t>
+        </is>
+      </c>
+      <c r="AJ94" s="8" t="inlineStr">
+        <is>
+          <t>1-star Pack</t>
+        </is>
+      </c>
+      <c r="AK94" s="8" t="inlineStr">
+        <is>
+          <t>2-star Pack</t>
+        </is>
+      </c>
+      <c r="AL94" s="8" t="inlineStr">
+        <is>
+          <t>3-star Pack</t>
+        </is>
+      </c>
+      <c r="AM94" s="8" t="inlineStr">
+        <is>
+          <t>4-star Pack</t>
+        </is>
+      </c>
+      <c r="AN94" s="8" t="inlineStr">
+        <is>
+          <t>5-star Pack</t>
+        </is>
+      </c>
+      <c r="AO94" s="8" t="inlineStr">
+        <is>
+          <t>6-star Pack</t>
         </is>
       </c>
     </row>
@@ -3692,22 +4840,34 @@
       <c r="M95" s="10" t="n"/>
       <c r="N95" s="10" t="n"/>
       <c r="O95" s="10" t="n"/>
-      <c r="Q95" s="11">
+      <c r="P95" s="10" t="n"/>
+      <c r="Q95" s="10" t="n"/>
+      <c r="R95" s="10" t="n"/>
+      <c r="S95" s="10" t="n"/>
+      <c r="T95" s="10" t="n"/>
+      <c r="U95" s="10" t="n"/>
+      <c r="W95" s="11">
         <f>LET(payer, $C$3, segment, $B$93, ECOGAINS_DIFF(payer, segment, sim_refresh!$A$1))</f>
         <v/>
       </c>
-      <c r="R95" s="11" t="n"/>
-      <c r="S95" s="11" t="n"/>
-      <c r="T95" s="11" t="n"/>
-      <c r="U95" s="11" t="n"/>
-      <c r="V95" s="11" t="n"/>
-      <c r="W95" s="11" t="n"/>
       <c r="X95" s="11" t="n"/>
       <c r="Y95" s="11" t="n"/>
       <c r="Z95" s="11" t="n"/>
       <c r="AA95" s="11" t="n"/>
       <c r="AB95" s="11" t="n"/>
       <c r="AC95" s="11" t="n"/>
+      <c r="AD95" s="11" t="n"/>
+      <c r="AE95" s="11" t="n"/>
+      <c r="AF95" s="11" t="n"/>
+      <c r="AG95" s="11" t="n"/>
+      <c r="AH95" s="11" t="n"/>
+      <c r="AI95" s="11" t="n"/>
+      <c r="AJ95" s="11" t="n"/>
+      <c r="AK95" s="11" t="n"/>
+      <c r="AL95" s="11" t="n"/>
+      <c r="AM95" s="11" t="n"/>
+      <c r="AN95" s="11" t="n"/>
+      <c r="AO95" s="11" t="n"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="B96" s="12" t="inlineStr">
@@ -3728,12 +4888,12 @@
       <c r="M96" s="13" t="n"/>
       <c r="N96" s="13" t="n"/>
       <c r="O96" s="13" t="n"/>
-      <c r="Q96" s="11" t="n"/>
-      <c r="R96" s="11" t="n"/>
-      <c r="S96" s="11" t="n"/>
-      <c r="T96" s="11" t="n"/>
-      <c r="U96" s="11" t="n"/>
-      <c r="V96" s="11" t="n"/>
+      <c r="P96" s="13" t="n"/>
+      <c r="Q96" s="13" t="n"/>
+      <c r="R96" s="13" t="n"/>
+      <c r="S96" s="13" t="n"/>
+      <c r="T96" s="13" t="n"/>
+      <c r="U96" s="13" t="n"/>
       <c r="W96" s="11" t="n"/>
       <c r="X96" s="11" t="n"/>
       <c r="Y96" s="11" t="n"/>
@@ -3741,6 +4901,18 @@
       <c r="AA96" s="11" t="n"/>
       <c r="AB96" s="11" t="n"/>
       <c r="AC96" s="11" t="n"/>
+      <c r="AD96" s="11" t="n"/>
+      <c r="AE96" s="11" t="n"/>
+      <c r="AF96" s="11" t="n"/>
+      <c r="AG96" s="11" t="n"/>
+      <c r="AH96" s="11" t="n"/>
+      <c r="AI96" s="11" t="n"/>
+      <c r="AJ96" s="11" t="n"/>
+      <c r="AK96" s="11" t="n"/>
+      <c r="AL96" s="11" t="n"/>
+      <c r="AM96" s="11" t="n"/>
+      <c r="AN96" s="11" t="n"/>
+      <c r="AO96" s="11" t="n"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="B97" s="12" t="inlineStr">
@@ -3761,12 +4933,12 @@
       <c r="M97" s="13" t="n"/>
       <c r="N97" s="13" t="n"/>
       <c r="O97" s="13" t="n"/>
-      <c r="Q97" s="11" t="n"/>
-      <c r="R97" s="11" t="n"/>
-      <c r="S97" s="11" t="n"/>
-      <c r="T97" s="11" t="n"/>
-      <c r="U97" s="11" t="n"/>
-      <c r="V97" s="11" t="n"/>
+      <c r="P97" s="13" t="n"/>
+      <c r="Q97" s="13" t="n"/>
+      <c r="R97" s="13" t="n"/>
+      <c r="S97" s="13" t="n"/>
+      <c r="T97" s="13" t="n"/>
+      <c r="U97" s="13" t="n"/>
       <c r="W97" s="11" t="n"/>
       <c r="X97" s="11" t="n"/>
       <c r="Y97" s="11" t="n"/>
@@ -3774,6 +4946,18 @@
       <c r="AA97" s="11" t="n"/>
       <c r="AB97" s="11" t="n"/>
       <c r="AC97" s="11" t="n"/>
+      <c r="AD97" s="11" t="n"/>
+      <c r="AE97" s="11" t="n"/>
+      <c r="AF97" s="11" t="n"/>
+      <c r="AG97" s="11" t="n"/>
+      <c r="AH97" s="11" t="n"/>
+      <c r="AI97" s="11" t="n"/>
+      <c r="AJ97" s="11" t="n"/>
+      <c r="AK97" s="11" t="n"/>
+      <c r="AL97" s="11" t="n"/>
+      <c r="AM97" s="11" t="n"/>
+      <c r="AN97" s="11" t="n"/>
+      <c r="AO97" s="11" t="n"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="B98" s="12" t="inlineStr">
@@ -3794,12 +4978,12 @@
       <c r="M98" s="13" t="n"/>
       <c r="N98" s="13" t="n"/>
       <c r="O98" s="13" t="n"/>
-      <c r="Q98" s="11" t="n"/>
-      <c r="R98" s="11" t="n"/>
-      <c r="S98" s="11" t="n"/>
-      <c r="T98" s="11" t="n"/>
-      <c r="U98" s="11" t="n"/>
-      <c r="V98" s="11" t="n"/>
+      <c r="P98" s="13" t="n"/>
+      <c r="Q98" s="13" t="n"/>
+      <c r="R98" s="13" t="n"/>
+      <c r="S98" s="13" t="n"/>
+      <c r="T98" s="13" t="n"/>
+      <c r="U98" s="13" t="n"/>
       <c r="W98" s="11" t="n"/>
       <c r="X98" s="11" t="n"/>
       <c r="Y98" s="11" t="n"/>
@@ -3807,6 +4991,18 @@
       <c r="AA98" s="11" t="n"/>
       <c r="AB98" s="11" t="n"/>
       <c r="AC98" s="11" t="n"/>
+      <c r="AD98" s="11" t="n"/>
+      <c r="AE98" s="11" t="n"/>
+      <c r="AF98" s="11" t="n"/>
+      <c r="AG98" s="11" t="n"/>
+      <c r="AH98" s="11" t="n"/>
+      <c r="AI98" s="11" t="n"/>
+      <c r="AJ98" s="11" t="n"/>
+      <c r="AK98" s="11" t="n"/>
+      <c r="AL98" s="11" t="n"/>
+      <c r="AM98" s="11" t="n"/>
+      <c r="AN98" s="11" t="n"/>
+      <c r="AO98" s="11" t="n"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="B99" s="9" t="inlineStr">
@@ -3827,12 +5023,12 @@
       <c r="M99" s="10" t="n"/>
       <c r="N99" s="10" t="n"/>
       <c r="O99" s="10" t="n"/>
-      <c r="Q99" s="11" t="n"/>
-      <c r="R99" s="11" t="n"/>
-      <c r="S99" s="11" t="n"/>
-      <c r="T99" s="11" t="n"/>
-      <c r="U99" s="11" t="n"/>
-      <c r="V99" s="11" t="n"/>
+      <c r="P99" s="10" t="n"/>
+      <c r="Q99" s="10" t="n"/>
+      <c r="R99" s="10" t="n"/>
+      <c r="S99" s="10" t="n"/>
+      <c r="T99" s="10" t="n"/>
+      <c r="U99" s="10" t="n"/>
       <c r="W99" s="11" t="n"/>
       <c r="X99" s="11" t="n"/>
       <c r="Y99" s="11" t="n"/>
@@ -3840,6 +5036,18 @@
       <c r="AA99" s="11" t="n"/>
       <c r="AB99" s="11" t="n"/>
       <c r="AC99" s="11" t="n"/>
+      <c r="AD99" s="11" t="n"/>
+      <c r="AE99" s="11" t="n"/>
+      <c r="AF99" s="11" t="n"/>
+      <c r="AG99" s="11" t="n"/>
+      <c r="AH99" s="11" t="n"/>
+      <c r="AI99" s="11" t="n"/>
+      <c r="AJ99" s="11" t="n"/>
+      <c r="AK99" s="11" t="n"/>
+      <c r="AL99" s="11" t="n"/>
+      <c r="AM99" s="11" t="n"/>
+      <c r="AN99" s="11" t="n"/>
+      <c r="AO99" s="11" t="n"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="B100" s="14" t="inlineStr">
@@ -3860,12 +5068,12 @@
       <c r="M100" s="13" t="n"/>
       <c r="N100" s="13" t="n"/>
       <c r="O100" s="13" t="n"/>
-      <c r="Q100" s="11" t="n"/>
-      <c r="R100" s="11" t="n"/>
-      <c r="S100" s="11" t="n"/>
-      <c r="T100" s="11" t="n"/>
-      <c r="U100" s="11" t="n"/>
-      <c r="V100" s="11" t="n"/>
+      <c r="P100" s="13" t="n"/>
+      <c r="Q100" s="13" t="n"/>
+      <c r="R100" s="13" t="n"/>
+      <c r="S100" s="13" t="n"/>
+      <c r="T100" s="13" t="n"/>
+      <c r="U100" s="13" t="n"/>
       <c r="W100" s="11" t="n"/>
       <c r="X100" s="11" t="n"/>
       <c r="Y100" s="11" t="n"/>
@@ -3873,6 +5081,18 @@
       <c r="AA100" s="11" t="n"/>
       <c r="AB100" s="11" t="n"/>
       <c r="AC100" s="11" t="n"/>
+      <c r="AD100" s="11" t="n"/>
+      <c r="AE100" s="11" t="n"/>
+      <c r="AF100" s="11" t="n"/>
+      <c r="AG100" s="11" t="n"/>
+      <c r="AH100" s="11" t="n"/>
+      <c r="AI100" s="11" t="n"/>
+      <c r="AJ100" s="11" t="n"/>
+      <c r="AK100" s="11" t="n"/>
+      <c r="AL100" s="11" t="n"/>
+      <c r="AM100" s="11" t="n"/>
+      <c r="AN100" s="11" t="n"/>
+      <c r="AO100" s="11" t="n"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="B101" s="14" t="inlineStr">
@@ -3893,12 +5113,12 @@
       <c r="M101" s="13" t="n"/>
       <c r="N101" s="13" t="n"/>
       <c r="O101" s="13" t="n"/>
-      <c r="Q101" s="11" t="n"/>
-      <c r="R101" s="11" t="n"/>
-      <c r="S101" s="11" t="n"/>
-      <c r="T101" s="11" t="n"/>
-      <c r="U101" s="11" t="n"/>
-      <c r="V101" s="11" t="n"/>
+      <c r="P101" s="13" t="n"/>
+      <c r="Q101" s="13" t="n"/>
+      <c r="R101" s="13" t="n"/>
+      <c r="S101" s="13" t="n"/>
+      <c r="T101" s="13" t="n"/>
+      <c r="U101" s="13" t="n"/>
       <c r="W101" s="11" t="n"/>
       <c r="X101" s="11" t="n"/>
       <c r="Y101" s="11" t="n"/>
@@ -3906,6 +5126,18 @@
       <c r="AA101" s="11" t="n"/>
       <c r="AB101" s="11" t="n"/>
       <c r="AC101" s="11" t="n"/>
+      <c r="AD101" s="11" t="n"/>
+      <c r="AE101" s="11" t="n"/>
+      <c r="AF101" s="11" t="n"/>
+      <c r="AG101" s="11" t="n"/>
+      <c r="AH101" s="11" t="n"/>
+      <c r="AI101" s="11" t="n"/>
+      <c r="AJ101" s="11" t="n"/>
+      <c r="AK101" s="11" t="n"/>
+      <c r="AL101" s="11" t="n"/>
+      <c r="AM101" s="11" t="n"/>
+      <c r="AN101" s="11" t="n"/>
+      <c r="AO101" s="11" t="n"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="B102" s="9" t="inlineStr">
@@ -3926,12 +5158,12 @@
       <c r="M102" s="10" t="n"/>
       <c r="N102" s="10" t="n"/>
       <c r="O102" s="10" t="n"/>
-      <c r="Q102" s="11" t="n"/>
-      <c r="R102" s="11" t="n"/>
-      <c r="S102" s="11" t="n"/>
-      <c r="T102" s="11" t="n"/>
-      <c r="U102" s="11" t="n"/>
-      <c r="V102" s="11" t="n"/>
+      <c r="P102" s="10" t="n"/>
+      <c r="Q102" s="10" t="n"/>
+      <c r="R102" s="10" t="n"/>
+      <c r="S102" s="10" t="n"/>
+      <c r="T102" s="10" t="n"/>
+      <c r="U102" s="10" t="n"/>
       <c r="W102" s="11" t="n"/>
       <c r="X102" s="11" t="n"/>
       <c r="Y102" s="11" t="n"/>
@@ -3939,6 +5171,18 @@
       <c r="AA102" s="11" t="n"/>
       <c r="AB102" s="11" t="n"/>
       <c r="AC102" s="11" t="n"/>
+      <c r="AD102" s="11" t="n"/>
+      <c r="AE102" s="11" t="n"/>
+      <c r="AF102" s="11" t="n"/>
+      <c r="AG102" s="11" t="n"/>
+      <c r="AH102" s="11" t="n"/>
+      <c r="AI102" s="11" t="n"/>
+      <c r="AJ102" s="11" t="n"/>
+      <c r="AK102" s="11" t="n"/>
+      <c r="AL102" s="11" t="n"/>
+      <c r="AM102" s="11" t="n"/>
+      <c r="AN102" s="11" t="n"/>
+      <c r="AO102" s="11" t="n"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="B103" s="12" t="inlineStr">
@@ -3959,12 +5203,12 @@
       <c r="M103" s="13" t="n"/>
       <c r="N103" s="13" t="n"/>
       <c r="O103" s="13" t="n"/>
-      <c r="Q103" s="11" t="n"/>
-      <c r="R103" s="11" t="n"/>
-      <c r="S103" s="11" t="n"/>
-      <c r="T103" s="11" t="n"/>
-      <c r="U103" s="11" t="n"/>
-      <c r="V103" s="11" t="n"/>
+      <c r="P103" s="13" t="n"/>
+      <c r="Q103" s="13" t="n"/>
+      <c r="R103" s="13" t="n"/>
+      <c r="S103" s="13" t="n"/>
+      <c r="T103" s="13" t="n"/>
+      <c r="U103" s="13" t="n"/>
       <c r="W103" s="11" t="n"/>
       <c r="X103" s="11" t="n"/>
       <c r="Y103" s="11" t="n"/>
@@ -3972,6 +5216,18 @@
       <c r="AA103" s="11" t="n"/>
       <c r="AB103" s="11" t="n"/>
       <c r="AC103" s="11" t="n"/>
+      <c r="AD103" s="11" t="n"/>
+      <c r="AE103" s="11" t="n"/>
+      <c r="AF103" s="11" t="n"/>
+      <c r="AG103" s="11" t="n"/>
+      <c r="AH103" s="11" t="n"/>
+      <c r="AI103" s="11" t="n"/>
+      <c r="AJ103" s="11" t="n"/>
+      <c r="AK103" s="11" t="n"/>
+      <c r="AL103" s="11" t="n"/>
+      <c r="AM103" s="11" t="n"/>
+      <c r="AN103" s="11" t="n"/>
+      <c r="AO103" s="11" t="n"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="B104" s="12" t="inlineStr">
@@ -3992,12 +5248,12 @@
       <c r="M104" s="13" t="n"/>
       <c r="N104" s="13" t="n"/>
       <c r="O104" s="13" t="n"/>
-      <c r="Q104" s="11" t="n"/>
-      <c r="R104" s="11" t="n"/>
-      <c r="S104" s="11" t="n"/>
-      <c r="T104" s="11" t="n"/>
-      <c r="U104" s="11" t="n"/>
-      <c r="V104" s="11" t="n"/>
+      <c r="P104" s="13" t="n"/>
+      <c r="Q104" s="13" t="n"/>
+      <c r="R104" s="13" t="n"/>
+      <c r="S104" s="13" t="n"/>
+      <c r="T104" s="13" t="n"/>
+      <c r="U104" s="13" t="n"/>
       <c r="W104" s="11" t="n"/>
       <c r="X104" s="11" t="n"/>
       <c r="Y104" s="11" t="n"/>
@@ -4005,6 +5261,18 @@
       <c r="AA104" s="11" t="n"/>
       <c r="AB104" s="11" t="n"/>
       <c r="AC104" s="11" t="n"/>
+      <c r="AD104" s="11" t="n"/>
+      <c r="AE104" s="11" t="n"/>
+      <c r="AF104" s="11" t="n"/>
+      <c r="AG104" s="11" t="n"/>
+      <c r="AH104" s="11" t="n"/>
+      <c r="AI104" s="11" t="n"/>
+      <c r="AJ104" s="11" t="n"/>
+      <c r="AK104" s="11" t="n"/>
+      <c r="AL104" s="11" t="n"/>
+      <c r="AM104" s="11" t="n"/>
+      <c r="AN104" s="11" t="n"/>
+      <c r="AO104" s="11" t="n"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="B105" s="12" t="inlineStr">
@@ -4025,12 +5293,12 @@
       <c r="M105" s="13" t="n"/>
       <c r="N105" s="13" t="n"/>
       <c r="O105" s="13" t="n"/>
-      <c r="Q105" s="11" t="n"/>
-      <c r="R105" s="11" t="n"/>
-      <c r="S105" s="11" t="n"/>
-      <c r="T105" s="11" t="n"/>
-      <c r="U105" s="11" t="n"/>
-      <c r="V105" s="11" t="n"/>
+      <c r="P105" s="13" t="n"/>
+      <c r="Q105" s="13" t="n"/>
+      <c r="R105" s="13" t="n"/>
+      <c r="S105" s="13" t="n"/>
+      <c r="T105" s="13" t="n"/>
+      <c r="U105" s="13" t="n"/>
       <c r="W105" s="11" t="n"/>
       <c r="X105" s="11" t="n"/>
       <c r="Y105" s="11" t="n"/>
@@ -4038,6 +5306,18 @@
       <c r="AA105" s="11" t="n"/>
       <c r="AB105" s="11" t="n"/>
       <c r="AC105" s="11" t="n"/>
+      <c r="AD105" s="11" t="n"/>
+      <c r="AE105" s="11" t="n"/>
+      <c r="AF105" s="11" t="n"/>
+      <c r="AG105" s="11" t="n"/>
+      <c r="AH105" s="11" t="n"/>
+      <c r="AI105" s="11" t="n"/>
+      <c r="AJ105" s="11" t="n"/>
+      <c r="AK105" s="11" t="n"/>
+      <c r="AL105" s="11" t="n"/>
+      <c r="AM105" s="11" t="n"/>
+      <c r="AN105" s="11" t="n"/>
+      <c r="AO105" s="11" t="n"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="B106" s="12" t="inlineStr">
@@ -4058,12 +5338,12 @@
       <c r="M106" s="13" t="n"/>
       <c r="N106" s="13" t="n"/>
       <c r="O106" s="13" t="n"/>
-      <c r="Q106" s="11" t="n"/>
-      <c r="R106" s="11" t="n"/>
-      <c r="S106" s="11" t="n"/>
-      <c r="T106" s="11" t="n"/>
-      <c r="U106" s="11" t="n"/>
-      <c r="V106" s="11" t="n"/>
+      <c r="P106" s="13" t="n"/>
+      <c r="Q106" s="13" t="n"/>
+      <c r="R106" s="13" t="n"/>
+      <c r="S106" s="13" t="n"/>
+      <c r="T106" s="13" t="n"/>
+      <c r="U106" s="13" t="n"/>
       <c r="W106" s="11" t="n"/>
       <c r="X106" s="11" t="n"/>
       <c r="Y106" s="11" t="n"/>
@@ -4071,6 +5351,18 @@
       <c r="AA106" s="11" t="n"/>
       <c r="AB106" s="11" t="n"/>
       <c r="AC106" s="11" t="n"/>
+      <c r="AD106" s="11" t="n"/>
+      <c r="AE106" s="11" t="n"/>
+      <c r="AF106" s="11" t="n"/>
+      <c r="AG106" s="11" t="n"/>
+      <c r="AH106" s="11" t="n"/>
+      <c r="AI106" s="11" t="n"/>
+      <c r="AJ106" s="11" t="n"/>
+      <c r="AK106" s="11" t="n"/>
+      <c r="AL106" s="11" t="n"/>
+      <c r="AM106" s="11" t="n"/>
+      <c r="AN106" s="11" t="n"/>
+      <c r="AO106" s="11" t="n"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="B107" s="9" t="inlineStr">
@@ -4091,12 +5383,12 @@
       <c r="M107" s="10" t="n"/>
       <c r="N107" s="10" t="n"/>
       <c r="O107" s="10" t="n"/>
-      <c r="Q107" s="11" t="n"/>
-      <c r="R107" s="11" t="n"/>
-      <c r="S107" s="11" t="n"/>
-      <c r="T107" s="11" t="n"/>
-      <c r="U107" s="11" t="n"/>
-      <c r="V107" s="11" t="n"/>
+      <c r="P107" s="10" t="n"/>
+      <c r="Q107" s="10" t="n"/>
+      <c r="R107" s="10" t="n"/>
+      <c r="S107" s="10" t="n"/>
+      <c r="T107" s="10" t="n"/>
+      <c r="U107" s="10" t="n"/>
       <c r="W107" s="11" t="n"/>
       <c r="X107" s="11" t="n"/>
       <c r="Y107" s="11" t="n"/>
@@ -4104,6 +5396,18 @@
       <c r="AA107" s="11" t="n"/>
       <c r="AB107" s="11" t="n"/>
       <c r="AC107" s="11" t="n"/>
+      <c r="AD107" s="11" t="n"/>
+      <c r="AE107" s="11" t="n"/>
+      <c r="AF107" s="11" t="n"/>
+      <c r="AG107" s="11" t="n"/>
+      <c r="AH107" s="11" t="n"/>
+      <c r="AI107" s="11" t="n"/>
+      <c r="AJ107" s="11" t="n"/>
+      <c r="AK107" s="11" t="n"/>
+      <c r="AL107" s="11" t="n"/>
+      <c r="AM107" s="11" t="n"/>
+      <c r="AN107" s="11" t="n"/>
+      <c r="AO107" s="11" t="n"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="B108" s="12" t="inlineStr">
@@ -4124,12 +5428,12 @@
       <c r="M108" s="13" t="n"/>
       <c r="N108" s="13" t="n"/>
       <c r="O108" s="13" t="n"/>
-      <c r="Q108" s="11" t="n"/>
-      <c r="R108" s="11" t="n"/>
-      <c r="S108" s="11" t="n"/>
-      <c r="T108" s="11" t="n"/>
-      <c r="U108" s="11" t="n"/>
-      <c r="V108" s="11" t="n"/>
+      <c r="P108" s="13" t="n"/>
+      <c r="Q108" s="13" t="n"/>
+      <c r="R108" s="13" t="n"/>
+      <c r="S108" s="13" t="n"/>
+      <c r="T108" s="13" t="n"/>
+      <c r="U108" s="13" t="n"/>
       <c r="W108" s="11" t="n"/>
       <c r="X108" s="11" t="n"/>
       <c r="Y108" s="11" t="n"/>
@@ -4137,6 +5441,18 @@
       <c r="AA108" s="11" t="n"/>
       <c r="AB108" s="11" t="n"/>
       <c r="AC108" s="11" t="n"/>
+      <c r="AD108" s="11" t="n"/>
+      <c r="AE108" s="11" t="n"/>
+      <c r="AF108" s="11" t="n"/>
+      <c r="AG108" s="11" t="n"/>
+      <c r="AH108" s="11" t="n"/>
+      <c r="AI108" s="11" t="n"/>
+      <c r="AJ108" s="11" t="n"/>
+      <c r="AK108" s="11" t="n"/>
+      <c r="AL108" s="11" t="n"/>
+      <c r="AM108" s="11" t="n"/>
+      <c r="AN108" s="11" t="n"/>
+      <c r="AO108" s="11" t="n"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="B109" s="12" t="inlineStr">
@@ -4157,12 +5473,12 @@
       <c r="M109" s="13" t="n"/>
       <c r="N109" s="13" t="n"/>
       <c r="O109" s="13" t="n"/>
-      <c r="Q109" s="11" t="n"/>
-      <c r="R109" s="11" t="n"/>
-      <c r="S109" s="11" t="n"/>
-      <c r="T109" s="11" t="n"/>
-      <c r="U109" s="11" t="n"/>
-      <c r="V109" s="11" t="n"/>
+      <c r="P109" s="13" t="n"/>
+      <c r="Q109" s="13" t="n"/>
+      <c r="R109" s="13" t="n"/>
+      <c r="S109" s="13" t="n"/>
+      <c r="T109" s="13" t="n"/>
+      <c r="U109" s="13" t="n"/>
       <c r="W109" s="11" t="n"/>
       <c r="X109" s="11" t="n"/>
       <c r="Y109" s="11" t="n"/>
@@ -4170,6 +5486,18 @@
       <c r="AA109" s="11" t="n"/>
       <c r="AB109" s="11" t="n"/>
       <c r="AC109" s="11" t="n"/>
+      <c r="AD109" s="11" t="n"/>
+      <c r="AE109" s="11" t="n"/>
+      <c r="AF109" s="11" t="n"/>
+      <c r="AG109" s="11" t="n"/>
+      <c r="AH109" s="11" t="n"/>
+      <c r="AI109" s="11" t="n"/>
+      <c r="AJ109" s="11" t="n"/>
+      <c r="AK109" s="11" t="n"/>
+      <c r="AL109" s="11" t="n"/>
+      <c r="AM109" s="11" t="n"/>
+      <c r="AN109" s="11" t="n"/>
+      <c r="AO109" s="11" t="n"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="B110" s="12" t="inlineStr">
@@ -4190,12 +5518,12 @@
       <c r="M110" s="13" t="n"/>
       <c r="N110" s="13" t="n"/>
       <c r="O110" s="13" t="n"/>
-      <c r="Q110" s="11" t="n"/>
-      <c r="R110" s="11" t="n"/>
-      <c r="S110" s="11" t="n"/>
-      <c r="T110" s="11" t="n"/>
-      <c r="U110" s="11" t="n"/>
-      <c r="V110" s="11" t="n"/>
+      <c r="P110" s="13" t="n"/>
+      <c r="Q110" s="13" t="n"/>
+      <c r="R110" s="13" t="n"/>
+      <c r="S110" s="13" t="n"/>
+      <c r="T110" s="13" t="n"/>
+      <c r="U110" s="13" t="n"/>
       <c r="W110" s="11" t="n"/>
       <c r="X110" s="11" t="n"/>
       <c r="Y110" s="11" t="n"/>
@@ -4203,6 +5531,18 @@
       <c r="AA110" s="11" t="n"/>
       <c r="AB110" s="11" t="n"/>
       <c r="AC110" s="11" t="n"/>
+      <c r="AD110" s="11" t="n"/>
+      <c r="AE110" s="11" t="n"/>
+      <c r="AF110" s="11" t="n"/>
+      <c r="AG110" s="11" t="n"/>
+      <c r="AH110" s="11" t="n"/>
+      <c r="AI110" s="11" t="n"/>
+      <c r="AJ110" s="11" t="n"/>
+      <c r="AK110" s="11" t="n"/>
+      <c r="AL110" s="11" t="n"/>
+      <c r="AM110" s="11" t="n"/>
+      <c r="AN110" s="11" t="n"/>
+      <c r="AO110" s="11" t="n"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="B111" s="14" t="inlineStr">
@@ -4223,12 +5563,12 @@
       <c r="M111" s="13" t="n"/>
       <c r="N111" s="13" t="n"/>
       <c r="O111" s="13" t="n"/>
-      <c r="Q111" s="11" t="n"/>
-      <c r="R111" s="11" t="n"/>
-      <c r="S111" s="11" t="n"/>
-      <c r="T111" s="11" t="n"/>
-      <c r="U111" s="11" t="n"/>
-      <c r="V111" s="11" t="n"/>
+      <c r="P111" s="13" t="n"/>
+      <c r="Q111" s="13" t="n"/>
+      <c r="R111" s="13" t="n"/>
+      <c r="S111" s="13" t="n"/>
+      <c r="T111" s="13" t="n"/>
+      <c r="U111" s="13" t="n"/>
       <c r="W111" s="11" t="n"/>
       <c r="X111" s="11" t="n"/>
       <c r="Y111" s="11" t="n"/>
@@ -4236,6 +5576,18 @@
       <c r="AA111" s="11" t="n"/>
       <c r="AB111" s="11" t="n"/>
       <c r="AC111" s="11" t="n"/>
+      <c r="AD111" s="11" t="n"/>
+      <c r="AE111" s="11" t="n"/>
+      <c r="AF111" s="11" t="n"/>
+      <c r="AG111" s="11" t="n"/>
+      <c r="AH111" s="11" t="n"/>
+      <c r="AI111" s="11" t="n"/>
+      <c r="AJ111" s="11" t="n"/>
+      <c r="AK111" s="11" t="n"/>
+      <c r="AL111" s="11" t="n"/>
+      <c r="AM111" s="11" t="n"/>
+      <c r="AN111" s="11" t="n"/>
+      <c r="AO111" s="11" t="n"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="B112" s="12" t="inlineStr">
@@ -4256,12 +5608,12 @@
       <c r="M112" s="13" t="n"/>
       <c r="N112" s="13" t="n"/>
       <c r="O112" s="13" t="n"/>
-      <c r="Q112" s="11" t="n"/>
-      <c r="R112" s="11" t="n"/>
-      <c r="S112" s="11" t="n"/>
-      <c r="T112" s="11" t="n"/>
-      <c r="U112" s="11" t="n"/>
-      <c r="V112" s="11" t="n"/>
+      <c r="P112" s="13" t="n"/>
+      <c r="Q112" s="13" t="n"/>
+      <c r="R112" s="13" t="n"/>
+      <c r="S112" s="13" t="n"/>
+      <c r="T112" s="13" t="n"/>
+      <c r="U112" s="13" t="n"/>
       <c r="W112" s="11" t="n"/>
       <c r="X112" s="11" t="n"/>
       <c r="Y112" s="11" t="n"/>
@@ -4269,6 +5621,18 @@
       <c r="AA112" s="11" t="n"/>
       <c r="AB112" s="11" t="n"/>
       <c r="AC112" s="11" t="n"/>
+      <c r="AD112" s="11" t="n"/>
+      <c r="AE112" s="11" t="n"/>
+      <c r="AF112" s="11" t="n"/>
+      <c r="AG112" s="11" t="n"/>
+      <c r="AH112" s="11" t="n"/>
+      <c r="AI112" s="11" t="n"/>
+      <c r="AJ112" s="11" t="n"/>
+      <c r="AK112" s="11" t="n"/>
+      <c r="AL112" s="11" t="n"/>
+      <c r="AM112" s="11" t="n"/>
+      <c r="AN112" s="11" t="n"/>
+      <c r="AO112" s="11" t="n"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="B113" s="12" t="inlineStr">
@@ -4289,12 +5653,12 @@
       <c r="M113" s="13" t="n"/>
       <c r="N113" s="13" t="n"/>
       <c r="O113" s="13" t="n"/>
-      <c r="Q113" s="11" t="n"/>
-      <c r="R113" s="11" t="n"/>
-      <c r="S113" s="11" t="n"/>
-      <c r="T113" s="11" t="n"/>
-      <c r="U113" s="11" t="n"/>
-      <c r="V113" s="11" t="n"/>
+      <c r="P113" s="13" t="n"/>
+      <c r="Q113" s="13" t="n"/>
+      <c r="R113" s="13" t="n"/>
+      <c r="S113" s="13" t="n"/>
+      <c r="T113" s="13" t="n"/>
+      <c r="U113" s="13" t="n"/>
       <c r="W113" s="11" t="n"/>
       <c r="X113" s="11" t="n"/>
       <c r="Y113" s="11" t="n"/>
@@ -4302,6 +5666,18 @@
       <c r="AA113" s="11" t="n"/>
       <c r="AB113" s="11" t="n"/>
       <c r="AC113" s="11" t="n"/>
+      <c r="AD113" s="11" t="n"/>
+      <c r="AE113" s="11" t="n"/>
+      <c r="AF113" s="11" t="n"/>
+      <c r="AG113" s="11" t="n"/>
+      <c r="AH113" s="11" t="n"/>
+      <c r="AI113" s="11" t="n"/>
+      <c r="AJ113" s="11" t="n"/>
+      <c r="AK113" s="11" t="n"/>
+      <c r="AL113" s="11" t="n"/>
+      <c r="AM113" s="11" t="n"/>
+      <c r="AN113" s="11" t="n"/>
+      <c r="AO113" s="11" t="n"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="B114" s="9" t="inlineStr">
@@ -4322,12 +5698,12 @@
       <c r="M114" s="10" t="n"/>
       <c r="N114" s="10" t="n"/>
       <c r="O114" s="10" t="n"/>
-      <c r="Q114" s="11" t="n"/>
-      <c r="R114" s="11" t="n"/>
-      <c r="S114" s="11" t="n"/>
-      <c r="T114" s="11" t="n"/>
-      <c r="U114" s="11" t="n"/>
-      <c r="V114" s="11" t="n"/>
+      <c r="P114" s="10" t="n"/>
+      <c r="Q114" s="10" t="n"/>
+      <c r="R114" s="10" t="n"/>
+      <c r="S114" s="10" t="n"/>
+      <c r="T114" s="10" t="n"/>
+      <c r="U114" s="10" t="n"/>
       <c r="W114" s="11" t="n"/>
       <c r="X114" s="11" t="n"/>
       <c r="Y114" s="11" t="n"/>
@@ -4335,6 +5711,18 @@
       <c r="AA114" s="11" t="n"/>
       <c r="AB114" s="11" t="n"/>
       <c r="AC114" s="11" t="n"/>
+      <c r="AD114" s="11" t="n"/>
+      <c r="AE114" s="11" t="n"/>
+      <c r="AF114" s="11" t="n"/>
+      <c r="AG114" s="11" t="n"/>
+      <c r="AH114" s="11" t="n"/>
+      <c r="AI114" s="11" t="n"/>
+      <c r="AJ114" s="11" t="n"/>
+      <c r="AK114" s="11" t="n"/>
+      <c r="AL114" s="11" t="n"/>
+      <c r="AM114" s="11" t="n"/>
+      <c r="AN114" s="11" t="n"/>
+      <c r="AO114" s="11" t="n"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="B115" s="9" t="inlineStr">
@@ -4355,12 +5743,12 @@
       <c r="M115" s="10" t="n"/>
       <c r="N115" s="10" t="n"/>
       <c r="O115" s="10" t="n"/>
-      <c r="Q115" s="11" t="n"/>
-      <c r="R115" s="11" t="n"/>
-      <c r="S115" s="11" t="n"/>
-      <c r="T115" s="11" t="n"/>
-      <c r="U115" s="11" t="n"/>
-      <c r="V115" s="11" t="n"/>
+      <c r="P115" s="10" t="n"/>
+      <c r="Q115" s="10" t="n"/>
+      <c r="R115" s="10" t="n"/>
+      <c r="S115" s="10" t="n"/>
+      <c r="T115" s="10" t="n"/>
+      <c r="U115" s="10" t="n"/>
       <c r="W115" s="11" t="n"/>
       <c r="X115" s="11" t="n"/>
       <c r="Y115" s="11" t="n"/>
@@ -4368,6 +5756,18 @@
       <c r="AA115" s="11" t="n"/>
       <c r="AB115" s="11" t="n"/>
       <c r="AC115" s="11" t="n"/>
+      <c r="AD115" s="11" t="n"/>
+      <c r="AE115" s="11" t="n"/>
+      <c r="AF115" s="11" t="n"/>
+      <c r="AG115" s="11" t="n"/>
+      <c r="AH115" s="11" t="n"/>
+      <c r="AI115" s="11" t="n"/>
+      <c r="AJ115" s="11" t="n"/>
+      <c r="AK115" s="11" t="n"/>
+      <c r="AL115" s="11" t="n"/>
+      <c r="AM115" s="11" t="n"/>
+      <c r="AN115" s="11" t="n"/>
+      <c r="AO115" s="11" t="n"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="B116" s="12" t="inlineStr">
@@ -4388,12 +5788,12 @@
       <c r="M116" s="13" t="n"/>
       <c r="N116" s="13" t="n"/>
       <c r="O116" s="13" t="n"/>
-      <c r="Q116" s="11" t="n"/>
-      <c r="R116" s="11" t="n"/>
-      <c r="S116" s="11" t="n"/>
-      <c r="T116" s="11" t="n"/>
-      <c r="U116" s="11" t="n"/>
-      <c r="V116" s="11" t="n"/>
+      <c r="P116" s="13" t="n"/>
+      <c r="Q116" s="13" t="n"/>
+      <c r="R116" s="13" t="n"/>
+      <c r="S116" s="13" t="n"/>
+      <c r="T116" s="13" t="n"/>
+      <c r="U116" s="13" t="n"/>
       <c r="W116" s="11" t="n"/>
       <c r="X116" s="11" t="n"/>
       <c r="Y116" s="11" t="n"/>
@@ -4401,6 +5801,18 @@
       <c r="AA116" s="11" t="n"/>
       <c r="AB116" s="11" t="n"/>
       <c r="AC116" s="11" t="n"/>
+      <c r="AD116" s="11" t="n"/>
+      <c r="AE116" s="11" t="n"/>
+      <c r="AF116" s="11" t="n"/>
+      <c r="AG116" s="11" t="n"/>
+      <c r="AH116" s="11" t="n"/>
+      <c r="AI116" s="11" t="n"/>
+      <c r="AJ116" s="11" t="n"/>
+      <c r="AK116" s="11" t="n"/>
+      <c r="AL116" s="11" t="n"/>
+      <c r="AM116" s="11" t="n"/>
+      <c r="AN116" s="11" t="n"/>
+      <c r="AO116" s="11" t="n"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="B117" s="9" t="inlineStr">
@@ -4421,12 +5833,12 @@
       <c r="M117" s="10" t="n"/>
       <c r="N117" s="10" t="n"/>
       <c r="O117" s="10" t="n"/>
-      <c r="Q117" s="11" t="n"/>
-      <c r="R117" s="11" t="n"/>
-      <c r="S117" s="11" t="n"/>
-      <c r="T117" s="11" t="n"/>
-      <c r="U117" s="11" t="n"/>
-      <c r="V117" s="11" t="n"/>
+      <c r="P117" s="10" t="n"/>
+      <c r="Q117" s="10" t="n"/>
+      <c r="R117" s="10" t="n"/>
+      <c r="S117" s="10" t="n"/>
+      <c r="T117" s="10" t="n"/>
+      <c r="U117" s="10" t="n"/>
       <c r="W117" s="11" t="n"/>
       <c r="X117" s="11" t="n"/>
       <c r="Y117" s="11" t="n"/>
@@ -4434,6 +5846,18 @@
       <c r="AA117" s="11" t="n"/>
       <c r="AB117" s="11" t="n"/>
       <c r="AC117" s="11" t="n"/>
+      <c r="AD117" s="11" t="n"/>
+      <c r="AE117" s="11" t="n"/>
+      <c r="AF117" s="11" t="n"/>
+      <c r="AG117" s="11" t="n"/>
+      <c r="AH117" s="11" t="n"/>
+      <c r="AI117" s="11" t="n"/>
+      <c r="AJ117" s="11" t="n"/>
+      <c r="AK117" s="11" t="n"/>
+      <c r="AL117" s="11" t="n"/>
+      <c r="AM117" s="11" t="n"/>
+      <c r="AN117" s="11" t="n"/>
+      <c r="AO117" s="11" t="n"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="B118" s="12" t="inlineStr">
@@ -4454,12 +5878,12 @@
       <c r="M118" s="13" t="n"/>
       <c r="N118" s="13" t="n"/>
       <c r="O118" s="13" t="n"/>
-      <c r="Q118" s="11" t="n"/>
-      <c r="R118" s="11" t="n"/>
-      <c r="S118" s="11" t="n"/>
-      <c r="T118" s="11" t="n"/>
-      <c r="U118" s="11" t="n"/>
-      <c r="V118" s="11" t="n"/>
+      <c r="P118" s="13" t="n"/>
+      <c r="Q118" s="13" t="n"/>
+      <c r="R118" s="13" t="n"/>
+      <c r="S118" s="13" t="n"/>
+      <c r="T118" s="13" t="n"/>
+      <c r="U118" s="13" t="n"/>
       <c r="W118" s="11" t="n"/>
       <c r="X118" s="11" t="n"/>
       <c r="Y118" s="11" t="n"/>
@@ -4467,6 +5891,18 @@
       <c r="AA118" s="11" t="n"/>
       <c r="AB118" s="11" t="n"/>
       <c r="AC118" s="11" t="n"/>
+      <c r="AD118" s="11" t="n"/>
+      <c r="AE118" s="11" t="n"/>
+      <c r="AF118" s="11" t="n"/>
+      <c r="AG118" s="11" t="n"/>
+      <c r="AH118" s="11" t="n"/>
+      <c r="AI118" s="11" t="n"/>
+      <c r="AJ118" s="11" t="n"/>
+      <c r="AK118" s="11" t="n"/>
+      <c r="AL118" s="11" t="n"/>
+      <c r="AM118" s="11" t="n"/>
+      <c r="AN118" s="11" t="n"/>
+      <c r="AO118" s="11" t="n"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
       <c r="B119" s="9" t="inlineStr">
@@ -4487,12 +5923,12 @@
       <c r="M119" s="10" t="n"/>
       <c r="N119" s="10" t="n"/>
       <c r="O119" s="10" t="n"/>
-      <c r="Q119" s="11" t="n"/>
-      <c r="R119" s="11" t="n"/>
-      <c r="S119" s="11" t="n"/>
-      <c r="T119" s="11" t="n"/>
-      <c r="U119" s="11" t="n"/>
-      <c r="V119" s="11" t="n"/>
+      <c r="P119" s="10" t="n"/>
+      <c r="Q119" s="10" t="n"/>
+      <c r="R119" s="10" t="n"/>
+      <c r="S119" s="10" t="n"/>
+      <c r="T119" s="10" t="n"/>
+      <c r="U119" s="10" t="n"/>
       <c r="W119" s="11" t="n"/>
       <c r="X119" s="11" t="n"/>
       <c r="Y119" s="11" t="n"/>
@@ -4500,6 +5936,18 @@
       <c r="AA119" s="11" t="n"/>
       <c r="AB119" s="11" t="n"/>
       <c r="AC119" s="11" t="n"/>
+      <c r="AD119" s="11" t="n"/>
+      <c r="AE119" s="11" t="n"/>
+      <c r="AF119" s="11" t="n"/>
+      <c r="AG119" s="11" t="n"/>
+      <c r="AH119" s="11" t="n"/>
+      <c r="AI119" s="11" t="n"/>
+      <c r="AJ119" s="11" t="n"/>
+      <c r="AK119" s="11" t="n"/>
+      <c r="AL119" s="11" t="n"/>
+      <c r="AM119" s="11" t="n"/>
+      <c r="AN119" s="11" t="n"/>
+      <c r="AO119" s="11" t="n"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="B122" s="5" t="inlineStr">
@@ -4512,7 +5960,7 @@
           <t>100+ Segment - Over Time Period</t>
         </is>
       </c>
-      <c r="Q122" s="6" t="inlineStr">
+      <c r="W122" s="6" t="inlineStr">
         <is>
           <t>100+ Segment - Over Time Period - Difference</t>
         </is>
@@ -4589,69 +6037,129 @@
           <t>SPTx2</t>
         </is>
       </c>
+      <c r="P123" s="8" t="inlineStr">
+        <is>
+          <t>1-star Pack</t>
+        </is>
+      </c>
       <c r="Q123" s="8" t="inlineStr">
         <is>
+          <t>2-star Pack</t>
+        </is>
+      </c>
+      <c r="R123" s="8" t="inlineStr">
+        <is>
+          <t>3-star Pack</t>
+        </is>
+      </c>
+      <c r="S123" s="8" t="inlineStr">
+        <is>
+          <t>4-star Pack</t>
+        </is>
+      </c>
+      <c r="T123" s="8" t="inlineStr">
+        <is>
+          <t>5-star Pack</t>
+        </is>
+      </c>
+      <c r="U123" s="8" t="inlineStr">
+        <is>
+          <t>6-star Pack</t>
+        </is>
+      </c>
+      <c r="W123" s="8" t="inlineStr">
+        <is>
           <t>HC</t>
         </is>
       </c>
-      <c r="R123" s="8" t="inlineStr">
+      <c r="X123" s="8" t="inlineStr">
         <is>
           <t>Slingshot</t>
         </is>
       </c>
-      <c r="S123" s="8" t="inlineStr">
+      <c r="Y123" s="8" t="inlineStr">
         <is>
           <t>Shuffle</t>
         </is>
       </c>
-      <c r="T123" s="8" t="inlineStr">
+      <c r="Z123" s="8" t="inlineStr">
         <is>
           <t>Comet</t>
         </is>
       </c>
-      <c r="U123" s="8" t="inlineStr">
+      <c r="AA123" s="8" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="V123" s="8" t="inlineStr">
+      <c r="AB123" s="8" t="inlineStr">
         <is>
           <t>Chuck</t>
         </is>
       </c>
-      <c r="W123" s="8" t="inlineStr">
+      <c r="AC123" s="8" t="inlineStr">
         <is>
           <t>Bomb</t>
         </is>
       </c>
-      <c r="X123" s="8" t="inlineStr">
+      <c r="AD123" s="8" t="inlineStr">
         <is>
           <t>UL Bomb</t>
         </is>
       </c>
-      <c r="Y123" s="8" t="inlineStr">
+      <c r="AE123" s="8" t="inlineStr">
         <is>
           <t>UL Chuck</t>
         </is>
       </c>
-      <c r="Z123" s="8" t="inlineStr">
+      <c r="AF123" s="8" t="inlineStr">
         <is>
           <t>UL Red</t>
         </is>
       </c>
-      <c r="AA123" s="8" t="inlineStr">
+      <c r="AG123" s="8" t="inlineStr">
         <is>
           <t>Unlimited Lives</t>
         </is>
       </c>
-      <c r="AB123" s="8" t="inlineStr">
+      <c r="AH123" s="8" t="inlineStr">
         <is>
           <t>SPT</t>
         </is>
       </c>
-      <c r="AC123" s="8" t="inlineStr">
+      <c r="AI123" s="8" t="inlineStr">
         <is>
           <t>SPTx2</t>
+        </is>
+      </c>
+      <c r="AJ123" s="8" t="inlineStr">
+        <is>
+          <t>1-star Pack</t>
+        </is>
+      </c>
+      <c r="AK123" s="8" t="inlineStr">
+        <is>
+          <t>2-star Pack</t>
+        </is>
+      </c>
+      <c r="AL123" s="8" t="inlineStr">
+        <is>
+          <t>3-star Pack</t>
+        </is>
+      </c>
+      <c r="AM123" s="8" t="inlineStr">
+        <is>
+          <t>4-star Pack</t>
+        </is>
+      </c>
+      <c r="AN123" s="8" t="inlineStr">
+        <is>
+          <t>5-star Pack</t>
+        </is>
+      </c>
+      <c r="AO123" s="8" t="inlineStr">
+        <is>
+          <t>6-star Pack</t>
         </is>
       </c>
     </row>
@@ -4677,22 +6185,34 @@
       <c r="M124" s="10" t="n"/>
       <c r="N124" s="10" t="n"/>
       <c r="O124" s="10" t="n"/>
-      <c r="Q124" s="11">
+      <c r="P124" s="10" t="n"/>
+      <c r="Q124" s="10" t="n"/>
+      <c r="R124" s="10" t="n"/>
+      <c r="S124" s="10" t="n"/>
+      <c r="T124" s="10" t="n"/>
+      <c r="U124" s="10" t="n"/>
+      <c r="W124" s="11">
         <f>LET(payer, $C$3, segment, $B$122, ECOGAINS_DIFF(payer, segment, sim_refresh!$A$1))</f>
         <v/>
       </c>
-      <c r="R124" s="11" t="n"/>
-      <c r="S124" s="11" t="n"/>
-      <c r="T124" s="11" t="n"/>
-      <c r="U124" s="11" t="n"/>
-      <c r="V124" s="11" t="n"/>
-      <c r="W124" s="11" t="n"/>
       <c r="X124" s="11" t="n"/>
       <c r="Y124" s="11" t="n"/>
       <c r="Z124" s="11" t="n"/>
       <c r="AA124" s="11" t="n"/>
       <c r="AB124" s="11" t="n"/>
       <c r="AC124" s="11" t="n"/>
+      <c r="AD124" s="11" t="n"/>
+      <c r="AE124" s="11" t="n"/>
+      <c r="AF124" s="11" t="n"/>
+      <c r="AG124" s="11" t="n"/>
+      <c r="AH124" s="11" t="n"/>
+      <c r="AI124" s="11" t="n"/>
+      <c r="AJ124" s="11" t="n"/>
+      <c r="AK124" s="11" t="n"/>
+      <c r="AL124" s="11" t="n"/>
+      <c r="AM124" s="11" t="n"/>
+      <c r="AN124" s="11" t="n"/>
+      <c r="AO124" s="11" t="n"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
       <c r="B125" s="12" t="inlineStr">
@@ -4713,12 +6233,12 @@
       <c r="M125" s="13" t="n"/>
       <c r="N125" s="13" t="n"/>
       <c r="O125" s="13" t="n"/>
-      <c r="Q125" s="11" t="n"/>
-      <c r="R125" s="11" t="n"/>
-      <c r="S125" s="11" t="n"/>
-      <c r="T125" s="11" t="n"/>
-      <c r="U125" s="11" t="n"/>
-      <c r="V125" s="11" t="n"/>
+      <c r="P125" s="13" t="n"/>
+      <c r="Q125" s="13" t="n"/>
+      <c r="R125" s="13" t="n"/>
+      <c r="S125" s="13" t="n"/>
+      <c r="T125" s="13" t="n"/>
+      <c r="U125" s="13" t="n"/>
       <c r="W125" s="11" t="n"/>
       <c r="X125" s="11" t="n"/>
       <c r="Y125" s="11" t="n"/>
@@ -4726,6 +6246,18 @@
       <c r="AA125" s="11" t="n"/>
       <c r="AB125" s="11" t="n"/>
       <c r="AC125" s="11" t="n"/>
+      <c r="AD125" s="11" t="n"/>
+      <c r="AE125" s="11" t="n"/>
+      <c r="AF125" s="11" t="n"/>
+      <c r="AG125" s="11" t="n"/>
+      <c r="AH125" s="11" t="n"/>
+      <c r="AI125" s="11" t="n"/>
+      <c r="AJ125" s="11" t="n"/>
+      <c r="AK125" s="11" t="n"/>
+      <c r="AL125" s="11" t="n"/>
+      <c r="AM125" s="11" t="n"/>
+      <c r="AN125" s="11" t="n"/>
+      <c r="AO125" s="11" t="n"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
       <c r="B126" s="12" t="inlineStr">
@@ -4746,12 +6278,12 @@
       <c r="M126" s="13" t="n"/>
       <c r="N126" s="13" t="n"/>
       <c r="O126" s="13" t="n"/>
-      <c r="Q126" s="11" t="n"/>
-      <c r="R126" s="11" t="n"/>
-      <c r="S126" s="11" t="n"/>
-      <c r="T126" s="11" t="n"/>
-      <c r="U126" s="11" t="n"/>
-      <c r="V126" s="11" t="n"/>
+      <c r="P126" s="13" t="n"/>
+      <c r="Q126" s="13" t="n"/>
+      <c r="R126" s="13" t="n"/>
+      <c r="S126" s="13" t="n"/>
+      <c r="T126" s="13" t="n"/>
+      <c r="U126" s="13" t="n"/>
       <c r="W126" s="11" t="n"/>
       <c r="X126" s="11" t="n"/>
       <c r="Y126" s="11" t="n"/>
@@ -4759,6 +6291,18 @@
       <c r="AA126" s="11" t="n"/>
       <c r="AB126" s="11" t="n"/>
       <c r="AC126" s="11" t="n"/>
+      <c r="AD126" s="11" t="n"/>
+      <c r="AE126" s="11" t="n"/>
+      <c r="AF126" s="11" t="n"/>
+      <c r="AG126" s="11" t="n"/>
+      <c r="AH126" s="11" t="n"/>
+      <c r="AI126" s="11" t="n"/>
+      <c r="AJ126" s="11" t="n"/>
+      <c r="AK126" s="11" t="n"/>
+      <c r="AL126" s="11" t="n"/>
+      <c r="AM126" s="11" t="n"/>
+      <c r="AN126" s="11" t="n"/>
+      <c r="AO126" s="11" t="n"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
       <c r="B127" s="12" t="inlineStr">
@@ -4779,12 +6323,12 @@
       <c r="M127" s="13" t="n"/>
       <c r="N127" s="13" t="n"/>
       <c r="O127" s="13" t="n"/>
-      <c r="Q127" s="11" t="n"/>
-      <c r="R127" s="11" t="n"/>
-      <c r="S127" s="11" t="n"/>
-      <c r="T127" s="11" t="n"/>
-      <c r="U127" s="11" t="n"/>
-      <c r="V127" s="11" t="n"/>
+      <c r="P127" s="13" t="n"/>
+      <c r="Q127" s="13" t="n"/>
+      <c r="R127" s="13" t="n"/>
+      <c r="S127" s="13" t="n"/>
+      <c r="T127" s="13" t="n"/>
+      <c r="U127" s="13" t="n"/>
       <c r="W127" s="11" t="n"/>
       <c r="X127" s="11" t="n"/>
       <c r="Y127" s="11" t="n"/>
@@ -4792,6 +6336,18 @@
       <c r="AA127" s="11" t="n"/>
       <c r="AB127" s="11" t="n"/>
       <c r="AC127" s="11" t="n"/>
+      <c r="AD127" s="11" t="n"/>
+      <c r="AE127" s="11" t="n"/>
+      <c r="AF127" s="11" t="n"/>
+      <c r="AG127" s="11" t="n"/>
+      <c r="AH127" s="11" t="n"/>
+      <c r="AI127" s="11" t="n"/>
+      <c r="AJ127" s="11" t="n"/>
+      <c r="AK127" s="11" t="n"/>
+      <c r="AL127" s="11" t="n"/>
+      <c r="AM127" s="11" t="n"/>
+      <c r="AN127" s="11" t="n"/>
+      <c r="AO127" s="11" t="n"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
       <c r="B128" s="9" t="inlineStr">
@@ -4812,12 +6368,12 @@
       <c r="M128" s="10" t="n"/>
       <c r="N128" s="10" t="n"/>
       <c r="O128" s="10" t="n"/>
-      <c r="Q128" s="11" t="n"/>
-      <c r="R128" s="11" t="n"/>
-      <c r="S128" s="11" t="n"/>
-      <c r="T128" s="11" t="n"/>
-      <c r="U128" s="11" t="n"/>
-      <c r="V128" s="11" t="n"/>
+      <c r="P128" s="10" t="n"/>
+      <c r="Q128" s="10" t="n"/>
+      <c r="R128" s="10" t="n"/>
+      <c r="S128" s="10" t="n"/>
+      <c r="T128" s="10" t="n"/>
+      <c r="U128" s="10" t="n"/>
       <c r="W128" s="11" t="n"/>
       <c r="X128" s="11" t="n"/>
       <c r="Y128" s="11" t="n"/>
@@ -4825,6 +6381,18 @@
       <c r="AA128" s="11" t="n"/>
       <c r="AB128" s="11" t="n"/>
       <c r="AC128" s="11" t="n"/>
+      <c r="AD128" s="11" t="n"/>
+      <c r="AE128" s="11" t="n"/>
+      <c r="AF128" s="11" t="n"/>
+      <c r="AG128" s="11" t="n"/>
+      <c r="AH128" s="11" t="n"/>
+      <c r="AI128" s="11" t="n"/>
+      <c r="AJ128" s="11" t="n"/>
+      <c r="AK128" s="11" t="n"/>
+      <c r="AL128" s="11" t="n"/>
+      <c r="AM128" s="11" t="n"/>
+      <c r="AN128" s="11" t="n"/>
+      <c r="AO128" s="11" t="n"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
       <c r="B129" s="14" t="inlineStr">
@@ -4845,12 +6413,12 @@
       <c r="M129" s="13" t="n"/>
       <c r="N129" s="13" t="n"/>
       <c r="O129" s="13" t="n"/>
-      <c r="Q129" s="11" t="n"/>
-      <c r="R129" s="11" t="n"/>
-      <c r="S129" s="11" t="n"/>
-      <c r="T129" s="11" t="n"/>
-      <c r="U129" s="11" t="n"/>
-      <c r="V129" s="11" t="n"/>
+      <c r="P129" s="13" t="n"/>
+      <c r="Q129" s="13" t="n"/>
+      <c r="R129" s="13" t="n"/>
+      <c r="S129" s="13" t="n"/>
+      <c r="T129" s="13" t="n"/>
+      <c r="U129" s="13" t="n"/>
       <c r="W129" s="11" t="n"/>
       <c r="X129" s="11" t="n"/>
       <c r="Y129" s="11" t="n"/>
@@ -4858,6 +6426,18 @@
       <c r="AA129" s="11" t="n"/>
       <c r="AB129" s="11" t="n"/>
       <c r="AC129" s="11" t="n"/>
+      <c r="AD129" s="11" t="n"/>
+      <c r="AE129" s="11" t="n"/>
+      <c r="AF129" s="11" t="n"/>
+      <c r="AG129" s="11" t="n"/>
+      <c r="AH129" s="11" t="n"/>
+      <c r="AI129" s="11" t="n"/>
+      <c r="AJ129" s="11" t="n"/>
+      <c r="AK129" s="11" t="n"/>
+      <c r="AL129" s="11" t="n"/>
+      <c r="AM129" s="11" t="n"/>
+      <c r="AN129" s="11" t="n"/>
+      <c r="AO129" s="11" t="n"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
       <c r="B130" s="14" t="inlineStr">
@@ -4878,12 +6458,12 @@
       <c r="M130" s="13" t="n"/>
       <c r="N130" s="13" t="n"/>
       <c r="O130" s="13" t="n"/>
-      <c r="Q130" s="11" t="n"/>
-      <c r="R130" s="11" t="n"/>
-      <c r="S130" s="11" t="n"/>
-      <c r="T130" s="11" t="n"/>
-      <c r="U130" s="11" t="n"/>
-      <c r="V130" s="11" t="n"/>
+      <c r="P130" s="13" t="n"/>
+      <c r="Q130" s="13" t="n"/>
+      <c r="R130" s="13" t="n"/>
+      <c r="S130" s="13" t="n"/>
+      <c r="T130" s="13" t="n"/>
+      <c r="U130" s="13" t="n"/>
       <c r="W130" s="11" t="n"/>
       <c r="X130" s="11" t="n"/>
       <c r="Y130" s="11" t="n"/>
@@ -4891,6 +6471,18 @@
       <c r="AA130" s="11" t="n"/>
       <c r="AB130" s="11" t="n"/>
       <c r="AC130" s="11" t="n"/>
+      <c r="AD130" s="11" t="n"/>
+      <c r="AE130" s="11" t="n"/>
+      <c r="AF130" s="11" t="n"/>
+      <c r="AG130" s="11" t="n"/>
+      <c r="AH130" s="11" t="n"/>
+      <c r="AI130" s="11" t="n"/>
+      <c r="AJ130" s="11" t="n"/>
+      <c r="AK130" s="11" t="n"/>
+      <c r="AL130" s="11" t="n"/>
+      <c r="AM130" s="11" t="n"/>
+      <c r="AN130" s="11" t="n"/>
+      <c r="AO130" s="11" t="n"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
       <c r="B131" s="9" t="inlineStr">
@@ -4911,12 +6503,12 @@
       <c r="M131" s="10" t="n"/>
       <c r="N131" s="10" t="n"/>
       <c r="O131" s="10" t="n"/>
-      <c r="Q131" s="11" t="n"/>
-      <c r="R131" s="11" t="n"/>
-      <c r="S131" s="11" t="n"/>
-      <c r="T131" s="11" t="n"/>
-      <c r="U131" s="11" t="n"/>
-      <c r="V131" s="11" t="n"/>
+      <c r="P131" s="10" t="n"/>
+      <c r="Q131" s="10" t="n"/>
+      <c r="R131" s="10" t="n"/>
+      <c r="S131" s="10" t="n"/>
+      <c r="T131" s="10" t="n"/>
+      <c r="U131" s="10" t="n"/>
       <c r="W131" s="11" t="n"/>
       <c r="X131" s="11" t="n"/>
       <c r="Y131" s="11" t="n"/>
@@ -4924,6 +6516,18 @@
       <c r="AA131" s="11" t="n"/>
       <c r="AB131" s="11" t="n"/>
       <c r="AC131" s="11" t="n"/>
+      <c r="AD131" s="11" t="n"/>
+      <c r="AE131" s="11" t="n"/>
+      <c r="AF131" s="11" t="n"/>
+      <c r="AG131" s="11" t="n"/>
+      <c r="AH131" s="11" t="n"/>
+      <c r="AI131" s="11" t="n"/>
+      <c r="AJ131" s="11" t="n"/>
+      <c r="AK131" s="11" t="n"/>
+      <c r="AL131" s="11" t="n"/>
+      <c r="AM131" s="11" t="n"/>
+      <c r="AN131" s="11" t="n"/>
+      <c r="AO131" s="11" t="n"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
       <c r="B132" s="12" t="inlineStr">
@@ -4944,12 +6548,12 @@
       <c r="M132" s="13" t="n"/>
       <c r="N132" s="13" t="n"/>
       <c r="O132" s="13" t="n"/>
-      <c r="Q132" s="11" t="n"/>
-      <c r="R132" s="11" t="n"/>
-      <c r="S132" s="11" t="n"/>
-      <c r="T132" s="11" t="n"/>
-      <c r="U132" s="11" t="n"/>
-      <c r="V132" s="11" t="n"/>
+      <c r="P132" s="13" t="n"/>
+      <c r="Q132" s="13" t="n"/>
+      <c r="R132" s="13" t="n"/>
+      <c r="S132" s="13" t="n"/>
+      <c r="T132" s="13" t="n"/>
+      <c r="U132" s="13" t="n"/>
       <c r="W132" s="11" t="n"/>
       <c r="X132" s="11" t="n"/>
       <c r="Y132" s="11" t="n"/>
@@ -4957,6 +6561,18 @@
       <c r="AA132" s="11" t="n"/>
       <c r="AB132" s="11" t="n"/>
       <c r="AC132" s="11" t="n"/>
+      <c r="AD132" s="11" t="n"/>
+      <c r="AE132" s="11" t="n"/>
+      <c r="AF132" s="11" t="n"/>
+      <c r="AG132" s="11" t="n"/>
+      <c r="AH132" s="11" t="n"/>
+      <c r="AI132" s="11" t="n"/>
+      <c r="AJ132" s="11" t="n"/>
+      <c r="AK132" s="11" t="n"/>
+      <c r="AL132" s="11" t="n"/>
+      <c r="AM132" s="11" t="n"/>
+      <c r="AN132" s="11" t="n"/>
+      <c r="AO132" s="11" t="n"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
       <c r="B133" s="12" t="inlineStr">
@@ -4977,12 +6593,12 @@
       <c r="M133" s="13" t="n"/>
       <c r="N133" s="13" t="n"/>
       <c r="O133" s="13" t="n"/>
-      <c r="Q133" s="11" t="n"/>
-      <c r="R133" s="11" t="n"/>
-      <c r="S133" s="11" t="n"/>
-      <c r="T133" s="11" t="n"/>
-      <c r="U133" s="11" t="n"/>
-      <c r="V133" s="11" t="n"/>
+      <c r="P133" s="13" t="n"/>
+      <c r="Q133" s="13" t="n"/>
+      <c r="R133" s="13" t="n"/>
+      <c r="S133" s="13" t="n"/>
+      <c r="T133" s="13" t="n"/>
+      <c r="U133" s="13" t="n"/>
       <c r="W133" s="11" t="n"/>
       <c r="X133" s="11" t="n"/>
       <c r="Y133" s="11" t="n"/>
@@ -4990,6 +6606,18 @@
       <c r="AA133" s="11" t="n"/>
       <c r="AB133" s="11" t="n"/>
       <c r="AC133" s="11" t="n"/>
+      <c r="AD133" s="11" t="n"/>
+      <c r="AE133" s="11" t="n"/>
+      <c r="AF133" s="11" t="n"/>
+      <c r="AG133" s="11" t="n"/>
+      <c r="AH133" s="11" t="n"/>
+      <c r="AI133" s="11" t="n"/>
+      <c r="AJ133" s="11" t="n"/>
+      <c r="AK133" s="11" t="n"/>
+      <c r="AL133" s="11" t="n"/>
+      <c r="AM133" s="11" t="n"/>
+      <c r="AN133" s="11" t="n"/>
+      <c r="AO133" s="11" t="n"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
       <c r="B134" s="12" t="inlineStr">
@@ -5010,12 +6638,12 @@
       <c r="M134" s="13" t="n"/>
       <c r="N134" s="13" t="n"/>
       <c r="O134" s="13" t="n"/>
-      <c r="Q134" s="11" t="n"/>
-      <c r="R134" s="11" t="n"/>
-      <c r="S134" s="11" t="n"/>
-      <c r="T134" s="11" t="n"/>
-      <c r="U134" s="11" t="n"/>
-      <c r="V134" s="11" t="n"/>
+      <c r="P134" s="13" t="n"/>
+      <c r="Q134" s="13" t="n"/>
+      <c r="R134" s="13" t="n"/>
+      <c r="S134" s="13" t="n"/>
+      <c r="T134" s="13" t="n"/>
+      <c r="U134" s="13" t="n"/>
       <c r="W134" s="11" t="n"/>
       <c r="X134" s="11" t="n"/>
       <c r="Y134" s="11" t="n"/>
@@ -5023,6 +6651,18 @@
       <c r="AA134" s="11" t="n"/>
       <c r="AB134" s="11" t="n"/>
       <c r="AC134" s="11" t="n"/>
+      <c r="AD134" s="11" t="n"/>
+      <c r="AE134" s="11" t="n"/>
+      <c r="AF134" s="11" t="n"/>
+      <c r="AG134" s="11" t="n"/>
+      <c r="AH134" s="11" t="n"/>
+      <c r="AI134" s="11" t="n"/>
+      <c r="AJ134" s="11" t="n"/>
+      <c r="AK134" s="11" t="n"/>
+      <c r="AL134" s="11" t="n"/>
+      <c r="AM134" s="11" t="n"/>
+      <c r="AN134" s="11" t="n"/>
+      <c r="AO134" s="11" t="n"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
       <c r="B135" s="12" t="inlineStr">
@@ -5043,12 +6683,12 @@
       <c r="M135" s="13" t="n"/>
       <c r="N135" s="13" t="n"/>
       <c r="O135" s="13" t="n"/>
-      <c r="Q135" s="11" t="n"/>
-      <c r="R135" s="11" t="n"/>
-      <c r="S135" s="11" t="n"/>
-      <c r="T135" s="11" t="n"/>
-      <c r="U135" s="11" t="n"/>
-      <c r="V135" s="11" t="n"/>
+      <c r="P135" s="13" t="n"/>
+      <c r="Q135" s="13" t="n"/>
+      <c r="R135" s="13" t="n"/>
+      <c r="S135" s="13" t="n"/>
+      <c r="T135" s="13" t="n"/>
+      <c r="U135" s="13" t="n"/>
       <c r="W135" s="11" t="n"/>
       <c r="X135" s="11" t="n"/>
       <c r="Y135" s="11" t="n"/>
@@ -5056,6 +6696,18 @@
       <c r="AA135" s="11" t="n"/>
       <c r="AB135" s="11" t="n"/>
       <c r="AC135" s="11" t="n"/>
+      <c r="AD135" s="11" t="n"/>
+      <c r="AE135" s="11" t="n"/>
+      <c r="AF135" s="11" t="n"/>
+      <c r="AG135" s="11" t="n"/>
+      <c r="AH135" s="11" t="n"/>
+      <c r="AI135" s="11" t="n"/>
+      <c r="AJ135" s="11" t="n"/>
+      <c r="AK135" s="11" t="n"/>
+      <c r="AL135" s="11" t="n"/>
+      <c r="AM135" s="11" t="n"/>
+      <c r="AN135" s="11" t="n"/>
+      <c r="AO135" s="11" t="n"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
       <c r="B136" s="9" t="inlineStr">
@@ -5076,12 +6728,12 @@
       <c r="M136" s="10" t="n"/>
       <c r="N136" s="10" t="n"/>
       <c r="O136" s="10" t="n"/>
-      <c r="Q136" s="11" t="n"/>
-      <c r="R136" s="11" t="n"/>
-      <c r="S136" s="11" t="n"/>
-      <c r="T136" s="11" t="n"/>
-      <c r="U136" s="11" t="n"/>
-      <c r="V136" s="11" t="n"/>
+      <c r="P136" s="10" t="n"/>
+      <c r="Q136" s="10" t="n"/>
+      <c r="R136" s="10" t="n"/>
+      <c r="S136" s="10" t="n"/>
+      <c r="T136" s="10" t="n"/>
+      <c r="U136" s="10" t="n"/>
       <c r="W136" s="11" t="n"/>
       <c r="X136" s="11" t="n"/>
       <c r="Y136" s="11" t="n"/>
@@ -5089,6 +6741,18 @@
       <c r="AA136" s="11" t="n"/>
       <c r="AB136" s="11" t="n"/>
       <c r="AC136" s="11" t="n"/>
+      <c r="AD136" s="11" t="n"/>
+      <c r="AE136" s="11" t="n"/>
+      <c r="AF136" s="11" t="n"/>
+      <c r="AG136" s="11" t="n"/>
+      <c r="AH136" s="11" t="n"/>
+      <c r="AI136" s="11" t="n"/>
+      <c r="AJ136" s="11" t="n"/>
+      <c r="AK136" s="11" t="n"/>
+      <c r="AL136" s="11" t="n"/>
+      <c r="AM136" s="11" t="n"/>
+      <c r="AN136" s="11" t="n"/>
+      <c r="AO136" s="11" t="n"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
       <c r="B137" s="12" t="inlineStr">
@@ -5109,12 +6773,12 @@
       <c r="M137" s="13" t="n"/>
       <c r="N137" s="13" t="n"/>
       <c r="O137" s="13" t="n"/>
-      <c r="Q137" s="11" t="n"/>
-      <c r="R137" s="11" t="n"/>
-      <c r="S137" s="11" t="n"/>
-      <c r="T137" s="11" t="n"/>
-      <c r="U137" s="11" t="n"/>
-      <c r="V137" s="11" t="n"/>
+      <c r="P137" s="13" t="n"/>
+      <c r="Q137" s="13" t="n"/>
+      <c r="R137" s="13" t="n"/>
+      <c r="S137" s="13" t="n"/>
+      <c r="T137" s="13" t="n"/>
+      <c r="U137" s="13" t="n"/>
       <c r="W137" s="11" t="n"/>
       <c r="X137" s="11" t="n"/>
       <c r="Y137" s="11" t="n"/>
@@ -5122,6 +6786,18 @@
       <c r="AA137" s="11" t="n"/>
       <c r="AB137" s="11" t="n"/>
       <c r="AC137" s="11" t="n"/>
+      <c r="AD137" s="11" t="n"/>
+      <c r="AE137" s="11" t="n"/>
+      <c r="AF137" s="11" t="n"/>
+      <c r="AG137" s="11" t="n"/>
+      <c r="AH137" s="11" t="n"/>
+      <c r="AI137" s="11" t="n"/>
+      <c r="AJ137" s="11" t="n"/>
+      <c r="AK137" s="11" t="n"/>
+      <c r="AL137" s="11" t="n"/>
+      <c r="AM137" s="11" t="n"/>
+      <c r="AN137" s="11" t="n"/>
+      <c r="AO137" s="11" t="n"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
       <c r="B138" s="12" t="inlineStr">
@@ -5142,12 +6818,12 @@
       <c r="M138" s="13" t="n"/>
       <c r="N138" s="13" t="n"/>
       <c r="O138" s="13" t="n"/>
-      <c r="Q138" s="11" t="n"/>
-      <c r="R138" s="11" t="n"/>
-      <c r="S138" s="11" t="n"/>
-      <c r="T138" s="11" t="n"/>
-      <c r="U138" s="11" t="n"/>
-      <c r="V138" s="11" t="n"/>
+      <c r="P138" s="13" t="n"/>
+      <c r="Q138" s="13" t="n"/>
+      <c r="R138" s="13" t="n"/>
+      <c r="S138" s="13" t="n"/>
+      <c r="T138" s="13" t="n"/>
+      <c r="U138" s="13" t="n"/>
       <c r="W138" s="11" t="n"/>
       <c r="X138" s="11" t="n"/>
       <c r="Y138" s="11" t="n"/>
@@ -5155,6 +6831,18 @@
       <c r="AA138" s="11" t="n"/>
       <c r="AB138" s="11" t="n"/>
       <c r="AC138" s="11" t="n"/>
+      <c r="AD138" s="11" t="n"/>
+      <c r="AE138" s="11" t="n"/>
+      <c r="AF138" s="11" t="n"/>
+      <c r="AG138" s="11" t="n"/>
+      <c r="AH138" s="11" t="n"/>
+      <c r="AI138" s="11" t="n"/>
+      <c r="AJ138" s="11" t="n"/>
+      <c r="AK138" s="11" t="n"/>
+      <c r="AL138" s="11" t="n"/>
+      <c r="AM138" s="11" t="n"/>
+      <c r="AN138" s="11" t="n"/>
+      <c r="AO138" s="11" t="n"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
       <c r="B139" s="12" t="inlineStr">
@@ -5175,12 +6863,12 @@
       <c r="M139" s="13" t="n"/>
       <c r="N139" s="13" t="n"/>
       <c r="O139" s="13" t="n"/>
-      <c r="Q139" s="11" t="n"/>
-      <c r="R139" s="11" t="n"/>
-      <c r="S139" s="11" t="n"/>
-      <c r="T139" s="11" t="n"/>
-      <c r="U139" s="11" t="n"/>
-      <c r="V139" s="11" t="n"/>
+      <c r="P139" s="13" t="n"/>
+      <c r="Q139" s="13" t="n"/>
+      <c r="R139" s="13" t="n"/>
+      <c r="S139" s="13" t="n"/>
+      <c r="T139" s="13" t="n"/>
+      <c r="U139" s="13" t="n"/>
       <c r="W139" s="11" t="n"/>
       <c r="X139" s="11" t="n"/>
       <c r="Y139" s="11" t="n"/>
@@ -5188,6 +6876,18 @@
       <c r="AA139" s="11" t="n"/>
       <c r="AB139" s="11" t="n"/>
       <c r="AC139" s="11" t="n"/>
+      <c r="AD139" s="11" t="n"/>
+      <c r="AE139" s="11" t="n"/>
+      <c r="AF139" s="11" t="n"/>
+      <c r="AG139" s="11" t="n"/>
+      <c r="AH139" s="11" t="n"/>
+      <c r="AI139" s="11" t="n"/>
+      <c r="AJ139" s="11" t="n"/>
+      <c r="AK139" s="11" t="n"/>
+      <c r="AL139" s="11" t="n"/>
+      <c r="AM139" s="11" t="n"/>
+      <c r="AN139" s="11" t="n"/>
+      <c r="AO139" s="11" t="n"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
       <c r="B140" s="14" t="inlineStr">
@@ -5208,12 +6908,12 @@
       <c r="M140" s="13" t="n"/>
       <c r="N140" s="13" t="n"/>
       <c r="O140" s="13" t="n"/>
-      <c r="Q140" s="11" t="n"/>
-      <c r="R140" s="11" t="n"/>
-      <c r="S140" s="11" t="n"/>
-      <c r="T140" s="11" t="n"/>
-      <c r="U140" s="11" t="n"/>
-      <c r="V140" s="11" t="n"/>
+      <c r="P140" s="13" t="n"/>
+      <c r="Q140" s="13" t="n"/>
+      <c r="R140" s="13" t="n"/>
+      <c r="S140" s="13" t="n"/>
+      <c r="T140" s="13" t="n"/>
+      <c r="U140" s="13" t="n"/>
       <c r="W140" s="11" t="n"/>
       <c r="X140" s="11" t="n"/>
       <c r="Y140" s="11" t="n"/>
@@ -5221,6 +6921,18 @@
       <c r="AA140" s="11" t="n"/>
       <c r="AB140" s="11" t="n"/>
       <c r="AC140" s="11" t="n"/>
+      <c r="AD140" s="11" t="n"/>
+      <c r="AE140" s="11" t="n"/>
+      <c r="AF140" s="11" t="n"/>
+      <c r="AG140" s="11" t="n"/>
+      <c r="AH140" s="11" t="n"/>
+      <c r="AI140" s="11" t="n"/>
+      <c r="AJ140" s="11" t="n"/>
+      <c r="AK140" s="11" t="n"/>
+      <c r="AL140" s="11" t="n"/>
+      <c r="AM140" s="11" t="n"/>
+      <c r="AN140" s="11" t="n"/>
+      <c r="AO140" s="11" t="n"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
       <c r="B141" s="12" t="inlineStr">
@@ -5241,12 +6953,12 @@
       <c r="M141" s="13" t="n"/>
       <c r="N141" s="13" t="n"/>
       <c r="O141" s="13" t="n"/>
-      <c r="Q141" s="11" t="n"/>
-      <c r="R141" s="11" t="n"/>
-      <c r="S141" s="11" t="n"/>
-      <c r="T141" s="11" t="n"/>
-      <c r="U141" s="11" t="n"/>
-      <c r="V141" s="11" t="n"/>
+      <c r="P141" s="13" t="n"/>
+      <c r="Q141" s="13" t="n"/>
+      <c r="R141" s="13" t="n"/>
+      <c r="S141" s="13" t="n"/>
+      <c r="T141" s="13" t="n"/>
+      <c r="U141" s="13" t="n"/>
       <c r="W141" s="11" t="n"/>
       <c r="X141" s="11" t="n"/>
       <c r="Y141" s="11" t="n"/>
@@ -5254,6 +6966,18 @@
       <c r="AA141" s="11" t="n"/>
       <c r="AB141" s="11" t="n"/>
       <c r="AC141" s="11" t="n"/>
+      <c r="AD141" s="11" t="n"/>
+      <c r="AE141" s="11" t="n"/>
+      <c r="AF141" s="11" t="n"/>
+      <c r="AG141" s="11" t="n"/>
+      <c r="AH141" s="11" t="n"/>
+      <c r="AI141" s="11" t="n"/>
+      <c r="AJ141" s="11" t="n"/>
+      <c r="AK141" s="11" t="n"/>
+      <c r="AL141" s="11" t="n"/>
+      <c r="AM141" s="11" t="n"/>
+      <c r="AN141" s="11" t="n"/>
+      <c r="AO141" s="11" t="n"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
       <c r="B142" s="12" t="inlineStr">
@@ -5274,12 +6998,12 @@
       <c r="M142" s="13" t="n"/>
       <c r="N142" s="13" t="n"/>
       <c r="O142" s="13" t="n"/>
-      <c r="Q142" s="11" t="n"/>
-      <c r="R142" s="11" t="n"/>
-      <c r="S142" s="11" t="n"/>
-      <c r="T142" s="11" t="n"/>
-      <c r="U142" s="11" t="n"/>
-      <c r="V142" s="11" t="n"/>
+      <c r="P142" s="13" t="n"/>
+      <c r="Q142" s="13" t="n"/>
+      <c r="R142" s="13" t="n"/>
+      <c r="S142" s="13" t="n"/>
+      <c r="T142" s="13" t="n"/>
+      <c r="U142" s="13" t="n"/>
       <c r="W142" s="11" t="n"/>
       <c r="X142" s="11" t="n"/>
       <c r="Y142" s="11" t="n"/>
@@ -5287,6 +7011,18 @@
       <c r="AA142" s="11" t="n"/>
       <c r="AB142" s="11" t="n"/>
       <c r="AC142" s="11" t="n"/>
+      <c r="AD142" s="11" t="n"/>
+      <c r="AE142" s="11" t="n"/>
+      <c r="AF142" s="11" t="n"/>
+      <c r="AG142" s="11" t="n"/>
+      <c r="AH142" s="11" t="n"/>
+      <c r="AI142" s="11" t="n"/>
+      <c r="AJ142" s="11" t="n"/>
+      <c r="AK142" s="11" t="n"/>
+      <c r="AL142" s="11" t="n"/>
+      <c r="AM142" s="11" t="n"/>
+      <c r="AN142" s="11" t="n"/>
+      <c r="AO142" s="11" t="n"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
       <c r="B143" s="9" t="inlineStr">
@@ -5307,12 +7043,12 @@
       <c r="M143" s="10" t="n"/>
       <c r="N143" s="10" t="n"/>
       <c r="O143" s="10" t="n"/>
-      <c r="Q143" s="11" t="n"/>
-      <c r="R143" s="11" t="n"/>
-      <c r="S143" s="11" t="n"/>
-      <c r="T143" s="11" t="n"/>
-      <c r="U143" s="11" t="n"/>
-      <c r="V143" s="11" t="n"/>
+      <c r="P143" s="10" t="n"/>
+      <c r="Q143" s="10" t="n"/>
+      <c r="R143" s="10" t="n"/>
+      <c r="S143" s="10" t="n"/>
+      <c r="T143" s="10" t="n"/>
+      <c r="U143" s="10" t="n"/>
       <c r="W143" s="11" t="n"/>
       <c r="X143" s="11" t="n"/>
       <c r="Y143" s="11" t="n"/>
@@ -5320,6 +7056,18 @@
       <c r="AA143" s="11" t="n"/>
       <c r="AB143" s="11" t="n"/>
       <c r="AC143" s="11" t="n"/>
+      <c r="AD143" s="11" t="n"/>
+      <c r="AE143" s="11" t="n"/>
+      <c r="AF143" s="11" t="n"/>
+      <c r="AG143" s="11" t="n"/>
+      <c r="AH143" s="11" t="n"/>
+      <c r="AI143" s="11" t="n"/>
+      <c r="AJ143" s="11" t="n"/>
+      <c r="AK143" s="11" t="n"/>
+      <c r="AL143" s="11" t="n"/>
+      <c r="AM143" s="11" t="n"/>
+      <c r="AN143" s="11" t="n"/>
+      <c r="AO143" s="11" t="n"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
       <c r="B144" s="9" t="inlineStr">
@@ -5340,12 +7088,12 @@
       <c r="M144" s="10" t="n"/>
       <c r="N144" s="10" t="n"/>
       <c r="O144" s="10" t="n"/>
-      <c r="Q144" s="11" t="n"/>
-      <c r="R144" s="11" t="n"/>
-      <c r="S144" s="11" t="n"/>
-      <c r="T144" s="11" t="n"/>
-      <c r="U144" s="11" t="n"/>
-      <c r="V144" s="11" t="n"/>
+      <c r="P144" s="10" t="n"/>
+      <c r="Q144" s="10" t="n"/>
+      <c r="R144" s="10" t="n"/>
+      <c r="S144" s="10" t="n"/>
+      <c r="T144" s="10" t="n"/>
+      <c r="U144" s="10" t="n"/>
       <c r="W144" s="11" t="n"/>
       <c r="X144" s="11" t="n"/>
       <c r="Y144" s="11" t="n"/>
@@ -5353,6 +7101,18 @@
       <c r="AA144" s="11" t="n"/>
       <c r="AB144" s="11" t="n"/>
       <c r="AC144" s="11" t="n"/>
+      <c r="AD144" s="11" t="n"/>
+      <c r="AE144" s="11" t="n"/>
+      <c r="AF144" s="11" t="n"/>
+      <c r="AG144" s="11" t="n"/>
+      <c r="AH144" s="11" t="n"/>
+      <c r="AI144" s="11" t="n"/>
+      <c r="AJ144" s="11" t="n"/>
+      <c r="AK144" s="11" t="n"/>
+      <c r="AL144" s="11" t="n"/>
+      <c r="AM144" s="11" t="n"/>
+      <c r="AN144" s="11" t="n"/>
+      <c r="AO144" s="11" t="n"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
       <c r="B145" s="12" t="inlineStr">
@@ -5373,12 +7133,12 @@
       <c r="M145" s="13" t="n"/>
       <c r="N145" s="13" t="n"/>
       <c r="O145" s="13" t="n"/>
-      <c r="Q145" s="11" t="n"/>
-      <c r="R145" s="11" t="n"/>
-      <c r="S145" s="11" t="n"/>
-      <c r="T145" s="11" t="n"/>
-      <c r="U145" s="11" t="n"/>
-      <c r="V145" s="11" t="n"/>
+      <c r="P145" s="13" t="n"/>
+      <c r="Q145" s="13" t="n"/>
+      <c r="R145" s="13" t="n"/>
+      <c r="S145" s="13" t="n"/>
+      <c r="T145" s="13" t="n"/>
+      <c r="U145" s="13" t="n"/>
       <c r="W145" s="11" t="n"/>
       <c r="X145" s="11" t="n"/>
       <c r="Y145" s="11" t="n"/>
@@ -5386,6 +7146,18 @@
       <c r="AA145" s="11" t="n"/>
       <c r="AB145" s="11" t="n"/>
       <c r="AC145" s="11" t="n"/>
+      <c r="AD145" s="11" t="n"/>
+      <c r="AE145" s="11" t="n"/>
+      <c r="AF145" s="11" t="n"/>
+      <c r="AG145" s="11" t="n"/>
+      <c r="AH145" s="11" t="n"/>
+      <c r="AI145" s="11" t="n"/>
+      <c r="AJ145" s="11" t="n"/>
+      <c r="AK145" s="11" t="n"/>
+      <c r="AL145" s="11" t="n"/>
+      <c r="AM145" s="11" t="n"/>
+      <c r="AN145" s="11" t="n"/>
+      <c r="AO145" s="11" t="n"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
       <c r="B146" s="9" t="inlineStr">
@@ -5406,12 +7178,12 @@
       <c r="M146" s="10" t="n"/>
       <c r="N146" s="10" t="n"/>
       <c r="O146" s="10" t="n"/>
-      <c r="Q146" s="11" t="n"/>
-      <c r="R146" s="11" t="n"/>
-      <c r="S146" s="11" t="n"/>
-      <c r="T146" s="11" t="n"/>
-      <c r="U146" s="11" t="n"/>
-      <c r="V146" s="11" t="n"/>
+      <c r="P146" s="10" t="n"/>
+      <c r="Q146" s="10" t="n"/>
+      <c r="R146" s="10" t="n"/>
+      <c r="S146" s="10" t="n"/>
+      <c r="T146" s="10" t="n"/>
+      <c r="U146" s="10" t="n"/>
       <c r="W146" s="11" t="n"/>
       <c r="X146" s="11" t="n"/>
       <c r="Y146" s="11" t="n"/>
@@ -5419,6 +7191,18 @@
       <c r="AA146" s="11" t="n"/>
       <c r="AB146" s="11" t="n"/>
       <c r="AC146" s="11" t="n"/>
+      <c r="AD146" s="11" t="n"/>
+      <c r="AE146" s="11" t="n"/>
+      <c r="AF146" s="11" t="n"/>
+      <c r="AG146" s="11" t="n"/>
+      <c r="AH146" s="11" t="n"/>
+      <c r="AI146" s="11" t="n"/>
+      <c r="AJ146" s="11" t="n"/>
+      <c r="AK146" s="11" t="n"/>
+      <c r="AL146" s="11" t="n"/>
+      <c r="AM146" s="11" t="n"/>
+      <c r="AN146" s="11" t="n"/>
+      <c r="AO146" s="11" t="n"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
       <c r="B147" s="12" t="inlineStr">
@@ -5439,12 +7223,12 @@
       <c r="M147" s="13" t="n"/>
       <c r="N147" s="13" t="n"/>
       <c r="O147" s="13" t="n"/>
-      <c r="Q147" s="11" t="n"/>
-      <c r="R147" s="11" t="n"/>
-      <c r="S147" s="11" t="n"/>
-      <c r="T147" s="11" t="n"/>
-      <c r="U147" s="11" t="n"/>
-      <c r="V147" s="11" t="n"/>
+      <c r="P147" s="13" t="n"/>
+      <c r="Q147" s="13" t="n"/>
+      <c r="R147" s="13" t="n"/>
+      <c r="S147" s="13" t="n"/>
+      <c r="T147" s="13" t="n"/>
+      <c r="U147" s="13" t="n"/>
       <c r="W147" s="11" t="n"/>
       <c r="X147" s="11" t="n"/>
       <c r="Y147" s="11" t="n"/>
@@ -5452,6 +7236,18 @@
       <c r="AA147" s="11" t="n"/>
       <c r="AB147" s="11" t="n"/>
       <c r="AC147" s="11" t="n"/>
+      <c r="AD147" s="11" t="n"/>
+      <c r="AE147" s="11" t="n"/>
+      <c r="AF147" s="11" t="n"/>
+      <c r="AG147" s="11" t="n"/>
+      <c r="AH147" s="11" t="n"/>
+      <c r="AI147" s="11" t="n"/>
+      <c r="AJ147" s="11" t="n"/>
+      <c r="AK147" s="11" t="n"/>
+      <c r="AL147" s="11" t="n"/>
+      <c r="AM147" s="11" t="n"/>
+      <c r="AN147" s="11" t="n"/>
+      <c r="AO147" s="11" t="n"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
       <c r="B148" s="9" t="inlineStr">
@@ -5472,12 +7268,12 @@
       <c r="M148" s="10" t="n"/>
       <c r="N148" s="10" t="n"/>
       <c r="O148" s="10" t="n"/>
-      <c r="Q148" s="11" t="n"/>
-      <c r="R148" s="11" t="n"/>
-      <c r="S148" s="11" t="n"/>
-      <c r="T148" s="11" t="n"/>
-      <c r="U148" s="11" t="n"/>
-      <c r="V148" s="11" t="n"/>
+      <c r="P148" s="10" t="n"/>
+      <c r="Q148" s="10" t="n"/>
+      <c r="R148" s="10" t="n"/>
+      <c r="S148" s="10" t="n"/>
+      <c r="T148" s="10" t="n"/>
+      <c r="U148" s="10" t="n"/>
       <c r="W148" s="11" t="n"/>
       <c r="X148" s="11" t="n"/>
       <c r="Y148" s="11" t="n"/>
@@ -5485,6 +7281,18 @@
       <c r="AA148" s="11" t="n"/>
       <c r="AB148" s="11" t="n"/>
       <c r="AC148" s="11" t="n"/>
+      <c r="AD148" s="11" t="n"/>
+      <c r="AE148" s="11" t="n"/>
+      <c r="AF148" s="11" t="n"/>
+      <c r="AG148" s="11" t="n"/>
+      <c r="AH148" s="11" t="n"/>
+      <c r="AI148" s="11" t="n"/>
+      <c r="AJ148" s="11" t="n"/>
+      <c r="AK148" s="11" t="n"/>
+      <c r="AL148" s="11" t="n"/>
+      <c r="AM148" s="11" t="n"/>
+      <c r="AN148" s="11" t="n"/>
+      <c r="AO148" s="11" t="n"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
       <c r="B151" s="5" t="inlineStr">
@@ -5497,7 +7305,7 @@
           <t>A. 0 Appendix - carried &amp; annotated (not simulated)</t>
         </is>
       </c>
-      <c r="Q151" s="6" t="inlineStr">
+      <c r="W151" s="6" t="inlineStr">
         <is>
           <t>A. 0 Appendix - Difference (config-only changes)</t>
         </is>
@@ -5574,69 +7382,129 @@
           <t>SPTx2</t>
         </is>
       </c>
+      <c r="P152" s="8" t="inlineStr">
+        <is>
+          <t>1-star Pack</t>
+        </is>
+      </c>
       <c r="Q152" s="8" t="inlineStr">
         <is>
+          <t>2-star Pack</t>
+        </is>
+      </c>
+      <c r="R152" s="8" t="inlineStr">
+        <is>
+          <t>3-star Pack</t>
+        </is>
+      </c>
+      <c r="S152" s="8" t="inlineStr">
+        <is>
+          <t>4-star Pack</t>
+        </is>
+      </c>
+      <c r="T152" s="8" t="inlineStr">
+        <is>
+          <t>5-star Pack</t>
+        </is>
+      </c>
+      <c r="U152" s="8" t="inlineStr">
+        <is>
+          <t>6-star Pack</t>
+        </is>
+      </c>
+      <c r="W152" s="8" t="inlineStr">
+        <is>
           <t>HC</t>
         </is>
       </c>
-      <c r="R152" s="8" t="inlineStr">
+      <c r="X152" s="8" t="inlineStr">
         <is>
           <t>Slingshot</t>
         </is>
       </c>
-      <c r="S152" s="8" t="inlineStr">
+      <c r="Y152" s="8" t="inlineStr">
         <is>
           <t>Shuffle</t>
         </is>
       </c>
-      <c r="T152" s="8" t="inlineStr">
+      <c r="Z152" s="8" t="inlineStr">
         <is>
           <t>Comet</t>
         </is>
       </c>
-      <c r="U152" s="8" t="inlineStr">
+      <c r="AA152" s="8" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="V152" s="8" t="inlineStr">
+      <c r="AB152" s="8" t="inlineStr">
         <is>
           <t>Chuck</t>
         </is>
       </c>
-      <c r="W152" s="8" t="inlineStr">
+      <c r="AC152" s="8" t="inlineStr">
         <is>
           <t>Bomb</t>
         </is>
       </c>
-      <c r="X152" s="8" t="inlineStr">
+      <c r="AD152" s="8" t="inlineStr">
         <is>
           <t>UL Bomb</t>
         </is>
       </c>
-      <c r="Y152" s="8" t="inlineStr">
+      <c r="AE152" s="8" t="inlineStr">
         <is>
           <t>UL Chuck</t>
         </is>
       </c>
-      <c r="Z152" s="8" t="inlineStr">
+      <c r="AF152" s="8" t="inlineStr">
         <is>
           <t>UL Red</t>
         </is>
       </c>
-      <c r="AA152" s="8" t="inlineStr">
+      <c r="AG152" s="8" t="inlineStr">
         <is>
           <t>Unlimited Lives</t>
         </is>
       </c>
-      <c r="AB152" s="8" t="inlineStr">
+      <c r="AH152" s="8" t="inlineStr">
         <is>
           <t>SPT</t>
         </is>
       </c>
-      <c r="AC152" s="8" t="inlineStr">
+      <c r="AI152" s="8" t="inlineStr">
         <is>
           <t>SPTx2</t>
+        </is>
+      </c>
+      <c r="AJ152" s="8" t="inlineStr">
+        <is>
+          <t>1-star Pack</t>
+        </is>
+      </c>
+      <c r="AK152" s="8" t="inlineStr">
+        <is>
+          <t>2-star Pack</t>
+        </is>
+      </c>
+      <c r="AL152" s="8" t="inlineStr">
+        <is>
+          <t>3-star Pack</t>
+        </is>
+      </c>
+      <c r="AM152" s="8" t="inlineStr">
+        <is>
+          <t>4-star Pack</t>
+        </is>
+      </c>
+      <c r="AN152" s="8" t="inlineStr">
+        <is>
+          <t>5-star Pack</t>
+        </is>
+      </c>
+      <c r="AO152" s="8" t="inlineStr">
+        <is>
+          <t>6-star Pack</t>
         </is>
       </c>
     </row>
@@ -5662,22 +7530,34 @@
       <c r="M153" s="10" t="n"/>
       <c r="N153" s="10" t="n"/>
       <c r="O153" s="10" t="n"/>
-      <c r="Q153" s="11">
+      <c r="P153" s="10" t="n"/>
+      <c r="Q153" s="10" t="n"/>
+      <c r="R153" s="10" t="n"/>
+      <c r="S153" s="10" t="n"/>
+      <c r="T153" s="10" t="n"/>
+      <c r="U153" s="10" t="n"/>
+      <c r="W153" s="11">
         <f>LET(payer, $C$3, segment, $B$151, ECOGAINS_DIFF(payer, segment, sim_refresh!$A$1))</f>
         <v/>
       </c>
-      <c r="R153" s="11" t="n"/>
-      <c r="S153" s="11" t="n"/>
-      <c r="T153" s="11" t="n"/>
-      <c r="U153" s="11" t="n"/>
-      <c r="V153" s="11" t="n"/>
-      <c r="W153" s="11" t="n"/>
       <c r="X153" s="11" t="n"/>
       <c r="Y153" s="11" t="n"/>
       <c r="Z153" s="11" t="n"/>
       <c r="AA153" s="11" t="n"/>
       <c r="AB153" s="11" t="n"/>
       <c r="AC153" s="11" t="n"/>
+      <c r="AD153" s="11" t="n"/>
+      <c r="AE153" s="11" t="n"/>
+      <c r="AF153" s="11" t="n"/>
+      <c r="AG153" s="11" t="n"/>
+      <c r="AH153" s="11" t="n"/>
+      <c r="AI153" s="11" t="n"/>
+      <c r="AJ153" s="11" t="n"/>
+      <c r="AK153" s="11" t="n"/>
+      <c r="AL153" s="11" t="n"/>
+      <c r="AM153" s="11" t="n"/>
+      <c r="AN153" s="11" t="n"/>
+      <c r="AO153" s="11" t="n"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
       <c r="B154" s="9" t="inlineStr">
@@ -5698,12 +7578,12 @@
       <c r="M154" s="10" t="n"/>
       <c r="N154" s="10" t="n"/>
       <c r="O154" s="10" t="n"/>
-      <c r="Q154" s="11" t="n"/>
-      <c r="R154" s="11" t="n"/>
-      <c r="S154" s="11" t="n"/>
-      <c r="T154" s="11" t="n"/>
-      <c r="U154" s="11" t="n"/>
-      <c r="V154" s="11" t="n"/>
+      <c r="P154" s="10" t="n"/>
+      <c r="Q154" s="10" t="n"/>
+      <c r="R154" s="10" t="n"/>
+      <c r="S154" s="10" t="n"/>
+      <c r="T154" s="10" t="n"/>
+      <c r="U154" s="10" t="n"/>
       <c r="W154" s="11" t="n"/>
       <c r="X154" s="11" t="n"/>
       <c r="Y154" s="11" t="n"/>
@@ -5711,6 +7591,18 @@
       <c r="AA154" s="11" t="n"/>
       <c r="AB154" s="11" t="n"/>
       <c r="AC154" s="11" t="n"/>
+      <c r="AD154" s="11" t="n"/>
+      <c r="AE154" s="11" t="n"/>
+      <c r="AF154" s="11" t="n"/>
+      <c r="AG154" s="11" t="n"/>
+      <c r="AH154" s="11" t="n"/>
+      <c r="AI154" s="11" t="n"/>
+      <c r="AJ154" s="11" t="n"/>
+      <c r="AK154" s="11" t="n"/>
+      <c r="AL154" s="11" t="n"/>
+      <c r="AM154" s="11" t="n"/>
+      <c r="AN154" s="11" t="n"/>
+      <c r="AO154" s="11" t="n"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
       <c r="B155" s="9" t="inlineStr">
@@ -5731,12 +7623,12 @@
       <c r="M155" s="10" t="n"/>
       <c r="N155" s="10" t="n"/>
       <c r="O155" s="10" t="n"/>
-      <c r="Q155" s="11" t="n"/>
-      <c r="R155" s="11" t="n"/>
-      <c r="S155" s="11" t="n"/>
-      <c r="T155" s="11" t="n"/>
-      <c r="U155" s="11" t="n"/>
-      <c r="V155" s="11" t="n"/>
+      <c r="P155" s="10" t="n"/>
+      <c r="Q155" s="10" t="n"/>
+      <c r="R155" s="10" t="n"/>
+      <c r="S155" s="10" t="n"/>
+      <c r="T155" s="10" t="n"/>
+      <c r="U155" s="10" t="n"/>
       <c r="W155" s="11" t="n"/>
       <c r="X155" s="11" t="n"/>
       <c r="Y155" s="11" t="n"/>
@@ -5744,6 +7636,18 @@
       <c r="AA155" s="11" t="n"/>
       <c r="AB155" s="11" t="n"/>
       <c r="AC155" s="11" t="n"/>
+      <c r="AD155" s="11" t="n"/>
+      <c r="AE155" s="11" t="n"/>
+      <c r="AF155" s="11" t="n"/>
+      <c r="AG155" s="11" t="n"/>
+      <c r="AH155" s="11" t="n"/>
+      <c r="AI155" s="11" t="n"/>
+      <c r="AJ155" s="11" t="n"/>
+      <c r="AK155" s="11" t="n"/>
+      <c r="AL155" s="11" t="n"/>
+      <c r="AM155" s="11" t="n"/>
+      <c r="AN155" s="11" t="n"/>
+      <c r="AO155" s="11" t="n"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
       <c r="B156" s="9" t="inlineStr">
@@ -5764,12 +7668,12 @@
       <c r="M156" s="10" t="n"/>
       <c r="N156" s="10" t="n"/>
       <c r="O156" s="10" t="n"/>
-      <c r="Q156" s="11" t="n"/>
-      <c r="R156" s="11" t="n"/>
-      <c r="S156" s="11" t="n"/>
-      <c r="T156" s="11" t="n"/>
-      <c r="U156" s="11" t="n"/>
-      <c r="V156" s="11" t="n"/>
+      <c r="P156" s="10" t="n"/>
+      <c r="Q156" s="10" t="n"/>
+      <c r="R156" s="10" t="n"/>
+      <c r="S156" s="10" t="n"/>
+      <c r="T156" s="10" t="n"/>
+      <c r="U156" s="10" t="n"/>
       <c r="W156" s="11" t="n"/>
       <c r="X156" s="11" t="n"/>
       <c r="Y156" s="11" t="n"/>
@@ -5777,6 +7681,18 @@
       <c r="AA156" s="11" t="n"/>
       <c r="AB156" s="11" t="n"/>
       <c r="AC156" s="11" t="n"/>
+      <c r="AD156" s="11" t="n"/>
+      <c r="AE156" s="11" t="n"/>
+      <c r="AF156" s="11" t="n"/>
+      <c r="AG156" s="11" t="n"/>
+      <c r="AH156" s="11" t="n"/>
+      <c r="AI156" s="11" t="n"/>
+      <c r="AJ156" s="11" t="n"/>
+      <c r="AK156" s="11" t="n"/>
+      <c r="AL156" s="11" t="n"/>
+      <c r="AM156" s="11" t="n"/>
+      <c r="AN156" s="11" t="n"/>
+      <c r="AO156" s="11" t="n"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
       <c r="B157" s="9" t="inlineStr">
@@ -5797,12 +7713,12 @@
       <c r="M157" s="10" t="n"/>
       <c r="N157" s="10" t="n"/>
       <c r="O157" s="10" t="n"/>
-      <c r="Q157" s="11" t="n"/>
-      <c r="R157" s="11" t="n"/>
-      <c r="S157" s="11" t="n"/>
-      <c r="T157" s="11" t="n"/>
-      <c r="U157" s="11" t="n"/>
-      <c r="V157" s="11" t="n"/>
+      <c r="P157" s="10" t="n"/>
+      <c r="Q157" s="10" t="n"/>
+      <c r="R157" s="10" t="n"/>
+      <c r="S157" s="10" t="n"/>
+      <c r="T157" s="10" t="n"/>
+      <c r="U157" s="10" t="n"/>
       <c r="W157" s="11" t="n"/>
       <c r="X157" s="11" t="n"/>
       <c r="Y157" s="11" t="n"/>
@@ -5810,6 +7726,18 @@
       <c r="AA157" s="11" t="n"/>
       <c r="AB157" s="11" t="n"/>
       <c r="AC157" s="11" t="n"/>
+      <c r="AD157" s="11" t="n"/>
+      <c r="AE157" s="11" t="n"/>
+      <c r="AF157" s="11" t="n"/>
+      <c r="AG157" s="11" t="n"/>
+      <c r="AH157" s="11" t="n"/>
+      <c r="AI157" s="11" t="n"/>
+      <c r="AJ157" s="11" t="n"/>
+      <c r="AK157" s="11" t="n"/>
+      <c r="AL157" s="11" t="n"/>
+      <c r="AM157" s="11" t="n"/>
+      <c r="AN157" s="11" t="n"/>
+      <c r="AO157" s="11" t="n"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
       <c r="B158" s="14" t="inlineStr">
@@ -5830,12 +7758,12 @@
       <c r="M158" s="13" t="n"/>
       <c r="N158" s="13" t="n"/>
       <c r="O158" s="13" t="n"/>
-      <c r="Q158" s="11" t="n"/>
-      <c r="R158" s="11" t="n"/>
-      <c r="S158" s="11" t="n"/>
-      <c r="T158" s="11" t="n"/>
-      <c r="U158" s="11" t="n"/>
-      <c r="V158" s="11" t="n"/>
+      <c r="P158" s="13" t="n"/>
+      <c r="Q158" s="13" t="n"/>
+      <c r="R158" s="13" t="n"/>
+      <c r="S158" s="13" t="n"/>
+      <c r="T158" s="13" t="n"/>
+      <c r="U158" s="13" t="n"/>
       <c r="W158" s="11" t="n"/>
       <c r="X158" s="11" t="n"/>
       <c r="Y158" s="11" t="n"/>
@@ -5843,6 +7771,18 @@
       <c r="AA158" s="11" t="n"/>
       <c r="AB158" s="11" t="n"/>
       <c r="AC158" s="11" t="n"/>
+      <c r="AD158" s="11" t="n"/>
+      <c r="AE158" s="11" t="n"/>
+      <c r="AF158" s="11" t="n"/>
+      <c r="AG158" s="11" t="n"/>
+      <c r="AH158" s="11" t="n"/>
+      <c r="AI158" s="11" t="n"/>
+      <c r="AJ158" s="11" t="n"/>
+      <c r="AK158" s="11" t="n"/>
+      <c r="AL158" s="11" t="n"/>
+      <c r="AM158" s="11" t="n"/>
+      <c r="AN158" s="11" t="n"/>
+      <c r="AO158" s="11" t="n"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
       <c r="B159" s="9" t="inlineStr">
@@ -5863,12 +7803,12 @@
       <c r="M159" s="10" t="n"/>
       <c r="N159" s="10" t="n"/>
       <c r="O159" s="10" t="n"/>
-      <c r="Q159" s="11" t="n"/>
-      <c r="R159" s="11" t="n"/>
-      <c r="S159" s="11" t="n"/>
-      <c r="T159" s="11" t="n"/>
-      <c r="U159" s="11" t="n"/>
-      <c r="V159" s="11" t="n"/>
+      <c r="P159" s="10" t="n"/>
+      <c r="Q159" s="10" t="n"/>
+      <c r="R159" s="10" t="n"/>
+      <c r="S159" s="10" t="n"/>
+      <c r="T159" s="10" t="n"/>
+      <c r="U159" s="10" t="n"/>
       <c r="W159" s="11" t="n"/>
       <c r="X159" s="11" t="n"/>
       <c r="Y159" s="11" t="n"/>
@@ -5876,6 +7816,18 @@
       <c r="AA159" s="11" t="n"/>
       <c r="AB159" s="11" t="n"/>
       <c r="AC159" s="11" t="n"/>
+      <c r="AD159" s="11" t="n"/>
+      <c r="AE159" s="11" t="n"/>
+      <c r="AF159" s="11" t="n"/>
+      <c r="AG159" s="11" t="n"/>
+      <c r="AH159" s="11" t="n"/>
+      <c r="AI159" s="11" t="n"/>
+      <c r="AJ159" s="11" t="n"/>
+      <c r="AK159" s="11" t="n"/>
+      <c r="AL159" s="11" t="n"/>
+      <c r="AM159" s="11" t="n"/>
+      <c r="AN159" s="11" t="n"/>
+      <c r="AO159" s="11" t="n"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
       <c r="B160" s="9" t="inlineStr">
@@ -5896,12 +7848,12 @@
       <c r="M160" s="10" t="n"/>
       <c r="N160" s="10" t="n"/>
       <c r="O160" s="10" t="n"/>
-      <c r="Q160" s="11" t="n"/>
-      <c r="R160" s="11" t="n"/>
-      <c r="S160" s="11" t="n"/>
-      <c r="T160" s="11" t="n"/>
-      <c r="U160" s="11" t="n"/>
-      <c r="V160" s="11" t="n"/>
+      <c r="P160" s="10" t="n"/>
+      <c r="Q160" s="10" t="n"/>
+      <c r="R160" s="10" t="n"/>
+      <c r="S160" s="10" t="n"/>
+      <c r="T160" s="10" t="n"/>
+      <c r="U160" s="10" t="n"/>
       <c r="W160" s="11" t="n"/>
       <c r="X160" s="11" t="n"/>
       <c r="Y160" s="11" t="n"/>
@@ -5909,6 +7861,18 @@
       <c r="AA160" s="11" t="n"/>
       <c r="AB160" s="11" t="n"/>
       <c r="AC160" s="11" t="n"/>
+      <c r="AD160" s="11" t="n"/>
+      <c r="AE160" s="11" t="n"/>
+      <c r="AF160" s="11" t="n"/>
+      <c r="AG160" s="11" t="n"/>
+      <c r="AH160" s="11" t="n"/>
+      <c r="AI160" s="11" t="n"/>
+      <c r="AJ160" s="11" t="n"/>
+      <c r="AK160" s="11" t="n"/>
+      <c r="AL160" s="11" t="n"/>
+      <c r="AM160" s="11" t="n"/>
+      <c r="AN160" s="11" t="n"/>
+      <c r="AO160" s="11" t="n"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
       <c r="B161" s="9" t="inlineStr">
@@ -5929,12 +7893,12 @@
       <c r="M161" s="10" t="n"/>
       <c r="N161" s="10" t="n"/>
       <c r="O161" s="10" t="n"/>
-      <c r="Q161" s="11" t="n"/>
-      <c r="R161" s="11" t="n"/>
-      <c r="S161" s="11" t="n"/>
-      <c r="T161" s="11" t="n"/>
-      <c r="U161" s="11" t="n"/>
-      <c r="V161" s="11" t="n"/>
+      <c r="P161" s="10" t="n"/>
+      <c r="Q161" s="10" t="n"/>
+      <c r="R161" s="10" t="n"/>
+      <c r="S161" s="10" t="n"/>
+      <c r="T161" s="10" t="n"/>
+      <c r="U161" s="10" t="n"/>
       <c r="W161" s="11" t="n"/>
       <c r="X161" s="11" t="n"/>
       <c r="Y161" s="11" t="n"/>
@@ -5942,6 +7906,18 @@
       <c r="AA161" s="11" t="n"/>
       <c r="AB161" s="11" t="n"/>
       <c r="AC161" s="11" t="n"/>
+      <c r="AD161" s="11" t="n"/>
+      <c r="AE161" s="11" t="n"/>
+      <c r="AF161" s="11" t="n"/>
+      <c r="AG161" s="11" t="n"/>
+      <c r="AH161" s="11" t="n"/>
+      <c r="AI161" s="11" t="n"/>
+      <c r="AJ161" s="11" t="n"/>
+      <c r="AK161" s="11" t="n"/>
+      <c r="AL161" s="11" t="n"/>
+      <c r="AM161" s="11" t="n"/>
+      <c r="AN161" s="11" t="n"/>
+      <c r="AO161" s="11" t="n"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
       <c r="B162" s="9" t="inlineStr">
@@ -5962,12 +7938,12 @@
       <c r="M162" s="10" t="n"/>
       <c r="N162" s="10" t="n"/>
       <c r="O162" s="10" t="n"/>
-      <c r="Q162" s="11" t="n"/>
-      <c r="R162" s="11" t="n"/>
-      <c r="S162" s="11" t="n"/>
-      <c r="T162" s="11" t="n"/>
-      <c r="U162" s="11" t="n"/>
-      <c r="V162" s="11" t="n"/>
+      <c r="P162" s="10" t="n"/>
+      <c r="Q162" s="10" t="n"/>
+      <c r="R162" s="10" t="n"/>
+      <c r="S162" s="10" t="n"/>
+      <c r="T162" s="10" t="n"/>
+      <c r="U162" s="10" t="n"/>
       <c r="W162" s="11" t="n"/>
       <c r="X162" s="11" t="n"/>
       <c r="Y162" s="11" t="n"/>
@@ -5975,6 +7951,18 @@
       <c r="AA162" s="11" t="n"/>
       <c r="AB162" s="11" t="n"/>
       <c r="AC162" s="11" t="n"/>
+      <c r="AD162" s="11" t="n"/>
+      <c r="AE162" s="11" t="n"/>
+      <c r="AF162" s="11" t="n"/>
+      <c r="AG162" s="11" t="n"/>
+      <c r="AH162" s="11" t="n"/>
+      <c r="AI162" s="11" t="n"/>
+      <c r="AJ162" s="11" t="n"/>
+      <c r="AK162" s="11" t="n"/>
+      <c r="AL162" s="11" t="n"/>
+      <c r="AM162" s="11" t="n"/>
+      <c r="AN162" s="11" t="n"/>
+      <c r="AO162" s="11" t="n"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
       <c r="B163" s="9" t="inlineStr">
@@ -5995,12 +7983,12 @@
       <c r="M163" s="10" t="n"/>
       <c r="N163" s="10" t="n"/>
       <c r="O163" s="10" t="n"/>
-      <c r="Q163" s="11" t="n"/>
-      <c r="R163" s="11" t="n"/>
-      <c r="S163" s="11" t="n"/>
-      <c r="T163" s="11" t="n"/>
-      <c r="U163" s="11" t="n"/>
-      <c r="V163" s="11" t="n"/>
+      <c r="P163" s="10" t="n"/>
+      <c r="Q163" s="10" t="n"/>
+      <c r="R163" s="10" t="n"/>
+      <c r="S163" s="10" t="n"/>
+      <c r="T163" s="10" t="n"/>
+      <c r="U163" s="10" t="n"/>
       <c r="W163" s="11" t="n"/>
       <c r="X163" s="11" t="n"/>
       <c r="Y163" s="11" t="n"/>
@@ -6008,6 +7996,18 @@
       <c r="AA163" s="11" t="n"/>
       <c r="AB163" s="11" t="n"/>
       <c r="AC163" s="11" t="n"/>
+      <c r="AD163" s="11" t="n"/>
+      <c r="AE163" s="11" t="n"/>
+      <c r="AF163" s="11" t="n"/>
+      <c r="AG163" s="11" t="n"/>
+      <c r="AH163" s="11" t="n"/>
+      <c r="AI163" s="11" t="n"/>
+      <c r="AJ163" s="11" t="n"/>
+      <c r="AK163" s="11" t="n"/>
+      <c r="AL163" s="11" t="n"/>
+      <c r="AM163" s="11" t="n"/>
+      <c r="AN163" s="11" t="n"/>
+      <c r="AO163" s="11" t="n"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
       <c r="B164" s="9" t="inlineStr">
@@ -6028,12 +8028,12 @@
       <c r="M164" s="10" t="n"/>
       <c r="N164" s="10" t="n"/>
       <c r="O164" s="10" t="n"/>
-      <c r="Q164" s="11" t="n"/>
-      <c r="R164" s="11" t="n"/>
-      <c r="S164" s="11" t="n"/>
-      <c r="T164" s="11" t="n"/>
-      <c r="U164" s="11" t="n"/>
-      <c r="V164" s="11" t="n"/>
+      <c r="P164" s="10" t="n"/>
+      <c r="Q164" s="10" t="n"/>
+      <c r="R164" s="10" t="n"/>
+      <c r="S164" s="10" t="n"/>
+      <c r="T164" s="10" t="n"/>
+      <c r="U164" s="10" t="n"/>
       <c r="W164" s="11" t="n"/>
       <c r="X164" s="11" t="n"/>
       <c r="Y164" s="11" t="n"/>
@@ -6041,6 +8041,18 @@
       <c r="AA164" s="11" t="n"/>
       <c r="AB164" s="11" t="n"/>
       <c r="AC164" s="11" t="n"/>
+      <c r="AD164" s="11" t="n"/>
+      <c r="AE164" s="11" t="n"/>
+      <c r="AF164" s="11" t="n"/>
+      <c r="AG164" s="11" t="n"/>
+      <c r="AH164" s="11" t="n"/>
+      <c r="AI164" s="11" t="n"/>
+      <c r="AJ164" s="11" t="n"/>
+      <c r="AK164" s="11" t="n"/>
+      <c r="AL164" s="11" t="n"/>
+      <c r="AM164" s="11" t="n"/>
+      <c r="AN164" s="11" t="n"/>
+      <c r="AO164" s="11" t="n"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
       <c r="B165" s="9" t="inlineStr">
@@ -6061,12 +8073,12 @@
       <c r="M165" s="10" t="n"/>
       <c r="N165" s="10" t="n"/>
       <c r="O165" s="10" t="n"/>
-      <c r="Q165" s="11" t="n"/>
-      <c r="R165" s="11" t="n"/>
-      <c r="S165" s="11" t="n"/>
-      <c r="T165" s="11" t="n"/>
-      <c r="U165" s="11" t="n"/>
-      <c r="V165" s="11" t="n"/>
+      <c r="P165" s="10" t="n"/>
+      <c r="Q165" s="10" t="n"/>
+      <c r="R165" s="10" t="n"/>
+      <c r="S165" s="10" t="n"/>
+      <c r="T165" s="10" t="n"/>
+      <c r="U165" s="10" t="n"/>
       <c r="W165" s="11" t="n"/>
       <c r="X165" s="11" t="n"/>
       <c r="Y165" s="11" t="n"/>
@@ -6074,6 +8086,18 @@
       <c r="AA165" s="11" t="n"/>
       <c r="AB165" s="11" t="n"/>
       <c r="AC165" s="11" t="n"/>
+      <c r="AD165" s="11" t="n"/>
+      <c r="AE165" s="11" t="n"/>
+      <c r="AF165" s="11" t="n"/>
+      <c r="AG165" s="11" t="n"/>
+      <c r="AH165" s="11" t="n"/>
+      <c r="AI165" s="11" t="n"/>
+      <c r="AJ165" s="11" t="n"/>
+      <c r="AK165" s="11" t="n"/>
+      <c r="AL165" s="11" t="n"/>
+      <c r="AM165" s="11" t="n"/>
+      <c r="AN165" s="11" t="n"/>
+      <c r="AO165" s="11" t="n"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
       <c r="B166" s="9" t="inlineStr">
@@ -6094,12 +8118,12 @@
       <c r="M166" s="10" t="n"/>
       <c r="N166" s="10" t="n"/>
       <c r="O166" s="10" t="n"/>
-      <c r="Q166" s="11" t="n"/>
-      <c r="R166" s="11" t="n"/>
-      <c r="S166" s="11" t="n"/>
-      <c r="T166" s="11" t="n"/>
-      <c r="U166" s="11" t="n"/>
-      <c r="V166" s="11" t="n"/>
+      <c r="P166" s="10" t="n"/>
+      <c r="Q166" s="10" t="n"/>
+      <c r="R166" s="10" t="n"/>
+      <c r="S166" s="10" t="n"/>
+      <c r="T166" s="10" t="n"/>
+      <c r="U166" s="10" t="n"/>
       <c r="W166" s="11" t="n"/>
       <c r="X166" s="11" t="n"/>
       <c r="Y166" s="11" t="n"/>
@@ -6107,6 +8131,18 @@
       <c r="AA166" s="11" t="n"/>
       <c r="AB166" s="11" t="n"/>
       <c r="AC166" s="11" t="n"/>
+      <c r="AD166" s="11" t="n"/>
+      <c r="AE166" s="11" t="n"/>
+      <c r="AF166" s="11" t="n"/>
+      <c r="AG166" s="11" t="n"/>
+      <c r="AH166" s="11" t="n"/>
+      <c r="AI166" s="11" t="n"/>
+      <c r="AJ166" s="11" t="n"/>
+      <c r="AK166" s="11" t="n"/>
+      <c r="AL166" s="11" t="n"/>
+      <c r="AM166" s="11" t="n"/>
+      <c r="AN166" s="11" t="n"/>
+      <c r="AO166" s="11" t="n"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
       <c r="B167" s="9" t="inlineStr">
@@ -6127,12 +8163,12 @@
       <c r="M167" s="10" t="n"/>
       <c r="N167" s="10" t="n"/>
       <c r="O167" s="10" t="n"/>
-      <c r="Q167" s="11" t="n"/>
-      <c r="R167" s="11" t="n"/>
-      <c r="S167" s="11" t="n"/>
-      <c r="T167" s="11" t="n"/>
-      <c r="U167" s="11" t="n"/>
-      <c r="V167" s="11" t="n"/>
+      <c r="P167" s="10" t="n"/>
+      <c r="Q167" s="10" t="n"/>
+      <c r="R167" s="10" t="n"/>
+      <c r="S167" s="10" t="n"/>
+      <c r="T167" s="10" t="n"/>
+      <c r="U167" s="10" t="n"/>
       <c r="W167" s="11" t="n"/>
       <c r="X167" s="11" t="n"/>
       <c r="Y167" s="11" t="n"/>
@@ -6140,6 +8176,18 @@
       <c r="AA167" s="11" t="n"/>
       <c r="AB167" s="11" t="n"/>
       <c r="AC167" s="11" t="n"/>
+      <c r="AD167" s="11" t="n"/>
+      <c r="AE167" s="11" t="n"/>
+      <c r="AF167" s="11" t="n"/>
+      <c r="AG167" s="11" t="n"/>
+      <c r="AH167" s="11" t="n"/>
+      <c r="AI167" s="11" t="n"/>
+      <c r="AJ167" s="11" t="n"/>
+      <c r="AK167" s="11" t="n"/>
+      <c r="AL167" s="11" t="n"/>
+      <c r="AM167" s="11" t="n"/>
+      <c r="AN167" s="11" t="n"/>
+      <c r="AO167" s="11" t="n"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
       <c r="B168" s="12" t="inlineStr">
@@ -6160,12 +8208,12 @@
       <c r="M168" s="13" t="n"/>
       <c r="N168" s="13" t="n"/>
       <c r="O168" s="13" t="n"/>
-      <c r="Q168" s="11" t="n"/>
-      <c r="R168" s="11" t="n"/>
-      <c r="S168" s="11" t="n"/>
-      <c r="T168" s="11" t="n"/>
-      <c r="U168" s="11" t="n"/>
-      <c r="V168" s="11" t="n"/>
+      <c r="P168" s="13" t="n"/>
+      <c r="Q168" s="13" t="n"/>
+      <c r="R168" s="13" t="n"/>
+      <c r="S168" s="13" t="n"/>
+      <c r="T168" s="13" t="n"/>
+      <c r="U168" s="13" t="n"/>
       <c r="W168" s="11" t="n"/>
       <c r="X168" s="11" t="n"/>
       <c r="Y168" s="11" t="n"/>
@@ -6173,6 +8221,18 @@
       <c r="AA168" s="11" t="n"/>
       <c r="AB168" s="11" t="n"/>
       <c r="AC168" s="11" t="n"/>
+      <c r="AD168" s="11" t="n"/>
+      <c r="AE168" s="11" t="n"/>
+      <c r="AF168" s="11" t="n"/>
+      <c r="AG168" s="11" t="n"/>
+      <c r="AH168" s="11" t="n"/>
+      <c r="AI168" s="11" t="n"/>
+      <c r="AJ168" s="11" t="n"/>
+      <c r="AK168" s="11" t="n"/>
+      <c r="AL168" s="11" t="n"/>
+      <c r="AM168" s="11" t="n"/>
+      <c r="AN168" s="11" t="n"/>
+      <c r="AO168" s="11" t="n"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
       <c r="B169" s="14" t="inlineStr">
@@ -6193,12 +8253,12 @@
       <c r="M169" s="13" t="n"/>
       <c r="N169" s="13" t="n"/>
       <c r="O169" s="13" t="n"/>
-      <c r="Q169" s="11" t="n"/>
-      <c r="R169" s="11" t="n"/>
-      <c r="S169" s="11" t="n"/>
-      <c r="T169" s="11" t="n"/>
-      <c r="U169" s="11" t="n"/>
-      <c r="V169" s="11" t="n"/>
+      <c r="P169" s="13" t="n"/>
+      <c r="Q169" s="13" t="n"/>
+      <c r="R169" s="13" t="n"/>
+      <c r="S169" s="13" t="n"/>
+      <c r="T169" s="13" t="n"/>
+      <c r="U169" s="13" t="n"/>
       <c r="W169" s="11" t="n"/>
       <c r="X169" s="11" t="n"/>
       <c r="Y169" s="11" t="n"/>
@@ -6206,6 +8266,18 @@
       <c r="AA169" s="11" t="n"/>
       <c r="AB169" s="11" t="n"/>
       <c r="AC169" s="11" t="n"/>
+      <c r="AD169" s="11" t="n"/>
+      <c r="AE169" s="11" t="n"/>
+      <c r="AF169" s="11" t="n"/>
+      <c r="AG169" s="11" t="n"/>
+      <c r="AH169" s="11" t="n"/>
+      <c r="AI169" s="11" t="n"/>
+      <c r="AJ169" s="11" t="n"/>
+      <c r="AK169" s="11" t="n"/>
+      <c r="AL169" s="11" t="n"/>
+      <c r="AM169" s="11" t="n"/>
+      <c r="AN169" s="11" t="n"/>
+      <c r="AO169" s="11" t="n"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
       <c r="B170" s="9" t="inlineStr">
@@ -6226,12 +8298,12 @@
       <c r="M170" s="10" t="n"/>
       <c r="N170" s="10" t="n"/>
       <c r="O170" s="10" t="n"/>
-      <c r="Q170" s="11" t="n"/>
-      <c r="R170" s="11" t="n"/>
-      <c r="S170" s="11" t="n"/>
-      <c r="T170" s="11" t="n"/>
-      <c r="U170" s="11" t="n"/>
-      <c r="V170" s="11" t="n"/>
+      <c r="P170" s="10" t="n"/>
+      <c r="Q170" s="10" t="n"/>
+      <c r="R170" s="10" t="n"/>
+      <c r="S170" s="10" t="n"/>
+      <c r="T170" s="10" t="n"/>
+      <c r="U170" s="10" t="n"/>
       <c r="W170" s="11" t="n"/>
       <c r="X170" s="11" t="n"/>
       <c r="Y170" s="11" t="n"/>
@@ -6239,6 +8311,18 @@
       <c r="AA170" s="11" t="n"/>
       <c r="AB170" s="11" t="n"/>
       <c r="AC170" s="11" t="n"/>
+      <c r="AD170" s="11" t="n"/>
+      <c r="AE170" s="11" t="n"/>
+      <c r="AF170" s="11" t="n"/>
+      <c r="AG170" s="11" t="n"/>
+      <c r="AH170" s="11" t="n"/>
+      <c r="AI170" s="11" t="n"/>
+      <c r="AJ170" s="11" t="n"/>
+      <c r="AK170" s="11" t="n"/>
+      <c r="AL170" s="11" t="n"/>
+      <c r="AM170" s="11" t="n"/>
+      <c r="AN170" s="11" t="n"/>
+      <c r="AO170" s="11" t="n"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
       <c r="B171" s="9" t="inlineStr">
@@ -6259,12 +8343,12 @@
       <c r="M171" s="10" t="n"/>
       <c r="N171" s="10" t="n"/>
       <c r="O171" s="10" t="n"/>
-      <c r="Q171" s="11" t="n"/>
-      <c r="R171" s="11" t="n"/>
-      <c r="S171" s="11" t="n"/>
-      <c r="T171" s="11" t="n"/>
-      <c r="U171" s="11" t="n"/>
-      <c r="V171" s="11" t="n"/>
+      <c r="P171" s="10" t="n"/>
+      <c r="Q171" s="10" t="n"/>
+      <c r="R171" s="10" t="n"/>
+      <c r="S171" s="10" t="n"/>
+      <c r="T171" s="10" t="n"/>
+      <c r="U171" s="10" t="n"/>
       <c r="W171" s="11" t="n"/>
       <c r="X171" s="11" t="n"/>
       <c r="Y171" s="11" t="n"/>
@@ -6272,6 +8356,18 @@
       <c r="AA171" s="11" t="n"/>
       <c r="AB171" s="11" t="n"/>
       <c r="AC171" s="11" t="n"/>
+      <c r="AD171" s="11" t="n"/>
+      <c r="AE171" s="11" t="n"/>
+      <c r="AF171" s="11" t="n"/>
+      <c r="AG171" s="11" t="n"/>
+      <c r="AH171" s="11" t="n"/>
+      <c r="AI171" s="11" t="n"/>
+      <c r="AJ171" s="11" t="n"/>
+      <c r="AK171" s="11" t="n"/>
+      <c r="AL171" s="11" t="n"/>
+      <c r="AM171" s="11" t="n"/>
+      <c r="AN171" s="11" t="n"/>
+      <c r="AO171" s="11" t="n"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
       <c r="B172" s="9" t="inlineStr">
@@ -6292,12 +8388,12 @@
       <c r="M172" s="10" t="n"/>
       <c r="N172" s="10" t="n"/>
       <c r="O172" s="10" t="n"/>
-      <c r="Q172" s="11" t="n"/>
-      <c r="R172" s="11" t="n"/>
-      <c r="S172" s="11" t="n"/>
-      <c r="T172" s="11" t="n"/>
-      <c r="U172" s="11" t="n"/>
-      <c r="V172" s="11" t="n"/>
+      <c r="P172" s="10" t="n"/>
+      <c r="Q172" s="10" t="n"/>
+      <c r="R172" s="10" t="n"/>
+      <c r="S172" s="10" t="n"/>
+      <c r="T172" s="10" t="n"/>
+      <c r="U172" s="10" t="n"/>
       <c r="W172" s="11" t="n"/>
       <c r="X172" s="11" t="n"/>
       <c r="Y172" s="11" t="n"/>
@@ -6305,6 +8401,18 @@
       <c r="AA172" s="11" t="n"/>
       <c r="AB172" s="11" t="n"/>
       <c r="AC172" s="11" t="n"/>
+      <c r="AD172" s="11" t="n"/>
+      <c r="AE172" s="11" t="n"/>
+      <c r="AF172" s="11" t="n"/>
+      <c r="AG172" s="11" t="n"/>
+      <c r="AH172" s="11" t="n"/>
+      <c r="AI172" s="11" t="n"/>
+      <c r="AJ172" s="11" t="n"/>
+      <c r="AK172" s="11" t="n"/>
+      <c r="AL172" s="11" t="n"/>
+      <c r="AM172" s="11" t="n"/>
+      <c r="AN172" s="11" t="n"/>
+      <c r="AO172" s="11" t="n"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
       <c r="B173" s="9" t="inlineStr">
@@ -6325,12 +8433,12 @@
       <c r="M173" s="10" t="n"/>
       <c r="N173" s="10" t="n"/>
       <c r="O173" s="10" t="n"/>
-      <c r="Q173" s="11" t="n"/>
-      <c r="R173" s="11" t="n"/>
-      <c r="S173" s="11" t="n"/>
-      <c r="T173" s="11" t="n"/>
-      <c r="U173" s="11" t="n"/>
-      <c r="V173" s="11" t="n"/>
+      <c r="P173" s="10" t="n"/>
+      <c r="Q173" s="10" t="n"/>
+      <c r="R173" s="10" t="n"/>
+      <c r="S173" s="10" t="n"/>
+      <c r="T173" s="10" t="n"/>
+      <c r="U173" s="10" t="n"/>
       <c r="W173" s="11" t="n"/>
       <c r="X173" s="11" t="n"/>
       <c r="Y173" s="11" t="n"/>
@@ -6338,6 +8446,18 @@
       <c r="AA173" s="11" t="n"/>
       <c r="AB173" s="11" t="n"/>
       <c r="AC173" s="11" t="n"/>
+      <c r="AD173" s="11" t="n"/>
+      <c r="AE173" s="11" t="n"/>
+      <c r="AF173" s="11" t="n"/>
+      <c r="AG173" s="11" t="n"/>
+      <c r="AH173" s="11" t="n"/>
+      <c r="AI173" s="11" t="n"/>
+      <c r="AJ173" s="11" t="n"/>
+      <c r="AK173" s="11" t="n"/>
+      <c r="AL173" s="11" t="n"/>
+      <c r="AM173" s="11" t="n"/>
+      <c r="AN173" s="11" t="n"/>
+      <c r="AO173" s="11" t="n"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
       <c r="B174" s="9" t="inlineStr">
@@ -6358,12 +8478,12 @@
       <c r="M174" s="10" t="n"/>
       <c r="N174" s="10" t="n"/>
       <c r="O174" s="10" t="n"/>
-      <c r="Q174" s="11" t="n"/>
-      <c r="R174" s="11" t="n"/>
-      <c r="S174" s="11" t="n"/>
-      <c r="T174" s="11" t="n"/>
-      <c r="U174" s="11" t="n"/>
-      <c r="V174" s="11" t="n"/>
+      <c r="P174" s="10" t="n"/>
+      <c r="Q174" s="10" t="n"/>
+      <c r="R174" s="10" t="n"/>
+      <c r="S174" s="10" t="n"/>
+      <c r="T174" s="10" t="n"/>
+      <c r="U174" s="10" t="n"/>
       <c r="W174" s="11" t="n"/>
       <c r="X174" s="11" t="n"/>
       <c r="Y174" s="11" t="n"/>
@@ -6371,6 +8491,18 @@
       <c r="AA174" s="11" t="n"/>
       <c r="AB174" s="11" t="n"/>
       <c r="AC174" s="11" t="n"/>
+      <c r="AD174" s="11" t="n"/>
+      <c r="AE174" s="11" t="n"/>
+      <c r="AF174" s="11" t="n"/>
+      <c r="AG174" s="11" t="n"/>
+      <c r="AH174" s="11" t="n"/>
+      <c r="AI174" s="11" t="n"/>
+      <c r="AJ174" s="11" t="n"/>
+      <c r="AK174" s="11" t="n"/>
+      <c r="AL174" s="11" t="n"/>
+      <c r="AM174" s="11" t="n"/>
+      <c r="AN174" s="11" t="n"/>
+      <c r="AO174" s="11" t="n"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
       <c r="B175" s="9" t="inlineStr">
@@ -6391,12 +8523,12 @@
       <c r="M175" s="10" t="n"/>
       <c r="N175" s="10" t="n"/>
       <c r="O175" s="10" t="n"/>
-      <c r="Q175" s="11" t="n"/>
-      <c r="R175" s="11" t="n"/>
-      <c r="S175" s="11" t="n"/>
-      <c r="T175" s="11" t="n"/>
-      <c r="U175" s="11" t="n"/>
-      <c r="V175" s="11" t="n"/>
+      <c r="P175" s="10" t="n"/>
+      <c r="Q175" s="10" t="n"/>
+      <c r="R175" s="10" t="n"/>
+      <c r="S175" s="10" t="n"/>
+      <c r="T175" s="10" t="n"/>
+      <c r="U175" s="10" t="n"/>
       <c r="W175" s="11" t="n"/>
       <c r="X175" s="11" t="n"/>
       <c r="Y175" s="11" t="n"/>
@@ -6404,6 +8536,18 @@
       <c r="AA175" s="11" t="n"/>
       <c r="AB175" s="11" t="n"/>
       <c r="AC175" s="11" t="n"/>
+      <c r="AD175" s="11" t="n"/>
+      <c r="AE175" s="11" t="n"/>
+      <c r="AF175" s="11" t="n"/>
+      <c r="AG175" s="11" t="n"/>
+      <c r="AH175" s="11" t="n"/>
+      <c r="AI175" s="11" t="n"/>
+      <c r="AJ175" s="11" t="n"/>
+      <c r="AK175" s="11" t="n"/>
+      <c r="AL175" s="11" t="n"/>
+      <c r="AM175" s="11" t="n"/>
+      <c r="AN175" s="11" t="n"/>
+      <c r="AO175" s="11" t="n"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
       <c r="B176" s="9" t="inlineStr">
@@ -6424,12 +8568,12 @@
       <c r="M176" s="10" t="n"/>
       <c r="N176" s="10" t="n"/>
       <c r="O176" s="10" t="n"/>
-      <c r="Q176" s="11" t="n"/>
-      <c r="R176" s="11" t="n"/>
-      <c r="S176" s="11" t="n"/>
-      <c r="T176" s="11" t="n"/>
-      <c r="U176" s="11" t="n"/>
-      <c r="V176" s="11" t="n"/>
+      <c r="P176" s="10" t="n"/>
+      <c r="Q176" s="10" t="n"/>
+      <c r="R176" s="10" t="n"/>
+      <c r="S176" s="10" t="n"/>
+      <c r="T176" s="10" t="n"/>
+      <c r="U176" s="10" t="n"/>
       <c r="W176" s="11" t="n"/>
       <c r="X176" s="11" t="n"/>
       <c r="Y176" s="11" t="n"/>
@@ -6437,6 +8581,18 @@
       <c r="AA176" s="11" t="n"/>
       <c r="AB176" s="11" t="n"/>
       <c r="AC176" s="11" t="n"/>
+      <c r="AD176" s="11" t="n"/>
+      <c r="AE176" s="11" t="n"/>
+      <c r="AF176" s="11" t="n"/>
+      <c r="AG176" s="11" t="n"/>
+      <c r="AH176" s="11" t="n"/>
+      <c r="AI176" s="11" t="n"/>
+      <c r="AJ176" s="11" t="n"/>
+      <c r="AK176" s="11" t="n"/>
+      <c r="AL176" s="11" t="n"/>
+      <c r="AM176" s="11" t="n"/>
+      <c r="AN176" s="11" t="n"/>
+      <c r="AO176" s="11" t="n"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
       <c r="B177" s="9" t="inlineStr">
@@ -6457,12 +8613,12 @@
       <c r="M177" s="10" t="n"/>
       <c r="N177" s="10" t="n"/>
       <c r="O177" s="10" t="n"/>
-      <c r="Q177" s="11" t="n"/>
-      <c r="R177" s="11" t="n"/>
-      <c r="S177" s="11" t="n"/>
-      <c r="T177" s="11" t="n"/>
-      <c r="U177" s="11" t="n"/>
-      <c r="V177" s="11" t="n"/>
+      <c r="P177" s="10" t="n"/>
+      <c r="Q177" s="10" t="n"/>
+      <c r="R177" s="10" t="n"/>
+      <c r="S177" s="10" t="n"/>
+      <c r="T177" s="10" t="n"/>
+      <c r="U177" s="10" t="n"/>
       <c r="W177" s="11" t="n"/>
       <c r="X177" s="11" t="n"/>
       <c r="Y177" s="11" t="n"/>
@@ -6470,6 +8626,18 @@
       <c r="AA177" s="11" t="n"/>
       <c r="AB177" s="11" t="n"/>
       <c r="AC177" s="11" t="n"/>
+      <c r="AD177" s="11" t="n"/>
+      <c r="AE177" s="11" t="n"/>
+      <c r="AF177" s="11" t="n"/>
+      <c r="AG177" s="11" t="n"/>
+      <c r="AH177" s="11" t="n"/>
+      <c r="AI177" s="11" t="n"/>
+      <c r="AJ177" s="11" t="n"/>
+      <c r="AK177" s="11" t="n"/>
+      <c r="AL177" s="11" t="n"/>
+      <c r="AM177" s="11" t="n"/>
+      <c r="AN177" s="11" t="n"/>
+      <c r="AO177" s="11" t="n"/>
     </row>
     <row r="181">
       <c r="B181" s="15" t="inlineStr">
@@ -6551,12 +8719,33 @@
     <row r="192">
       <c r="B192" s="4" t="inlineStr">
         <is>
+          <t>PACKS (19-resource universe since 2026-08-03, D19): the six card-collection pack tiers, appended as the last six columns. They are SIMULATED-SIDE ONLY - data_gains has no pack rows, so the measured anchor is 0 and 'measured x R x D x T' can never produce one. Each source instead prices packs BOTTOM-UP on cal_new: packs = E_v2 x participation_rate x SUM(reach(inst)), reusing the same expected ladder payout E the R ratio is built from (no D term - a pack is a rank/milestone payout already priced through E). Consequence: the DIFF column for a pack equals its simulated value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" s="4" t="inlineStr">
+        <is>
+          <t>PACK sources: every source with a config sheet pays packs, including Team Event and Flock Flurry, which stay CARRIED for all 13 other resources and get only a pack overlay. Team Race, Ads and IAPs have no config sheet -&gt; 0 packs. A. 0 has no behaviour telemetry to price reach -&gt; 0 packs. FLAGGED: reach and participation_rate both encode activity, so their product mildly UNDER-counts high-participation events; and Team Event has no data_event_inst rows, so its ladder is priced at a FLAT rank average (the crudest pricing in the model).</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" s="4" t="inlineStr">
+        <is>
+          <t>PACK values are AUTHORED BY HAND on the config sheets (the 1-star Dly .. 6-star Dly columns, which exist on every ladder). Until you type a number there, every pack column reads 0 - that is correct, not a plumbing failure. The card-collection sim (SimOutput, menu EcoGainsSim ▸ Simulate card pack openings) consumes this pack flow per day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" s="4" t="inlineStr">
+        <is>
           <t>After editing a calendar: menu EcoGainsSim ▸ Precompute calendars (writes hidden cal_parsed; engine prefers it). Sanity canary: the Kite Festival row must GROW ~x1.3 vs measured. If every event row equals measured, the calendar read failed.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="Q8:AC32">
+  <conditionalFormatting sqref="W8:AO32">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -6564,7 +8753,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q37:AC61">
+  <conditionalFormatting sqref="W37:AO61">
     <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -6572,7 +8761,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q66:AC90">
+  <conditionalFormatting sqref="W66:AO90">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -6580,7 +8769,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q95:AC119">
+  <conditionalFormatting sqref="W95:AO119">
     <cfRule type="cellIs" priority="7" operator="lessThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -6588,7 +8777,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q124:AC148">
+  <conditionalFormatting sqref="W124:AO148">
     <cfRule type="cellIs" priority="9" operator="lessThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -6596,7 +8785,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q153:AC177">
+  <conditionalFormatting sqref="W153:AO177">
     <cfRule type="cellIs" priority="11" operator="lessThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
